--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
     <sheet name="已删" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">在播剧更新时间表!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已删!$A$1:$J$48</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="518">
   <si>
     <t>剧名</t>
   </si>
@@ -1080,6 +1080,19 @@
     <t xml:space="preserve">链接: https://pan.baidu.com/s/17IfE4v3SrPF6Y18CdlHkaA 提取码: kxjd </t>
   </si>
   <si>
+    <t>爱情来了</t>
+  </si>
+  <si>
+    <t>16/50</t>
+  </si>
+  <si>
+    <t>安喜延 / 河锡辰</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/c2c8aa7ff0c2?pwd=JZEy
+提取码：JZEy</t>
+  </si>
+  <si>
     <t>神的游戏</t>
   </si>
   <si>
@@ -1423,25 +1436,16 @@
     <t>玩具总动员5</t>
   </si>
   <si>
-    <t>黑胶旅途</t>
-  </si>
-  <si>
     <t>爱恋成婚</t>
   </si>
   <si>
-    <t>野兽赛跑</t>
+    <t>智能车劫</t>
   </si>
   <si>
     <t>追踪者游戏W 水鱼交融</t>
   </si>
   <si>
-    <t>智能车劫</t>
-  </si>
-  <si>
-    <t>歪心狼对阵</t>
-  </si>
-  <si>
-    <t>群狼绝境</t>
+    <t>歪心狼对阵ACME</t>
   </si>
   <si>
     <t>鲨笼绝境</t>
@@ -1453,10 +1457,206 @@
     <t>最后的刺客</t>
   </si>
   <si>
-    <t>潜伏6</t>
-  </si>
-  <si>
-    <t>挽救计划</t>
+    <t>顺风车杀手</t>
+  </si>
+  <si>
+    <t>95分</t>
+  </si>
+  <si>
+    <t>核战边缘</t>
+  </si>
+  <si>
+    <t>117分</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>小黄人与大怪兽</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>奇幻变身大冒险</t>
+  </si>
+  <si>
+    <t>乌女山怪谈</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.5"/>
+        <color rgb="FF494949"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>罪案重现</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.5"/>
+        <color rgb="FF494949"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>空枪</t>
+  </si>
+  <si>
+    <t>和平精英：地铁逃生</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>2026惊悚片《滑索惊魂》</t>
+  </si>
+  <si>
+    <t>失控的关系</t>
+  </si>
+  <si>
+    <t>奇门遁甲：逢凶化吉</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>阴风诡影</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>热血部落</t>
+  </si>
+  <si>
+    <t>最新动作片</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>山竹刀</t>
+  </si>
+  <si>
+    <t>最新武侠片</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>古寨枪声</t>
+  </si>
+  <si>
+    <t>最新战争片</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>午夜车库</t>
+  </si>
+  <si>
+    <t>最新恐怖片</t>
+  </si>
+  <si>
+    <t>非法闯入者</t>
+  </si>
+  <si>
+    <t>连环杀人案揭露网络信任危机和家庭暴力之恶</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>河神之渡阴</t>
+  </si>
+  <si>
+    <t>最新悬疑大片</t>
+  </si>
+  <si>
+    <t>58+68</t>
+  </si>
+  <si>
+    <t>我为什么又结婚了</t>
+  </si>
+  <si>
+    <t>最新喜剧片</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>生化杀机</t>
+  </si>
+  <si>
+    <t>恐怖丧尸片</t>
+  </si>
+  <si>
+    <t>蜂鸟行动</t>
+  </si>
+  <si>
+    <t>任贤齐最新战争大片</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>暴烈司机</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>崩溃边缘</t>
+  </si>
+  <si>
+    <t>最新惊悚大片</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>管控成瘾</t>
+  </si>
+  <si>
+    <t>最新科幻</t>
+  </si>
+  <si>
+    <t>醉胆追凶</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>冰雪猴</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>逃出绝命街</t>
+  </si>
+  <si>
+    <t>安妮·海瑟薇最新科幻大片</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>韩国死灵</t>
+  </si>
+  <si>
+    <t>最新奇幻喜剧大片</t>
+  </si>
+  <si>
+    <t>150</t>
   </si>
   <si>
     <t>序号</t>
@@ -1988,9 +2188,6 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/10adBSzL63iK0CsWUdKtXsQ 提取码: tj5r </t>
-  </si>
-  <si>
-    <t>爱情来了</t>
   </si>
   <si>
     <t>夏日狂热</t>
@@ -2027,7 +2224,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2246,11 +2443,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2259,14 +2459,25 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="19.5"/>
+      <color rgb="FF494949"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <b/>
+      <sz val="19.5"/>
+      <color rgb="FF494949"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="35">
@@ -2798,7 +3009,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2935,6 +3146,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2953,7 +3167,22 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3497,18 +3726,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
     <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="34.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="10.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.375" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="26.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="79.125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="9" style="5" customWidth="1"/>
     <col min="10" max="10" width="74.5" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="6"/>
   </cols>
@@ -4148,8 +4376,8 @@
       <c r="D21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="7">
-        <v>12</v>
+      <c r="E21" s="46">
+        <v>13</v>
       </c>
       <c r="F21" s="23" t="s">
         <v>14</v>
@@ -4160,7 +4388,7 @@
       <c r="H21" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="I21" s="46" t="s">
+      <c r="I21" s="47" t="s">
         <v>110</v>
       </c>
       <c r="J21" s="7" t="s">
@@ -4192,7 +4420,7 @@
       <c r="H22" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="I22" s="47" t="s">
+      <c r="I22" s="48" t="s">
         <v>115</v>
       </c>
       <c r="J22" s="7" t="s">
@@ -4224,7 +4452,7 @@
       <c r="H23" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="I23" s="47" t="s">
+      <c r="I23" s="48" t="s">
         <v>120</v>
       </c>
       <c r="J23" s="7" t="s">
@@ -4256,7 +4484,7 @@
       <c r="H24" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="I24" s="47" t="s">
+      <c r="I24" s="48" t="s">
         <v>125</v>
       </c>
       <c r="J24" s="7" t="s">
@@ -4288,7 +4516,7 @@
       <c r="H25" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="I25" s="47" t="s">
+      <c r="I25" s="48" t="s">
         <v>130</v>
       </c>
       <c r="J25" s="7" t="s">
@@ -4440,7 +4668,7 @@
       <c r="H30" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="I30" s="47" t="s">
+      <c r="I30" s="48" t="s">
         <v>152</v>
       </c>
       <c r="J30" s="1" t="s">
@@ -4472,7 +4700,7 @@
       <c r="H31" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="I31" s="47" t="s">
+      <c r="I31" s="48" t="s">
         <v>157</v>
       </c>
       <c r="J31" s="1" t="s">
@@ -4518,7 +4746,7 @@
       <c r="B33" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="49" t="s">
         <v>165</v>
       </c>
       <c r="D33" s="23" t="s">
@@ -4550,7 +4778,7 @@
       <c r="B34" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="50" t="s">
         <v>170</v>
       </c>
       <c r="D34" s="23" t="s">
@@ -4568,10 +4796,10 @@
       <c r="H34" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="I34" s="50" t="s">
+      <c r="I34" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="J34" s="51"/>
+      <c r="J34" s="52"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A35" s="25" t="s">
@@ -4598,7 +4826,7 @@
       <c r="H35" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="I35" s="47" t="s">
+      <c r="I35" s="48" t="s">
         <v>177</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -4612,7 +4840,7 @@
       <c r="B36" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C36" s="51" t="s">
+      <c r="C36" s="52" t="s">
         <v>180</v>
       </c>
       <c r="D36" s="7"/>
@@ -4631,21 +4859,21 @@
       </c>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A37" s="25" t="s">
+    <row r="37" s="6" customFormat="1" ht="34" customHeight="1" spans="1:10">
+      <c r="A37" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="B37" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>185</v>
+      <c r="B37" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>30</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="23">
-        <v>7</v>
+      <c r="E37" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="F37" s="23" t="s">
         <v>14</v>
@@ -4653,671 +4881,569 @@
       <c r="G37" s="23">
         <v>2026</v>
       </c>
-      <c r="H37" s="23"/>
-      <c r="I37" s="47" t="s">
+      <c r="H37" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="J37" s="23" t="s">
+      <c r="I37" s="24"/>
+      <c r="J37" s="53" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A38" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="23">
-        <v>10</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H38" s="46"/>
-      <c r="I38" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="J38" s="23" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A39" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="23">
-        <v>2</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H39" s="46"/>
-      <c r="I39" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="J39" s="23" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A40" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="23">
-        <v>4</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H40" s="46"/>
-      <c r="I40" s="47" t="s">
-        <v>196</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A41" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C41" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H41" s="23"/>
-      <c r="I41" s="24" t="s">
-        <v>200</v>
-      </c>
+    <row r="38" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A38" s="21"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="7"/>
+    </row>
+    <row r="39" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A39" s="21"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="7"/>
+    </row>
+    <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A40" s="21"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="7"/>
+    </row>
+    <row r="41" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A41" s="21"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="24"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A42" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C42" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="23">
-        <v>2026</v>
-      </c>
+    <row r="42" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A42" s="21"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
       <c r="H42" s="23"/>
-      <c r="I42" s="24" t="s">
-        <v>202</v>
-      </c>
+      <c r="I42" s="24"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A43" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C43" s="7"/>
+    <row r="43" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A43" s="21"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="52"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
-      <c r="F43" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="F43" s="7"/>
       <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A44" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C44" s="7"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="7"/>
+    </row>
+    <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A44" s="21"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="52"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
-      <c r="F44" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="F44" s="7"/>
       <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A45" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C45" s="7"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="7"/>
+    </row>
+    <row r="45" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A45" s="21"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="52"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
-      <c r="F45" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="F45" s="7"/>
       <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A46" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C46" s="7"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="7"/>
+    </row>
+    <row r="46" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A46" s="21"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="52"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="F46" s="7"/>
       <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
+      <c r="H46" s="23"/>
       <c r="I46" s="24"/>
-      <c r="J46" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A47" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>217</v>
-      </c>
+      <c r="J46" s="7"/>
+    </row>
+    <row r="47" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A47" s="21"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="52"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="7">
-        <v>10</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G47" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="48" ht="25" customHeight="1" spans="1:10">
-      <c r="A48" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C48" s="34" t="s">
-        <v>222</v>
-      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="7"/>
+    </row>
+    <row r="48" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A48" s="21"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="52"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>224</v>
-      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="23"/>
       <c r="I48" s="24"/>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" ht="25" customHeight="1" spans="1:10">
-      <c r="A49" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>222</v>
-      </c>
+    <row r="49" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A49" s="21"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="52"/>
       <c r="D49" s="7"/>
-      <c r="E49" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>227</v>
-      </c>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="23"/>
       <c r="I49" s="24"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" ht="25" customHeight="1" spans="1:10">
+    <row r="50" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A50" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C50" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="D50" s="7"/>
-      <c r="E50" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="F50" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="23">
+        <v>7</v>
+      </c>
+      <c r="F50" s="23" t="s">
         <v>14</v>
       </c>
       <c r="G50" s="23">
         <v>2026</v>
       </c>
-      <c r="H50" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="I50" s="24"/>
-      <c r="J50" s="7"/>
-    </row>
-    <row r="51" ht="22" customHeight="1" spans="1:10">
+      <c r="H50" s="23"/>
+      <c r="I50" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="J50" s="23" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A51" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C51" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="D51" s="7"/>
-      <c r="E51" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="F51" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="23">
+        <v>10</v>
+      </c>
+      <c r="F51" s="23" t="s">
         <v>14</v>
       </c>
       <c r="G51" s="23">
         <v>2026</v>
       </c>
-      <c r="H51" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="I51" s="24"/>
-      <c r="J51" s="7"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="J51" s="23" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A52" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="23">
+        <v>2</v>
+      </c>
+      <c r="F52" s="23" t="s">
         <v>14</v>
       </c>
       <c r="G52" s="23">
         <v>2026</v>
       </c>
-      <c r="H52" s="7"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="7"/>
-    </row>
-    <row r="53" ht="25" customHeight="1" spans="1:10">
-      <c r="A53" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22" t="s">
-        <v>20</v>
+      <c r="H52" s="47"/>
+      <c r="I52" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="J52" s="23" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A53" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="23">
+        <v>4</v>
+      </c>
+      <c r="F53" s="23" t="s">
+        <v>14</v>
       </c>
       <c r="G53" s="23">
         <v>2026</v>
       </c>
-      <c r="H53" s="7"/>
-      <c r="I53" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="J53" s="21" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="54" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="H53" s="47"/>
+      <c r="I53" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A54" s="21" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="52"/>
+      <c r="F54" s="52" t="s">
         <v>20</v>
       </c>
       <c r="G54" s="23">
         <v>2026</v>
       </c>
-      <c r="H54" s="7" t="s">
-        <v>242</v>
-      </c>
+      <c r="H54" s="23"/>
       <c r="I54" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="J54" s="24" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="55" ht="25" customHeight="1" spans="1:10">
+        <v>204</v>
+      </c>
+      <c r="J54" s="7"/>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A55" s="21" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D55" s="7"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="D55" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="52"/>
+      <c r="F55" s="52" t="s">
         <v>20</v>
       </c>
       <c r="G55" s="23">
         <v>2026</v>
       </c>
-      <c r="H55" s="7" t="s">
-        <v>247</v>
-      </c>
+      <c r="H55" s="23"/>
       <c r="I55" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="J55" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="56" ht="25" customHeight="1" spans="1:10">
+        <v>206</v>
+      </c>
+      <c r="J55" s="7"/>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A56" s="21" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>251</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C56" s="7"/>
       <c r="D56" s="7"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22" t="s">
+      <c r="E56" s="7"/>
+      <c r="F56" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G56" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>252</v>
-      </c>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
       <c r="I56" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="J56" s="24" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="57" ht="25" customHeight="1" spans="1:10">
-      <c r="A57" s="21"/>
-      <c r="B57" s="7"/>
+        <v>209</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A57" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>208</v>
+      </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="23"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" s="7"/>
       <c r="H57" s="7"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="24"/>
-    </row>
-    <row r="58" ht="25" customHeight="1" spans="1:10">
-      <c r="A58" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="B58" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="C58" s="52" t="s">
-        <v>155</v>
-      </c>
+      <c r="I57" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A58" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="7"/>
       <c r="D58" s="7"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22" t="s">
+      <c r="E58" s="7"/>
+      <c r="F58" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G58" s="23">
-        <v>8.25</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="I58" s="24"/>
-      <c r="J58" s="21"/>
-    </row>
-    <row r="59" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A59" s="42" t="s">
-        <v>257</v>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A59" s="21" t="s">
+        <v>217</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22" t="s">
+      <c r="E59" s="7"/>
+      <c r="F59" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G59" s="23" t="s">
-        <v>258</v>
-      </c>
+      <c r="G59" s="7"/>
       <c r="H59" s="7"/>
       <c r="I59" s="24"/>
-      <c r="J59" s="21"/>
-    </row>
-    <row r="60" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A60" s="42" t="s">
-        <v>259</v>
+      <c r="J59" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A60" s="25" t="s">
+        <v>219</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="7"/>
+        <v>220</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>221</v>
+      </c>
       <c r="D60" s="7"/>
-      <c r="E60" s="22"/>
+      <c r="E60" s="7">
+        <v>10</v>
+      </c>
       <c r="F60" s="22" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G60" s="23">
-        <v>8.23</v>
-      </c>
-      <c r="H60" s="7"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="21"/>
-    </row>
-    <row r="61" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A61" s="42" t="s">
-        <v>260</v>
+        <v>2026</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" ht="25" customHeight="1" spans="1:10">
+      <c r="A61" s="25" t="s">
+        <v>225</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="7"/>
+        <v>220</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>226</v>
+      </c>
       <c r="D61" s="7"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="H61" s="7"/>
+      <c r="E61" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>228</v>
+      </c>
       <c r="I61" s="24"/>
-      <c r="J61" s="21"/>
-    </row>
-    <row r="62" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A62" s="21" t="s">
-        <v>261</v>
+      <c r="J61" s="7"/>
+    </row>
+    <row r="62" ht="25" customHeight="1" spans="1:10">
+      <c r="A62" s="25" t="s">
+        <v>229</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C62" s="7"/>
+        <v>220</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>226</v>
+      </c>
       <c r="D62" s="7"/>
-      <c r="E62" s="22"/>
+      <c r="E62" s="22" t="s">
+        <v>230</v>
+      </c>
       <c r="F62" s="22" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G62" s="23">
-        <v>8.24</v>
-      </c>
-      <c r="H62" s="7"/>
+        <v>2026</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>231</v>
+      </c>
       <c r="I62" s="24"/>
-      <c r="J62" s="21"/>
-    </row>
-    <row r="63" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A63" s="42" t="s">
-        <v>262</v>
+      <c r="J62" s="7"/>
+    </row>
+    <row r="63" ht="25" customHeight="1" spans="1:10">
+      <c r="A63" s="25" t="s">
+        <v>232</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C63" s="7"/>
+        <v>220</v>
+      </c>
+      <c r="C63" s="26" t="s">
+        <v>233</v>
+      </c>
       <c r="D63" s="7"/>
-      <c r="E63" s="22"/>
+      <c r="E63" s="22" t="s">
+        <v>234</v>
+      </c>
       <c r="F63" s="22" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G63" s="23">
-        <v>8.21</v>
-      </c>
-      <c r="H63" s="7"/>
+        <v>2026</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>235</v>
+      </c>
       <c r="I63" s="24"/>
-      <c r="J63" s="21"/>
-    </row>
-    <row r="64" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A64" s="21" t="s">
-        <v>263</v>
+      <c r="J63" s="7"/>
+    </row>
+    <row r="64" ht="22" customHeight="1" spans="1:10">
+      <c r="A64" s="25" t="s">
+        <v>236</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64" s="7"/>
+        <v>237</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>238</v>
+      </c>
       <c r="D64" s="7"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
+      <c r="E64" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>14</v>
+      </c>
       <c r="G64" s="23">
-        <v>3.17</v>
-      </c>
-      <c r="H64" s="7"/>
+        <v>2026</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>240</v>
+      </c>
       <c r="I64" s="24"/>
-      <c r="J64" s="21"/>
-    </row>
-    <row r="65" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A65" s="21" t="s">
-        <v>264</v>
+      <c r="J64" s="7"/>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A65" s="25" t="s">
+        <v>241</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="22" t="s">
+        <v>14</v>
+      </c>
       <c r="G65" s="23">
-        <v>5.15</v>
+        <v>2026</v>
       </c>
       <c r="H65" s="7"/>
       <c r="I65" s="24"/>
-      <c r="J65" s="21"/>
-    </row>
-    <row r="66" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="J65" s="7"/>
+    </row>
+    <row r="66" ht="25" customHeight="1" spans="1:10">
       <c r="A66" s="21" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>69</v>
@@ -5325,58 +5451,104 @@
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="23"/>
+      <c r="F66" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="23">
+        <v>2026</v>
+      </c>
       <c r="H66" s="7"/>
-      <c r="I66" s="24"/>
-      <c r="J66" s="21"/>
+      <c r="I66" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="J66" s="21" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="67" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A67" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="B67" s="7"/>
+        <v>245</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="23"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="24"/>
-      <c r="J67" s="21"/>
-    </row>
-    <row r="68" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="F67" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="I67" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="J67" s="24" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1" spans="1:10">
       <c r="A68" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
+        <v>249</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>250</v>
+      </c>
       <c r="D68" s="7"/>
       <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="23"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="24"/>
-      <c r="J68" s="21"/>
-    </row>
-    <row r="69" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="F68" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="I68" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="J68" s="24" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="69" ht="25" customHeight="1" spans="1:10">
       <c r="A69" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
+        <v>254</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>255</v>
+      </c>
       <c r="D69" s="7"/>
       <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="24"/>
-      <c r="J69" s="21"/>
-    </row>
-    <row r="70" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A70" s="21" t="s">
-        <v>269</v>
-      </c>
+      <c r="F69" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I69" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="J69" s="24" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="70" ht="25" customHeight="1" spans="1:10">
+      <c r="A70" s="21"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -5385,76 +5557,750 @@
       <c r="G70" s="23"/>
       <c r="H70" s="7"/>
       <c r="I70" s="24"/>
-      <c r="J70" s="21"/>
-    </row>
-    <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A71" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
+      <c r="J70" s="24"/>
+    </row>
+    <row r="71" ht="25" customHeight="1" spans="1:10">
+      <c r="A71" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="B71" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71" s="46" t="s">
+        <v>155</v>
+      </c>
       <c r="D71" s="7"/>
       <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="7"/>
+      <c r="F71" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="23">
+        <v>8.25</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>260</v>
+      </c>
       <c r="I71" s="24"/>
       <c r="J71" s="21"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A72" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="B72" s="7"/>
+      <c r="A72" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="23"/>
+      <c r="F72" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" s="23" t="s">
+        <v>262</v>
+      </c>
       <c r="H72" s="7"/>
       <c r="I72" s="24"/>
       <c r="J72" s="21"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A73" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="B73" s="7"/>
+      <c r="A73" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
       <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="23"/>
+      <c r="F73" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" s="23">
+        <v>8.23</v>
+      </c>
       <c r="H73" s="7"/>
       <c r="I73" s="24"/>
       <c r="J73" s="21"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A74" s="21"/>
-      <c r="B74" s="7"/>
+      <c r="A74" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="22"/>
       <c r="F74" s="22"/>
-      <c r="G74" s="23"/>
+      <c r="G74" s="23" t="s">
+        <v>262</v>
+      </c>
       <c r="H74" s="7"/>
       <c r="I74" s="24"/>
       <c r="J74" s="21"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A75" s="21"/>
-      <c r="B75" s="7"/>
+      <c r="A75" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="23"/>
+      <c r="F75" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="23">
+        <v>8.21</v>
+      </c>
       <c r="H75" s="7"/>
       <c r="I75" s="24"/>
       <c r="J75" s="21"/>
     </row>
+    <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A76" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="24"/>
+      <c r="J76" s="21"/>
+    </row>
+    <row r="77" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A77" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="23">
+        <v>5.15</v>
+      </c>
+      <c r="H77" s="7"/>
+      <c r="I77" s="24"/>
+      <c r="J77" s="21"/>
+    </row>
+    <row r="78" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A78" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="24"/>
+      <c r="J78" s="21"/>
+    </row>
+    <row r="79" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
+      <c r="A79" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="24"/>
+      <c r="J79" s="21"/>
+    </row>
+    <row r="80" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A80" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="23"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="21"/>
+    </row>
+    <row r="81" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A81" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="23"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="24"/>
+      <c r="J81" s="21"/>
+    </row>
+    <row r="82" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A82" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="G82" s="23"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="24"/>
+      <c r="J82" s="24"/>
+    </row>
+    <row r="83" ht="25" customHeight="1" spans="1:10">
+      <c r="A83" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="G83" s="23"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="24"/>
+      <c r="J83" s="24"/>
+    </row>
+    <row r="84" ht="25" customHeight="1" spans="1:10">
+      <c r="A84" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="G84" s="23"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="24"/>
+      <c r="J84" s="24"/>
+    </row>
+    <row r="85" ht="25" customHeight="1" spans="1:10">
+      <c r="A85" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="G85" s="23"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="24"/>
+      <c r="J85" s="24"/>
+    </row>
+    <row r="86" ht="25" customHeight="1" spans="1:10">
+      <c r="A86" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22">
+        <v>102</v>
+      </c>
+      <c r="G86" s="23"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="24"/>
+      <c r="J86" s="24"/>
+    </row>
+    <row r="87" ht="25" customHeight="1" spans="1:10">
+      <c r="A87" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="22">
+        <v>69</v>
+      </c>
+      <c r="G87" s="23"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="24"/>
+      <c r="J87" s="24"/>
+    </row>
+    <row r="88" ht="25" customHeight="1" spans="1:10">
+      <c r="A88" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="22">
+        <v>86</v>
+      </c>
+      <c r="G88" s="23"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="24"/>
+      <c r="J88" s="24"/>
+    </row>
+    <row r="89" ht="25" customHeight="1" spans="1:10">
+      <c r="A89" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="24"/>
+      <c r="J89" s="24"/>
+    </row>
+    <row r="90" ht="25" customHeight="1" spans="1:10">
+      <c r="A90" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="B90" s="7"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="G90" s="23"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="24"/>
+      <c r="J90" s="24"/>
+    </row>
+    <row r="91" ht="25" customHeight="1" spans="1:10">
+      <c r="A91" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="B91" s="7"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="23"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="24"/>
+      <c r="J91" s="24"/>
+    </row>
+    <row r="92" ht="25" customHeight="1" spans="1:10">
+      <c r="A92" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="23"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="24"/>
+      <c r="J92" s="24"/>
+    </row>
+    <row r="93" ht="25" customHeight="1" spans="1:10">
+      <c r="A93" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="G93" s="23"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="24"/>
+      <c r="J93" s="24"/>
+    </row>
+    <row r="94" ht="25" customHeight="1" spans="1:10">
+      <c r="A94" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="B94" s="7"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="G94" s="23"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="24"/>
+    </row>
+    <row r="95" ht="25" customHeight="1" spans="1:10">
+      <c r="A95" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D95" s="7"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="G95" s="23"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="24"/>
+      <c r="J95" s="24"/>
+    </row>
+    <row r="96" ht="25" customHeight="1" spans="1:10">
+      <c r="A96" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="B96" s="7"/>
+      <c r="C96" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D96" s="7"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="G96" s="23"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="24"/>
+      <c r="J96" s="24"/>
+    </row>
+    <row r="97" ht="25" customHeight="1" spans="1:10">
+      <c r="A97" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D97" s="7"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="G97" s="23"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="24"/>
+      <c r="J97" s="24"/>
+    </row>
+    <row r="98" ht="25" customHeight="1" spans="1:10">
+      <c r="A98" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D98" s="7"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="G98" s="23"/>
+      <c r="H98" s="7"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
+    </row>
+    <row r="99" ht="25" customHeight="1" spans="1:10">
+      <c r="A99" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="B99" s="7"/>
+      <c r="C99" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D99" s="7"/>
+      <c r="E99" s="22"/>
+      <c r="F99" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="G99" s="23"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="24"/>
+      <c r="J99" s="24"/>
+    </row>
+    <row r="100" ht="25" customHeight="1" spans="1:10">
+      <c r="A100" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D100" s="7"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="G100" s="23"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="24"/>
+      <c r="J100" s="24"/>
+    </row>
+    <row r="101" ht="25" customHeight="1" spans="1:10">
+      <c r="A101" s="42" t="s">
+        <v>308</v>
+      </c>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D101" s="7"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="G101" s="23"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="24"/>
+      <c r="J101" s="24"/>
+    </row>
+    <row r="102" ht="25" customHeight="1" spans="1:10">
+      <c r="A102" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D102" s="7"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="G102" s="23"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="24"/>
+      <c r="J102" s="24"/>
+    </row>
+    <row r="103" ht="25" customHeight="1" spans="1:10">
+      <c r="A103" s="42" t="s">
+        <v>313</v>
+      </c>
+      <c r="B103" s="7"/>
+      <c r="C103" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D103" s="7"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="G103" s="23"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="24"/>
+      <c r="J103" s="24"/>
+    </row>
+    <row r="104" ht="25" customHeight="1" spans="1:10">
+      <c r="A104" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D104" s="7"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="G104" s="23"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="24"/>
+      <c r="J104" s="24"/>
+    </row>
+    <row r="105" ht="25" customHeight="1" spans="1:10">
+      <c r="A105" s="42" t="s">
+        <v>318</v>
+      </c>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D105" s="7"/>
+      <c r="E105" s="22"/>
+      <c r="F105" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="G105" s="23"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="24"/>
+      <c r="J105" s="24"/>
+    </row>
+    <row r="106" ht="25" customHeight="1" spans="1:10">
+      <c r="A106" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="B106" s="46"/>
+      <c r="C106" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="D106" s="46"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="G106" s="56"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="24"/>
+      <c r="J106" s="24"/>
+    </row>
+    <row r="107" ht="25" customHeight="1" spans="1:10">
+      <c r="A107" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="B107" s="46"/>
+      <c r="C107" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="D107" s="46"/>
+      <c r="E107" s="55"/>
+      <c r="F107" s="55" t="s">
+        <v>324</v>
+      </c>
+      <c r="G107" s="56"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="24"/>
+    </row>
+    <row r="108" ht="25" customHeight="1" spans="1:10">
+      <c r="A108" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="B108" s="46"/>
+      <c r="C108" s="46"/>
+      <c r="D108" s="46"/>
+      <c r="E108" s="55"/>
+      <c r="F108" s="55" t="s">
+        <v>326</v>
+      </c>
+      <c r="G108" s="56"/>
+      <c r="H108" s="7"/>
+      <c r="I108" s="24"/>
+      <c r="J108" s="24"/>
+    </row>
+    <row r="109" ht="25" customHeight="1" spans="1:10">
+      <c r="A109" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="B109" s="46"/>
+      <c r="C109" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="D109" s="46"/>
+      <c r="E109" s="55"/>
+      <c r="F109" s="55" t="s">
+        <v>329</v>
+      </c>
+      <c r="G109" s="23"/>
+      <c r="H109" s="7"/>
+      <c r="I109" s="24"/>
+      <c r="J109" s="24"/>
+    </row>
+    <row r="110" ht="25" customHeight="1" spans="1:10">
+      <c r="A110" s="42" t="s">
+        <v>330</v>
+      </c>
+      <c r="B110" s="46"/>
+      <c r="C110" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="D110" s="46"/>
+      <c r="E110" s="55"/>
+      <c r="F110" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="G110" s="23"/>
+      <c r="H110" s="7"/>
+      <c r="I110" s="24"/>
+      <c r="J110" s="24"/>
+    </row>
+    <row r="111" ht="25" customHeight="1" spans="1:10">
+      <c r="A111" s="13"/>
+      <c r="B111" s="57"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="57"/>
+      <c r="E111" s="58"/>
+      <c r="F111" s="20"/>
+      <c r="G111" s="10"/>
+      <c r="H111" s="57"/>
+      <c r="I111" s="24"/>
+      <c r="J111" s="24"/>
+    </row>
+    <row r="112" ht="25" customHeight="1" spans="1:10">
+      <c r="A112" s="21"/>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="22"/>
+      <c r="G112" s="23"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="24"/>
+      <c r="J112" s="24"/>
+    </row>
+    <row r="113" ht="25" customHeight="1" spans="1:10">
+      <c r="A113" s="21"/>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="22"/>
+      <c r="G113" s="23"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="24"/>
+      <c r="J113" s="24"/>
+    </row>
+    <row r="114" ht="25" customHeight="1" spans="1:10">
+      <c r="A114" s="42"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="22"/>
+      <c r="G114" s="23"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="24"/>
+      <c r="J114" s="24"/>
+    </row>
+    <row r="115" ht="25" customHeight="1" spans="1:10">
+      <c r="A115" s="42"/>
+      <c r="B115" s="7"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="23"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J72" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J110" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <colorFilter dxfId="0"/>
       <extLst>
@@ -5477,7 +6323,7 @@
         </dxfs>
       </extLst>
     </filterColumn>
-    <sortState ref="A1:J72">
+    <sortState ref="A1:J110">
       <sortCondition ref="F1:F87"/>
     </sortState>
     <extLst/>
@@ -5509,7 +6355,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -5518,22 +6364,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>274</v>
+        <v>334</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>275</v>
+        <v>335</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>276</v>
+        <v>336</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>277</v>
+        <v>337</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>278</v>
+        <v>338</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -5547,22 +6393,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>281</v>
+        <v>341</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>282</v>
+        <v>342</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -5576,22 +6422,22 @@
         <v>11</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>286</v>
+        <v>346</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>287</v>
+        <v>347</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>288</v>
+        <v>348</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>289</v>
+        <v>349</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -5605,22 +6451,22 @@
         <v>11</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>291</v>
+        <v>351</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>292</v>
+        <v>352</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>293</v>
+        <v>353</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>294</v>
+        <v>354</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -5634,22 +6480,22 @@
         <v>11</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>295</v>
+        <v>355</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>296</v>
+        <v>356</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -5663,22 +6509,22 @@
         <v>11</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>301</v>
+        <v>361</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -5692,22 +6538,22 @@
         <v>103</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>302</v>
+        <v>362</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>303</v>
+        <v>363</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -5721,22 +6567,22 @@
         <v>103</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>307</v>
+        <v>367</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -5750,22 +6596,22 @@
         <v>149</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>308</v>
+        <v>368</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>309</v>
+        <v>369</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -5779,22 +6625,22 @@
         <v>149</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>313</v>
+        <v>373</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -5808,22 +6654,22 @@
         <v>103</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>314</v>
+        <v>374</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>315</v>
+        <v>375</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -5837,22 +6683,22 @@
         <v>103</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>316</v>
+        <v>376</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>317</v>
+        <v>377</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -5866,22 +6712,22 @@
         <v>103</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>319</v>
+        <v>379</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -5895,22 +6741,22 @@
         <v>174</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>321</v>
+        <v>381</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -5918,28 +6764,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>149</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>323</v>
+        <v>383</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>324</v>
+        <v>384</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>325</v>
+        <v>385</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>325</v>
+        <v>385</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>326</v>
+        <v>386</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>327</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -5947,28 +6793,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>149</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>329</v>
+        <v>389</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>327</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -5976,28 +6822,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>149</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>327</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -6005,28 +6851,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>149</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>332</v>
+        <v>392</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>327</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -6034,28 +6880,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>333</v>
+        <v>393</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -6063,28 +6909,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>336</v>
+        <v>396</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>337</v>
+        <v>397</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -6092,28 +6938,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>341</v>
+        <v>401</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -6121,28 +6967,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>342</v>
+        <v>402</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>343</v>
+        <v>403</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -6150,28 +6996,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>344</v>
+        <v>404</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>345</v>
+        <v>405</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>346</v>
+        <v>406</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -6188,7 +7034,7 @@
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>348</v>
+        <v>408</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -6268,13 +7114,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>349</v>
+        <v>409</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -6289,28 +7135,28 @@
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>353</v>
+        <v>413</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>20</v>
@@ -6319,28 +7165,28 @@
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>20</v>
@@ -6349,22 +7195,22 @@
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>363</v>
+        <v>423</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>364</v>
+        <v>424</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
@@ -6379,28 +7225,28 @@
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>20</v>
@@ -6409,28 +7255,28 @@
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>373</v>
+        <v>433</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>20</v>
@@ -6439,28 +7285,28 @@
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>376</v>
+        <v>436</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>378</v>
+        <v>438</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>20</v>
@@ -6469,28 +7315,28 @@
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>381</v>
+        <v>441</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>382</v>
+        <v>442</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>384</v>
+        <v>444</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>20</v>
@@ -6499,28 +7345,28 @@
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>387</v>
+        <v>447</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>388</v>
+        <v>448</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>389</v>
+        <v>449</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>20</v>
@@ -6529,28 +7375,28 @@
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>391</v>
+        <v>451</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>392</v>
+        <v>452</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>393</v>
+        <v>453</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>20</v>
@@ -6559,28 +7405,28 @@
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>397</v>
+        <v>457</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>20</v>
@@ -6589,28 +7435,28 @@
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>401</v>
+        <v>461</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>20</v>
@@ -6619,28 +7465,28 @@
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>403</v>
+        <v>463</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>404</v>
+        <v>464</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>405</v>
+        <v>465</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>406</v>
+        <v>466</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>384</v>
+        <v>444</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
@@ -6649,28 +7495,28 @@
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>407</v>
+        <v>467</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>408</v>
+        <v>468</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>409</v>
+        <v>469</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>384</v>
+        <v>444</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>20</v>
@@ -6679,22 +7525,22 @@
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>411</v>
+        <v>471</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>413</v>
+        <v>473</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>414</v>
+        <v>474</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>415</v>
+        <v>475</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
@@ -6709,16 +7555,16 @@
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>417</v>
+        <v>477</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>418</v>
+        <v>478</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -6730,13 +7576,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>419</v>
+        <v>479</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -6748,13 +7594,13 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -6766,13 +7612,13 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>423</v>
+        <v>483</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -6783,13 +7629,13 @@
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>425</v>
+        <v>485</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>426</v>
+        <v>486</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -6801,13 +7647,13 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>427</v>
+        <v>487</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -6818,13 +7664,13 @@
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>429</v>
+        <v>489</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>430</v>
+        <v>490</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -6836,13 +7682,13 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>431</v>
+        <v>491</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>432</v>
+        <v>492</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -6854,13 +7700,13 @@
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>433</v>
+        <v>493</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>434</v>
+        <v>494</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6871,13 +7717,13 @@
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>435</v>
+        <v>495</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>436</v>
+        <v>496</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -6889,13 +7735,13 @@
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>437</v>
+        <v>497</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6907,16 +7753,16 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>439</v>
+        <v>499</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -6927,16 +7773,16 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>441</v>
+        <v>501</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>442</v>
+        <v>502</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -6947,16 +7793,16 @@
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>443</v>
+        <v>503</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>444</v>
+        <v>504</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -6967,16 +7813,16 @@
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>445</v>
+        <v>505</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>446</v>
+        <v>506</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -6987,16 +7833,16 @@
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>447</v>
+        <v>507</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>448</v>
+        <v>508</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -7007,7 +7853,7 @@
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>449</v>
+        <v>509</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -7025,13 +7871,13 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
@@ -7044,18 +7890,18 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>450</v>
+        <v>184</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -7069,7 +7915,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>451</v>
+        <v>510</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -7083,7 +7929,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>452</v>
+        <v>511</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -7097,7 +7943,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>453</v>
+        <v>512</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -7111,7 +7957,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>454</v>
+        <v>513</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -7124,7 +7970,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>455</v>
+        <v>514</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -7138,7 +7984,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>456</v>
+        <v>515</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -7151,7 +7997,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>457</v>
+        <v>516</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -7164,7 +8010,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>458</v>
+        <v>517</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -7177,17 +8023,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>14</v>
@@ -7196,24 +8042,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>14</v>
@@ -7222,24 +8068,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>14</v>
@@ -7248,24 +8094,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>14</v>
@@ -7274,17 +8120,17 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="522">
   <si>
     <t>剧名</t>
   </si>
@@ -581,6 +581,9 @@
     <t>剧情 / 犯罪</t>
   </si>
   <si>
+    <t>26/100</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 张瑞希 / 田惠媛 / 薛正焕 / 周清晨 / 尹海英 /</t>
   </si>
   <si>
@@ -1091,6 +1094,15 @@
   <si>
     <t>链接：https://pan.quark.cn/s/c2c8aa7ff0c2?pwd=JZEy
 提取码：JZEy</t>
+  </si>
+  <si>
+    <t>我们愉快的好日子</t>
+  </si>
+  <si>
+    <t>严贤京/尹仲勋/申正允/尹多英/金惠玉</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/77097bff82c1?pwd=G2jr  提取码：G2jr</t>
   </si>
   <si>
     <t>神的游戏</t>
@@ -2443,22 +2455,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="19.5"/>
       <color rgb="FF494949"/>
@@ -2473,11 +2469,27 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -3009,7 +3021,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3177,12 +3189,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3731,12 +3737,12 @@
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
     <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="43.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.125" style="1" customWidth="1"/>
     <col min="5" max="6" width="10.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="5" customWidth="1"/>
+    <col min="8" max="8" width="36.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="4.875" style="5" customWidth="1"/>
     <col min="10" max="10" width="74.5" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="6"/>
   </cols>
@@ -4376,8 +4382,8 @@
       <c r="D21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="46">
-        <v>13</v>
+      <c r="E21" s="46" t="s">
+        <v>109</v>
       </c>
       <c r="F21" s="23" t="s">
         <v>14</v>
@@ -4386,24 +4392,24 @@
         <v>2026</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I21" s="47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>13</v>
@@ -4418,24 +4424,24 @@
         <v>2026</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I22" s="48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>13</v>
@@ -4450,24 +4456,24 @@
         <v>2026</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I23" s="48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D24" s="23" t="s">
         <v>13</v>
@@ -4482,24 +4488,24 @@
         <v>2026</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I24" s="48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>13</v>
@@ -4514,24 +4520,24 @@
         <v>2026</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I25" s="48" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>13</v>
@@ -4546,16 +4552,16 @@
         <v>2026</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J26" s="7"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>11</v>
@@ -4576,28 +4582,28 @@
         <v>2026</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J27" s="7"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>20</v>
@@ -4606,28 +4612,28 @@
         <v>2026</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J28" s="7"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>20</v>
@@ -4636,22 +4642,22 @@
         <v>2026</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J29" s="7"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D30" s="23" t="s">
         <v>13</v>
@@ -4666,24 +4672,24 @@
         <v>2026</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I30" s="48" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>13</v>
@@ -4698,24 +4704,24 @@
         <v>2026</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I31" s="48" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>103</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D32" s="23" t="s">
         <v>13</v>
@@ -4730,24 +4736,24 @@
         <v>2026</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A33" s="25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>103</v>
       </c>
       <c r="C33" s="49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>13</v>
@@ -4762,24 +4768,24 @@
         <v>2026</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>103</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>13</v>
@@ -4794,22 +4800,22 @@
         <v>2026</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I34" s="51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J34" s="52"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A35" s="25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>13</v>
@@ -4824,44 +4830,44 @@
         <v>2026</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I35" s="48" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C36" s="52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I36" s="24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J36" s="7"/>
     </row>
     <row r="37" s="6" customFormat="1" ht="34" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>103</v>
@@ -4873,7 +4879,7 @@
         <v>13</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F37" s="23" t="s">
         <v>14</v>
@@ -4882,27 +4888,44 @@
         <v>2026</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I37" s="24"/>
       <c r="J37" s="53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A38" s="21"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="23"/>
+      <c r="A38" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="7">
+        <v>119</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H38" s="23" t="s">
+        <v>190</v>
+      </c>
       <c r="I38" s="24"/>
-      <c r="J38" s="7"/>
+      <c r="J38" s="7" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="39" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A39" s="21"/>
       <c r="B39" s="7"/>
       <c r="C39" s="52"/>
       <c r="D39" s="7"/>
@@ -5035,13 +5058,13 @@
     </row>
     <row r="50" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A50" s="25" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>13</v>
@@ -5057,21 +5080,21 @@
       </c>
       <c r="H50" s="23"/>
       <c r="I50" s="48" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="J50" s="23" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A51" s="25" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>13</v>
@@ -5087,18 +5110,18 @@
       </c>
       <c r="H51" s="47"/>
       <c r="I51" s="48" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J51" s="23" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A52" s="25" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C52" s="23"/>
       <c r="D52" s="23" t="s">
@@ -5115,18 +5138,18 @@
       </c>
       <c r="H52" s="47"/>
       <c r="I52" s="48" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J52" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A53" s="25" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C53" s="23"/>
       <c r="D53" s="23" t="s">
@@ -5143,21 +5166,21 @@
       </c>
       <c r="H53" s="47"/>
       <c r="I53" s="48" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A54" s="21" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C54" s="52" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>13</v>
@@ -5171,19 +5194,19 @@
       </c>
       <c r="H54" s="23"/>
       <c r="I54" s="24" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J54" s="7"/>
     </row>
     <row r="55" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A55" s="21" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C55" s="52" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>13</v>
@@ -5197,16 +5220,16 @@
       </c>
       <c r="H55" s="23"/>
       <c r="I55" s="24" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J55" s="7"/>
     </row>
     <row r="56" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A56" s="21" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -5217,18 +5240,18 @@
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="24" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -5239,18 +5262,18 @@
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="24" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -5261,18 +5284,18 @@
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
       <c r="I58" s="24" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A59" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -5284,18 +5307,18 @@
       <c r="H59" s="7"/>
       <c r="I59" s="24"/>
       <c r="J59" s="7" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A60" s="25" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="7">
@@ -5308,28 +5331,28 @@
         <v>2026</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:10">
       <c r="A61" s="25" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D61" s="7"/>
       <c r="E61" s="22" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F61" s="22" t="s">
         <v>14</v>
@@ -5338,24 +5361,24 @@
         <v>2026</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I61" s="24"/>
       <c r="J61" s="7"/>
     </row>
     <row r="62" ht="25" customHeight="1" spans="1:10">
       <c r="A62" s="25" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D62" s="7"/>
       <c r="E62" s="22" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F62" s="22" t="s">
         <v>14</v>
@@ -5364,24 +5387,24 @@
         <v>2026</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I62" s="24"/>
       <c r="J62" s="7"/>
     </row>
     <row r="63" ht="25" customHeight="1" spans="1:10">
       <c r="A63" s="25" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="22" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F63" s="22" t="s">
         <v>14</v>
@@ -5390,24 +5413,24 @@
         <v>2026</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I63" s="24"/>
       <c r="J63" s="7"/>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:10">
       <c r="A64" s="25" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D64" s="7"/>
       <c r="E64" s="22" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F64" s="22" t="s">
         <v>14</v>
@@ -5416,17 +5439,17 @@
         <v>2026</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I64" s="24"/>
       <c r="J64" s="7"/>
     </row>
     <row r="65" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A65" s="25" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -5443,7 +5466,7 @@
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:10">
       <c r="A66" s="21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>69</v>
@@ -5459,15 +5482,15 @@
       </c>
       <c r="H66" s="7"/>
       <c r="I66" s="24" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J66" s="21" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="67" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A67" s="21" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>69</v>
@@ -5482,24 +5505,24 @@
         <v>2026</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J67" s="24" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:10">
       <c r="A68" s="21" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="22"/>
@@ -5510,24 +5533,24 @@
         <v>2026</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J68" s="24" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:10">
       <c r="A69" s="21" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D69" s="7"/>
       <c r="E69" s="22"/>
@@ -5538,13 +5561,13 @@
         <v>2026</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J69" s="24" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:10">
@@ -5561,13 +5584,13 @@
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:10">
       <c r="A71" s="42" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B71" s="46" t="s">
         <v>69</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="22"/>
@@ -5578,14 +5601,14 @@
         <v>8.25</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I71" s="24"/>
       <c r="J71" s="21"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A72" s="42" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>69</v>
@@ -5597,7 +5620,7 @@
         <v>20</v>
       </c>
       <c r="G72" s="23" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H72" s="7"/>
       <c r="I72" s="24"/>
@@ -5605,7 +5628,7 @@
     </row>
     <row r="73" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A73" s="42" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>69</v>
@@ -5625,7 +5648,7 @@
     </row>
     <row r="74" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A74" s="42" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>69</v>
@@ -5635,7 +5658,7 @@
       <c r="E74" s="22"/>
       <c r="F74" s="22"/>
       <c r="G74" s="23" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H74" s="7"/>
       <c r="I74" s="24"/>
@@ -5643,7 +5666,7 @@
     </row>
     <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A75" s="42" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>69</v>
@@ -5663,7 +5686,7 @@
     </row>
     <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A76" s="42" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>69</v>
@@ -5679,7 +5702,7 @@
     </row>
     <row r="77" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A77" s="42" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>69</v>
@@ -5697,7 +5720,7 @@
     </row>
     <row r="78" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A78" s="42" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -5711,7 +5734,7 @@
     </row>
     <row r="79" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
       <c r="A79" s="42" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -5725,7 +5748,7 @@
     </row>
     <row r="80" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A80" s="42" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -5739,7 +5762,7 @@
     </row>
     <row r="81" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A81" s="42" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -5753,14 +5776,14 @@
     </row>
     <row r="82" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A82" s="42" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="22"/>
       <c r="F82" s="22" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G82" s="23"/>
       <c r="H82" s="7"/>
@@ -5769,14 +5792,14 @@
     </row>
     <row r="83" ht="25" customHeight="1" spans="1:10">
       <c r="A83" s="42" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="22"/>
       <c r="F83" s="22" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G83" s="23"/>
       <c r="H83" s="7"/>
@@ -5785,14 +5808,14 @@
     </row>
     <row r="84" ht="25" customHeight="1" spans="1:10">
       <c r="A84" s="21" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="22"/>
       <c r="F84" s="22" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G84" s="23"/>
       <c r="H84" s="7"/>
@@ -5801,14 +5824,14 @@
     </row>
     <row r="85" ht="25" customHeight="1" spans="1:10">
       <c r="A85" s="42" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="22"/>
       <c r="F85" s="22" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G85" s="23"/>
       <c r="H85" s="7"/>
@@ -5817,7 +5840,7 @@
     </row>
     <row r="86" ht="25" customHeight="1" spans="1:10">
       <c r="A86" s="42" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -5833,7 +5856,7 @@
     </row>
     <row r="87" ht="25" customHeight="1" spans="1:10">
       <c r="A87" s="42" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -5849,7 +5872,7 @@
     </row>
     <row r="88" ht="25" customHeight="1" spans="1:10">
       <c r="A88" s="42" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -5865,7 +5888,7 @@
     </row>
     <row r="89" ht="25" customHeight="1" spans="1:10">
       <c r="A89" s="42" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -5879,14 +5902,14 @@
     </row>
     <row r="90" ht="25" customHeight="1" spans="1:10">
       <c r="A90" s="42" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="22"/>
       <c r="F90" s="22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G90" s="23"/>
       <c r="H90" s="7"/>
@@ -5895,7 +5918,7 @@
     </row>
     <row r="91" ht="25" customHeight="1" spans="1:10">
       <c r="A91" s="42" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -5909,7 +5932,7 @@
     </row>
     <row r="92" ht="25" customHeight="1" spans="1:10">
       <c r="A92" s="42" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -5923,14 +5946,14 @@
     </row>
     <row r="93" ht="25" customHeight="1" spans="1:10">
       <c r="A93" s="42" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G93" s="23"/>
       <c r="H93" s="7"/>
@@ -5939,14 +5962,14 @@
     </row>
     <row r="94" ht="25" customHeight="1" spans="1:10">
       <c r="A94" s="42" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="22"/>
       <c r="F94" s="22" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G94" s="23"/>
       <c r="H94" s="7"/>
@@ -5955,16 +5978,16 @@
     </row>
     <row r="95" ht="25" customHeight="1" spans="1:10">
       <c r="A95" s="42" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G95" s="23"/>
       <c r="H95" s="7"/>
@@ -5973,16 +5996,16 @@
     </row>
     <row r="96" ht="25" customHeight="1" spans="1:10">
       <c r="A96" s="42" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="22"/>
       <c r="F96" s="22" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G96" s="23"/>
       <c r="H96" s="7"/>
@@ -5991,16 +6014,16 @@
     </row>
     <row r="97" ht="25" customHeight="1" spans="1:10">
       <c r="A97" s="42" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G97" s="23"/>
       <c r="H97" s="7"/>
@@ -6009,16 +6032,16 @@
     </row>
     <row r="98" ht="25" customHeight="1" spans="1:10">
       <c r="A98" s="42" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="22"/>
       <c r="F98" s="22" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G98" s="23"/>
       <c r="H98" s="7"/>
@@ -6027,16 +6050,16 @@
     </row>
     <row r="99" ht="25" customHeight="1" spans="1:10">
       <c r="A99" s="42" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="22"/>
       <c r="F99" s="22" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G99" s="23"/>
       <c r="H99" s="7"/>
@@ -6045,16 +6068,16 @@
     </row>
     <row r="100" ht="25" customHeight="1" spans="1:10">
       <c r="A100" s="42" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="22"/>
       <c r="F100" s="22" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G100" s="23"/>
       <c r="H100" s="7"/>
@@ -6063,16 +6086,16 @@
     </row>
     <row r="101" ht="25" customHeight="1" spans="1:10">
       <c r="A101" s="42" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="22"/>
       <c r="F101" s="22" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G101" s="23"/>
       <c r="H101" s="7"/>
@@ -6081,16 +6104,16 @@
     </row>
     <row r="102" ht="25" customHeight="1" spans="1:10">
       <c r="A102" s="42" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="22"/>
       <c r="F102" s="22" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G102" s="23"/>
       <c r="H102" s="7"/>
@@ -6099,16 +6122,16 @@
     </row>
     <row r="103" ht="25" customHeight="1" spans="1:10">
       <c r="A103" s="42" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="22"/>
       <c r="F103" s="22" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G103" s="23"/>
       <c r="H103" s="7"/>
@@ -6117,16 +6140,16 @@
     </row>
     <row r="104" ht="25" customHeight="1" spans="1:10">
       <c r="A104" s="42" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D104" s="7"/>
       <c r="E104" s="22"/>
       <c r="F104" s="22" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G104" s="23"/>
       <c r="H104" s="7"/>
@@ -6135,16 +6158,16 @@
     </row>
     <row r="105" ht="25" customHeight="1" spans="1:10">
       <c r="A105" s="42" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="22"/>
       <c r="F105" s="22" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G105" s="23"/>
       <c r="H105" s="7"/>
@@ -6153,16 +6176,16 @@
     </row>
     <row r="106" ht="25" customHeight="1" spans="1:10">
       <c r="A106" s="42" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B106" s="46"/>
       <c r="C106" s="46" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D106" s="46"/>
       <c r="E106" s="55"/>
       <c r="F106" s="55" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G106" s="56"/>
       <c r="H106" s="7"/>
@@ -6171,16 +6194,16 @@
     </row>
     <row r="107" ht="25" customHeight="1" spans="1:10">
       <c r="A107" s="42" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B107" s="46"/>
       <c r="C107" s="46" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D107" s="46"/>
       <c r="E107" s="55"/>
       <c r="F107" s="55" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G107" s="56"/>
       <c r="H107" s="7"/>
@@ -6189,14 +6212,14 @@
     </row>
     <row r="108" ht="25" customHeight="1" spans="1:10">
       <c r="A108" s="42" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B108" s="46"/>
       <c r="C108" s="46"/>
       <c r="D108" s="46"/>
       <c r="E108" s="55"/>
       <c r="F108" s="55" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G108" s="56"/>
       <c r="H108" s="7"/>
@@ -6205,16 +6228,16 @@
     </row>
     <row r="109" ht="25" customHeight="1" spans="1:10">
       <c r="A109" s="42" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B109" s="46"/>
       <c r="C109" s="46" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D109" s="46"/>
       <c r="E109" s="55"/>
       <c r="F109" s="55" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G109" s="23"/>
       <c r="H109" s="7"/>
@@ -6223,16 +6246,16 @@
     </row>
     <row r="110" ht="25" customHeight="1" spans="1:10">
       <c r="A110" s="42" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B110" s="46"/>
       <c r="C110" s="46" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D110" s="46"/>
       <c r="E110" s="55"/>
       <c r="F110" s="55" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G110" s="23"/>
       <c r="H110" s="7"/>
@@ -6241,13 +6264,13 @@
     </row>
     <row r="111" ht="25" customHeight="1" spans="1:10">
       <c r="A111" s="13"/>
-      <c r="B111" s="57"/>
+      <c r="B111" s="11"/>
       <c r="C111" s="11"/>
-      <c r="D111" s="57"/>
-      <c r="E111" s="58"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="20"/>
       <c r="F111" s="20"/>
       <c r="G111" s="10"/>
-      <c r="H111" s="57"/>
+      <c r="H111" s="11"/>
       <c r="I111" s="24"/>
       <c r="J111" s="24"/>
     </row>
@@ -6355,7 +6378,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6364,22 +6387,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6393,22 +6416,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6422,22 +6445,22 @@
         <v>11</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F3" s="39" t="s">
+        <v>352</v>
+      </c>
+      <c r="G3" s="39" t="s">
+        <v>353</v>
+      </c>
+      <c r="H3" s="39" t="s">
         <v>348</v>
       </c>
-      <c r="G3" s="39" t="s">
-        <v>349</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>344</v>
-      </c>
       <c r="I3" s="39" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6451,22 +6474,22 @@
         <v>11</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="H4" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" s="39" t="s">
         <v>354</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6480,22 +6503,22 @@
         <v>11</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6509,22 +6532,22 @@
         <v>11</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6538,22 +6561,22 @@
         <v>103</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6567,22 +6590,22 @@
         <v>103</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6590,28 +6613,28 @@
         <v>9</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6619,28 +6642,28 @@
         <v>10</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -6648,28 +6671,28 @@
         <v>11</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>103</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -6677,28 +6700,28 @@
         <v>12</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>103</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -6706,28 +6729,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>103</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -6735,28 +6758,28 @@
         <v>14</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -6764,28 +6787,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -6793,28 +6816,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -6822,28 +6845,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F17" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="I17" s="39" t="s">
         <v>391</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>391</v>
-      </c>
-      <c r="H17" s="39" t="s">
-        <v>391</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -6851,28 +6874,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F18" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="I18" s="39" t="s">
         <v>391</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>391</v>
-      </c>
-      <c r="H18" s="39" t="s">
-        <v>391</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -6880,28 +6903,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -6909,28 +6932,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -6938,28 +6961,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -6967,28 +6990,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -6996,28 +7019,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -7034,7 +7057,7 @@
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -7114,13 +7137,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -7135,28 +7158,28 @@
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>20</v>
@@ -7165,28 +7188,28 @@
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>20</v>
@@ -7195,28 +7218,28 @@
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>20</v>
@@ -7225,28 +7248,28 @@
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>20</v>
@@ -7255,28 +7278,28 @@
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>20</v>
@@ -7285,28 +7308,28 @@
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>20</v>
@@ -7315,28 +7338,28 @@
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>20</v>
@@ -7345,28 +7368,28 @@
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>20</v>
@@ -7375,28 +7398,28 @@
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>20</v>
@@ -7405,28 +7428,28 @@
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>20</v>
@@ -7435,28 +7458,28 @@
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>20</v>
@@ -7465,28 +7488,28 @@
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
@@ -7495,28 +7518,28 @@
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>20</v>
@@ -7525,28 +7548,28 @@
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>20</v>
@@ -7555,16 +7578,16 @@
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7576,13 +7599,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7594,13 +7617,13 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7612,13 +7635,13 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7629,13 +7652,13 @@
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -7647,13 +7670,13 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7664,13 +7687,13 @@
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7682,13 +7705,13 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7700,13 +7723,13 @@
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7717,13 +7740,13 @@
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7735,13 +7758,13 @@
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7753,16 +7776,16 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -7773,16 +7796,16 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -7793,16 +7816,16 @@
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -7813,16 +7836,16 @@
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -7833,16 +7856,16 @@
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -7853,7 +7876,7 @@
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -7871,13 +7894,13 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
@@ -7890,18 +7913,18 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -7915,7 +7938,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -7929,7 +7952,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -7943,7 +7966,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -7957,7 +7980,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -7970,7 +7993,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -7984,7 +8007,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -7997,7 +8020,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -8010,7 +8033,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -8023,17 +8046,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>14</v>
@@ -8042,24 +8065,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>14</v>
@@ -8068,24 +8091,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>14</v>
@@ -8094,24 +8117,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>14</v>
@@ -8120,17 +8143,17 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
     <sheet name="已删" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">在播剧更新时间表!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已删!$A$1:$J$48</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="527">
   <si>
     <t>剧名</t>
   </si>
@@ -83,7 +83,7 @@
     <t>1080P</t>
   </si>
   <si>
-    <t>更新中</t>
+    <t>已完结</t>
   </si>
   <si>
     <t>丁禹兮/邓恩熙/尤靖茹/白澍/吕晓霖</t>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>剧情</t>
-  </si>
-  <si>
-    <t>已完结</t>
   </si>
   <si>
     <t xml:space="preserve">黄景瑜/蒋奇明/于和伟/闫佩伦/张佳宁 </t>
@@ -560,145 +557,291 @@
     <t>链接：https://pan.quark.cn/s/c7ed8245bb94?pwd=5Wcp 提取码：5Wcp</t>
   </si>
   <si>
-    <t>家庭关系证明书</t>
+    <t>九门2</t>
+  </si>
+  <si>
+    <t>剧情 / 奇幻 / 冒险</t>
+  </si>
+  <si>
+    <t xml:space="preserve">陈伟霆/陈瑶/曾舜晞/王茂蕾/王奕婷/李乃文/释小龙/应灏铭/季肖冰/胡耘豪/徐正溪 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1V8VWsfDlUm1NhfIO2dMB0Q 提取码: a5m2 </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/16702c9b9e93?pwd=Sqz1 提取码：Sqz1</t>
+  </si>
+  <si>
+    <t>御廷谣</t>
+  </si>
+  <si>
+    <t>爱情/古装</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吴谨言 / 陈哲远 / 梁永棋 / 赵昭仪 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1o9b-WmhM1MJozXH7W07kdA 提取码: 2dh5 </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/348364bd7156?pwd=pr1p 提取码：pr1p</t>
+  </si>
+  <si>
+    <t>这一秒过火</t>
+  </si>
+  <si>
+    <t>民国/虐恋</t>
+  </si>
+  <si>
+    <t>张凌赫/王楚然/付辛博</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1igi7TfeKtpNgFbDbABLN4w 提取码: kt7b </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/26bf9778b8c6?pwd=LMzc 提取码：LMzc</t>
+  </si>
+  <si>
+    <t>兵自风中来</t>
+  </si>
+  <si>
+    <t>剧情/动作</t>
+  </si>
+  <si>
+    <t> 欧豪/蓝盈莹/丁勇岱/史兰芽/刘奕君 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1sg514-ZHQvotLItTuc9AXA 提取码: e4nt </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/b477bb878fc2?pwd=LnpB 提取码：LnpB</t>
+  </si>
+  <si>
+    <t>人鱼</t>
+  </si>
+  <si>
+    <t>剧情 / 悬疑</t>
+  </si>
+  <si>
+    <t>刘孜 / 张开泰 / 黄杨钿甜 / 董勇 / 张帆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1IlMOG0CUaK-K2B0cE7xlog 提取码: yywj </t>
+  </si>
+  <si>
+    <t>盲盒</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 于雯 / 王艺哲 / 王泓鑫 / 卜冠今 / 孙天</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ywExzVDz8cLIpxmvsHOWCw 提取码: 84g6 </t>
+  </si>
+  <si>
+    <t>百花杀</t>
+  </si>
+  <si>
+    <t>古装/权谋/2026</t>
+  </si>
+  <si>
+    <t>36集全</t>
+  </si>
+  <si>
+    <t>孟子义/何与</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Hco99f2una6nu9nHPGnB2A 提取码: rvv5 </t>
+  </si>
+  <si>
+    <t>京城奇探</t>
+  </si>
+  <si>
+    <t>民国/探案/悬疑</t>
+  </si>
+  <si>
+    <t>翟子路/马思超</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1BMDbhC5GY1iiHf058EGm-A 提取码: cpbj </t>
+  </si>
+  <si>
+    <t>杀手妈咪</t>
   </si>
   <si>
     <t>韩剧</t>
   </si>
   <si>
-    <t xml:space="preserve">朴世荣 / 韩高恩 / 林志恩 / 成伊言 / 朴率拉 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1inTr-QEh-UzsyRlDfM0gbA?pwd=4t8g 提取码: 4t8g </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/1ff35bc35c9e?pwd=XNbw 提取码：XNbw</t>
-  </si>
-  <si>
-    <t>欲望的陷阱</t>
-  </si>
-  <si>
-    <t>剧情 / 犯罪</t>
-  </si>
-  <si>
-    <t>26/100</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 张瑞希 / 田惠媛 / 薛正焕 / 周清晨 / 尹海英 /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1RGqtoh0fV1lUW7LgB0erEA?pwd=ndie 提取码: ndie </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/996d38348f46?pwd=6rC8 提取码：6rC8</t>
-  </si>
-  <si>
-    <t>九门2</t>
-  </si>
-  <si>
-    <t>剧情 / 奇幻 / 冒险</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陈伟霆/陈瑶/曾舜晞/王茂蕾/王奕婷/李乃文/释小龙/应灏铭/季肖冰/胡耘豪/徐正溪 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1V8VWsfDlUm1NhfIO2dMB0Q 提取码: a5m2 </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/16702c9b9e93?pwd=Sqz1 提取码：Sqz1</t>
-  </si>
-  <si>
-    <t>御廷谣</t>
-  </si>
-  <si>
-    <t>爱情/古装</t>
-  </si>
-  <si>
-    <t xml:space="preserve">吴谨言 / 陈哲远 / 梁永棋 / 赵昭仪 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1o9b-WmhM1MJozXH7W07kdA 提取码: 2dh5 </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/348364bd7156?pwd=pr1p 提取码：pr1p</t>
-  </si>
-  <si>
-    <t>这一秒过火</t>
-  </si>
-  <si>
-    <t>民国/虐恋</t>
-  </si>
-  <si>
-    <t>张凌赫/王楚然/付辛博</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1igi7TfeKtpNgFbDbABLN4w 提取码: kt7b </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/26bf9778b8c6?pwd=LMzc 提取码：LMzc</t>
-  </si>
-  <si>
-    <t>兵自风中来</t>
-  </si>
-  <si>
-    <t>剧情/动作</t>
-  </si>
-  <si>
-    <t> 欧豪/蓝盈莹/丁勇岱/史兰芽/刘奕君 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1sg514-ZHQvotLItTuc9AXA 提取码: e4nt </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/b477bb878fc2?pwd=LnpB 提取码：LnpB</t>
-  </si>
-  <si>
-    <t>人鱼</t>
-  </si>
-  <si>
-    <t>剧情 / 悬疑</t>
-  </si>
-  <si>
-    <t>刘孜 / 张开泰 / 黄杨钿甜 / 董勇 / 张帆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1IlMOG0CUaK-K2B0cE7xlog 提取码: yywj </t>
-  </si>
-  <si>
-    <t>盲盒</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 于雯 / 王艺哲 / 王泓鑫 / 卜冠今 / 孙天</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ywExzVDz8cLIpxmvsHOWCw 提取码: 84g6 </t>
-  </si>
-  <si>
-    <t>百花杀</t>
-  </si>
-  <si>
-    <t>古装/权谋/2026</t>
-  </si>
-  <si>
-    <t>36集全</t>
-  </si>
-  <si>
-    <t>孟子义/何与</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Hco99f2una6nu9nHPGnB2A 提取码: rvv5 </t>
-  </si>
-  <si>
-    <t>京城奇探</t>
-  </si>
-  <si>
-    <t>民国/探案/悬疑</t>
-  </si>
-  <si>
-    <t>翟子路/马思超</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1BMDbhC5GY1iiHf058EGm-A 提取码: cpbj </t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>惊悚</t>
+    </r>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>孔晓振</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>郑浚远</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李相二</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成东日</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1nduXuhFEN-emGjxKdEnY-A 提取码: tsum </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/047b884565d5?pwd=TMD7 提取码：TMD7</t>
+  </si>
+  <si>
+    <t>绘梦婚礼</t>
+  </si>
+  <si>
+    <t>泰剧</t>
+  </si>
+  <si>
+    <t>泰剧/爱情</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>邝玲玲/珙恩娜帕·瑟塔拉塔那彭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1x2-yT0DcRgCtCvnYSO-KIg 提取码: ggm6 </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/66acd7fe79aa?pwd=RLnq 提取码：RLnq</t>
+  </si>
+  <si>
+    <t>宿敌恋人</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爱情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同性</t>
+    </r>
+  </si>
+  <si>
+    <t>10集全</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普洛伊湘普·素帕莎 / 芭莉雅皮·余 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/17IfE4v3SrPF6Y18CdlHkaA 提取码: kxjd </t>
   </si>
   <si>
     <t>李熊猫</t>
@@ -708,6 +851,9 @@
   </si>
   <si>
     <t>喜剧/动作/动画/奇幻</t>
+  </si>
+  <si>
+    <t>更新中</t>
   </si>
   <si>
     <t>齐璇/小连杀/ 魏一凡/ 朱祎</t>
@@ -755,6 +901,9 @@
       </rPr>
       <t>剧情</t>
     </r>
+  </si>
+  <si>
+    <t>12/14</t>
   </si>
   <si>
     <r>
@@ -838,249 +987,34 @@
     <t>链接：https://pan.quark.cn/s/3b6a404a18cf?pwd=KZQM 提取码：KZQM</t>
   </si>
   <si>
-    <t>杀手妈咪</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111111"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>剧情</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111111"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>惊悚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>孔晓振</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>郑浚远</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>李相二</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>成东日</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1nduXuhFEN-emGjxKdEnY-A 提取码: tsum </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/047b884565d5?pwd=TMD7 提取码：TMD7</t>
-  </si>
-  <si>
-    <t>我的偶像总裁</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>喜剧</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>爱情</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>姜勋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>金慧埈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>车禹闵</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1b4kgz-PlK3oQ_N89iSuweg 提取码: 98fh </t>
-  </si>
-  <si>
-    <t>绘梦婚礼</t>
-  </si>
-  <si>
-    <t>泰剧</t>
-  </si>
-  <si>
-    <t>韩剧/爱情</t>
-  </si>
-  <si>
-    <t>邝玲玲/珙恩娜帕·瑟塔拉塔那彭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1x2-yT0DcRgCtCvnYSO-KIg 提取码: ggm6 </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/66acd7fe79aa?pwd=RLnq 提取码：RLnq</t>
-  </si>
-  <si>
-    <t>宿敌恋人</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>剧情</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>爱情</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>同性</t>
-    </r>
-  </si>
-  <si>
-    <t>10集全</t>
-  </si>
-  <si>
-    <t xml:space="preserve">普洛伊湘普·素帕莎 / 芭莉雅皮·余 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/17IfE4v3SrPF6Y18CdlHkaA 提取码: kxjd </t>
+    <t>家庭关系证明书</t>
+  </si>
+  <si>
+    <t xml:space="preserve">朴世荣 / 韩高恩 / 林志恩 / 成伊言 / 朴率拉 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1inTr-QEh-UzsyRlDfM0gbA?pwd=4t8g 提取码: 4t8g </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/1ff35bc35c9e?pwd=XNbw 提取码：XNbw</t>
+  </si>
+  <si>
+    <t>欲望的陷阱</t>
+  </si>
+  <si>
+    <t>剧情 / 犯罪</t>
+  </si>
+  <si>
+    <t>26/100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 张瑞希 / 田惠媛 / 薛正焕 / 周清晨 / 尹海英 /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1RGqtoh0fV1lUW7LgB0erEA?pwd=ndie 提取码: ndie </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/996d38348f46?pwd=6rC8 提取码：6rC8</t>
   </si>
   <si>
     <t>爱情来了</t>
@@ -1103,6 +1037,12 @@
   </si>
   <si>
     <t>链接：https://pan.quark.cn/s/77097bff82c1?pwd=G2jr  提取码：G2jr</t>
+  </si>
+  <si>
+    <t>从犯规开始吧？</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/9a4c405f64dc?pwd=UvZi 提取码：UvZi</t>
   </si>
   <si>
     <t>神的游戏</t>
@@ -1238,6 +1178,868 @@
   </si>
   <si>
     <t>链接：https://pan.quark.cn/s/3e5d38724fff?pwd=jeHy 提取码：jeHy</t>
+  </si>
+  <si>
+    <t>去你的岛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1mU5VCAnqvFIxwFfFcBWvPA?pwd=dhwb 提取码: dhwb </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/644c46729a6d?pwd=SyGd 提取码：SyGd</t>
+  </si>
+  <si>
+    <t>抓特务</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 雷佳音/胡歌/啜妮/张瑶/林晓凡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1PpNPs5ANcuuvHmUmczbz1A?pwd=3gqi 提取码: 3gqi </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/d53679b91d3b?pwd=iq9C 提取码：iq9C</t>
+  </si>
+  <si>
+    <t>污点</t>
+  </si>
+  <si>
+    <t>喜剧/恐怖</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 瑛法·瓦拉哈/莎露彩·查金哈/杰迪帕·迪拉朋帕</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1k1jN616TWuYJ0fDa4530uA?pwd=i78c 提取码: i78c </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/30bbfab35499?pwd=MvVq 提取码：MvVq</t>
+  </si>
+  <si>
+    <t>千门之群龙夺宝</t>
+  </si>
+  <si>
+    <t>剧情/悬疑/奇幻</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 薛闻君/刘凡菲/王俊棠/申琦/许子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1M3LF03DrwRa-MA-idGBqpA?pwd=db78 提取码: db78 </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/3ac561799dd2?pwd=JYsB 提取码：JYsB</t>
+  </si>
+  <si>
+    <t>杯雪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">藤新/李兰陵/杨昕燃/常蓉珊/沈念如 </t>
+  </si>
+  <si>
+    <t>怒之杀</t>
+  </si>
+  <si>
+    <t>未上映</t>
+  </si>
+  <si>
+    <t>第九层反转</t>
+  </si>
+  <si>
+    <t>玩具总动员5</t>
+  </si>
+  <si>
+    <t>爱恋成婚</t>
+  </si>
+  <si>
+    <t>智能车劫</t>
+  </si>
+  <si>
+    <t>追踪者游戏W 水鱼交融</t>
+  </si>
+  <si>
+    <t>歪心狼对阵ACME</t>
+  </si>
+  <si>
+    <t>鲨笼绝境</t>
+  </si>
+  <si>
+    <t>蝙蝠侠：骑士陨落 第一部</t>
+  </si>
+  <si>
+    <t>最后的刺客</t>
+  </si>
+  <si>
+    <t>顺风车杀手</t>
+  </si>
+  <si>
+    <t>95分</t>
+  </si>
+  <si>
+    <t>核战边缘</t>
+  </si>
+  <si>
+    <t>117分</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>小黄人与大怪兽</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>奇幻变身大冒险</t>
+  </si>
+  <si>
+    <t>乌女山怪谈</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.5"/>
+        <color rgb="FF494949"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>罪案重现</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.5"/>
+        <color rgb="FF494949"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>空枪</t>
+  </si>
+  <si>
+    <t>和平精英：地铁逃生</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>2026惊悚片《滑索惊魂》</t>
+  </si>
+  <si>
+    <t>失控的关系</t>
+  </si>
+  <si>
+    <t>奇门遁甲：逢凶化吉</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>阴风诡影</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>热血部落</t>
+  </si>
+  <si>
+    <t>最新动作片</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>山竹刀</t>
+  </si>
+  <si>
+    <t>最新武侠片</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>古寨枪声</t>
+  </si>
+  <si>
+    <t>最新战争片</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>午夜车库</t>
+  </si>
+  <si>
+    <t>最新恐怖片</t>
+  </si>
+  <si>
+    <t>非法闯入者</t>
+  </si>
+  <si>
+    <t>连环杀人案揭露网络信任危机和家庭暴力之恶</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>河神之渡阴</t>
+  </si>
+  <si>
+    <t>最新悬疑大片</t>
+  </si>
+  <si>
+    <t>58+68</t>
+  </si>
+  <si>
+    <t>我为什么又结婚了</t>
+  </si>
+  <si>
+    <t>最新喜剧片</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>生化杀机</t>
+  </si>
+  <si>
+    <t>恐怖丧尸片</t>
+  </si>
+  <si>
+    <t>蜂鸟行动</t>
+  </si>
+  <si>
+    <t>任贤齐最新战争大片</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>暴烈司机</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>崩溃边缘</t>
+  </si>
+  <si>
+    <t>最新惊悚大片</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>管控成瘾</t>
+  </si>
+  <si>
+    <t>最新科幻</t>
+  </si>
+  <si>
+    <t>醉胆追凶</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>冰雪猴</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>逃出绝命街</t>
+  </si>
+  <si>
+    <t>安妮·海瑟薇最新科幻大片</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>韩国死灵</t>
+  </si>
+  <si>
+    <t>最新奇幻喜剧大片</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>惩罚者</t>
+  </si>
+  <si>
+    <t>东游令</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>播出平台</t>
+  </si>
+  <si>
+    <t>更新日历（每周几/几点）</t>
+  </si>
+  <si>
+    <t>SVIP更新时间</t>
+  </si>
+  <si>
+    <t>普通VIP更新时间</t>
+  </si>
+  <si>
+    <t>非会员/中字资源</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>腾讯视频（全网独播）＋东方卫视</t>
+  </si>
+  <si>
+    <t>8月9日起每日18:00更新，连更8天；东方卫视8月11日起每晚19:30</t>
+  </si>
+  <si>
+    <t>SVIP抢先看1集（首日可看到第4集）</t>
+  </si>
+  <si>
+    <t>会员首日12:00更3集，之后每日18:00更1集</t>
+  </si>
+  <si>
+    <t>未查到</t>
+  </si>
+  <si>
+    <t>置信度：高</t>
+  </si>
+  <si>
+    <t>CCTV-1＋腾讯视频（全网独播）</t>
+  </si>
+  <si>
+    <t>8月17日起央一20:00（周一/二/四/五两集连播），腾讯视频同步</t>
+  </si>
+  <si>
+    <t>SVIP抢先看（具体时点未明确）</t>
+  </si>
+  <si>
+    <t>会员首更3集，之后跟随央视进度</t>
+  </si>
+  <si>
+    <t>置信度：中</t>
+  </si>
+  <si>
+    <t>腾讯视频（精品短剧）</t>
+  </si>
+  <si>
+    <t>8月19日起每日更新，首更6集</t>
+  </si>
+  <si>
+    <t>会员每日可看新集</t>
+  </si>
+  <si>
+    <t>9月4日起可看</t>
+  </si>
+  <si>
+    <t>芒果TV＋湖南卫视</t>
+  </si>
+  <si>
+    <t>8月16日12:00起每日12:00连更（共23集）；湖南卫视8月18日起20:10</t>
+  </si>
+  <si>
+    <t>SVIP更新日抢先看2集</t>
+  </si>
+  <si>
+    <t>会员每日12:00更新</t>
+  </si>
+  <si>
+    <t>腾讯视频</t>
+  </si>
+  <si>
+    <t>8月14日12:00开播，会员每日12:00更2集（首更6集），次周二起每日1集</t>
+  </si>
+  <si>
+    <t>8月30日起每日12:00更2集</t>
+  </si>
+  <si>
+    <t>韩国MBC（日日剧）</t>
+  </si>
+  <si>
+    <t>7月6日起每周一至五晚19:05（韩国时间）</t>
+  </si>
+  <si>
+    <t>无国内平台，不适用</t>
+  </si>
+  <si>
+    <t>中字资源一般次日上午流出</t>
+  </si>
+  <si>
+    <t>韩国KBS2（日日剧）</t>
+  </si>
+  <si>
+    <t>8月10日起每周一至五晚19:50（韩国时间）</t>
+  </si>
+  <si>
+    <t>爱奇艺＋bilibili</t>
+  </si>
+  <si>
+    <t>7月29日起每周三9:00更新1集</t>
+  </si>
+  <si>
+    <t>VIP抢先看2集（爱奇艺VIP首日可看3集）</t>
+  </si>
+  <si>
+    <t>优酷（全网独播）</t>
+  </si>
+  <si>
+    <t>7月16日起每周四10:00更新（优酷YouTube周五10:00抢先看1集）</t>
+  </si>
+  <si>
+    <t>每周四更新</t>
+  </si>
+  <si>
+    <t>韩国SBS（金土剧）＋Disney+</t>
+  </si>
+  <si>
+    <t>8月7日起每周五、六晚21:50（韩国时间）；Disney+约22:30更新</t>
+  </si>
+  <si>
+    <t>韩国MBC（金土剧）</t>
+  </si>
+  <si>
+    <t>7月31日起每周五、六晚21:50（韩国时间）</t>
+  </si>
+  <si>
+    <t>我的偶像总裁</t>
+  </si>
+  <si>
+    <t>韩国tvN（月火剧）＋TVING/Wavve</t>
+  </si>
+  <si>
+    <t>8月3日起每周一、二晚20:45（韩国时间），共12集</t>
+  </si>
+  <si>
+    <t>泰国Ch3</t>
+  </si>
+  <si>
+    <t>6月19日起每周五晚20:30（泰国时间）</t>
+  </si>
+  <si>
+    <t>粉丝中字一般次日流出</t>
+  </si>
+  <si>
+    <t>抖音（创作者账号发布）</t>
+  </si>
+  <si>
+    <t>无固定排播日历，已更约7集</t>
+  </si>
+  <si>
+    <t>不适用（免费内容）</t>
+  </si>
+  <si>
+    <t>免费观看</t>
+  </si>
+  <si>
+    <t>置信度：低</t>
+  </si>
+  <si>
+    <t>抖音AI短剧（疑似）</t>
+  </si>
+  <si>
+    <t>未查到固定排播</t>
+  </si>
+  <si>
+    <t>不适用</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>腾讯视频动漫片单（排播未定）</t>
+  </si>
+  <si>
+    <t>我遇见的精神病患者</t>
+  </si>
+  <si>
+    <t>韩国MBN＋SBS Plus</t>
+  </si>
+  <si>
+    <t>7月12日起每周日晚22:20（韩国时间）</t>
+  </si>
+  <si>
+    <t>韩国MBC</t>
+  </si>
+  <si>
+    <t>6月22日起每周一晚22:50（韩国时间）</t>
+  </si>
+  <si>
+    <t>血战X</t>
+  </si>
+  <si>
+    <t>韩国Wavve原创</t>
+  </si>
+  <si>
+    <t>7月3日起每周五上午11:00（韩国时间）上线</t>
+  </si>
+  <si>
+    <t>中字一般当日/次日流出</t>
+  </si>
+  <si>
+    <t>宇宙年糕店</t>
+  </si>
+  <si>
+    <t>韩国tvN</t>
+  </si>
+  <si>
+    <t>7月31日起每周五晚20:35（韩国时间）</t>
+  </si>
+  <si>
+    <t>我的AI伴侣-奇异恋爱</t>
+  </si>
+  <si>
+    <t>韩国SBS＋Netflix</t>
+  </si>
+  <si>
+    <t>8月20日起每周四晚21:00（韩国时间），共6集</t>
+  </si>
+  <si>
+    <t>中字一般次日流出</t>
+  </si>
+  <si>
+    <t>会员每日12:00更新2集</t>
+  </si>
+  <si>
+    <t>折金枝</t>
+  </si>
+  <si>
+    <t>古装/权谋</t>
+  </si>
+  <si>
+    <t>张赫/徐轸轸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1C11-1DhDULL7qOeytJ9LTw 提取码: fp76 </t>
+  </si>
+  <si>
+    <t>小芳</t>
+  </si>
+  <si>
+    <t>农村/情感/2026</t>
+  </si>
+  <si>
+    <t>18集全</t>
+  </si>
+  <si>
+    <t>王影璐/辛云来</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ow0W65MWHf51XG9MTlOU_w 提取码: qjkw </t>
+  </si>
+  <si>
+    <t>枭起青壤</t>
+  </si>
+  <si>
+    <t>悬疑/奇幻/爱情</t>
+  </si>
+  <si>
+    <t>32集全</t>
+  </si>
+  <si>
+    <t>迪丽热巴/陈星旭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1OtogokYutIkEdJC47cJ7Uw 提取码: am27 </t>
+  </si>
+  <si>
+    <t>凶宅专卖店</t>
+  </si>
+  <si>
+    <t>悬疑/恐怖/台剧</t>
+  </si>
+  <si>
+    <t>李铭顺/范少勋/陈妍霏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Xe0o3SA2YWGEoOvg_XaMJw 提取码: jm1m </t>
+  </si>
+  <si>
+    <t>雨霖铃</t>
+  </si>
+  <si>
+    <t>古装/武侠/2026</t>
+  </si>
+  <si>
+    <t>37集全</t>
+  </si>
+  <si>
+    <t>杨洋/章若楠/方逸伦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1DIzSpxH1kMM9r2MOUMpcVg 提取码: ivs6 </t>
+  </si>
+  <si>
+    <t>朱雀堂</t>
+  </si>
+  <si>
+    <t>古装/悬疑/探案</t>
+  </si>
+  <si>
+    <t>30集全</t>
+  </si>
+  <si>
+    <t>万茜/秦俊杰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1tv-7aShAXEZhRe1AxOaPyQ 提取码: kvc8 </t>
+  </si>
+  <si>
+    <t>太平年</t>
+  </si>
+  <si>
+    <t>古装/历史/权谋</t>
+  </si>
+  <si>
+    <t>48集全</t>
+  </si>
+  <si>
+    <t>白宇/周雨彤/朱亚文</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1iMRM-dpEHO328-BeMbIJvg 提取码: 5w93 </t>
+  </si>
+  <si>
+    <t>莫离</t>
+  </si>
+  <si>
+    <t>古装/爱情/2026</t>
+  </si>
+  <si>
+    <t>40集全</t>
+  </si>
+  <si>
+    <t>白鹿/丞磊</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1wcJvHR1DXO-IDqqcqggo9g 提取码: 8h5y </t>
+  </si>
+  <si>
+    <t>探晴安</t>
+  </si>
+  <si>
+    <t>古装/探案/甜宠</t>
+  </si>
+  <si>
+    <t>22集全</t>
+  </si>
+  <si>
+    <t>常华森/赵晴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1-usXmAkDWkwDpAChYI9BXQ 提取码: tgzx </t>
+  </si>
+  <si>
+    <t>九重紫</t>
+  </si>
+  <si>
+    <t>古装/言情/复仇</t>
+  </si>
+  <si>
+    <t>34集全</t>
+  </si>
+  <si>
+    <t>孟子义/李昀锐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1VDPCPrgJRrzSUit3JtFD5g 提取码: attp </t>
+  </si>
+  <si>
+    <t>江湖夜雨十年灯</t>
+  </si>
+  <si>
+    <t>周翊然/包上恩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/16q3tuC7Z-ENEjFxZjcFKIg 提取码: j31c </t>
+  </si>
+  <si>
+    <t>她的盛宴</t>
+  </si>
+  <si>
+    <t>民国/悬疑/重生</t>
+  </si>
+  <si>
+    <t>28集全</t>
+  </si>
+  <si>
+    <t>何泓姗/谢彬彬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Op4yj0nzXgxj7NgnhzOIlA 提取码: ixxm </t>
+  </si>
+  <si>
+    <t>佳偶天成</t>
+  </si>
+  <si>
+    <t>古装/仙侠/2026</t>
+  </si>
+  <si>
+    <t>任嘉伦/王鹤润</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1DoxyX8OQiw1lMhJJzMd2hQ 提取码: 763y </t>
+  </si>
+  <si>
+    <t>问心2</t>
+  </si>
+  <si>
+    <t>都市/医疗/2026</t>
+  </si>
+  <si>
+    <t>赵又廷/毛晓彤/金世佳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1BCWZnWrZ0VVSTi-cgrGKtQ 提取码: nfdv </t>
+  </si>
+  <si>
+    <t>聪明镇</t>
+  </si>
+  <si>
+    <t>外剧</t>
+  </si>
+  <si>
+    <t>台剧/恐怖/惊悚</t>
+  </si>
+  <si>
+    <t>梁咏琪/陈妍霏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1hvzPTW2hEZD5_Z1m70cnhg 提取码: rrtb </t>
+  </si>
+  <si>
+    <t>为你而来</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1zpmelbjW0vTTsJXTpweg8w 提取码: 5brf </t>
+  </si>
+  <si>
+    <t>克制升温</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ukZSNK8Hi_u8JkZrfQX0UQ 提取码: m4qh </t>
+  </si>
+  <si>
+    <t>双姝美探</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Eh9u_MsoQHh5Ro8Hw_A6Hw 提取码: jy66 </t>
+  </si>
+  <si>
+    <t>江城诡事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Je7fJUQWiJhSXabGeJptcg 提取码: r5ce </t>
+  </si>
+  <si>
+    <t>雀骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/112zScgtCZSCJA71H_NFvYA 提取码: c1bn </t>
+  </si>
+  <si>
+    <t>君子盟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1jEaj80_pR_BEpEkkR550ow 提取码: hkfe </t>
+  </si>
+  <si>
+    <t>画梦录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1r5Zl6G1ZZSxDvKvIjgRvWw 提取码: 5un7 </t>
+  </si>
+  <si>
+    <t>千香</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/13dGU3tDoYZz5hRuqdbcWJQ 提取码: m98v </t>
+  </si>
+  <si>
+    <t>白日提灯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1tWOzn5C4rph_0fNHtCh-Ug 提取码: 6nkf </t>
+  </si>
+  <si>
+    <t>灿如繁星</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/17tvlk-SaPIbw1OvewsPWzQ 提取码: uvtw </t>
+  </si>
+  <si>
+    <t>灵魂摆渡·十年</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1pyPI3AVM2R37E_FepNFYdg 提取码: cqm8 </t>
+  </si>
+  <si>
+    <t>况钟系列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/15IIk4fUTGwXSN9WooKQ-5g 提取码: 4hhu </t>
+  </si>
+  <si>
+    <t>施世伦系列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1jf3E03DXXI5Tk6F4TTzXBg 提取码: 7mdf </t>
+  </si>
+  <si>
+    <t>包拯系列电影</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1bhqXKnw-2P1G2DicV9JTMg 提取码: au92 </t>
+  </si>
+  <si>
+    <t>宋慈系列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1dpGGDyDQ1rMhPp7LVjQNwg 提取码: a372 </t>
+  </si>
+  <si>
+    <t>袁天罡系列电影</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/10adBSzL63iK0CsWUdKtXsQ 提取码: tj5r </t>
+  </si>
+  <si>
+    <t>夏日狂热</t>
+  </si>
+  <si>
+    <t>初智齿</t>
+  </si>
+  <si>
+    <t>烟灰</t>
+  </si>
+  <si>
+    <t>针线缘</t>
+  </si>
+  <si>
+    <t>赴海</t>
+  </si>
+  <si>
+    <t>成名在望</t>
+  </si>
+  <si>
+    <t>整个世界，只有你连上了我</t>
+  </si>
+  <si>
+    <t>两颗心</t>
   </si>
   <si>
     <r>
@@ -1294,9 +2096,6 @@
   </si>
   <si>
     <t>李尚敏/洪榛浩</t>
-  </si>
-  <si>
-    <t>宇宙年糕店</t>
   </si>
   <si>
     <t>4/12</t>
@@ -1377,853 +2176,6 @@
   </si>
   <si>
     <t>我遇见的精神病态者</t>
-  </si>
-  <si>
-    <t>去你的岛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1mU5VCAnqvFIxwFfFcBWvPA?pwd=dhwb 提取码: dhwb </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/644c46729a6d?pwd=SyGd 提取码：SyGd</t>
-  </si>
-  <si>
-    <t>抓特务</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 雷佳音/胡歌/啜妮/张瑶/林晓凡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1PpNPs5ANcuuvHmUmczbz1A?pwd=3gqi 提取码: 3gqi </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/d53679b91d3b?pwd=iq9C 提取码：iq9C</t>
-  </si>
-  <si>
-    <t>污点</t>
-  </si>
-  <si>
-    <t>喜剧/恐怖</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 瑛法·瓦拉哈/莎露彩·查金哈/杰迪帕·迪拉朋帕</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1k1jN616TWuYJ0fDa4530uA?pwd=i78c 提取码: i78c </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/30bbfab35499?pwd=MvVq 提取码：MvVq</t>
-  </si>
-  <si>
-    <t>千门之群龙夺宝</t>
-  </si>
-  <si>
-    <t>剧情/悬疑/奇幻</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 薛闻君/刘凡菲/王俊棠/申琦/许子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1M3LF03DrwRa-MA-idGBqpA?pwd=db78 提取码: db78 </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/3ac561799dd2?pwd=JYsB 提取码：JYsB</t>
-  </si>
-  <si>
-    <t>杯雪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">藤新/李兰陵/杨昕燃/常蓉珊/沈念如 </t>
-  </si>
-  <si>
-    <t>怒之杀</t>
-  </si>
-  <si>
-    <t>未上映</t>
-  </si>
-  <si>
-    <t>第九层反转</t>
-  </si>
-  <si>
-    <t>玩具总动员5</t>
-  </si>
-  <si>
-    <t>爱恋成婚</t>
-  </si>
-  <si>
-    <t>智能车劫</t>
-  </si>
-  <si>
-    <t>追踪者游戏W 水鱼交融</t>
-  </si>
-  <si>
-    <t>歪心狼对阵ACME</t>
-  </si>
-  <si>
-    <t>鲨笼绝境</t>
-  </si>
-  <si>
-    <t>蝙蝠侠：骑士陨落 第一部</t>
-  </si>
-  <si>
-    <t>最后的刺客</t>
-  </si>
-  <si>
-    <t>顺风车杀手</t>
-  </si>
-  <si>
-    <t>95分</t>
-  </si>
-  <si>
-    <t>核战边缘</t>
-  </si>
-  <si>
-    <t>117分</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>小黄人与大怪兽</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>奇幻变身大冒险</t>
-  </si>
-  <si>
-    <t>乌女山怪谈</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.5"/>
-        <color rgb="FF494949"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>罪案重现</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.5"/>
-        <color rgb="FF494949"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>空枪</t>
-  </si>
-  <si>
-    <t>和平精英：地铁逃生</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>2026惊悚片《滑索惊魂》</t>
-  </si>
-  <si>
-    <t>失控的关系</t>
-  </si>
-  <si>
-    <t>奇门遁甲：逢凶化吉</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>阴风诡影</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>热血部落</t>
-  </si>
-  <si>
-    <t>最新动作片</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>山竹刀</t>
-  </si>
-  <si>
-    <t>最新武侠片</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>古寨枪声</t>
-  </si>
-  <si>
-    <t>最新战争片</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>午夜车库</t>
-  </si>
-  <si>
-    <t>最新恐怖片</t>
-  </si>
-  <si>
-    <t>非法闯入者</t>
-  </si>
-  <si>
-    <t>连环杀人案揭露网络信任危机和家庭暴力之恶</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>河神之渡阴</t>
-  </si>
-  <si>
-    <t>最新悬疑大片</t>
-  </si>
-  <si>
-    <t>58+68</t>
-  </si>
-  <si>
-    <t>我为什么又结婚了</t>
-  </si>
-  <si>
-    <t>最新喜剧片</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>生化杀机</t>
-  </si>
-  <si>
-    <t>恐怖丧尸片</t>
-  </si>
-  <si>
-    <t>蜂鸟行动</t>
-  </si>
-  <si>
-    <t>任贤齐最新战争大片</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>暴烈司机</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>崩溃边缘</t>
-  </si>
-  <si>
-    <t>最新惊悚大片</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>管控成瘾</t>
-  </si>
-  <si>
-    <t>最新科幻</t>
-  </si>
-  <si>
-    <t>醉胆追凶</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>冰雪猴</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>逃出绝命街</t>
-  </si>
-  <si>
-    <t>安妮·海瑟薇最新科幻大片</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>韩国死灵</t>
-  </si>
-  <si>
-    <t>最新奇幻喜剧大片</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>播出平台</t>
-  </si>
-  <si>
-    <t>更新日历（每周几/几点）</t>
-  </si>
-  <si>
-    <t>SVIP更新时间</t>
-  </si>
-  <si>
-    <t>普通VIP更新时间</t>
-  </si>
-  <si>
-    <t>非会员/中字资源</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>腾讯视频（全网独播）＋东方卫视</t>
-  </si>
-  <si>
-    <t>8月9日起每日18:00更新，连更8天；东方卫视8月11日起每晚19:30</t>
-  </si>
-  <si>
-    <t>SVIP抢先看1集（首日可看到第4集）</t>
-  </si>
-  <si>
-    <t>会员首日12:00更3集，之后每日18:00更1集</t>
-  </si>
-  <si>
-    <t>未查到</t>
-  </si>
-  <si>
-    <t>置信度：高</t>
-  </si>
-  <si>
-    <t>CCTV-1＋腾讯视频（全网独播）</t>
-  </si>
-  <si>
-    <t>8月17日起央一20:00（周一/二/四/五两集连播），腾讯视频同步</t>
-  </si>
-  <si>
-    <t>SVIP抢先看（具体时点未明确）</t>
-  </si>
-  <si>
-    <t>会员首更3集，之后跟随央视进度</t>
-  </si>
-  <si>
-    <t>置信度：中</t>
-  </si>
-  <si>
-    <t>腾讯视频（精品短剧）</t>
-  </si>
-  <si>
-    <t>8月19日起每日更新，首更6集</t>
-  </si>
-  <si>
-    <t>会员每日可看新集</t>
-  </si>
-  <si>
-    <t>9月4日起可看</t>
-  </si>
-  <si>
-    <t>芒果TV＋湖南卫视</t>
-  </si>
-  <si>
-    <t>8月16日12:00起每日12:00连更（共23集）；湖南卫视8月18日起20:10</t>
-  </si>
-  <si>
-    <t>SVIP更新日抢先看2集</t>
-  </si>
-  <si>
-    <t>会员每日12:00更新</t>
-  </si>
-  <si>
-    <t>腾讯视频</t>
-  </si>
-  <si>
-    <t>8月14日12:00开播，会员每日12:00更2集（首更6集），次周二起每日1集</t>
-  </si>
-  <si>
-    <t>8月30日起每日12:00更2集</t>
-  </si>
-  <si>
-    <t>韩国MBC（日日剧）</t>
-  </si>
-  <si>
-    <t>7月6日起每周一至五晚19:05（韩国时间）</t>
-  </si>
-  <si>
-    <t>无国内平台，不适用</t>
-  </si>
-  <si>
-    <t>中字资源一般次日上午流出</t>
-  </si>
-  <si>
-    <t>韩国KBS2（日日剧）</t>
-  </si>
-  <si>
-    <t>8月10日起每周一至五晚19:50（韩国时间）</t>
-  </si>
-  <si>
-    <t>爱奇艺＋bilibili</t>
-  </si>
-  <si>
-    <t>7月29日起每周三9:00更新1集</t>
-  </si>
-  <si>
-    <t>VIP抢先看2集（爱奇艺VIP首日可看3集）</t>
-  </si>
-  <si>
-    <t>优酷（全网独播）</t>
-  </si>
-  <si>
-    <t>7月16日起每周四10:00更新（优酷YouTube周五10:00抢先看1集）</t>
-  </si>
-  <si>
-    <t>每周四更新</t>
-  </si>
-  <si>
-    <t>韩国SBS（金土剧）＋Disney+</t>
-  </si>
-  <si>
-    <t>8月7日起每周五、六晚21:50（韩国时间）；Disney+约22:30更新</t>
-  </si>
-  <si>
-    <t>韩国MBC（金土剧）</t>
-  </si>
-  <si>
-    <t>7月31日起每周五、六晚21:50（韩国时间）</t>
-  </si>
-  <si>
-    <t>韩国tvN（月火剧）＋TVING/Wavve</t>
-  </si>
-  <si>
-    <t>8月3日起每周一、二晚20:45（韩国时间），共12集</t>
-  </si>
-  <si>
-    <t>泰国Ch3</t>
-  </si>
-  <si>
-    <t>6月19日起每周五晚20:30（泰国时间）</t>
-  </si>
-  <si>
-    <t>粉丝中字一般次日流出</t>
-  </si>
-  <si>
-    <t>抖音（创作者账号发布）</t>
-  </si>
-  <si>
-    <t>无固定排播日历，已更约7集</t>
-  </si>
-  <si>
-    <t>不适用（免费内容）</t>
-  </si>
-  <si>
-    <t>免费观看</t>
-  </si>
-  <si>
-    <t>置信度：低</t>
-  </si>
-  <si>
-    <t>抖音AI短剧（疑似）</t>
-  </si>
-  <si>
-    <t>未查到固定排播</t>
-  </si>
-  <si>
-    <t>不适用</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>腾讯视频动漫片单（排播未定）</t>
-  </si>
-  <si>
-    <t>我遇见的精神病患者</t>
-  </si>
-  <si>
-    <t>韩国MBN＋SBS Plus</t>
-  </si>
-  <si>
-    <t>7月12日起每周日晚22:20（韩国时间）</t>
-  </si>
-  <si>
-    <t>韩国MBC</t>
-  </si>
-  <si>
-    <t>6月22日起每周一晚22:50（韩国时间）</t>
-  </si>
-  <si>
-    <t>血战X</t>
-  </si>
-  <si>
-    <t>韩国Wavve原创</t>
-  </si>
-  <si>
-    <t>7月3日起每周五上午11:00（韩国时间）上线</t>
-  </si>
-  <si>
-    <t>中字一般当日/次日流出</t>
-  </si>
-  <si>
-    <t>韩国tvN</t>
-  </si>
-  <si>
-    <t>7月31日起每周五晚20:35（韩国时间）</t>
-  </si>
-  <si>
-    <t>我的AI伴侣-奇异恋爱</t>
-  </si>
-  <si>
-    <t>韩国SBS＋Netflix</t>
-  </si>
-  <si>
-    <t>8月20日起每周四晚21:00（韩国时间），共6集</t>
-  </si>
-  <si>
-    <t>中字一般次日流出</t>
-  </si>
-  <si>
-    <t>会员每日12:00更新2集</t>
-  </si>
-  <si>
-    <t>折金枝</t>
-  </si>
-  <si>
-    <t>古装/权谋</t>
-  </si>
-  <si>
-    <t>张赫/徐轸轸</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1C11-1DhDULL7qOeytJ9LTw 提取码: fp76 </t>
-  </si>
-  <si>
-    <t>小芳</t>
-  </si>
-  <si>
-    <t>农村/情感/2026</t>
-  </si>
-  <si>
-    <t>18集全</t>
-  </si>
-  <si>
-    <t>王影璐/辛云来</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ow0W65MWHf51XG9MTlOU_w 提取码: qjkw </t>
-  </si>
-  <si>
-    <t>枭起青壤</t>
-  </si>
-  <si>
-    <t>悬疑/奇幻/爱情</t>
-  </si>
-  <si>
-    <t>32集全</t>
-  </si>
-  <si>
-    <t>迪丽热巴/陈星旭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1OtogokYutIkEdJC47cJ7Uw 提取码: am27 </t>
-  </si>
-  <si>
-    <t>凶宅专卖店</t>
-  </si>
-  <si>
-    <t>悬疑/恐怖/台剧</t>
-  </si>
-  <si>
-    <t>李铭顺/范少勋/陈妍霏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Xe0o3SA2YWGEoOvg_XaMJw 提取码: jm1m </t>
-  </si>
-  <si>
-    <t>雨霖铃</t>
-  </si>
-  <si>
-    <t>古装/武侠/2026</t>
-  </si>
-  <si>
-    <t>37集全</t>
-  </si>
-  <si>
-    <t>杨洋/章若楠/方逸伦</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1DIzSpxH1kMM9r2MOUMpcVg 提取码: ivs6 </t>
-  </si>
-  <si>
-    <t>朱雀堂</t>
-  </si>
-  <si>
-    <t>古装/悬疑/探案</t>
-  </si>
-  <si>
-    <t>30集全</t>
-  </si>
-  <si>
-    <t>万茜/秦俊杰</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1tv-7aShAXEZhRe1AxOaPyQ 提取码: kvc8 </t>
-  </si>
-  <si>
-    <t>太平年</t>
-  </si>
-  <si>
-    <t>古装/历史/权谋</t>
-  </si>
-  <si>
-    <t>48集全</t>
-  </si>
-  <si>
-    <t>白宇/周雨彤/朱亚文</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1iMRM-dpEHO328-BeMbIJvg 提取码: 5w93 </t>
-  </si>
-  <si>
-    <t>莫离</t>
-  </si>
-  <si>
-    <t>古装/爱情/2026</t>
-  </si>
-  <si>
-    <t>40集全</t>
-  </si>
-  <si>
-    <t>白鹿/丞磊</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1wcJvHR1DXO-IDqqcqggo9g 提取码: 8h5y </t>
-  </si>
-  <si>
-    <t>探晴安</t>
-  </si>
-  <si>
-    <t>古装/探案/甜宠</t>
-  </si>
-  <si>
-    <t>22集全</t>
-  </si>
-  <si>
-    <t>常华森/赵晴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1-usXmAkDWkwDpAChYI9BXQ 提取码: tgzx </t>
-  </si>
-  <si>
-    <t>九重紫</t>
-  </si>
-  <si>
-    <t>古装/言情/复仇</t>
-  </si>
-  <si>
-    <t>34集全</t>
-  </si>
-  <si>
-    <t>孟子义/李昀锐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1VDPCPrgJRrzSUit3JtFD5g 提取码: attp </t>
-  </si>
-  <si>
-    <t>江湖夜雨十年灯</t>
-  </si>
-  <si>
-    <t>周翊然/包上恩</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/16q3tuC7Z-ENEjFxZjcFKIg 提取码: j31c </t>
-  </si>
-  <si>
-    <t>她的盛宴</t>
-  </si>
-  <si>
-    <t>民国/悬疑/重生</t>
-  </si>
-  <si>
-    <t>28集全</t>
-  </si>
-  <si>
-    <t>何泓姗/谢彬彬</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Op4yj0nzXgxj7NgnhzOIlA 提取码: ixxm </t>
-  </si>
-  <si>
-    <t>佳偶天成</t>
-  </si>
-  <si>
-    <t>古装/仙侠/2026</t>
-  </si>
-  <si>
-    <t>任嘉伦/王鹤润</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1DoxyX8OQiw1lMhJJzMd2hQ 提取码: 763y </t>
-  </si>
-  <si>
-    <t>问心2</t>
-  </si>
-  <si>
-    <t>都市/医疗/2026</t>
-  </si>
-  <si>
-    <t>赵又廷/毛晓彤/金世佳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1BCWZnWrZ0VVSTi-cgrGKtQ 提取码: nfdv </t>
-  </si>
-  <si>
-    <t>聪明镇</t>
-  </si>
-  <si>
-    <t>外剧</t>
-  </si>
-  <si>
-    <t>台剧/恐怖/惊悚</t>
-  </si>
-  <si>
-    <t>梁咏琪/陈妍霏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1hvzPTW2hEZD5_Z1m70cnhg 提取码: rrtb </t>
-  </si>
-  <si>
-    <t>为你而来</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1zpmelbjW0vTTsJXTpweg8w 提取码: 5brf </t>
-  </si>
-  <si>
-    <t>克制升温</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ukZSNK8Hi_u8JkZrfQX0UQ 提取码: m4qh </t>
-  </si>
-  <si>
-    <t>双姝美探</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Eh9u_MsoQHh5Ro8Hw_A6Hw 提取码: jy66 </t>
-  </si>
-  <si>
-    <t>江城诡事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Je7fJUQWiJhSXabGeJptcg 提取码: r5ce </t>
-  </si>
-  <si>
-    <t>雀骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/112zScgtCZSCJA71H_NFvYA 提取码: c1bn </t>
-  </si>
-  <si>
-    <t>君子盟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1jEaj80_pR_BEpEkkR550ow 提取码: hkfe </t>
-  </si>
-  <si>
-    <t>画梦录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1r5Zl6G1ZZSxDvKvIjgRvWw 提取码: 5un7 </t>
-  </si>
-  <si>
-    <t>千香</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/13dGU3tDoYZz5hRuqdbcWJQ 提取码: m98v </t>
-  </si>
-  <si>
-    <t>白日提灯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1tWOzn5C4rph_0fNHtCh-Ug 提取码: 6nkf </t>
-  </si>
-  <si>
-    <t>灿如繁星</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/17tvlk-SaPIbw1OvewsPWzQ 提取码: uvtw </t>
-  </si>
-  <si>
-    <t>灵魂摆渡·十年</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1pyPI3AVM2R37E_FepNFYdg 提取码: cqm8 </t>
-  </si>
-  <si>
-    <t>况钟系列</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/15IIk4fUTGwXSN9WooKQ-5g 提取码: 4hhu </t>
-  </si>
-  <si>
-    <t>施世伦系列</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1jf3E03DXXI5Tk6F4TTzXBg 提取码: 7mdf </t>
-  </si>
-  <si>
-    <t>包拯系列电影</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1bhqXKnw-2P1G2DicV9JTMg 提取码: au92 </t>
-  </si>
-  <si>
-    <t>宋慈系列</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1dpGGDyDQ1rMhPp7LVjQNwg 提取码: a372 </t>
-  </si>
-  <si>
-    <t>袁天罡系列电影</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/10adBSzL63iK0CsWUdKtXsQ 提取码: tj5r </t>
-  </si>
-  <si>
-    <t>夏日狂热</t>
-  </si>
-  <si>
-    <t>初智齿</t>
-  </si>
-  <si>
-    <t>烟灰</t>
-  </si>
-  <si>
-    <t>针线缘</t>
-  </si>
-  <si>
-    <t>赴海</t>
-  </si>
-  <si>
-    <t>成名在望</t>
-  </si>
-  <si>
-    <t>整个世界，只有你连上了我</t>
-  </si>
-  <si>
-    <t>两颗心</t>
   </si>
 </sst>
 </file>
@@ -2302,11 +2254,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF111111"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2455,6 +2402,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="19.5"/>
       <color rgb="FF494949"/>
@@ -2469,12 +2426,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
@@ -2482,17 +2433,18 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2503,6 +2455,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
         <bgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -2891,137 +2849,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3143,53 +3101,104 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3732,14 +3741,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
     <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="10.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="41" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="36.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="4.875" style="5" customWidth="1"/>
@@ -3760,7 +3770,7 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="42" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
@@ -3792,8 +3802,8 @@
       <c r="D2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="23">
-        <v>31</v>
+      <c r="E2" s="43">
+        <v>36</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>14</v>
@@ -3804,7 +3814,7 @@
       <c r="H2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="44" t="s">
         <v>16</v>
       </c>
       <c r="J2" s="7" t="s">
@@ -3824,40 +3834,40 @@
       <c r="D3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="42">
         <v>33</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G3" s="23">
         <v>2026</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="J3" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="7">
-        <v>14</v>
+      <c r="E4" s="45">
+        <v>23</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>14</v>
@@ -3866,30 +3876,30 @@
         <v>2026</v>
       </c>
       <c r="H4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="7" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A5" s="21" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A5" s="42" t="s">
-        <v>29</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="7">
-        <v>15</v>
+      <c r="E5" s="45">
+        <v>23</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>14</v>
@@ -3898,30 +3908,30 @@
         <v>2026</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="J5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="7" t="s">
+    </row>
+    <row r="6" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A6" s="21" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A6" s="42" t="s">
-        <v>34</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="7">
-        <v>13</v>
+      <c r="E6" s="45">
+        <v>24</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>14</v>
@@ -3930,18 +3940,18 @@
         <v>2026</v>
       </c>
       <c r="H6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="7" t="s">
+    </row>
+    <row r="7" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A7" s="46" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A7" s="43" t="s">
-        <v>39</v>
       </c>
       <c r="B7" s="29" t="s">
         <v>11</v>
@@ -3952,406 +3962,406 @@
       <c r="D7" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="27">
-        <v>24</v>
-      </c>
-      <c r="F7" s="29" t="s">
+      <c r="E7" s="47">
+        <v>32</v>
+      </c>
+      <c r="F7" s="48" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="29">
         <v>2026</v>
       </c>
       <c r="H7" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="J7" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="44" t="s">
-        <v>44</v>
+      <c r="C8" s="49" t="s">
+        <v>43</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="42">
         <v>24</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G8" s="23">
         <v>2026</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="J8" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="42">
         <v>24</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G9" s="23">
         <v>2026</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="J9" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="10" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="42">
         <v>25</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G10" s="23">
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="J10" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="11" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="42">
         <v>26</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G11" s="23">
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="J11" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="42">
         <v>24</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G12" s="23">
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="J12" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="13" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="C13" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G13" s="23">
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="J13" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="14" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="42"/>
       <c r="F14" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G14" s="23">
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="I14" s="24" t="s">
+      <c r="J14" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="15" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="42"/>
       <c r="F15" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G15" s="23">
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="I15" s="24" t="s">
+      <c r="J15" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="42"/>
       <c r="F16" s="7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G16" s="23">
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>87</v>
       </c>
       <c r="J16" s="7"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="42"/>
       <c r="F17" s="7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G17" s="23">
         <v>2026</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="24" t="s">
         <v>90</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>91</v>
       </c>
       <c r="J17" s="7"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="D18" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="42"/>
       <c r="F18" s="7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G18" s="23">
         <v>2026</v>
       </c>
       <c r="H18" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="J18" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="42"/>
       <c r="F19" s="7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G19" s="23">
         <v>2026</v>
       </c>
       <c r="H19" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="I19" s="24" t="s">
+      <c r="J19" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="J19" s="7" t="s">
+    </row>
+    <row r="20" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A20" s="25" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="20" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A20" s="21" t="s">
+      <c r="B20" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>102</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="7">
-        <v>36</v>
+      <c r="E20" s="51">
+        <v>30</v>
       </c>
       <c r="F20" s="23" t="s">
         <v>14</v>
@@ -4359,31 +4369,31 @@
       <c r="G20" s="23">
         <v>2026</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="I20" s="24" t="s">
+      <c r="J20" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="J20" s="1" t="s">
+    </row>
+    <row r="21" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A21" s="25" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="21" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A21" s="21" t="s">
+      <c r="B21" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="23" t="s">
         <v>107</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="46" t="s">
-        <v>109</v>
+      <c r="E21" s="51">
+        <v>32</v>
       </c>
       <c r="F21" s="23" t="s">
         <v>14</v>
@@ -4391,545 +4401,544 @@
       <c r="G21" s="23">
         <v>2026</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="I21" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="23">
-        <v>30</v>
+      <c r="E22" s="51">
+        <v>33</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G22" s="23">
         <v>2026</v>
       </c>
       <c r="H22" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="I22" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="23">
-        <v>32</v>
+      <c r="E23" s="51">
+        <v>36</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G23" s="23">
         <v>2026</v>
       </c>
       <c r="H23" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="48" t="s">
+    </row>
+    <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A24" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="B24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A24" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>124</v>
       </c>
       <c r="D24" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="23">
-        <v>33</v>
-      </c>
-      <c r="F24" s="23" t="s">
-        <v>20</v>
+      <c r="E24" s="42">
+        <v>22</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="G24" s="23">
         <v>2026</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="J24" s="7"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A25" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="I24" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A25" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="23" t="s">
-        <v>129</v>
+      <c r="C25" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="23">
-        <v>36</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>20</v>
+      <c r="E25" s="42">
+        <v>24</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="G25" s="23">
         <v>2026</v>
       </c>
-      <c r="H25" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="I25" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>132</v>
-      </c>
+      <c r="H25" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D26" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E26" s="7">
-        <v>22</v>
+      <c r="E26" s="42" t="s">
+        <v>130</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="23">
+        <v>14</v>
+      </c>
+      <c r="G26" s="7">
         <v>2026</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>136</v>
+        <v>131</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>132</v>
       </c>
       <c r="J26" s="7"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="21" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="7">
-        <v>24</v>
+      <c r="E27" s="42" t="s">
+        <v>130</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="23">
+        <v>14</v>
+      </c>
+      <c r="G27" s="7">
         <v>2026</v>
       </c>
       <c r="H27" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="J27" s="7"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A28" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="I27" s="24" t="s">
+      <c r="C28" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="J27" s="7"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A28" s="21" t="s">
+      <c r="D28" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="F28" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H28" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="I28" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A29" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D29" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="7">
+      <c r="E29" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="23">
         <v>2026</v>
       </c>
-      <c r="H28" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J28" s="7"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A29" s="21" t="s">
+      <c r="H29" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="I29" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A30" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="7">
-        <v>2026</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="I29" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="J29" s="7"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A30" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="23">
-        <v>6</v>
-      </c>
-      <c r="F30" s="23" t="s">
+      <c r="C30" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="23">
-        <v>2026</v>
-      </c>
+      <c r="G30" s="7"/>
       <c r="H30" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="I30" s="48" t="s">
-        <v>153</v>
-      </c>
-      <c r="J30" s="1" t="s">
         <v>154</v>
       </c>
+      <c r="I30" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="J30" s="7"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="23">
-        <v>7</v>
+      <c r="E31" s="43">
+        <v>9</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G31" s="23">
         <v>2026</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="I31" s="48" t="s">
-        <v>158</v>
+        <v>160</v>
+      </c>
+      <c r="I31" s="52" t="s">
+        <v>161</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="25" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D32" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="23">
-        <v>6</v>
+      <c r="E32" s="43">
+        <v>9</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G32" s="23">
         <v>2026</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="I32" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I32" s="52" t="s">
+        <v>166</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A33" s="25" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="49" t="s">
-        <v>166</v>
+        <v>138</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="23">
-        <v>7</v>
+      <c r="E33" s="54" t="s">
+        <v>170</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G33" s="23">
         <v>2026</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="34" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A34" s="25" t="s">
-        <v>170</v>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A34" s="21" t="s">
+        <v>174</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="50" t="s">
-        <v>171</v>
+        <v>138</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="23">
-        <v>8</v>
+      <c r="E34" s="45">
+        <v>50</v>
       </c>
       <c r="F34" s="23" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G34" s="23">
         <v>2026</v>
       </c>
-      <c r="H34" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="I34" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="J34" s="52"/>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A35" s="25" t="s">
-        <v>174</v>
+      <c r="H34" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A35" s="21" t="s">
+        <v>178</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>176</v>
+        <v>138</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>179</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="23">
-        <v>10</v>
+      <c r="E35" s="45" t="s">
+        <v>180</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G35" s="23">
         <v>2026</v>
       </c>
-      <c r="H35" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="I35" s="48" t="s">
-        <v>178</v>
+      <c r="H35" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="I35" s="56" t="s">
+        <v>182</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="36" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" s="6" customFormat="1" ht="34" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C36" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="7"/>
+        <v>138</v>
+      </c>
+      <c r="C36" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G36" s="23">
+        <v>2026</v>
+      </c>
       <c r="H36" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="J36" s="7"/>
-    </row>
-    <row r="37" s="6" customFormat="1" ht="34" customHeight="1" spans="1:10">
+        <v>186</v>
+      </c>
+      <c r="I36" s="24"/>
+      <c r="J36" s="57" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="52" t="s">
-        <v>30</v>
+        <v>138</v>
+      </c>
+      <c r="C37" s="55" t="s">
+        <v>19</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>186</v>
+      <c r="E37" s="58">
+        <v>120</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G37" s="23">
         <v>2026</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I37" s="24"/>
-      <c r="J37" s="53" t="s">
-        <v>188</v>
+      <c r="J37" s="7" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="38" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A38" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" s="52" t="s">
+      <c r="A38" s="59" t="s">
+        <v>191</v>
+      </c>
+      <c r="B38" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="7">
-        <v>119</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="23">
+      <c r="E38" s="58">
+        <v>1</v>
+      </c>
+      <c r="F38" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="G38" s="61">
         <v>2026</v>
       </c>
-      <c r="H38" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="I38" s="24"/>
-      <c r="J38" s="7" t="s">
-        <v>191</v>
+      <c r="H38" s="61"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="58" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="39" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A39" s="21"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="52"/>
+      <c r="C39" s="55"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="E39" s="42"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="23"/>
@@ -4939,33 +4948,33 @@
     <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A40" s="21"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="52"/>
+      <c r="C40" s="55"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
+      <c r="E40" s="42"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
-      <c r="H40" s="23"/>
+      <c r="H40" s="63"/>
       <c r="I40" s="24"/>
       <c r="J40" s="7"/>
     </row>
     <row r="41" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A41" s="21"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="52"/>
+      <c r="C41" s="55"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+      <c r="E41" s="42"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
-      <c r="H41" s="54"/>
+      <c r="H41" s="23"/>
       <c r="I41" s="24"/>
       <c r="J41" s="7"/>
     </row>
     <row r="42" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A42" s="21"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="52"/>
+      <c r="C42" s="55"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
+      <c r="E42" s="42"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="23"/>
@@ -4975,9 +4984,9 @@
     <row r="43" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A43" s="21"/>
       <c r="B43" s="7"/>
-      <c r="C43" s="52"/>
+      <c r="C43" s="55"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
+      <c r="E43" s="42"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="23"/>
@@ -4987,9 +4996,9 @@
     <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A44" s="21"/>
       <c r="B44" s="7"/>
-      <c r="C44" s="52"/>
+      <c r="C44" s="55"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
+      <c r="E44" s="42"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="23"/>
@@ -4999,9 +5008,9 @@
     <row r="45" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A45" s="21"/>
       <c r="B45" s="7"/>
-      <c r="C45" s="52"/>
+      <c r="C45" s="55"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
+      <c r="E45" s="42"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="23"/>
@@ -5011,9 +5020,9 @@
     <row r="46" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A46" s="21"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="52"/>
+      <c r="C46" s="55"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
+      <c r="E46" s="42"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="23"/>
@@ -5023,9 +5032,9 @@
     <row r="47" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A47" s="21"/>
       <c r="B47" s="7"/>
-      <c r="C47" s="52"/>
+      <c r="C47" s="55"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
+      <c r="E47" s="42"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="23"/>
@@ -5035,325 +5044,333 @@
     <row r="48" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A48" s="21"/>
       <c r="B48" s="7"/>
-      <c r="C48" s="52"/>
+      <c r="C48" s="55"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
+      <c r="E48" s="42"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="23"/>
       <c r="I48" s="24"/>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A49" s="21"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
+    <row r="49" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A49" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="51">
+        <v>7</v>
+      </c>
+      <c r="F49" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G49" s="23">
+        <v>2026</v>
+      </c>
       <c r="H49" s="23"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="7"/>
+      <c r="I49" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="J49" s="23" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A50" s="25" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E50" s="23">
-        <v>7</v>
+      <c r="E50" s="51">
+        <v>10</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G50" s="23">
         <v>2026</v>
       </c>
-      <c r="H50" s="23"/>
-      <c r="I50" s="48" t="s">
-        <v>194</v>
+      <c r="H50" s="56"/>
+      <c r="I50" s="52" t="s">
+        <v>199</v>
       </c>
       <c r="J50" s="23" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A51" s="25" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>197</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C51" s="23"/>
       <c r="D51" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="23">
-        <v>10</v>
+      <c r="E51" s="51">
+        <v>2</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G51" s="23">
         <v>2026</v>
       </c>
-      <c r="H51" s="47"/>
-      <c r="I51" s="48" t="s">
-        <v>198</v>
+      <c r="H51" s="56"/>
+      <c r="I51" s="52" t="s">
+        <v>202</v>
       </c>
       <c r="J51" s="23" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A52" s="25" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C52" s="23"/>
       <c r="D52" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E52" s="23">
-        <v>2</v>
+      <c r="E52" s="51">
+        <v>4</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G52" s="23">
         <v>2026</v>
       </c>
-      <c r="H52" s="47"/>
-      <c r="I52" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="J52" s="23" t="s">
-        <v>202</v>
+      <c r="H52" s="56"/>
+      <c r="I52" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A53" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="B53" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" s="23"/>
+      <c r="A53" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" s="55" t="s">
+        <v>208</v>
+      </c>
       <c r="D53" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="23">
-        <v>4</v>
-      </c>
-      <c r="F53" s="23" t="s">
+      <c r="E53" s="64"/>
+      <c r="F53" s="55" t="s">
         <v>14</v>
       </c>
       <c r="G53" s="23">
         <v>2026</v>
       </c>
-      <c r="H53" s="47"/>
-      <c r="I53" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>205</v>
-      </c>
+      <c r="H53" s="23"/>
+      <c r="I53" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="J53" s="7"/>
     </row>
     <row r="54" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A54" s="21" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C54" s="52" t="s">
-        <v>207</v>
+        <v>157</v>
+      </c>
+      <c r="C54" s="55" t="s">
+        <v>208</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52" t="s">
-        <v>20</v>
+      <c r="E54" s="64"/>
+      <c r="F54" s="55" t="s">
+        <v>14</v>
       </c>
       <c r="G54" s="23">
         <v>2026</v>
       </c>
       <c r="H54" s="23"/>
       <c r="I54" s="24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J54" s="7"/>
     </row>
     <row r="55" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A55" s="21" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H55" s="23"/>
+        <v>213</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
       <c r="I55" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="J55" s="7"/>
+        <v>214</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A56" s="21" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
+      <c r="E56" s="42"/>
       <c r="F56" s="7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="24" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
+      <c r="E57" s="42"/>
       <c r="F57" s="7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="24" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
+      <c r="E58" s="42"/>
       <c r="F58" s="7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
-      <c r="I58" s="24" t="s">
-        <v>219</v>
-      </c>
+      <c r="I58" s="24"/>
       <c r="J58" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A59" s="21" t="s">
-        <v>221</v>
+      <c r="A59" s="25" t="s">
+        <v>224</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C59" s="7"/>
+        <v>225</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>226</v>
+      </c>
       <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="24"/>
+      <c r="E59" s="42">
+        <v>10</v>
+      </c>
+      <c r="F59" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="G59" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>228</v>
+      </c>
       <c r="J59" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A60" s="25" t="s">
-        <v>223</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="60" ht="25" customHeight="1" spans="1:10">
+      <c r="A60" s="21" t="s">
+        <v>230</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C60" s="26" t="s">
-        <v>225</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C60" s="7"/>
       <c r="D60" s="7"/>
-      <c r="E60" s="7">
-        <v>10</v>
-      </c>
+      <c r="E60" s="65"/>
       <c r="F60" s="22" t="s">
         <v>14</v>
       </c>
       <c r="G60" s="23">
         <v>2026</v>
       </c>
-      <c r="H60" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" ht="25" customHeight="1" spans="1:10">
-      <c r="A61" s="25" t="s">
-        <v>229</v>
+      <c r="H60" s="7"/>
+      <c r="I60" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="J60" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="61" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A61" s="21" t="s">
+        <v>233</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C61" s="34" t="s">
-        <v>230</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C61" s="7"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="22" t="s">
-        <v>231</v>
-      </c>
+      <c r="E61" s="65"/>
       <c r="F61" s="22" t="s">
         <v>14</v>
       </c>
@@ -5361,25 +5378,27 @@
         <v>2026</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="I61" s="24"/>
-      <c r="J61" s="7"/>
-    </row>
-    <row r="62" ht="25" customHeight="1" spans="1:10">
-      <c r="A62" s="25" t="s">
-        <v>233</v>
+        <v>234</v>
+      </c>
+      <c r="I61" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="J61" s="24" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1" spans="1:10">
+      <c r="A62" s="21" t="s">
+        <v>237</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C62" s="34" t="s">
-        <v>230</v>
+        <v>68</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>238</v>
       </c>
       <c r="D62" s="7"/>
-      <c r="E62" s="22" t="s">
-        <v>234</v>
-      </c>
+      <c r="E62" s="65"/>
       <c r="F62" s="22" t="s">
         <v>14</v>
       </c>
@@ -5387,25 +5406,27 @@
         <v>2026</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="I62" s="24"/>
-      <c r="J62" s="7"/>
+        <v>239</v>
+      </c>
+      <c r="I62" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="J62" s="24" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="63" ht="25" customHeight="1" spans="1:10">
-      <c r="A63" s="25" t="s">
-        <v>236</v>
+      <c r="A63" s="21" t="s">
+        <v>242</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C63" s="26" t="s">
-        <v>237</v>
+        <v>68</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="D63" s="7"/>
-      <c r="E63" s="22" t="s">
-        <v>238</v>
-      </c>
+      <c r="E63" s="65"/>
       <c r="F63" s="22" t="s">
         <v>14</v>
       </c>
@@ -5413,377 +5434,325 @@
         <v>2026</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="I63" s="24"/>
-      <c r="J63" s="7"/>
-    </row>
-    <row r="64" ht="22" customHeight="1" spans="1:10">
-      <c r="A64" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C64" s="26" t="s">
-        <v>242</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="I63" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="J63" s="24" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="64" ht="25" customHeight="1" spans="1:10">
+      <c r="A64" s="21"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
       <c r="D64" s="7"/>
-      <c r="E64" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="F64" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G64" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>244</v>
-      </c>
+      <c r="E64" s="65"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="7"/>
       <c r="I64" s="24"/>
-      <c r="J64" s="7"/>
-    </row>
-    <row r="65" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A65" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C65" s="7"/>
+      <c r="J64" s="24"/>
+    </row>
+    <row r="65" ht="25" customHeight="1" spans="1:10">
+      <c r="A65" s="66" t="s">
+        <v>247</v>
+      </c>
+      <c r="B65" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" s="58" t="s">
+        <v>164</v>
+      </c>
       <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
+      <c r="E65" s="65"/>
       <c r="F65" s="22" t="s">
         <v>14</v>
       </c>
       <c r="G65" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H65" s="7"/>
+        <v>8.25</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>248</v>
+      </c>
       <c r="I65" s="24"/>
-      <c r="J65" s="7"/>
-    </row>
-    <row r="66" ht="25" customHeight="1" spans="1:10">
-      <c r="A66" s="21" t="s">
-        <v>246</v>
+      <c r="J65" s="21"/>
+    </row>
+    <row r="66" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A66" s="66" t="s">
+        <v>249</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
-      <c r="E66" s="22"/>
+      <c r="E66" s="65"/>
       <c r="F66" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G66" s="23">
-        <v>2026</v>
+        <v>14</v>
+      </c>
+      <c r="G66" s="23" t="s">
+        <v>250</v>
       </c>
       <c r="H66" s="7"/>
-      <c r="I66" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="J66" s="21" t="s">
-        <v>248</v>
-      </c>
+      <c r="I66" s="24"/>
+      <c r="J66" s="21"/>
     </row>
     <row r="67" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A67" s="21" t="s">
-        <v>249</v>
+      <c r="A67" s="66" t="s">
+        <v>251</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
-      <c r="E67" s="22"/>
+      <c r="E67" s="65"/>
       <c r="F67" s="22" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G67" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H67" s="7" t="s">
+        <v>8.23</v>
+      </c>
+      <c r="H67" s="7"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="21"/>
+    </row>
+    <row r="68" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A68" s="66" t="s">
+        <v>252</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="65"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="I67" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="J67" s="24" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="68" ht="24" customHeight="1" spans="1:10">
-      <c r="A68" s="21" t="s">
+      <c r="H68" s="7"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="21"/>
+    </row>
+    <row r="69" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A69" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="7" t="s">
+      <c r="B69" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="65"/>
+      <c r="F69" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="23">
+        <v>8.21</v>
+      </c>
+      <c r="H69" s="7"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="21"/>
+    </row>
+    <row r="70" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A70" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="D68" s="7"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G68" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="I68" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="J68" s="24" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="69" ht="25" customHeight="1" spans="1:10">
-      <c r="A69" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D69" s="7"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G69" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="I69" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="J69" s="24" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="70" ht="25" customHeight="1" spans="1:10">
-      <c r="A70" s="21"/>
-      <c r="B70" s="7"/>
+      <c r="B70" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
-      <c r="E70" s="22"/>
+      <c r="E70" s="65"/>
       <c r="F70" s="22"/>
       <c r="G70" s="23"/>
       <c r="H70" s="7"/>
       <c r="I70" s="24"/>
-      <c r="J70" s="24"/>
-    </row>
-    <row r="71" ht="25" customHeight="1" spans="1:10">
-      <c r="A71" s="42" t="s">
-        <v>263</v>
-      </c>
-      <c r="B71" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="C71" s="46" t="s">
-        <v>156</v>
-      </c>
+      <c r="J70" s="21"/>
+    </row>
+    <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A71" s="66" t="s">
+        <v>255</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C71" s="7"/>
       <c r="D71" s="7"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22" t="s">
-        <v>20</v>
-      </c>
+      <c r="E71" s="65"/>
+      <c r="F71" s="22"/>
       <c r="G71" s="23">
-        <v>8.25</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>264</v>
-      </c>
+        <v>5.15</v>
+      </c>
+      <c r="H71" s="7"/>
       <c r="I71" s="24"/>
       <c r="J71" s="21"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A72" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>69</v>
-      </c>
+      <c r="A72" s="66" t="s">
+        <v>256</v>
+      </c>
+      <c r="B72" s="7"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G72" s="23" t="s">
-        <v>266</v>
-      </c>
+      <c r="E72" s="65"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="23"/>
       <c r="H72" s="7"/>
       <c r="I72" s="24"/>
       <c r="J72" s="21"/>
     </row>
-    <row r="73" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A73" s="42" t="s">
-        <v>267</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>69</v>
-      </c>
+    <row r="73" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
+      <c r="A73" s="66" t="s">
+        <v>257</v>
+      </c>
+      <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G73" s="23">
-        <v>8.23</v>
-      </c>
+      <c r="E73" s="65"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="23"/>
       <c r="H73" s="7"/>
       <c r="I73" s="24"/>
       <c r="J73" s="21"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A74" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>69</v>
-      </c>
+      <c r="A74" s="66" t="s">
+        <v>258</v>
+      </c>
+      <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
-      <c r="E74" s="22"/>
+      <c r="E74" s="65"/>
       <c r="F74" s="22"/>
-      <c r="G74" s="23" t="s">
-        <v>266</v>
-      </c>
+      <c r="G74" s="23"/>
       <c r="H74" s="7"/>
       <c r="I74" s="24"/>
       <c r="J74" s="21"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A75" s="42" t="s">
-        <v>269</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>69</v>
-      </c>
+      <c r="A75" s="66" t="s">
+        <v>259</v>
+      </c>
+      <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G75" s="23">
-        <v>8.21</v>
-      </c>
+      <c r="E75" s="65"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="23"/>
       <c r="H75" s="7"/>
       <c r="I75" s="24"/>
       <c r="J75" s="21"/>
     </row>
     <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A76" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>69</v>
-      </c>
+      <c r="A76" s="66" t="s">
+        <v>260</v>
+      </c>
+      <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
+      <c r="E76" s="65"/>
+      <c r="F76" s="22" t="s">
+        <v>261</v>
+      </c>
       <c r="G76" s="23"/>
       <c r="H76" s="7"/>
       <c r="I76" s="24"/>
-      <c r="J76" s="21"/>
-    </row>
-    <row r="77" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A77" s="42" t="s">
-        <v>271</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>69</v>
-      </c>
+      <c r="J76" s="24"/>
+    </row>
+    <row r="77" ht="25" customHeight="1" spans="1:10">
+      <c r="A77" s="66" t="s">
+        <v>262</v>
+      </c>
+      <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="23">
-        <v>5.15</v>
-      </c>
+      <c r="E77" s="65"/>
+      <c r="F77" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="G77" s="23"/>
       <c r="H77" s="7"/>
       <c r="I77" s="24"/>
-      <c r="J77" s="21"/>
-    </row>
-    <row r="78" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A78" s="42" t="s">
-        <v>272</v>
+      <c r="J77" s="24"/>
+    </row>
+    <row r="78" ht="25" customHeight="1" spans="1:10">
+      <c r="A78" s="21" t="s">
+        <v>237</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="22" t="s">
+        <v>264</v>
+      </c>
       <c r="G78" s="23"/>
       <c r="H78" s="7"/>
       <c r="I78" s="24"/>
-      <c r="J78" s="21"/>
-    </row>
-    <row r="79" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A79" s="42" t="s">
-        <v>273</v>
+      <c r="J78" s="24"/>
+    </row>
+    <row r="79" ht="25" customHeight="1" spans="1:10">
+      <c r="A79" s="66" t="s">
+        <v>265</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
+      <c r="E79" s="65"/>
+      <c r="F79" s="22" t="s">
+        <v>266</v>
+      </c>
       <c r="G79" s="23"/>
       <c r="H79" s="7"/>
       <c r="I79" s="24"/>
-      <c r="J79" s="21"/>
-    </row>
-    <row r="80" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A80" s="42" t="s">
-        <v>274</v>
+      <c r="J79" s="24"/>
+    </row>
+    <row r="80" ht="25" customHeight="1" spans="1:10">
+      <c r="A80" s="66" t="s">
+        <v>267</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="22">
+        <v>102</v>
+      </c>
       <c r="G80" s="23"/>
       <c r="H80" s="7"/>
       <c r="I80" s="24"/>
-      <c r="J80" s="21"/>
-    </row>
-    <row r="81" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A81" s="42" t="s">
-        <v>275</v>
+      <c r="J80" s="24"/>
+    </row>
+    <row r="81" ht="25" customHeight="1" spans="1:10">
+      <c r="A81" s="66" t="s">
+        <v>268</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
-      <c r="E81" s="22"/>
-      <c r="F81" s="22"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="22">
+        <v>69</v>
+      </c>
       <c r="G81" s="23"/>
       <c r="H81" s="7"/>
       <c r="I81" s="24"/>
-      <c r="J81" s="21"/>
-    </row>
-    <row r="82" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A82" s="42" t="s">
-        <v>276</v>
+      <c r="J81" s="24"/>
+    </row>
+    <row r="82" ht="25" customHeight="1" spans="1:10">
+      <c r="A82" s="66" t="s">
+        <v>269</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22" t="s">
-        <v>277</v>
+      <c r="E82" s="65"/>
+      <c r="F82" s="22">
+        <v>86</v>
       </c>
       <c r="G82" s="23"/>
       <c r="H82" s="7"/>
@@ -5791,31 +5760,29 @@
       <c r="J82" s="24"/>
     </row>
     <row r="83" ht="25" customHeight="1" spans="1:10">
-      <c r="A83" s="42" t="s">
-        <v>278</v>
+      <c r="A83" s="66" t="s">
+        <v>270</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22" t="s">
-        <v>279</v>
-      </c>
+      <c r="E83" s="65"/>
+      <c r="F83" s="22"/>
       <c r="G83" s="23"/>
       <c r="H83" s="7"/>
       <c r="I83" s="24"/>
       <c r="J83" s="24"/>
     </row>
     <row r="84" ht="25" customHeight="1" spans="1:10">
-      <c r="A84" s="21" t="s">
-        <v>253</v>
+      <c r="A84" s="66" t="s">
+        <v>271</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
-      <c r="E84" s="22"/>
+      <c r="E84" s="65"/>
       <c r="F84" s="22" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G84" s="23"/>
       <c r="H84" s="7"/>
@@ -5823,47 +5790,43 @@
       <c r="J84" s="24"/>
     </row>
     <row r="85" ht="25" customHeight="1" spans="1:10">
-      <c r="A85" s="42" t="s">
-        <v>281</v>
+      <c r="A85" s="66" t="s">
+        <v>273</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22" t="s">
-        <v>282</v>
-      </c>
+      <c r="E85" s="65"/>
+      <c r="F85" s="22"/>
       <c r="G85" s="23"/>
       <c r="H85" s="7"/>
       <c r="I85" s="24"/>
       <c r="J85" s="24"/>
     </row>
     <row r="86" ht="25" customHeight="1" spans="1:10">
-      <c r="A86" s="42" t="s">
-        <v>283</v>
+      <c r="A86" s="66" t="s">
+        <v>274</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
-      <c r="E86" s="22"/>
-      <c r="F86" s="22">
-        <v>102</v>
-      </c>
+      <c r="E86" s="65"/>
+      <c r="F86" s="22"/>
       <c r="G86" s="23"/>
       <c r="H86" s="7"/>
       <c r="I86" s="24"/>
       <c r="J86" s="24"/>
     </row>
     <row r="87" ht="25" customHeight="1" spans="1:10">
-      <c r="A87" s="42" t="s">
-        <v>284</v>
+      <c r="A87" s="66" t="s">
+        <v>275</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22">
-        <v>69</v>
+      <c r="E87" s="65"/>
+      <c r="F87" s="22" t="s">
+        <v>276</v>
       </c>
       <c r="G87" s="23"/>
       <c r="H87" s="7"/>
@@ -5871,15 +5834,15 @@
       <c r="J87" s="24"/>
     </row>
     <row r="88" ht="25" customHeight="1" spans="1:10">
-      <c r="A88" s="42" t="s">
-        <v>285</v>
+      <c r="A88" s="66" t="s">
+        <v>277</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22">
-        <v>86</v>
+      <c r="E88" s="65"/>
+      <c r="F88" s="22" t="s">
+        <v>278</v>
       </c>
       <c r="G88" s="23"/>
       <c r="H88" s="7"/>
@@ -5887,29 +5850,35 @@
       <c r="J88" s="24"/>
     </row>
     <row r="89" ht="25" customHeight="1" spans="1:10">
-      <c r="A89" s="42" t="s">
-        <v>286</v>
+      <c r="A89" s="66" t="s">
+        <v>279</v>
       </c>
       <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
+      <c r="C89" s="7" t="s">
+        <v>280</v>
+      </c>
       <c r="D89" s="7"/>
-      <c r="E89" s="22"/>
-      <c r="F89" s="22"/>
+      <c r="E89" s="65"/>
+      <c r="F89" s="22" t="s">
+        <v>281</v>
+      </c>
       <c r="G89" s="23"/>
       <c r="H89" s="7"/>
       <c r="I89" s="24"/>
       <c r="J89" s="24"/>
     </row>
     <row r="90" ht="25" customHeight="1" spans="1:10">
-      <c r="A90" s="42" t="s">
-        <v>287</v>
+      <c r="A90" s="66" t="s">
+        <v>282</v>
       </c>
       <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
+      <c r="C90" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="D90" s="7"/>
-      <c r="E90" s="22"/>
+      <c r="E90" s="65"/>
       <c r="F90" s="22" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G90" s="23"/>
       <c r="H90" s="7"/>
@@ -5917,41 +5886,51 @@
       <c r="J90" s="24"/>
     </row>
     <row r="91" ht="25" customHeight="1" spans="1:10">
-      <c r="A91" s="42" t="s">
-        <v>289</v>
+      <c r="A91" s="66" t="s">
+        <v>285</v>
       </c>
       <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
+      <c r="C91" s="7" t="s">
+        <v>286</v>
+      </c>
       <c r="D91" s="7"/>
-      <c r="E91" s="22"/>
-      <c r="F91" s="22"/>
+      <c r="E91" s="65"/>
+      <c r="F91" s="22" t="s">
+        <v>287</v>
+      </c>
       <c r="G91" s="23"/>
       <c r="H91" s="7"/>
       <c r="I91" s="24"/>
       <c r="J91" s="24"/>
     </row>
     <row r="92" ht="25" customHeight="1" spans="1:10">
-      <c r="A92" s="42" t="s">
-        <v>290</v>
+      <c r="A92" s="66" t="s">
+        <v>288</v>
       </c>
       <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
+      <c r="C92" s="7" t="s">
+        <v>289</v>
+      </c>
       <c r="D92" s="7"/>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
+      <c r="E92" s="65"/>
+      <c r="F92" s="22" t="s">
+        <v>278</v>
+      </c>
       <c r="G92" s="23"/>
       <c r="H92" s="7"/>
       <c r="I92" s="24"/>
       <c r="J92" s="24"/>
     </row>
     <row r="93" ht="25" customHeight="1" spans="1:10">
-      <c r="A93" s="42" t="s">
+      <c r="A93" s="66" t="s">
+        <v>290</v>
+      </c>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
       <c r="D93" s="7"/>
-      <c r="E93" s="22"/>
+      <c r="E93" s="65"/>
       <c r="F93" s="22" t="s">
         <v>292</v>
       </c>
@@ -5961,15 +5940,17 @@
       <c r="J93" s="24"/>
     </row>
     <row r="94" ht="25" customHeight="1" spans="1:10">
-      <c r="A94" s="42" t="s">
+      <c r="A94" s="66" t="s">
         <v>293</v>
       </c>
       <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
+      <c r="C94" s="7" t="s">
+        <v>294</v>
+      </c>
       <c r="D94" s="7"/>
-      <c r="E94" s="22"/>
+      <c r="E94" s="65"/>
       <c r="F94" s="22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G94" s="23"/>
       <c r="H94" s="7"/>
@@ -5977,17 +5958,17 @@
       <c r="J94" s="24"/>
     </row>
     <row r="95" ht="25" customHeight="1" spans="1:10">
-      <c r="A95" s="42" t="s">
-        <v>295</v>
+      <c r="A95" s="66" t="s">
+        <v>296</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D95" s="7"/>
-      <c r="E95" s="22"/>
+      <c r="E95" s="65"/>
       <c r="F95" s="22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G95" s="23"/>
       <c r="H95" s="7"/>
@@ -5995,17 +5976,17 @@
       <c r="J95" s="24"/>
     </row>
     <row r="96" ht="25" customHeight="1" spans="1:10">
-      <c r="A96" s="42" t="s">
-        <v>298</v>
+      <c r="A96" s="66" t="s">
+        <v>299</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D96" s="7"/>
-      <c r="E96" s="22"/>
+      <c r="E96" s="65"/>
       <c r="F96" s="22" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="G96" s="23"/>
       <c r="H96" s="7"/>
@@ -6013,7 +5994,7 @@
       <c r="J96" s="24"/>
     </row>
     <row r="97" ht="25" customHeight="1" spans="1:10">
-      <c r="A97" s="42" t="s">
+      <c r="A97" s="66" t="s">
         <v>301</v>
       </c>
       <c r="B97" s="7"/>
@@ -6021,7 +6002,7 @@
         <v>302</v>
       </c>
       <c r="D97" s="7"/>
-      <c r="E97" s="22"/>
+      <c r="E97" s="65"/>
       <c r="F97" s="22" t="s">
         <v>303</v>
       </c>
@@ -6031,17 +6012,17 @@
       <c r="J97" s="24"/>
     </row>
     <row r="98" ht="25" customHeight="1" spans="1:10">
-      <c r="A98" s="42" t="s">
+      <c r="A98" s="66" t="s">
         <v>304</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D98" s="7"/>
+      <c r="E98" s="65"/>
+      <c r="F98" s="22" t="s">
         <v>305</v>
-      </c>
-      <c r="D98" s="7"/>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22" t="s">
-        <v>294</v>
       </c>
       <c r="G98" s="23"/>
       <c r="H98" s="7"/>
@@ -6049,7 +6030,7 @@
       <c r="J98" s="24"/>
     </row>
     <row r="99" ht="25" customHeight="1" spans="1:10">
-      <c r="A99" s="42" t="s">
+      <c r="A99" s="66" t="s">
         <v>306</v>
       </c>
       <c r="B99" s="7"/>
@@ -6057,7 +6038,7 @@
         <v>307</v>
       </c>
       <c r="D99" s="7"/>
-      <c r="E99" s="22"/>
+      <c r="E99" s="65"/>
       <c r="F99" s="22" t="s">
         <v>308</v>
       </c>
@@ -6067,71 +6048,69 @@
       <c r="J99" s="24"/>
     </row>
     <row r="100" ht="25" customHeight="1" spans="1:10">
-      <c r="A100" s="42" t="s">
+      <c r="A100" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7" t="s">
+      <c r="B100" s="58"/>
+      <c r="C100" s="58" t="s">
         <v>310</v>
       </c>
-      <c r="D100" s="7"/>
-      <c r="E100" s="22"/>
-      <c r="F100" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="G100" s="23"/>
+      <c r="D100" s="58"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="G100" s="61"/>
       <c r="H100" s="7"/>
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
     </row>
     <row r="101" ht="25" customHeight="1" spans="1:10">
-      <c r="A101" s="42" t="s">
+      <c r="A101" s="66" t="s">
+        <v>311</v>
+      </c>
+      <c r="B101" s="58"/>
+      <c r="C101" s="58" t="s">
+        <v>289</v>
+      </c>
+      <c r="D101" s="58"/>
+      <c r="E101" s="67"/>
+      <c r="F101" s="68" t="s">
         <v>312</v>
       </c>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D101" s="7"/>
-      <c r="E101" s="22"/>
-      <c r="F101" s="22" t="s">
-        <v>314</v>
-      </c>
-      <c r="G101" s="23"/>
+      <c r="G101" s="61"/>
       <c r="H101" s="7"/>
       <c r="I101" s="24"/>
       <c r="J101" s="24"/>
     </row>
     <row r="102" ht="25" customHeight="1" spans="1:10">
-      <c r="A102" s="42" t="s">
-        <v>315</v>
-      </c>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D102" s="7"/>
-      <c r="E102" s="22"/>
-      <c r="F102" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="G102" s="23"/>
+      <c r="A102" s="66" t="s">
+        <v>313</v>
+      </c>
+      <c r="B102" s="58"/>
+      <c r="C102" s="58"/>
+      <c r="D102" s="58"/>
+      <c r="E102" s="67"/>
+      <c r="F102" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="G102" s="61"/>
       <c r="H102" s="7"/>
       <c r="I102" s="24"/>
       <c r="J102" s="24"/>
     </row>
     <row r="103" ht="25" customHeight="1" spans="1:10">
-      <c r="A103" s="42" t="s">
+      <c r="A103" s="66" t="s">
+        <v>315</v>
+      </c>
+      <c r="B103" s="58"/>
+      <c r="C103" s="58" t="s">
+        <v>316</v>
+      </c>
+      <c r="D103" s="58"/>
+      <c r="E103" s="67"/>
+      <c r="F103" s="68" t="s">
         <v>317</v>
-      </c>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="D103" s="7"/>
-      <c r="E103" s="22"/>
-      <c r="F103" s="22" t="s">
-        <v>319</v>
       </c>
       <c r="G103" s="23"/>
       <c r="H103" s="7"/>
@@ -6139,191 +6118,95 @@
       <c r="J103" s="24"/>
     </row>
     <row r="104" ht="25" customHeight="1" spans="1:10">
-      <c r="A104" s="42" t="s">
+      <c r="A104" s="66" t="s">
+        <v>318</v>
+      </c>
+      <c r="B104" s="58"/>
+      <c r="C104" s="58" t="s">
+        <v>319</v>
+      </c>
+      <c r="D104" s="58"/>
+      <c r="E104" s="67"/>
+      <c r="F104" s="68" t="s">
         <v>320</v>
-      </c>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="D104" s="7"/>
-      <c r="E104" s="22"/>
-      <c r="F104" s="22" t="s">
-        <v>321</v>
       </c>
       <c r="G104" s="23"/>
       <c r="H104" s="7"/>
       <c r="I104" s="24"/>
       <c r="J104" s="24"/>
     </row>
-    <row r="105" ht="25" customHeight="1" spans="1:10">
-      <c r="A105" s="42" t="s">
+    <row r="105" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A105" s="69" t="s">
+        <v>321</v>
+      </c>
+      <c r="B105" s="55"/>
+      <c r="C105" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="D105" s="55"/>
+      <c r="E105" s="70"/>
+      <c r="F105" s="71" t="s">
+        <v>278</v>
+      </c>
+      <c r="G105" s="23"/>
+      <c r="H105" s="55"/>
+      <c r="I105" s="72"/>
+      <c r="J105" s="72"/>
+    </row>
+    <row r="106" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A106" s="69" t="s">
         <v>322</v>
       </c>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7" t="s">
+      <c r="B106" s="55"/>
+      <c r="C106" s="55"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="70"/>
+      <c r="F106" s="71" t="s">
         <v>323</v>
       </c>
-      <c r="D105" s="7"/>
-      <c r="E105" s="22"/>
-      <c r="F105" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="G105" s="23"/>
-      <c r="H105" s="7"/>
-      <c r="I105" s="24"/>
-      <c r="J105" s="24"/>
-    </row>
-    <row r="106" ht="25" customHeight="1" spans="1:10">
-      <c r="A106" s="42" t="s">
-        <v>325</v>
-      </c>
-      <c r="B106" s="46"/>
-      <c r="C106" s="46" t="s">
-        <v>326</v>
-      </c>
-      <c r="D106" s="46"/>
-      <c r="E106" s="55"/>
-      <c r="F106" s="55" t="s">
-        <v>294</v>
-      </c>
-      <c r="G106" s="56"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="24"/>
-      <c r="J106" s="24"/>
-    </row>
-    <row r="107" ht="25" customHeight="1" spans="1:10">
-      <c r="A107" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="B107" s="46"/>
-      <c r="C107" s="46" t="s">
-        <v>305</v>
-      </c>
-      <c r="D107" s="46"/>
-      <c r="E107" s="55"/>
-      <c r="F107" s="55" t="s">
-        <v>328</v>
-      </c>
-      <c r="G107" s="56"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="24"/>
-      <c r="J107" s="24"/>
+      <c r="G106" s="23"/>
+      <c r="H106" s="55"/>
+      <c r="I106" s="72"/>
+      <c r="J106" s="72"/>
+    </row>
+    <row r="107" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A107" s="73"/>
+      <c r="B107" s="55"/>
+      <c r="C107" s="55"/>
+      <c r="D107" s="55"/>
+      <c r="E107" s="70"/>
+      <c r="F107" s="71"/>
+      <c r="G107" s="23"/>
+      <c r="H107" s="55"/>
+      <c r="I107" s="72"/>
+      <c r="J107" s="72"/>
     </row>
     <row r="108" ht="25" customHeight="1" spans="1:10">
-      <c r="A108" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="B108" s="46"/>
-      <c r="C108" s="46"/>
-      <c r="D108" s="46"/>
-      <c r="E108" s="55"/>
-      <c r="F108" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="G108" s="56"/>
+      <c r="A108" s="66"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="65"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="23"/>
       <c r="H108" s="7"/>
       <c r="I108" s="24"/>
       <c r="J108" s="24"/>
     </row>
     <row r="109" ht="25" customHeight="1" spans="1:10">
-      <c r="A109" s="42" t="s">
-        <v>331</v>
-      </c>
-      <c r="B109" s="46"/>
-      <c r="C109" s="46" t="s">
-        <v>332</v>
-      </c>
-      <c r="D109" s="46"/>
-      <c r="E109" s="55"/>
-      <c r="F109" s="55" t="s">
-        <v>333</v>
-      </c>
+      <c r="A109" s="66"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="65"/>
+      <c r="F109" s="22"/>
       <c r="G109" s="23"/>
       <c r="H109" s="7"/>
       <c r="I109" s="24"/>
       <c r="J109" s="24"/>
     </row>
-    <row r="110" ht="25" customHeight="1" spans="1:10">
-      <c r="A110" s="42" t="s">
-        <v>334</v>
-      </c>
-      <c r="B110" s="46"/>
-      <c r="C110" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="D110" s="46"/>
-      <c r="E110" s="55"/>
-      <c r="F110" s="55" t="s">
-        <v>336</v>
-      </c>
-      <c r="G110" s="23"/>
-      <c r="H110" s="7"/>
-      <c r="I110" s="24"/>
-      <c r="J110" s="24"/>
-    </row>
-    <row r="111" ht="25" customHeight="1" spans="1:10">
-      <c r="A111" s="13"/>
-      <c r="B111" s="11"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="20"/>
-      <c r="F111" s="20"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="11"/>
-      <c r="I111" s="24"/>
-      <c r="J111" s="24"/>
-    </row>
-    <row r="112" ht="25" customHeight="1" spans="1:10">
-      <c r="A112" s="21"/>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="22"/>
-      <c r="F112" s="22"/>
-      <c r="G112" s="23"/>
-      <c r="H112" s="7"/>
-      <c r="I112" s="24"/>
-      <c r="J112" s="24"/>
-    </row>
-    <row r="113" ht="25" customHeight="1" spans="1:10">
-      <c r="A113" s="21"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="22"/>
-      <c r="F113" s="22"/>
-      <c r="G113" s="23"/>
-      <c r="H113" s="7"/>
-      <c r="I113" s="24"/>
-      <c r="J113" s="24"/>
-    </row>
-    <row r="114" ht="25" customHeight="1" spans="1:10">
-      <c r="A114" s="42"/>
-      <c r="B114" s="7"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="22"/>
-      <c r="F114" s="22"/>
-      <c r="G114" s="23"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="24"/>
-      <c r="J114" s="24"/>
-    </row>
-    <row r="115" ht="25" customHeight="1" spans="1:10">
-      <c r="A115" s="42"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22"/>
-      <c r="G115" s="23"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J110" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J106" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <colorFilter dxfId="0"/>
       <extLst>
@@ -6346,13 +6229,13 @@
         </dxfs>
       </extLst>
     </filterColumn>
-    <sortState ref="A1:J110">
+    <sortState ref="A1:J106">
       <sortCondition ref="F1:F87"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H36" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H30" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6378,7 +6261,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6387,22 +6270,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6416,22 +6299,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6439,28 +6322,28 @@
         <v>3</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6468,28 +6351,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6497,28 +6380,28 @@
         <v>5</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6526,28 +6409,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6555,28 +6438,28 @@
         <v>7</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6584,28 +6467,28 @@
         <v>8</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6613,28 +6496,28 @@
         <v>9</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6642,28 +6525,28 @@
         <v>10</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -6671,28 +6554,28 @@
         <v>11</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -6700,28 +6583,28 @@
         <v>12</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -6729,28 +6612,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>170</v>
+        <v>369</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -6758,28 +6641,28 @@
         <v>14</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -6787,28 +6670,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -6816,28 +6699,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -6845,28 +6728,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -6874,28 +6757,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -6903,28 +6786,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -6932,28 +6815,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -6961,28 +6844,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -6990,28 +6873,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>233</v>
+        <v>394</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -7019,28 +6902,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -7048,7 +6931,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>11</v>
@@ -7057,7 +6940,7 @@
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -7137,13 +7020,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -7152,731 +7035,731 @@
         <v>24</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G2" s="10">
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G3" s="11">
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G4" s="11">
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G5" s="11">
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G6" s="11">
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G7" s="11">
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G8" s="11">
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G9" s="11">
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G10" s="11">
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G11" s="11">
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G12" s="11">
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G13" s="11">
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G14" s="11">
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G15" s="11">
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G16" s="11">
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -7894,37 +7777,37 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
         <v>9</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G34" s="23">
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -7938,7 +7821,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -7952,7 +7835,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -7966,7 +7849,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -7980,7 +7863,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -7993,7 +7876,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -8007,7 +7890,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -8020,7 +7903,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -8033,7 +7916,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -8046,120 +7929,120 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>229</v>
+        <v>511</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>230</v>
+        <v>512</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G44" s="23">
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>232</v>
+        <v>514</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>233</v>
+        <v>394</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>230</v>
+        <v>512</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>234</v>
+        <v>515</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G45" s="23">
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>235</v>
+        <v>516</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>236</v>
+        <v>517</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>237</v>
+        <v>518</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>238</v>
+        <v>519</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G46" s="23">
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>239</v>
+        <v>520</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>240</v>
+        <v>521</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>241</v>
+        <v>522</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>242</v>
+        <v>523</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>243</v>
+        <v>524</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G47" s="23">
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>244</v>
+        <v>525</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>245</v>
+        <v>526</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="22" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="G48" s="23">
         <v>2026</v>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
     <sheet name="已删" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">在播剧更新时间表!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已删!$A$1:$J$48</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="537">
   <si>
     <t>剧名</t>
   </si>
@@ -1005,7 +1005,7 @@
     <t>剧情 / 犯罪</t>
   </si>
   <si>
-    <t>26/100</t>
+    <t>27/100</t>
   </si>
   <si>
     <t xml:space="preserve"> 张瑞希 / 田惠媛 / 薛正焕 / 周清晨 / 尹海英 /</t>
@@ -1043,6 +1043,21 @@
   </si>
   <si>
     <t>链接：https://pan.quark.cn/s/9a4c405f64dc?pwd=UvZi 提取码：UvZi</t>
+  </si>
+  <si>
+    <t>中头奖还是要上班</t>
+  </si>
+  <si>
+    <t>剧情 / 喜剧</t>
+  </si>
+  <si>
+    <t>2/10</t>
+  </si>
+  <si>
+    <t>李浚赫 / 徐现宇 / 吴代焕 / 玉子妍</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/9bd91cf9b311?pwd=Nzk6   提取码：Nzk6</t>
   </si>
   <si>
     <t>神的游戏</t>
@@ -1479,6 +1494,21 @@
   </si>
   <si>
     <t>101</t>
+  </si>
+  <si>
+    <t>完美复制品</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>最后之吻</t>
+  </si>
+  <si>
+    <t>悬疑</t>
+  </si>
+  <si>
+    <t>97</t>
   </si>
   <si>
     <t>序号</t>
@@ -2402,13 +2432,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2426,25 +2464,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <sz val="10.5"/>
+      <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2455,12 +2485,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
         <bgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -2855,7 +2879,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2879,16 +2903,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2897,89 +2921,89 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3098,101 +3122,83 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3748,7 +3754,7 @@
     <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="41" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="35" customWidth="1"/>
     <col min="6" max="6" width="10.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="36.25" style="1" customWidth="1"/>
@@ -3770,7 +3776,7 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
@@ -3802,7 +3808,7 @@
       <c r="D2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="43">
+      <c r="E2" s="42">
         <v>36</v>
       </c>
       <c r="F2" s="23" t="s">
@@ -3814,7 +3820,7 @@
       <c r="H2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="43" t="s">
         <v>16</v>
       </c>
       <c r="J2" s="7" t="s">
@@ -3834,7 +3840,7 @@
       <c r="D3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="42">
+      <c r="E3" s="22">
         <v>33</v>
       </c>
       <c r="F3" s="23" t="s">
@@ -3846,7 +3852,7 @@
       <c r="H3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="43" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="7" t="s">
@@ -3866,7 +3872,7 @@
       <c r="D4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="22">
         <v>23</v>
       </c>
       <c r="F4" s="23" t="s">
@@ -3898,7 +3904,7 @@
       <c r="D5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="22">
         <v>23</v>
       </c>
       <c r="F5" s="23" t="s">
@@ -3930,7 +3936,7 @@
       <c r="D6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="22">
         <v>24</v>
       </c>
       <c r="F6" s="23" t="s">
@@ -3950,7 +3956,7 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="44" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="29" t="s">
@@ -3962,10 +3968,10 @@
       <c r="D7" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="45">
         <v>32</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="46" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="29">
@@ -3988,13 +3994,13 @@
       <c r="B8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="47" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="22">
         <v>24</v>
       </c>
       <c r="F8" s="23" t="s">
@@ -4026,7 +4032,7 @@
       <c r="D9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="22">
         <v>24</v>
       </c>
       <c r="F9" s="23" t="s">
@@ -4058,7 +4064,7 @@
       <c r="D10" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="22">
         <v>25</v>
       </c>
       <c r="F10" s="23" t="s">
@@ -4090,7 +4096,7 @@
       <c r="D11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="22">
         <v>26</v>
       </c>
       <c r="F11" s="23" t="s">
@@ -4122,7 +4128,7 @@
       <c r="D12" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="22">
         <v>24</v>
       </c>
       <c r="F12" s="23" t="s">
@@ -4154,7 +4160,7 @@
       <c r="D13" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="42"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="23" t="s">
         <v>14</v>
       </c>
@@ -4184,7 +4190,7 @@
       <c r="D14" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="42"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="23" t="s">
         <v>14</v>
       </c>
@@ -4214,7 +4220,7 @@
       <c r="D15" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="42"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="23" t="s">
         <v>14</v>
       </c>
@@ -4244,7 +4250,7 @@
       <c r="D16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="42"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="7" t="s">
         <v>14</v>
       </c>
@@ -4272,14 +4278,14 @@
       <c r="D17" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="42"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G17" s="23">
         <v>2026</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="48" t="s">
         <v>89</v>
       </c>
       <c r="I17" s="24" t="s">
@@ -4300,7 +4306,7 @@
       <c r="D18" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="42"/>
+      <c r="E18" s="22"/>
       <c r="F18" s="7" t="s">
         <v>14</v>
       </c>
@@ -4330,7 +4336,7 @@
       <c r="D19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="42"/>
+      <c r="E19" s="22"/>
       <c r="F19" s="7" t="s">
         <v>14</v>
       </c>
@@ -4360,7 +4366,7 @@
       <c r="D20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="42">
         <v>30</v>
       </c>
       <c r="F20" s="23" t="s">
@@ -4372,7 +4378,7 @@
       <c r="H20" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="52" t="s">
+      <c r="I20" s="49" t="s">
         <v>104</v>
       </c>
       <c r="J20" s="7" t="s">
@@ -4392,7 +4398,7 @@
       <c r="D21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="42">
         <v>32</v>
       </c>
       <c r="F21" s="23" t="s">
@@ -4404,7 +4410,7 @@
       <c r="H21" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="52" t="s">
+      <c r="I21" s="49" t="s">
         <v>109</v>
       </c>
       <c r="J21" s="7" t="s">
@@ -4424,7 +4430,7 @@
       <c r="D22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="42">
         <v>33</v>
       </c>
       <c r="F22" s="23" t="s">
@@ -4436,7 +4442,7 @@
       <c r="H22" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="I22" s="52" t="s">
+      <c r="I22" s="49" t="s">
         <v>114</v>
       </c>
       <c r="J22" s="7" t="s">
@@ -4456,7 +4462,7 @@
       <c r="D23" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="42">
         <v>36</v>
       </c>
       <c r="F23" s="23" t="s">
@@ -4468,7 +4474,7 @@
       <c r="H23" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="52" t="s">
+      <c r="I23" s="49" t="s">
         <v>119</v>
       </c>
       <c r="J23" s="7" t="s">
@@ -4488,7 +4494,7 @@
       <c r="D24" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="22">
         <v>22</v>
       </c>
       <c r="F24" s="7" t="s">
@@ -4518,7 +4524,7 @@
       <c r="D25" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="42">
+      <c r="E25" s="22">
         <v>24</v>
       </c>
       <c r="F25" s="7" t="s">
@@ -4548,7 +4554,7 @@
       <c r="D26" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E26" s="42" t="s">
+      <c r="E26" s="22" t="s">
         <v>130</v>
       </c>
       <c r="F26" s="7" t="s">
@@ -4578,7 +4584,7 @@
       <c r="D27" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="42" t="s">
+      <c r="E27" s="22" t="s">
         <v>130</v>
       </c>
       <c r="F27" s="7" t="s">
@@ -4602,13 +4608,13 @@
       <c r="B28" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="53" t="s">
+      <c r="C28" s="50" t="s">
         <v>139</v>
       </c>
       <c r="D28" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="54" t="s">
+      <c r="E28" s="42" t="s">
         <v>140</v>
       </c>
       <c r="F28" s="23" t="s">
@@ -4640,7 +4646,7 @@
       <c r="D29" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="54" t="s">
+      <c r="E29" s="42" t="s">
         <v>147</v>
       </c>
       <c r="F29" s="23" t="s">
@@ -4652,7 +4658,7 @@
       <c r="H29" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="I29" s="52" t="s">
+      <c r="I29" s="49" t="s">
         <v>149</v>
       </c>
       <c r="J29" s="7" t="s">
@@ -4666,11 +4672,11 @@
       <c r="B30" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="55" t="s">
+      <c r="C30" s="51" t="s">
         <v>152</v>
       </c>
       <c r="D30" s="7"/>
-      <c r="E30" s="42" t="s">
+      <c r="E30" s="22" t="s">
         <v>153</v>
       </c>
       <c r="F30" s="7" t="s">
@@ -4698,7 +4704,7 @@
       <c r="D31" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="43">
+      <c r="E31" s="42">
         <v>9</v>
       </c>
       <c r="F31" s="23" t="s">
@@ -4710,7 +4716,7 @@
       <c r="H31" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="I31" s="52" t="s">
+      <c r="I31" s="49" t="s">
         <v>161</v>
       </c>
       <c r="J31" s="1" t="s">
@@ -4730,7 +4736,7 @@
       <c r="D32" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="43">
+      <c r="E32" s="42">
         <v>9</v>
       </c>
       <c r="F32" s="23" t="s">
@@ -4742,7 +4748,7 @@
       <c r="H32" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="I32" s="52" t="s">
+      <c r="I32" s="49" t="s">
         <v>166</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -4762,7 +4768,7 @@
       <c r="D33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="54" t="s">
+      <c r="E33" s="42" t="s">
         <v>170</v>
       </c>
       <c r="F33" s="23" t="s">
@@ -4794,8 +4800,8 @@
       <c r="D34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="45">
-        <v>50</v>
+      <c r="E34" s="52">
+        <v>51</v>
       </c>
       <c r="F34" s="23" t="s">
         <v>159</v>
@@ -4826,7 +4832,7 @@
       <c r="D35" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="45" t="s">
+      <c r="E35" s="52" t="s">
         <v>180</v>
       </c>
       <c r="F35" s="23" t="s">
@@ -4838,7 +4844,7 @@
       <c r="H35" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="I35" s="56" t="s">
+      <c r="I35" s="53" t="s">
         <v>182</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -4852,13 +4858,13 @@
       <c r="B36" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C36" s="55" t="s">
+      <c r="C36" s="51" t="s">
         <v>29</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="42" t="s">
+      <c r="E36" s="22" t="s">
         <v>185</v>
       </c>
       <c r="F36" s="23" t="s">
@@ -4871,7 +4877,7 @@
         <v>186</v>
       </c>
       <c r="I36" s="24"/>
-      <c r="J36" s="57" t="s">
+      <c r="J36" s="54" t="s">
         <v>187</v>
       </c>
     </row>
@@ -4882,14 +4888,14 @@
       <c r="B37" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C37" s="55" t="s">
+      <c r="C37" s="51" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="58">
-        <v>120</v>
+      <c r="E37" s="52">
+        <v>121</v>
       </c>
       <c r="F37" s="23" t="s">
         <v>159</v>
@@ -4905,64 +4911,82 @@
         <v>190</v>
       </c>
     </row>
-    <row r="38" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A38" s="59" t="s">
+    <row r="38" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A38" s="55" t="s">
         <v>191</v>
       </c>
-      <c r="B38" s="58" t="s">
+      <c r="B38" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="C38" s="60" t="s">
+      <c r="C38" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="61" t="s">
+      <c r="D38" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="58">
+      <c r="E38" s="59">
         <v>1</v>
       </c>
-      <c r="F38" s="61" t="s">
+      <c r="F38" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="G38" s="61">
+      <c r="G38" s="58">
         <v>2026</v>
       </c>
-      <c r="H38" s="61"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="58" t="s">
+      <c r="H38" s="58"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="56" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="39" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A39" s="21"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="23"/>
+      <c r="A39" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="D39" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F39" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="G39" s="58">
+        <v>2026</v>
+      </c>
+      <c r="H39" s="23" t="s">
+        <v>196</v>
+      </c>
       <c r="I39" s="24"/>
-      <c r="J39" s="7"/>
+      <c r="J39" s="7" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A40" s="21"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="55"/>
+      <c r="C40" s="51"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="42"/>
+      <c r="E40" s="22"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
-      <c r="H40" s="63"/>
+      <c r="H40" s="61"/>
       <c r="I40" s="24"/>
       <c r="J40" s="7"/>
     </row>
     <row r="41" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A41" s="21"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="55"/>
+      <c r="C41" s="51"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="42"/>
+      <c r="E41" s="22"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="23"/>
@@ -4972,9 +4996,9 @@
     <row r="42" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A42" s="21"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="55"/>
+      <c r="C42" s="51"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="42"/>
+      <c r="E42" s="22"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="23"/>
@@ -4984,9 +5008,9 @@
     <row r="43" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A43" s="21"/>
       <c r="B43" s="7"/>
-      <c r="C43" s="55"/>
+      <c r="C43" s="51"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="42"/>
+      <c r="E43" s="22"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="23"/>
@@ -4996,9 +5020,9 @@
     <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A44" s="21"/>
       <c r="B44" s="7"/>
-      <c r="C44" s="55"/>
+      <c r="C44" s="51"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="42"/>
+      <c r="E44" s="22"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="23"/>
@@ -5008,9 +5032,9 @@
     <row r="45" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A45" s="21"/>
       <c r="B45" s="7"/>
-      <c r="C45" s="55"/>
+      <c r="C45" s="51"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="42"/>
+      <c r="E45" s="22"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="23"/>
@@ -5020,9 +5044,9 @@
     <row r="46" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A46" s="21"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="55"/>
+      <c r="C46" s="51"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="42"/>
+      <c r="E46" s="22"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="23"/>
@@ -5032,9 +5056,9 @@
     <row r="47" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A47" s="21"/>
       <c r="B47" s="7"/>
-      <c r="C47" s="55"/>
+      <c r="C47" s="51"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="42"/>
+      <c r="E47" s="22"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="23"/>
@@ -5044,9 +5068,9 @@
     <row r="48" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A48" s="21"/>
       <c r="B48" s="7"/>
-      <c r="C48" s="55"/>
+      <c r="C48" s="51"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="42"/>
+      <c r="E48" s="22"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="23"/>
@@ -5055,18 +5079,18 @@
     </row>
     <row r="49" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A49" s="25" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>157</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="51">
+      <c r="E49" s="42">
         <v>7</v>
       </c>
       <c r="F49" s="23" t="s">
@@ -5076,27 +5100,27 @@
         <v>2026</v>
       </c>
       <c r="H49" s="23"/>
-      <c r="I49" s="52" t="s">
-        <v>195</v>
+      <c r="I49" s="49" t="s">
+        <v>200</v>
       </c>
       <c r="J49" s="23" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A50" s="25" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>157</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E50" s="51">
+      <c r="E50" s="42">
         <v>10</v>
       </c>
       <c r="F50" s="23" t="s">
@@ -5105,17 +5129,17 @@
       <c r="G50" s="23">
         <v>2026</v>
       </c>
-      <c r="H50" s="56"/>
-      <c r="I50" s="52" t="s">
-        <v>199</v>
+      <c r="H50" s="53"/>
+      <c r="I50" s="49" t="s">
+        <v>204</v>
       </c>
       <c r="J50" s="23" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A51" s="25" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>157</v>
@@ -5124,7 +5148,7 @@
       <c r="D51" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="51">
+      <c r="E51" s="42">
         <v>2</v>
       </c>
       <c r="F51" s="23" t="s">
@@ -5133,17 +5157,17 @@
       <c r="G51" s="23">
         <v>2026</v>
       </c>
-      <c r="H51" s="56"/>
-      <c r="I51" s="52" t="s">
-        <v>202</v>
+      <c r="H51" s="53"/>
+      <c r="I51" s="49" t="s">
+        <v>207</v>
       </c>
       <c r="J51" s="23" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A52" s="25" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B52" s="23" t="s">
         <v>157</v>
@@ -5152,7 +5176,7 @@
       <c r="D52" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E52" s="51">
+      <c r="E52" s="42">
         <v>4</v>
       </c>
       <c r="F52" s="23" t="s">
@@ -5161,29 +5185,29 @@
       <c r="G52" s="23">
         <v>2026</v>
       </c>
-      <c r="H52" s="56"/>
-      <c r="I52" s="52" t="s">
-        <v>205</v>
+      <c r="H52" s="53"/>
+      <c r="I52" s="49" t="s">
+        <v>210</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A53" s="21" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C53" s="55" t="s">
-        <v>208</v>
+      <c r="C53" s="51" t="s">
+        <v>213</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="64"/>
-      <c r="F53" s="55" t="s">
+      <c r="E53" s="62"/>
+      <c r="F53" s="51" t="s">
         <v>14</v>
       </c>
       <c r="G53" s="23">
@@ -5191,25 +5215,25 @@
       </c>
       <c r="H53" s="23"/>
       <c r="I53" s="24" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J53" s="7"/>
     </row>
     <row r="54" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A54" s="21" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C54" s="55" t="s">
-        <v>208</v>
+      <c r="C54" s="51" t="s">
+        <v>213</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="64"/>
-      <c r="F54" s="55" t="s">
+      <c r="E54" s="62"/>
+      <c r="F54" s="51" t="s">
         <v>14</v>
       </c>
       <c r="G54" s="23">
@@ -5217,86 +5241,86 @@
       </c>
       <c r="H54" s="23"/>
       <c r="I54" s="24" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J54" s="7"/>
     </row>
     <row r="55" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A55" s="21" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="42"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
       <c r="I55" s="24" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A56" s="21" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
-      <c r="E56" s="42"/>
+      <c r="E56" s="22"/>
       <c r="F56" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="24" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
-      <c r="E57" s="42"/>
+      <c r="E57" s="22"/>
       <c r="F57" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="24" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
-      <c r="E58" s="42"/>
+      <c r="E58" s="22"/>
       <c r="F58" s="7" t="s">
         <v>14</v>
       </c>
@@ -5304,21 +5328,21 @@
       <c r="H58" s="7"/>
       <c r="I58" s="24"/>
       <c r="J58" s="7" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A59" s="25" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D59" s="7"/>
-      <c r="E59" s="42">
+      <c r="E59" s="22">
         <v>10</v>
       </c>
       <c r="F59" s="22" t="s">
@@ -5328,25 +5352,25 @@
         <v>2026</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:10">
       <c r="A60" s="21" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
-      <c r="E60" s="65"/>
+      <c r="E60" s="22"/>
       <c r="F60" s="22" t="s">
         <v>14</v>
       </c>
@@ -5355,22 +5379,22 @@
       </c>
       <c r="H60" s="7"/>
       <c r="I60" s="24" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="J60" s="21" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A61" s="21" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="65"/>
+      <c r="E61" s="22"/>
       <c r="F61" s="22" t="s">
         <v>14</v>
       </c>
@@ -5378,27 +5402,27 @@
         <v>2026</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="J61" s="24" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:10">
       <c r="A62" s="21" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D62" s="7"/>
-      <c r="E62" s="65"/>
+      <c r="E62" s="22"/>
       <c r="F62" s="22" t="s">
         <v>14</v>
       </c>
@@ -5406,27 +5430,27 @@
         <v>2026</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J62" s="24" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1" spans="1:10">
       <c r="A63" s="21" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D63" s="7"/>
-      <c r="E63" s="65"/>
+      <c r="E63" s="22"/>
       <c r="F63" s="22" t="s">
         <v>14</v>
       </c>
@@ -5434,13 +5458,13 @@
         <v>2026</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="J63" s="24" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1" spans="1:10">
@@ -5448,7 +5472,7 @@
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
-      <c r="E64" s="65"/>
+      <c r="E64" s="22"/>
       <c r="F64" s="22"/>
       <c r="G64" s="23"/>
       <c r="H64" s="7"/>
@@ -5456,17 +5480,17 @@
       <c r="J64" s="24"/>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:10">
-      <c r="A65" s="66" t="s">
-        <v>247</v>
-      </c>
-      <c r="B65" s="58" t="s">
+      <c r="A65" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="B65" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="58" t="s">
+      <c r="C65" s="64" t="s">
         <v>164</v>
       </c>
       <c r="D65" s="7"/>
-      <c r="E65" s="65"/>
+      <c r="E65" s="22"/>
       <c r="F65" s="22" t="s">
         <v>14</v>
       </c>
@@ -5474,41 +5498,41 @@
         <v>8.25</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I65" s="24"/>
       <c r="J65" s="21"/>
     </row>
     <row r="66" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A66" s="66" t="s">
-        <v>249</v>
+      <c r="A66" s="63" t="s">
+        <v>254</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
-      <c r="E66" s="65"/>
+      <c r="E66" s="22"/>
       <c r="F66" s="22" t="s">
         <v>14</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H66" s="7"/>
       <c r="I66" s="24"/>
       <c r="J66" s="21"/>
     </row>
     <row r="67" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A67" s="66" t="s">
-        <v>251</v>
+      <c r="A67" s="63" t="s">
+        <v>256</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
-      <c r="E67" s="65"/>
+      <c r="E67" s="22"/>
       <c r="F67" s="22" t="s">
         <v>14</v>
       </c>
@@ -5520,33 +5544,33 @@
       <c r="J67" s="21"/>
     </row>
     <row r="68" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A68" s="66" t="s">
-        <v>252</v>
+      <c r="A68" s="63" t="s">
+        <v>257</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
-      <c r="E68" s="65"/>
+      <c r="E68" s="22"/>
       <c r="F68" s="22"/>
       <c r="G68" s="23" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="24"/>
       <c r="J68" s="21"/>
     </row>
     <row r="69" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A69" s="66" t="s">
-        <v>253</v>
+      <c r="A69" s="63" t="s">
+        <v>258</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
-      <c r="E69" s="65"/>
+      <c r="E69" s="22"/>
       <c r="F69" s="22" t="s">
         <v>14</v>
       </c>
@@ -5558,15 +5582,15 @@
       <c r="J69" s="21"/>
     </row>
     <row r="70" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A70" s="66" t="s">
-        <v>254</v>
+      <c r="A70" s="63" t="s">
+        <v>259</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
-      <c r="E70" s="65"/>
+      <c r="E70" s="22"/>
       <c r="F70" s="22"/>
       <c r="G70" s="23"/>
       <c r="H70" s="7"/>
@@ -5574,15 +5598,15 @@
       <c r="J70" s="21"/>
     </row>
     <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A71" s="66" t="s">
-        <v>255</v>
+      <c r="A71" s="63" t="s">
+        <v>260</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
-      <c r="E71" s="65"/>
+      <c r="E71" s="22"/>
       <c r="F71" s="22"/>
       <c r="G71" s="23">
         <v>5.15</v>
@@ -5592,13 +5616,13 @@
       <c r="J71" s="21"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A72" s="66" t="s">
-        <v>256</v>
+      <c r="A72" s="63" t="s">
+        <v>261</v>
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
-      <c r="E72" s="65"/>
+      <c r="E72" s="22"/>
       <c r="F72" s="22"/>
       <c r="G72" s="23"/>
       <c r="H72" s="7"/>
@@ -5606,13 +5630,13 @@
       <c r="J72" s="21"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A73" s="66" t="s">
-        <v>257</v>
+      <c r="A73" s="63" t="s">
+        <v>262</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
-      <c r="E73" s="65"/>
+      <c r="E73" s="22"/>
       <c r="F73" s="22"/>
       <c r="G73" s="23"/>
       <c r="H73" s="7"/>
@@ -5620,13 +5644,13 @@
       <c r="J73" s="21"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A74" s="66" t="s">
-        <v>258</v>
+      <c r="A74" s="63" t="s">
+        <v>263</v>
       </c>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
-      <c r="E74" s="65"/>
+      <c r="E74" s="22"/>
       <c r="F74" s="22"/>
       <c r="G74" s="23"/>
       <c r="H74" s="7"/>
@@ -5634,13 +5658,13 @@
       <c r="J74" s="21"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A75" s="66" t="s">
-        <v>259</v>
+      <c r="A75" s="63" t="s">
+        <v>264</v>
       </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
-      <c r="E75" s="65"/>
+      <c r="E75" s="22"/>
       <c r="F75" s="22"/>
       <c r="G75" s="23"/>
       <c r="H75" s="7"/>
@@ -5648,15 +5672,15 @@
       <c r="J75" s="21"/>
     </row>
     <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A76" s="66" t="s">
-        <v>260</v>
+      <c r="A76" s="63" t="s">
+        <v>265</v>
       </c>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
-      <c r="E76" s="65"/>
+      <c r="E76" s="22"/>
       <c r="F76" s="22" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G76" s="23"/>
       <c r="H76" s="7"/>
@@ -5664,15 +5688,15 @@
       <c r="J76" s="24"/>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:10">
-      <c r="A77" s="66" t="s">
-        <v>262</v>
+      <c r="A77" s="63" t="s">
+        <v>267</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
-      <c r="E77" s="65"/>
+      <c r="E77" s="22"/>
       <c r="F77" s="22" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G77" s="23"/>
       <c r="H77" s="7"/>
@@ -5681,14 +5705,14 @@
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:10">
       <c r="A78" s="21" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
-      <c r="E78" s="65"/>
+      <c r="E78" s="22"/>
       <c r="F78" s="22" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G78" s="23"/>
       <c r="H78" s="7"/>
@@ -5696,15 +5720,15 @@
       <c r="J78" s="24"/>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:10">
-      <c r="A79" s="66" t="s">
-        <v>265</v>
+      <c r="A79" s="63" t="s">
+        <v>270</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
-      <c r="E79" s="65"/>
+      <c r="E79" s="22"/>
       <c r="F79" s="22" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G79" s="23"/>
       <c r="H79" s="7"/>
@@ -5712,13 +5736,13 @@
       <c r="J79" s="24"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:10">
-      <c r="A80" s="66" t="s">
-        <v>267</v>
+      <c r="A80" s="63" t="s">
+        <v>272</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
-      <c r="E80" s="65"/>
+      <c r="E80" s="22"/>
       <c r="F80" s="22">
         <v>102</v>
       </c>
@@ -5728,13 +5752,13 @@
       <c r="J80" s="24"/>
     </row>
     <row r="81" ht="25" customHeight="1" spans="1:10">
-      <c r="A81" s="66" t="s">
-        <v>268</v>
+      <c r="A81" s="63" t="s">
+        <v>273</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
-      <c r="E81" s="65"/>
+      <c r="E81" s="22"/>
       <c r="F81" s="22">
         <v>69</v>
       </c>
@@ -5744,13 +5768,13 @@
       <c r="J81" s="24"/>
     </row>
     <row r="82" ht="25" customHeight="1" spans="1:10">
-      <c r="A82" s="66" t="s">
-        <v>269</v>
+      <c r="A82" s="63" t="s">
+        <v>274</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
-      <c r="E82" s="65"/>
+      <c r="E82" s="22"/>
       <c r="F82" s="22">
         <v>86</v>
       </c>
@@ -5760,13 +5784,13 @@
       <c r="J82" s="24"/>
     </row>
     <row r="83" ht="25" customHeight="1" spans="1:10">
-      <c r="A83" s="66" t="s">
-        <v>270</v>
+      <c r="A83" s="63" t="s">
+        <v>275</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
-      <c r="E83" s="65"/>
+      <c r="E83" s="22"/>
       <c r="F83" s="22"/>
       <c r="G83" s="23"/>
       <c r="H83" s="7"/>
@@ -5774,15 +5798,15 @@
       <c r="J83" s="24"/>
     </row>
     <row r="84" ht="25" customHeight="1" spans="1:10">
-      <c r="A84" s="66" t="s">
-        <v>271</v>
+      <c r="A84" s="63" t="s">
+        <v>276</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
-      <c r="E84" s="65"/>
+      <c r="E84" s="22"/>
       <c r="F84" s="22" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G84" s="23"/>
       <c r="H84" s="7"/>
@@ -5790,13 +5814,13 @@
       <c r="J84" s="24"/>
     </row>
     <row r="85" ht="25" customHeight="1" spans="1:10">
-      <c r="A85" s="66" t="s">
-        <v>273</v>
+      <c r="A85" s="63" t="s">
+        <v>278</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
-      <c r="E85" s="65"/>
+      <c r="E85" s="22"/>
       <c r="F85" s="22"/>
       <c r="G85" s="23"/>
       <c r="H85" s="7"/>
@@ -5804,13 +5828,13 @@
       <c r="J85" s="24"/>
     </row>
     <row r="86" ht="25" customHeight="1" spans="1:10">
-      <c r="A86" s="66" t="s">
-        <v>274</v>
+      <c r="A86" s="63" t="s">
+        <v>279</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
-      <c r="E86" s="65"/>
+      <c r="E86" s="22"/>
       <c r="F86" s="22"/>
       <c r="G86" s="23"/>
       <c r="H86" s="7"/>
@@ -5818,15 +5842,15 @@
       <c r="J86" s="24"/>
     </row>
     <row r="87" ht="25" customHeight="1" spans="1:10">
-      <c r="A87" s="66" t="s">
-        <v>275</v>
+      <c r="A87" s="63" t="s">
+        <v>280</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
-      <c r="E87" s="65"/>
+      <c r="E87" s="22"/>
       <c r="F87" s="22" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G87" s="23"/>
       <c r="H87" s="7"/>
@@ -5834,15 +5858,15 @@
       <c r="J87" s="24"/>
     </row>
     <row r="88" ht="25" customHeight="1" spans="1:10">
-      <c r="A88" s="66" t="s">
-        <v>277</v>
+      <c r="A88" s="63" t="s">
+        <v>282</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
-      <c r="E88" s="65"/>
+      <c r="E88" s="22"/>
       <c r="F88" s="22" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G88" s="23"/>
       <c r="H88" s="7"/>
@@ -5850,17 +5874,17 @@
       <c r="J88" s="24"/>
     </row>
     <row r="89" ht="25" customHeight="1" spans="1:10">
-      <c r="A89" s="66" t="s">
-        <v>279</v>
+      <c r="A89" s="63" t="s">
+        <v>284</v>
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="7" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D89" s="7"/>
-      <c r="E89" s="65"/>
+      <c r="E89" s="22"/>
       <c r="F89" s="22" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G89" s="23"/>
       <c r="H89" s="7"/>
@@ -5868,17 +5892,17 @@
       <c r="J89" s="24"/>
     </row>
     <row r="90" ht="25" customHeight="1" spans="1:10">
-      <c r="A90" s="66" t="s">
-        <v>282</v>
+      <c r="A90" s="63" t="s">
+        <v>287</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D90" s="7"/>
-      <c r="E90" s="65"/>
+      <c r="E90" s="22"/>
       <c r="F90" s="22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G90" s="23"/>
       <c r="H90" s="7"/>
@@ -5886,17 +5910,17 @@
       <c r="J90" s="24"/>
     </row>
     <row r="91" ht="25" customHeight="1" spans="1:10">
-      <c r="A91" s="66" t="s">
-        <v>285</v>
+      <c r="A91" s="63" t="s">
+        <v>290</v>
       </c>
       <c r="B91" s="7"/>
       <c r="C91" s="7" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D91" s="7"/>
-      <c r="E91" s="65"/>
+      <c r="E91" s="22"/>
       <c r="F91" s="22" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G91" s="23"/>
       <c r="H91" s="7"/>
@@ -5904,17 +5928,17 @@
       <c r="J91" s="24"/>
     </row>
     <row r="92" ht="25" customHeight="1" spans="1:10">
-      <c r="A92" s="66" t="s">
-        <v>288</v>
+      <c r="A92" s="63" t="s">
+        <v>293</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D92" s="7"/>
-      <c r="E92" s="65"/>
+      <c r="E92" s="22"/>
       <c r="F92" s="22" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G92" s="23"/>
       <c r="H92" s="7"/>
@@ -5922,17 +5946,17 @@
       <c r="J92" s="24"/>
     </row>
     <row r="93" ht="25" customHeight="1" spans="1:10">
-      <c r="A93" s="66" t="s">
-        <v>290</v>
+      <c r="A93" s="63" t="s">
+        <v>295</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D93" s="7"/>
-      <c r="E93" s="65"/>
+      <c r="E93" s="22"/>
       <c r="F93" s="22" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="G93" s="23"/>
       <c r="H93" s="7"/>
@@ -5940,17 +5964,17 @@
       <c r="J93" s="24"/>
     </row>
     <row r="94" ht="25" customHeight="1" spans="1:10">
-      <c r="A94" s="66" t="s">
-        <v>293</v>
+      <c r="A94" s="63" t="s">
+        <v>298</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D94" s="7"/>
-      <c r="E94" s="65"/>
+      <c r="E94" s="22"/>
       <c r="F94" s="22" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="G94" s="23"/>
       <c r="H94" s="7"/>
@@ -5958,17 +5982,17 @@
       <c r="J94" s="24"/>
     </row>
     <row r="95" ht="25" customHeight="1" spans="1:10">
-      <c r="A95" s="66" t="s">
-        <v>296</v>
+      <c r="A95" s="63" t="s">
+        <v>301</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D95" s="7"/>
-      <c r="E95" s="65"/>
+      <c r="E95" s="22"/>
       <c r="F95" s="22" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="G95" s="23"/>
       <c r="H95" s="7"/>
@@ -5976,17 +6000,17 @@
       <c r="J95" s="24"/>
     </row>
     <row r="96" ht="25" customHeight="1" spans="1:10">
-      <c r="A96" s="66" t="s">
-        <v>299</v>
+      <c r="A96" s="63" t="s">
+        <v>304</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D96" s="7"/>
-      <c r="E96" s="65"/>
+      <c r="E96" s="22"/>
       <c r="F96" s="22" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G96" s="23"/>
       <c r="H96" s="7"/>
@@ -5994,17 +6018,17 @@
       <c r="J96" s="24"/>
     </row>
     <row r="97" ht="25" customHeight="1" spans="1:10">
-      <c r="A97" s="66" t="s">
-        <v>301</v>
+      <c r="A97" s="63" t="s">
+        <v>306</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D97" s="7"/>
-      <c r="E97" s="65"/>
+      <c r="E97" s="22"/>
       <c r="F97" s="22" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G97" s="23"/>
       <c r="H97" s="7"/>
@@ -6012,17 +6036,17 @@
       <c r="J97" s="24"/>
     </row>
     <row r="98" ht="25" customHeight="1" spans="1:10">
-      <c r="A98" s="66" t="s">
-        <v>304</v>
+      <c r="A98" s="63" t="s">
+        <v>309</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D98" s="7"/>
-      <c r="E98" s="65"/>
+      <c r="E98" s="22"/>
       <c r="F98" s="22" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G98" s="23"/>
       <c r="H98" s="7"/>
@@ -6030,17 +6054,17 @@
       <c r="J98" s="24"/>
     </row>
     <row r="99" ht="25" customHeight="1" spans="1:10">
-      <c r="A99" s="66" t="s">
-        <v>306</v>
+      <c r="A99" s="63" t="s">
+        <v>311</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D99" s="7"/>
-      <c r="E99" s="65"/>
+      <c r="E99" s="22"/>
       <c r="F99" s="22" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G99" s="23"/>
       <c r="H99" s="7"/>
@@ -6048,69 +6072,69 @@
       <c r="J99" s="24"/>
     </row>
     <row r="100" ht="25" customHeight="1" spans="1:10">
-      <c r="A100" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="B100" s="58"/>
-      <c r="C100" s="58" t="s">
-        <v>310</v>
-      </c>
-      <c r="D100" s="58"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="68" t="s">
-        <v>278</v>
-      </c>
-      <c r="G100" s="61"/>
+      <c r="A100" s="63" t="s">
+        <v>314</v>
+      </c>
+      <c r="B100" s="64"/>
+      <c r="C100" s="64" t="s">
+        <v>315</v>
+      </c>
+      <c r="D100" s="64"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="52" t="s">
+        <v>283</v>
+      </c>
+      <c r="G100" s="46"/>
       <c r="H100" s="7"/>
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
     </row>
     <row r="101" ht="25" customHeight="1" spans="1:10">
-      <c r="A101" s="66" t="s">
-        <v>311</v>
-      </c>
-      <c r="B101" s="58"/>
-      <c r="C101" s="58" t="s">
-        <v>289</v>
-      </c>
-      <c r="D101" s="58"/>
-      <c r="E101" s="67"/>
-      <c r="F101" s="68" t="s">
-        <v>312</v>
-      </c>
-      <c r="G101" s="61"/>
+      <c r="A101" s="63" t="s">
+        <v>316</v>
+      </c>
+      <c r="B101" s="64"/>
+      <c r="C101" s="64" t="s">
+        <v>294</v>
+      </c>
+      <c r="D101" s="64"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="52" t="s">
+        <v>317</v>
+      </c>
+      <c r="G101" s="46"/>
       <c r="H101" s="7"/>
       <c r="I101" s="24"/>
       <c r="J101" s="24"/>
     </row>
     <row r="102" ht="25" customHeight="1" spans="1:10">
-      <c r="A102" s="66" t="s">
-        <v>313</v>
-      </c>
-      <c r="B102" s="58"/>
-      <c r="C102" s="58"/>
-      <c r="D102" s="58"/>
-      <c r="E102" s="67"/>
-      <c r="F102" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="G102" s="61"/>
+      <c r="A102" s="63" t="s">
+        <v>318</v>
+      </c>
+      <c r="B102" s="64"/>
+      <c r="C102" s="64"/>
+      <c r="D102" s="64"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="G102" s="46"/>
       <c r="H102" s="7"/>
       <c r="I102" s="24"/>
       <c r="J102" s="24"/>
     </row>
     <row r="103" ht="25" customHeight="1" spans="1:10">
-      <c r="A103" s="66" t="s">
-        <v>315</v>
-      </c>
-      <c r="B103" s="58"/>
-      <c r="C103" s="58" t="s">
-        <v>316</v>
-      </c>
-      <c r="D103" s="58"/>
-      <c r="E103" s="67"/>
-      <c r="F103" s="68" t="s">
-        <v>317</v>
+      <c r="A103" s="63" t="s">
+        <v>320</v>
+      </c>
+      <c r="B103" s="64"/>
+      <c r="C103" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="D103" s="64"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="52" t="s">
+        <v>322</v>
       </c>
       <c r="G103" s="23"/>
       <c r="H103" s="7"/>
@@ -6118,87 +6142,99 @@
       <c r="J103" s="24"/>
     </row>
     <row r="104" ht="25" customHeight="1" spans="1:10">
-      <c r="A104" s="66" t="s">
-        <v>318</v>
-      </c>
-      <c r="B104" s="58"/>
-      <c r="C104" s="58" t="s">
-        <v>319</v>
-      </c>
-      <c r="D104" s="58"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="68" t="s">
-        <v>320</v>
+      <c r="A104" s="63" t="s">
+        <v>323</v>
+      </c>
+      <c r="B104" s="64"/>
+      <c r="C104" s="64" t="s">
+        <v>324</v>
+      </c>
+      <c r="D104" s="64"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="52" t="s">
+        <v>325</v>
       </c>
       <c r="G104" s="23"/>
       <c r="H104" s="7"/>
       <c r="I104" s="24"/>
       <c r="J104" s="24"/>
     </row>
-    <row r="105" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A105" s="69" t="s">
-        <v>321</v>
-      </c>
-      <c r="B105" s="55"/>
-      <c r="C105" s="55" t="s">
-        <v>280</v>
-      </c>
-      <c r="D105" s="55"/>
-      <c r="E105" s="70"/>
-      <c r="F105" s="71" t="s">
-        <v>278</v>
+    <row r="105" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A105" s="65" t="s">
+        <v>326</v>
+      </c>
+      <c r="B105" s="51"/>
+      <c r="C105" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="D105" s="51"/>
+      <c r="E105" s="62"/>
+      <c r="F105" s="62" t="s">
+        <v>283</v>
       </c>
       <c r="G105" s="23"/>
-      <c r="H105" s="55"/>
-      <c r="I105" s="72"/>
-      <c r="J105" s="72"/>
-    </row>
-    <row r="106" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A106" s="69" t="s">
-        <v>322</v>
-      </c>
-      <c r="B106" s="55"/>
-      <c r="C106" s="55"/>
-      <c r="D106" s="55"/>
-      <c r="E106" s="70"/>
-      <c r="F106" s="71" t="s">
-        <v>323</v>
+      <c r="H105" s="51"/>
+      <c r="I105" s="66"/>
+      <c r="J105" s="66"/>
+    </row>
+    <row r="106" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A106" s="65" t="s">
+        <v>327</v>
+      </c>
+      <c r="B106" s="51"/>
+      <c r="C106" s="51"/>
+      <c r="D106" s="51"/>
+      <c r="E106" s="62"/>
+      <c r="F106" s="62" t="s">
+        <v>328</v>
       </c>
       <c r="G106" s="23"/>
-      <c r="H106" s="55"/>
-      <c r="I106" s="72"/>
-      <c r="J106" s="72"/>
-    </row>
-    <row r="107" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A107" s="73"/>
-      <c r="B107" s="55"/>
-      <c r="C107" s="55"/>
-      <c r="D107" s="55"/>
-      <c r="E107" s="70"/>
-      <c r="F107" s="71"/>
+      <c r="H106" s="51"/>
+      <c r="I106" s="66"/>
+      <c r="J106" s="66"/>
+    </row>
+    <row r="107" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A107" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="B107" s="51"/>
+      <c r="C107" s="64" t="s">
+        <v>315</v>
+      </c>
+      <c r="D107" s="51"/>
+      <c r="E107" s="62"/>
+      <c r="F107" s="62" t="s">
+        <v>330</v>
+      </c>
       <c r="G107" s="23"/>
-      <c r="H107" s="55"/>
-      <c r="I107" s="72"/>
-      <c r="J107" s="72"/>
+      <c r="H107" s="51"/>
+      <c r="I107" s="66"/>
+      <c r="J107" s="66"/>
     </row>
     <row r="108" ht="25" customHeight="1" spans="1:10">
-      <c r="A108" s="66"/>
+      <c r="A108" s="63" t="s">
+        <v>331</v>
+      </c>
       <c r="B108" s="7"/>
-      <c r="C108" s="7"/>
+      <c r="C108" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="D108" s="7"/>
-      <c r="E108" s="65"/>
-      <c r="F108" s="22"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22" t="s">
+        <v>333</v>
+      </c>
       <c r="G108" s="23"/>
       <c r="H108" s="7"/>
       <c r="I108" s="24"/>
       <c r="J108" s="24"/>
     </row>
     <row r="109" ht="25" customHeight="1" spans="1:10">
-      <c r="A109" s="66"/>
+      <c r="A109" s="63"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
-      <c r="E109" s="65"/>
+      <c r="E109" s="22"/>
       <c r="F109" s="22"/>
       <c r="G109" s="23"/>
       <c r="H109" s="7"/>
@@ -6206,7 +6242,7 @@
       <c r="J109" s="24"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J106" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J108" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <colorFilter dxfId="0"/>
       <extLst>
@@ -6229,7 +6265,7 @@
         </dxfs>
       </extLst>
     </filterColumn>
-    <sortState ref="A1:J106">
+    <sortState ref="A1:J108">
       <sortCondition ref="F1:F87"/>
     </sortState>
     <extLst/>
@@ -6261,7 +6297,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6270,22 +6306,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6299,22 +6335,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6328,22 +6364,22 @@
         <v>11</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6357,22 +6393,22 @@
         <v>11</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6386,22 +6422,22 @@
         <v>11</v>
       </c>
       <c r="D5" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>359</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>345</v>
+      </c>
+      <c r="I5" s="39" t="s">
         <v>346</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>347</v>
-      </c>
-      <c r="F5" s="39" t="s">
-        <v>348</v>
-      </c>
-      <c r="G5" s="39" t="s">
-        <v>349</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>335</v>
-      </c>
-      <c r="I5" s="39" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6415,22 +6451,22 @@
         <v>11</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6444,22 +6480,22 @@
         <v>138</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6473,22 +6509,22 @@
         <v>138</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6502,22 +6538,22 @@
         <v>157</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6531,22 +6567,22 @@
         <v>157</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -6560,22 +6596,22 @@
         <v>138</v>
       </c>
       <c r="D11" s="39" t="s">
+        <v>375</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="F11" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="G11" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="H11" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="F11" s="39" t="s">
-        <v>355</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>355</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>356</v>
-      </c>
       <c r="I11" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -6589,22 +6625,22 @@
         <v>138</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -6612,28 +6648,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -6647,22 +6683,22 @@
         <v>145</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -6670,28 +6706,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -6699,28 +6735,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -6728,28 +6764,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -6757,28 +6793,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -6786,28 +6822,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -6815,28 +6851,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -6844,28 +6880,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -6873,28 +6909,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -6902,28 +6938,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -6940,7 +6976,7 @@
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -7020,13 +7056,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -7041,28 +7077,28 @@
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>14</v>
@@ -7071,28 +7107,28 @@
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>14</v>
@@ -7101,22 +7137,22 @@
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
@@ -7131,28 +7167,28 @@
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>14</v>
@@ -7161,28 +7197,28 @@
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>14</v>
@@ -7191,28 +7227,28 @@
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>14</v>
@@ -7221,28 +7257,28 @@
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>14</v>
@@ -7251,28 +7287,28 @@
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>14</v>
@@ -7281,28 +7317,28 @@
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>14</v>
@@ -7311,28 +7347,28 @@
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>14</v>
@@ -7341,28 +7377,28 @@
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>14</v>
@@ -7371,28 +7407,28 @@
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>14</v>
@@ -7401,28 +7437,28 @@
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>14</v>
@@ -7431,22 +7467,22 @@
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
@@ -7461,16 +7497,16 @@
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7482,13 +7518,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7500,13 +7536,13 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7518,13 +7554,13 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7535,13 +7571,13 @@
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -7553,13 +7589,13 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7570,13 +7606,13 @@
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7588,13 +7624,13 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7606,13 +7642,13 @@
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7623,13 +7659,13 @@
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7641,13 +7677,13 @@
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7659,16 +7695,16 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -7679,16 +7715,16 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -7699,16 +7735,16 @@
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -7719,16 +7755,16 @@
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -7739,16 +7775,16 @@
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -7759,7 +7795,7 @@
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -7777,13 +7813,13 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
@@ -7796,13 +7832,13 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
@@ -7821,7 +7857,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -7835,7 +7871,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -7849,7 +7885,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -7863,7 +7899,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -7876,7 +7912,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -7890,7 +7926,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -7903,7 +7939,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -7916,7 +7952,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -7929,17 +7965,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>159</v>
@@ -7948,24 +7984,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>159</v>
@@ -7974,24 +8010,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>159</v>
@@ -8000,24 +8036,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>159</v>
@@ -8026,17 +8062,17 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
     <sheet name="已删" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">在播剧更新时间表!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已删!$A$1:$J$48</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="561">
   <si>
     <t>剧名</t>
   </si>
@@ -990,6 +990,9 @@
     <t>家庭关系证明书</t>
   </si>
   <si>
+    <t>52</t>
+  </si>
+  <si>
     <t xml:space="preserve">朴世荣 / 韩高恩 / 林志恩 / 成伊言 / 朴率拉 </t>
   </si>
   <si>
@@ -1005,7 +1008,7 @@
     <t>剧情 / 犯罪</t>
   </si>
   <si>
-    <t>27/100</t>
+    <t>28/100</t>
   </si>
   <si>
     <t xml:space="preserve"> 张瑞希 / 田惠媛 / 薛正焕 / 周清晨 / 尹海英 /</t>
@@ -1033,6 +1036,9 @@
     <t>我们愉快的好日子</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>严贤京/尹仲勋/申正允/尹多英/金惠玉</t>
   </si>
   <si>
@@ -1051,13 +1057,46 @@
     <t>剧情 / 喜剧</t>
   </si>
   <si>
-    <t>2/10</t>
+    <t>4/10</t>
   </si>
   <si>
     <t>李浚赫 / 徐现宇 / 吴代焕 / 玉子妍</t>
   </si>
   <si>
     <t>链接：https://pan.quark.cn/s/9bd91cf9b311?pwd=Nzk6   提取码：Nzk6</t>
+  </si>
+  <si>
+    <t>不是你的恋爱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">剧情 / 爱情 </t>
+  </si>
+  <si>
+    <t>2/14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 徐康俊 / 安恩真 / 李周安 / 赵雅兰</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/547e99636d86?pwd=daM5  提取码：daM5</t>
+  </si>
+  <si>
+    <t>寄生之心</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/902364e3ea98?pwd=6375  提取码：6375</t>
+  </si>
+  <si>
+    <t>/~172c3awu68~:/</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/902364e3ea98?pwd=6375</t>
+  </si>
+  <si>
+    <t>提取码：6375</t>
   </si>
   <si>
     <t>神的游戏</t>
@@ -1509,6 +1548,39 @@
   </si>
   <si>
     <t>97</t>
+  </si>
+  <si>
+    <t>荒山野店</t>
+  </si>
+  <si>
+    <t>狮拳 </t>
+  </si>
+  <si>
+    <t>歌剧般的潜入搜查官</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>当世主宰</t>
+  </si>
+  <si>
+    <t>这一切究竟是失控的科技，还是潜藏于世的邪恶力量</t>
+  </si>
+  <si>
+    <t>鬼界网红</t>
+  </si>
+  <si>
+    <t>最新喜剧</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>诺顿溪大屠杀</t>
+  </si>
+  <si>
+    <t>71</t>
   </si>
   <si>
     <t>序号</t>
@@ -2432,13 +2504,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2447,6 +2512,16 @@
       <sz val="11"/>
       <color rgb="FF111111"/>
       <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2464,14 +2539,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <b/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="35">
@@ -3003,7 +3075,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3122,9 +3194,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -3137,74 +3206,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3258,12 +3309,20 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3460,25 +3519,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3747,7 +3806,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
@@ -3795,7 +3854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" ht="21" hidden="1" customHeight="1" spans="1:10">
       <c r="A2" s="25" t="s">
         <v>10</v>
       </c>
@@ -3808,7 +3867,7 @@
       <c r="D2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="42">
+      <c r="E2" s="41">
         <v>36</v>
       </c>
       <c r="F2" s="23" t="s">
@@ -3820,14 +3879,14 @@
       <c r="H2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="I2" s="42" t="s">
         <v>16</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="3" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A3" s="21" t="s">
         <v>18</v>
       </c>
@@ -3852,14 +3911,14 @@
       <c r="H3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="I3" s="42" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="4" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A4" s="21" t="s">
         <v>23</v>
       </c>
@@ -3891,7 +3950,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="5" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A5" s="21" t="s">
         <v>28</v>
       </c>
@@ -3923,7 +3982,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="6" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A6" s="21" t="s">
         <v>33</v>
       </c>
@@ -3955,8 +4014,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A7" s="44" t="s">
+    <row r="7" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A7" s="43" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="29" t="s">
@@ -3968,10 +4027,10 @@
       <c r="D7" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="28">
         <v>32</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F7" s="23" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="29">
@@ -3987,14 +4046,14 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="8" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A8" s="21" t="s">
         <v>42</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="44" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="23" t="s">
@@ -4019,7 +4078,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="9" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A9" s="25" t="s">
         <v>47</v>
       </c>
@@ -4051,7 +4110,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="10" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A10" s="21" t="s">
         <v>52</v>
       </c>
@@ -4083,7 +4142,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="11" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A11" s="21" t="s">
         <v>57</v>
       </c>
@@ -4115,7 +4174,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="12" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A12" s="21" t="s">
         <v>62</v>
       </c>
@@ -4147,7 +4206,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="13" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A13" s="25" t="s">
         <v>67</v>
       </c>
@@ -4177,7 +4236,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="14" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A14" s="25" t="s">
         <v>73</v>
       </c>
@@ -4207,7 +4266,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="15" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A15" s="25" t="s">
         <v>78</v>
       </c>
@@ -4237,7 +4296,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="16" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A16" s="21" t="s">
         <v>83</v>
       </c>
@@ -4265,7 +4324,7 @@
       </c>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="17" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A17" s="21" t="s">
         <v>87</v>
       </c>
@@ -4285,7 +4344,7 @@
       <c r="G17" s="23">
         <v>2026</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="H17" s="45" t="s">
         <v>89</v>
       </c>
       <c r="I17" s="24" t="s">
@@ -4293,7 +4352,7 @@
       </c>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="18" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A18" s="21" t="s">
         <v>91</v>
       </c>
@@ -4323,7 +4382,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="19" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A19" s="21" t="s">
         <v>96</v>
       </c>
@@ -4353,7 +4412,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="20" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A20" s="25" t="s">
         <v>101</v>
       </c>
@@ -4366,7 +4425,7 @@
       <c r="D20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="41">
         <v>30</v>
       </c>
       <c r="F20" s="23" t="s">
@@ -4378,14 +4437,14 @@
       <c r="H20" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="49" t="s">
+      <c r="I20" s="46" t="s">
         <v>104</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="21" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A21" s="25" t="s">
         <v>106</v>
       </c>
@@ -4398,7 +4457,7 @@
       <c r="D21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="42">
+      <c r="E21" s="41">
         <v>32</v>
       </c>
       <c r="F21" s="23" t="s">
@@ -4410,14 +4469,14 @@
       <c r="H21" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="49" t="s">
+      <c r="I21" s="46" t="s">
         <v>109</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="22" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A22" s="25" t="s">
         <v>111</v>
       </c>
@@ -4430,7 +4489,7 @@
       <c r="D22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="41">
         <v>33</v>
       </c>
       <c r="F22" s="23" t="s">
@@ -4442,14 +4501,14 @@
       <c r="H22" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="I22" s="49" t="s">
+      <c r="I22" s="46" t="s">
         <v>114</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="23" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A23" s="25" t="s">
         <v>116</v>
       </c>
@@ -4462,7 +4521,7 @@
       <c r="D23" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="41">
         <v>36</v>
       </c>
       <c r="F23" s="23" t="s">
@@ -4474,14 +4533,14 @@
       <c r="H23" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="49" t="s">
+      <c r="I23" s="46" t="s">
         <v>119</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="24" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A24" s="21" t="s">
         <v>121</v>
       </c>
@@ -4511,7 +4570,7 @@
       </c>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="25" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A25" s="21" t="s">
         <v>125</v>
       </c>
@@ -4541,7 +4600,7 @@
       </c>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="26" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A26" s="21" t="s">
         <v>128</v>
       </c>
@@ -4571,7 +4630,7 @@
       </c>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="27" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A27" s="21" t="s">
         <v>133</v>
       </c>
@@ -4601,20 +4660,20 @@
       </c>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="28" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A28" s="25" t="s">
         <v>137</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="50" t="s">
+      <c r="C28" s="47" t="s">
         <v>139</v>
       </c>
       <c r="D28" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="42" t="s">
+      <c r="E28" s="41" t="s">
         <v>140</v>
       </c>
       <c r="F28" s="23" t="s">
@@ -4633,7 +4692,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="29" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A29" s="25" t="s">
         <v>144</v>
       </c>
@@ -4646,7 +4705,7 @@
       <c r="D29" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="42" t="s">
+      <c r="E29" s="41" t="s">
         <v>147</v>
       </c>
       <c r="F29" s="23" t="s">
@@ -4658,21 +4717,21 @@
       <c r="H29" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="I29" s="49" t="s">
+      <c r="I29" s="46" t="s">
         <v>149</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="30" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="30" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A30" s="21" t="s">
         <v>151</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="48" t="s">
         <v>152</v>
       </c>
       <c r="D30" s="7"/>
@@ -4691,7 +4750,7 @@
       </c>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="31" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A31" s="25" t="s">
         <v>156</v>
       </c>
@@ -4704,7 +4763,7 @@
       <c r="D31" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="42">
+      <c r="E31" s="41">
         <v>9</v>
       </c>
       <c r="F31" s="23" t="s">
@@ -4716,14 +4775,14 @@
       <c r="H31" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="I31" s="49" t="s">
+      <c r="I31" s="46" t="s">
         <v>161</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="32" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A32" s="25" t="s">
         <v>163</v>
       </c>
@@ -4736,7 +4795,7 @@
       <c r="D32" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="42">
+      <c r="E32" s="41">
         <v>9</v>
       </c>
       <c r="F32" s="23" t="s">
@@ -4748,14 +4807,14 @@
       <c r="H32" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="I32" s="49" t="s">
+      <c r="I32" s="46" t="s">
         <v>166</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="33" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A33" s="25" t="s">
         <v>168</v>
       </c>
@@ -4768,7 +4827,7 @@
       <c r="D33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="42" t="s">
+      <c r="E33" s="41" t="s">
         <v>170</v>
       </c>
       <c r="F33" s="23" t="s">
@@ -4800,8 +4859,8 @@
       <c r="D34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="52">
-        <v>51</v>
+      <c r="E34" s="49" t="s">
+        <v>175</v>
       </c>
       <c r="F34" s="23" t="s">
         <v>159</v>
@@ -4810,30 +4869,30 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>138</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="52" t="s">
-        <v>180</v>
+      <c r="E35" s="49" t="s">
+        <v>181</v>
       </c>
       <c r="F35" s="23" t="s">
         <v>159</v>
@@ -4842,30 +4901,30 @@
         <v>2026</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="I35" s="53" t="s">
         <v>182</v>
       </c>
+      <c r="I35" s="50" t="s">
+        <v>183</v>
+      </c>
       <c r="J35" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" s="6" customFormat="1" ht="34" customHeight="1" spans="1:10">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" s="6" customFormat="1" ht="34" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C36" s="51" t="s">
+      <c r="C36" s="48" t="s">
         <v>29</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F36" s="23" t="s">
         <v>159</v>
@@ -4874,28 +4933,28 @@
         <v>2026</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I36" s="24"/>
-      <c r="J36" s="54" t="s">
-        <v>187</v>
+      <c r="J36" s="51" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="37" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C37" s="51" t="s">
+      <c r="C37" s="48" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="52">
-        <v>121</v>
+      <c r="E37" s="49" t="s">
+        <v>190</v>
       </c>
       <c r="F37" s="23" t="s">
         <v>159</v>
@@ -4904,135 +4963,173 @@
         <v>2026</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I37" s="24"/>
       <c r="J37" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="38" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A38" s="55" t="s">
-        <v>191</v>
-      </c>
-      <c r="B38" s="56" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A38" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C38" s="57" t="s">
+      <c r="C38" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="58" t="s">
+      <c r="D38" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="59">
+      <c r="E38" s="22">
         <v>1</v>
       </c>
-      <c r="F38" s="58" t="s">
+      <c r="F38" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G38" s="58">
+      <c r="G38" s="23">
         <v>2026</v>
       </c>
-      <c r="H38" s="58"/>
-      <c r="I38" s="60"/>
-      <c r="J38" s="56" t="s">
-        <v>192</v>
+      <c r="H38" s="23"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="7" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="39" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="B39" s="56" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C39" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="D39" s="58" t="s">
+      <c r="C39" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="D39" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="F39" s="58" t="s">
+      <c r="E39" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="F39" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G39" s="58">
+      <c r="G39" s="23">
         <v>2026</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I39" s="24"/>
       <c r="J39" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A40" s="21"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="7"/>
+      <c r="A40" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="B40" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="54" t="s">
+        <v>201</v>
+      </c>
+      <c r="D40" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="F40" s="55" t="s">
+        <v>159</v>
+      </c>
+      <c r="G40" s="55">
+        <v>2026</v>
+      </c>
+      <c r="H40" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="I40" s="57"/>
+      <c r="J40" s="53" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="41" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A41" s="21"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="7"/>
-    </row>
-    <row r="42" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A41" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" s="55" t="s">
+        <v>159</v>
+      </c>
+      <c r="G41" s="53"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="42" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="51"/>
+      <c r="C42" s="48"/>
       <c r="D42" s="7"/>
       <c r="E42" s="22"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="23"/>
       <c r="I42" s="24"/>
-      <c r="J42" s="7"/>
-    </row>
-    <row r="43" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="J42" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="43" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="21"/>
       <c r="B43" s="7"/>
-      <c r="C43" s="51"/>
+      <c r="C43" s="48"/>
       <c r="D43" s="7"/>
       <c r="E43" s="22"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="23"/>
       <c r="I43" s="24"/>
-      <c r="J43" s="7"/>
-    </row>
-    <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="J43" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="21"/>
       <c r="B44" s="7"/>
-      <c r="C44" s="51"/>
+      <c r="C44" s="48"/>
       <c r="D44" s="7"/>
       <c r="E44" s="22"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="23"/>
       <c r="I44" s="24"/>
-      <c r="J44" s="7"/>
-    </row>
-    <row r="45" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="J44" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="21"/>
       <c r="B45" s="7"/>
-      <c r="C45" s="51"/>
+      <c r="C45" s="48"/>
       <c r="D45" s="7"/>
       <c r="E45" s="22"/>
       <c r="F45" s="7"/>
@@ -5041,10 +5138,10 @@
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="46" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="21"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="51"/>
+      <c r="C46" s="48"/>
       <c r="D46" s="7"/>
       <c r="E46" s="22"/>
       <c r="F46" s="7"/>
@@ -5053,10 +5150,10 @@
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="47" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="21"/>
       <c r="B47" s="7"/>
-      <c r="C47" s="51"/>
+      <c r="C47" s="48"/>
       <c r="D47" s="7"/>
       <c r="E47" s="22"/>
       <c r="F47" s="7"/>
@@ -5065,10 +5162,10 @@
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="48" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="21"/>
       <c r="B48" s="7"/>
-      <c r="C48" s="51"/>
+      <c r="C48" s="48"/>
       <c r="D48" s="7"/>
       <c r="E48" s="22"/>
       <c r="F48" s="7"/>
@@ -5077,20 +5174,20 @@
       <c r="I48" s="24"/>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="49" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A49" s="25" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>157</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="42">
+      <c r="E49" s="41">
         <v>7</v>
       </c>
       <c r="F49" s="23" t="s">
@@ -5100,27 +5197,27 @@
         <v>2026</v>
       </c>
       <c r="H49" s="23"/>
-      <c r="I49" s="49" t="s">
-        <v>200</v>
+      <c r="I49" s="46" t="s">
+        <v>213</v>
       </c>
       <c r="J49" s="23" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A50" s="25" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>157</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E50" s="42">
+      <c r="E50" s="41">
         <v>10</v>
       </c>
       <c r="F50" s="23" t="s">
@@ -5129,17 +5226,17 @@
       <c r="G50" s="23">
         <v>2026</v>
       </c>
-      <c r="H50" s="53"/>
-      <c r="I50" s="49" t="s">
-        <v>204</v>
+      <c r="H50" s="50"/>
+      <c r="I50" s="46" t="s">
+        <v>217</v>
       </c>
       <c r="J50" s="23" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A51" s="25" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>157</v>
@@ -5148,7 +5245,7 @@
       <c r="D51" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="42">
+      <c r="E51" s="41">
         <v>2</v>
       </c>
       <c r="F51" s="23" t="s">
@@ -5157,17 +5254,17 @@
       <c r="G51" s="23">
         <v>2026</v>
       </c>
-      <c r="H51" s="53"/>
-      <c r="I51" s="49" t="s">
-        <v>207</v>
+      <c r="H51" s="50"/>
+      <c r="I51" s="46" t="s">
+        <v>220</v>
       </c>
       <c r="J51" s="23" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A52" s="25" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B52" s="23" t="s">
         <v>157</v>
@@ -5176,7 +5273,7 @@
       <c r="D52" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E52" s="42">
+      <c r="E52" s="41">
         <v>4</v>
       </c>
       <c r="F52" s="23" t="s">
@@ -5185,29 +5282,29 @@
       <c r="G52" s="23">
         <v>2026</v>
       </c>
-      <c r="H52" s="53"/>
-      <c r="I52" s="49" t="s">
-        <v>210</v>
+      <c r="H52" s="50"/>
+      <c r="I52" s="46" t="s">
+        <v>223</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A53" s="21" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C53" s="51" t="s">
-        <v>213</v>
+      <c r="C53" s="48" t="s">
+        <v>226</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="62"/>
-      <c r="F53" s="51" t="s">
+      <c r="E53" s="58"/>
+      <c r="F53" s="48" t="s">
         <v>14</v>
       </c>
       <c r="G53" s="23">
@@ -5215,25 +5312,25 @@
       </c>
       <c r="H53" s="23"/>
       <c r="I53" s="24" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="54" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A54" s="21" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C54" s="51" t="s">
-        <v>213</v>
+      <c r="C54" s="48" t="s">
+        <v>226</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="62"/>
-      <c r="F54" s="51" t="s">
+      <c r="E54" s="58"/>
+      <c r="F54" s="48" t="s">
         <v>14</v>
       </c>
       <c r="G54" s="23">
@@ -5241,16 +5338,16 @@
       </c>
       <c r="H54" s="23"/>
       <c r="I54" s="24" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="J54" s="7"/>
     </row>
-    <row r="55" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="55" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A55" s="21" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -5261,18 +5358,18 @@
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
       <c r="I55" s="24" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A56" s="21" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -5283,18 +5380,18 @@
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="24" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -5305,18 +5402,18 @@
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="24" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -5328,18 +5425,18 @@
       <c r="H58" s="7"/>
       <c r="I58" s="24"/>
       <c r="J58" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A59" s="25" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D59" s="7"/>
       <c r="E59" s="22">
@@ -5352,18 +5449,18 @@
         <v>2026</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="60" ht="25" customHeight="1" spans="1:10">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A60" s="21" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>68</v>
@@ -5379,15 +5476,15 @@
       </c>
       <c r="H60" s="7"/>
       <c r="I60" s="24" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="J60" s="21" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="61" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="61" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A61" s="21" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>68</v>
@@ -5402,24 +5499,24 @@
         <v>2026</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="J61" s="24" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1" spans="1:10">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="62" ht="24" hidden="1" customHeight="1" spans="1:10">
       <c r="A62" s="21" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="D62" s="7"/>
       <c r="E62" s="22"/>
@@ -5430,24 +5527,24 @@
         <v>2026</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="J62" s="24" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="63" ht="25" customHeight="1" spans="1:10">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="63" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A63" s="21" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="22"/>
@@ -5458,16 +5555,16 @@
         <v>2026</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="J63" s="24" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="64" ht="25" customHeight="1" spans="1:10">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="64" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A64" s="21"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -5479,14 +5576,14 @@
       <c r="I64" s="24"/>
       <c r="J64" s="24"/>
     </row>
-    <row r="65" ht="25" customHeight="1" spans="1:10">
-      <c r="A65" s="63" t="s">
-        <v>252</v>
-      </c>
-      <c r="B65" s="64" t="s">
+    <row r="65" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A65" s="52" t="s">
+        <v>265</v>
+      </c>
+      <c r="B65" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="64" t="s">
+      <c r="C65" s="53" t="s">
         <v>164</v>
       </c>
       <c r="D65" s="7"/>
@@ -5498,14 +5595,14 @@
         <v>8.25</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="I65" s="24"/>
       <c r="J65" s="21"/>
     </row>
-    <row r="66" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A66" s="63" t="s">
-        <v>254</v>
+    <row r="66" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A66" s="52" t="s">
+        <v>267</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>68</v>
@@ -5517,15 +5614,15 @@
         <v>14</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="H66" s="7"/>
       <c r="I66" s="24"/>
       <c r="J66" s="21"/>
     </row>
-    <row r="67" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A67" s="63" t="s">
-        <v>256</v>
+    <row r="67" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A67" s="52" t="s">
+        <v>269</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>68</v>
@@ -5543,9 +5640,9 @@
       <c r="I67" s="24"/>
       <c r="J67" s="21"/>
     </row>
-    <row r="68" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A68" s="63" t="s">
-        <v>257</v>
+    <row r="68" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A68" s="52" t="s">
+        <v>270</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>68</v>
@@ -5555,15 +5652,15 @@
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
       <c r="G68" s="23" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="24"/>
       <c r="J68" s="21"/>
     </row>
-    <row r="69" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A69" s="63" t="s">
-        <v>258</v>
+    <row r="69" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A69" s="52" t="s">
+        <v>271</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>68</v>
@@ -5581,9 +5678,9 @@
       <c r="I69" s="24"/>
       <c r="J69" s="21"/>
     </row>
-    <row r="70" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A70" s="63" t="s">
-        <v>259</v>
+    <row r="70" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A70" s="52" t="s">
+        <v>272</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>68</v>
@@ -5597,9 +5694,9 @@
       <c r="I70" s="24"/>
       <c r="J70" s="21"/>
     </row>
-    <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A71" s="63" t="s">
-        <v>260</v>
+    <row r="71" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A71" s="52" t="s">
+        <v>273</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>68</v>
@@ -5615,9 +5712,9 @@
       <c r="I71" s="24"/>
       <c r="J71" s="21"/>
     </row>
-    <row r="72" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A72" s="63" t="s">
-        <v>261</v>
+    <row r="72" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A72" s="52" t="s">
+        <v>274</v>
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -5629,9 +5726,9 @@
       <c r="I72" s="24"/>
       <c r="J72" s="21"/>
     </row>
-    <row r="73" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A73" s="63" t="s">
-        <v>262</v>
+    <row r="73" s="6" customFormat="1" ht="30" hidden="1" customHeight="1" spans="1:10">
+      <c r="A73" s="52" t="s">
+        <v>275</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -5643,9 +5740,9 @@
       <c r="I73" s="24"/>
       <c r="J73" s="21"/>
     </row>
-    <row r="74" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A74" s="63" t="s">
-        <v>263</v>
+    <row r="74" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A74" s="52" t="s">
+        <v>276</v>
       </c>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -5657,9 +5754,9 @@
       <c r="I74" s="24"/>
       <c r="J74" s="21"/>
     </row>
-    <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A75" s="63" t="s">
-        <v>264</v>
+    <row r="75" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A75" s="52" t="s">
+        <v>277</v>
       </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -5671,73 +5768,73 @@
       <c r="I75" s="24"/>
       <c r="J75" s="21"/>
     </row>
-    <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A76" s="63" t="s">
-        <v>265</v>
+    <row r="76" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A76" s="52" t="s">
+        <v>278</v>
       </c>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="22"/>
       <c r="F76" s="22" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="G76" s="23"/>
       <c r="H76" s="7"/>
       <c r="I76" s="24"/>
       <c r="J76" s="24"/>
     </row>
-    <row r="77" ht="25" customHeight="1" spans="1:10">
-      <c r="A77" s="63" t="s">
-        <v>267</v>
+    <row r="77" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A77" s="52" t="s">
+        <v>280</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="22"/>
       <c r="F77" s="22" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="G77" s="23"/>
       <c r="H77" s="7"/>
       <c r="I77" s="24"/>
       <c r="J77" s="24"/>
     </row>
-    <row r="78" ht="25" customHeight="1" spans="1:10">
+    <row r="78" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A78" s="21" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="22"/>
       <c r="F78" s="22" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="G78" s="23"/>
       <c r="H78" s="7"/>
       <c r="I78" s="24"/>
       <c r="J78" s="24"/>
     </row>
-    <row r="79" ht="25" customHeight="1" spans="1:10">
-      <c r="A79" s="63" t="s">
-        <v>270</v>
+    <row r="79" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A79" s="52" t="s">
+        <v>283</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="22"/>
       <c r="F79" s="22" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="G79" s="23"/>
       <c r="H79" s="7"/>
       <c r="I79" s="24"/>
       <c r="J79" s="24"/>
     </row>
-    <row r="80" ht="25" customHeight="1" spans="1:10">
-      <c r="A80" s="63" t="s">
-        <v>272</v>
+    <row r="80" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A80" s="52" t="s">
+        <v>285</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -5751,9 +5848,9 @@
       <c r="I80" s="24"/>
       <c r="J80" s="24"/>
     </row>
-    <row r="81" ht="25" customHeight="1" spans="1:10">
-      <c r="A81" s="63" t="s">
-        <v>273</v>
+    <row r="81" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A81" s="52" t="s">
+        <v>286</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -5767,9 +5864,9 @@
       <c r="I81" s="24"/>
       <c r="J81" s="24"/>
     </row>
-    <row r="82" ht="25" customHeight="1" spans="1:10">
-      <c r="A82" s="63" t="s">
-        <v>274</v>
+    <row r="82" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A82" s="52" t="s">
+        <v>287</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -5783,9 +5880,9 @@
       <c r="I82" s="24"/>
       <c r="J82" s="24"/>
     </row>
-    <row r="83" ht="25" customHeight="1" spans="1:10">
-      <c r="A83" s="63" t="s">
-        <v>275</v>
+    <row r="83" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A83" s="52" t="s">
+        <v>288</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -5797,25 +5894,25 @@
       <c r="I83" s="24"/>
       <c r="J83" s="24"/>
     </row>
-    <row r="84" ht="25" customHeight="1" spans="1:10">
-      <c r="A84" s="63" t="s">
-        <v>276</v>
+    <row r="84" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A84" s="52" t="s">
+        <v>289</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="22"/>
       <c r="F84" s="22" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="G84" s="23"/>
       <c r="H84" s="7"/>
       <c r="I84" s="24"/>
       <c r="J84" s="24"/>
     </row>
-    <row r="85" ht="25" customHeight="1" spans="1:10">
-      <c r="A85" s="63" t="s">
-        <v>278</v>
+    <row r="85" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A85" s="52" t="s">
+        <v>291</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -5827,9 +5924,9 @@
       <c r="I85" s="24"/>
       <c r="J85" s="24"/>
     </row>
-    <row r="86" ht="25" customHeight="1" spans="1:10">
-      <c r="A86" s="63" t="s">
-        <v>279</v>
+    <row r="86" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A86" s="52" t="s">
+        <v>292</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -5841,408 +5938,588 @@
       <c r="I86" s="24"/>
       <c r="J86" s="24"/>
     </row>
-    <row r="87" ht="25" customHeight="1" spans="1:10">
-      <c r="A87" s="63" t="s">
-        <v>280</v>
+    <row r="87" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A87" s="52" t="s">
+        <v>293</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="22"/>
       <c r="F87" s="22" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="G87" s="23"/>
       <c r="H87" s="7"/>
       <c r="I87" s="24"/>
       <c r="J87" s="24"/>
     </row>
-    <row r="88" ht="25" customHeight="1" spans="1:10">
-      <c r="A88" s="63" t="s">
-        <v>282</v>
+    <row r="88" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A88" s="52" t="s">
+        <v>295</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="22"/>
       <c r="F88" s="22" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="G88" s="23"/>
       <c r="H88" s="7"/>
       <c r="I88" s="24"/>
       <c r="J88" s="24"/>
     </row>
-    <row r="89" ht="25" customHeight="1" spans="1:10">
-      <c r="A89" s="63" t="s">
-        <v>284</v>
+    <row r="89" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A89" s="52" t="s">
+        <v>297</v>
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="7" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D89" s="7"/>
       <c r="E89" s="22"/>
       <c r="F89" s="22" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="G89" s="23"/>
       <c r="H89" s="7"/>
       <c r="I89" s="24"/>
       <c r="J89" s="24"/>
     </row>
-    <row r="90" ht="25" customHeight="1" spans="1:10">
-      <c r="A90" s="63" t="s">
-        <v>287</v>
+    <row r="90" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A90" s="52" t="s">
+        <v>300</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D90" s="7"/>
       <c r="E90" s="22"/>
       <c r="F90" s="22" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="G90" s="23"/>
       <c r="H90" s="7"/>
       <c r="I90" s="24"/>
       <c r="J90" s="24"/>
     </row>
-    <row r="91" ht="25" customHeight="1" spans="1:10">
-      <c r="A91" s="63" t="s">
-        <v>290</v>
+    <row r="91" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A91" s="52" t="s">
+        <v>303</v>
       </c>
       <c r="B91" s="7"/>
       <c r="C91" s="7" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="22"/>
       <c r="F91" s="22" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="G91" s="23"/>
       <c r="H91" s="7"/>
       <c r="I91" s="24"/>
       <c r="J91" s="24"/>
     </row>
-    <row r="92" ht="25" customHeight="1" spans="1:10">
-      <c r="A92" s="63" t="s">
-        <v>293</v>
+    <row r="92" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A92" s="52" t="s">
+        <v>306</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="D92" s="7"/>
       <c r="E92" s="22"/>
       <c r="F92" s="22" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="G92" s="23"/>
       <c r="H92" s="7"/>
       <c r="I92" s="24"/>
       <c r="J92" s="24"/>
     </row>
-    <row r="93" ht="25" customHeight="1" spans="1:10">
-      <c r="A93" s="63" t="s">
-        <v>295</v>
+    <row r="93" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A93" s="52" t="s">
+        <v>308</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="G93" s="23"/>
       <c r="H93" s="7"/>
       <c r="I93" s="24"/>
       <c r="J93" s="24"/>
     </row>
-    <row r="94" ht="25" customHeight="1" spans="1:10">
-      <c r="A94" s="63" t="s">
-        <v>298</v>
+    <row r="94" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A94" s="52" t="s">
+        <v>311</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="22"/>
       <c r="F94" s="22" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="G94" s="23"/>
       <c r="H94" s="7"/>
       <c r="I94" s="24"/>
       <c r="J94" s="24"/>
     </row>
-    <row r="95" ht="25" customHeight="1" spans="1:10">
-      <c r="A95" s="63" t="s">
-        <v>301</v>
+    <row r="95" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A95" s="52" t="s">
+        <v>314</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="G95" s="23"/>
       <c r="H95" s="7"/>
       <c r="I95" s="24"/>
       <c r="J95" s="24"/>
     </row>
-    <row r="96" ht="25" customHeight="1" spans="1:10">
-      <c r="A96" s="63" t="s">
-        <v>304</v>
+    <row r="96" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A96" s="52" t="s">
+        <v>317</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="22"/>
       <c r="F96" s="22" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="G96" s="23"/>
       <c r="H96" s="7"/>
       <c r="I96" s="24"/>
       <c r="J96" s="24"/>
     </row>
-    <row r="97" ht="25" customHeight="1" spans="1:10">
-      <c r="A97" s="63" t="s">
-        <v>306</v>
+    <row r="97" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A97" s="52" t="s">
+        <v>319</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="G97" s="23"/>
       <c r="H97" s="7"/>
       <c r="I97" s="24"/>
       <c r="J97" s="24"/>
     </row>
-    <row r="98" ht="25" customHeight="1" spans="1:10">
-      <c r="A98" s="63" t="s">
-        <v>309</v>
+    <row r="98" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A98" s="52" t="s">
+        <v>322</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="22"/>
       <c r="F98" s="22" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="G98" s="23"/>
       <c r="H98" s="7"/>
       <c r="I98" s="24"/>
       <c r="J98" s="24"/>
     </row>
-    <row r="99" ht="25" customHeight="1" spans="1:10">
-      <c r="A99" s="63" t="s">
-        <v>311</v>
+    <row r="99" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A99" s="52" t="s">
+        <v>324</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="22"/>
       <c r="F99" s="22" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="G99" s="23"/>
       <c r="H99" s="7"/>
       <c r="I99" s="24"/>
       <c r="J99" s="24"/>
     </row>
-    <row r="100" ht="25" customHeight="1" spans="1:10">
-      <c r="A100" s="63" t="s">
-        <v>314</v>
-      </c>
-      <c r="B100" s="64"/>
-      <c r="C100" s="64" t="s">
-        <v>315</v>
-      </c>
-      <c r="D100" s="64"/>
+    <row r="100" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A100" s="52" t="s">
+        <v>327</v>
+      </c>
+      <c r="B100" s="53"/>
+      <c r="C100" s="53" t="s">
+        <v>328</v>
+      </c>
+      <c r="D100" s="53"/>
       <c r="E100" s="22"/>
-      <c r="F100" s="52" t="s">
-        <v>283</v>
-      </c>
-      <c r="G100" s="46"/>
+      <c r="F100" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="G100" s="55"/>
       <c r="H100" s="7"/>
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
     </row>
-    <row r="101" ht="25" customHeight="1" spans="1:10">
-      <c r="A101" s="63" t="s">
-        <v>316</v>
-      </c>
-      <c r="B101" s="64"/>
-      <c r="C101" s="64" t="s">
-        <v>294</v>
-      </c>
-      <c r="D101" s="64"/>
+    <row r="101" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A101" s="52" t="s">
+        <v>329</v>
+      </c>
+      <c r="B101" s="53"/>
+      <c r="C101" s="53" t="s">
+        <v>307</v>
+      </c>
+      <c r="D101" s="53"/>
       <c r="E101" s="22"/>
-      <c r="F101" s="52" t="s">
-        <v>317</v>
-      </c>
-      <c r="G101" s="46"/>
+      <c r="F101" s="49" t="s">
+        <v>330</v>
+      </c>
+      <c r="G101" s="55"/>
       <c r="H101" s="7"/>
       <c r="I101" s="24"/>
       <c r="J101" s="24"/>
     </row>
-    <row r="102" ht="25" customHeight="1" spans="1:10">
-      <c r="A102" s="63" t="s">
-        <v>318</v>
-      </c>
-      <c r="B102" s="64"/>
-      <c r="C102" s="64"/>
-      <c r="D102" s="64"/>
+    <row r="102" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A102" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="B102" s="53"/>
+      <c r="C102" s="53"/>
+      <c r="D102" s="53"/>
       <c r="E102" s="22"/>
-      <c r="F102" s="52" t="s">
-        <v>319</v>
-      </c>
-      <c r="G102" s="46"/>
+      <c r="F102" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="G102" s="55"/>
       <c r="H102" s="7"/>
       <c r="I102" s="24"/>
       <c r="J102" s="24"/>
     </row>
-    <row r="103" ht="25" customHeight="1" spans="1:10">
-      <c r="A103" s="63" t="s">
-        <v>320</v>
-      </c>
-      <c r="B103" s="64"/>
-      <c r="C103" s="64" t="s">
-        <v>321</v>
-      </c>
-      <c r="D103" s="64"/>
+    <row r="103" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A103" s="52" t="s">
+        <v>333</v>
+      </c>
+      <c r="B103" s="53"/>
+      <c r="C103" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="D103" s="53"/>
       <c r="E103" s="22"/>
-      <c r="F103" s="52" t="s">
-        <v>322</v>
+      <c r="F103" s="49" t="s">
+        <v>335</v>
       </c>
       <c r="G103" s="23"/>
       <c r="H103" s="7"/>
       <c r="I103" s="24"/>
       <c r="J103" s="24"/>
     </row>
-    <row r="104" ht="25" customHeight="1" spans="1:10">
-      <c r="A104" s="63" t="s">
-        <v>323</v>
-      </c>
-      <c r="B104" s="64"/>
-      <c r="C104" s="64" t="s">
-        <v>324</v>
-      </c>
-      <c r="D104" s="64"/>
+    <row r="104" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A104" s="52" t="s">
+        <v>336</v>
+      </c>
+      <c r="B104" s="53"/>
+      <c r="C104" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="D104" s="53"/>
       <c r="E104" s="22"/>
-      <c r="F104" s="52" t="s">
-        <v>325</v>
+      <c r="F104" s="49" t="s">
+        <v>338</v>
       </c>
       <c r="G104" s="23"/>
       <c r="H104" s="7"/>
       <c r="I104" s="24"/>
       <c r="J104" s="24"/>
     </row>
-    <row r="105" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A105" s="65" t="s">
-        <v>326</v>
-      </c>
-      <c r="B105" s="51"/>
-      <c r="C105" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="D105" s="51"/>
-      <c r="E105" s="62"/>
-      <c r="F105" s="62" t="s">
-        <v>283</v>
+    <row r="105" s="40" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A105" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="B105" s="48"/>
+      <c r="C105" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="D105" s="48"/>
+      <c r="E105" s="58"/>
+      <c r="F105" s="58" t="s">
+        <v>296</v>
       </c>
       <c r="G105" s="23"/>
-      <c r="H105" s="51"/>
-      <c r="I105" s="66"/>
-      <c r="J105" s="66"/>
-    </row>
-    <row r="106" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A106" s="65" t="s">
-        <v>327</v>
-      </c>
-      <c r="B106" s="51"/>
-      <c r="C106" s="51"/>
-      <c r="D106" s="51"/>
-      <c r="E106" s="62"/>
-      <c r="F106" s="62" t="s">
+      <c r="H105" s="48"/>
+      <c r="I105" s="60"/>
+      <c r="J105" s="60"/>
+    </row>
+    <row r="106" s="40" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A106" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="B106" s="48"/>
+      <c r="C106" s="48"/>
+      <c r="D106" s="48"/>
+      <c r="E106" s="58"/>
+      <c r="F106" s="58" t="s">
+        <v>341</v>
+      </c>
+      <c r="G106" s="23"/>
+      <c r="H106" s="48"/>
+      <c r="I106" s="60"/>
+      <c r="J106" s="60"/>
+    </row>
+    <row r="107" s="40" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A107" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="B107" s="48"/>
+      <c r="C107" s="53" t="s">
         <v>328</v>
       </c>
-      <c r="G106" s="23"/>
-      <c r="H106" s="51"/>
-      <c r="I106" s="66"/>
-      <c r="J106" s="66"/>
-    </row>
-    <row r="107" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A107" s="67" t="s">
-        <v>329</v>
-      </c>
-      <c r="B107" s="51"/>
-      <c r="C107" s="64" t="s">
-        <v>315</v>
-      </c>
-      <c r="D107" s="51"/>
-      <c r="E107" s="62"/>
-      <c r="F107" s="62" t="s">
-        <v>330</v>
+      <c r="D107" s="48"/>
+      <c r="E107" s="58"/>
+      <c r="F107" s="58" t="s">
+        <v>343</v>
       </c>
       <c r="G107" s="23"/>
-      <c r="H107" s="51"/>
-      <c r="I107" s="66"/>
-      <c r="J107" s="66"/>
-    </row>
-    <row r="108" ht="25" customHeight="1" spans="1:10">
-      <c r="A108" s="63" t="s">
-        <v>331</v>
+      <c r="H107" s="48"/>
+      <c r="I107" s="60"/>
+      <c r="J107" s="60"/>
+    </row>
+    <row r="108" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A108" s="52" t="s">
+        <v>344</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="D108" s="7"/>
       <c r="E108" s="22"/>
       <c r="F108" s="22" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="G108" s="23"/>
       <c r="H108" s="7"/>
       <c r="I108" s="24"/>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" ht="25" customHeight="1" spans="1:10">
-      <c r="A109" s="63"/>
+    <row r="109" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A109" s="52" t="s">
+        <v>347</v>
+      </c>
       <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
+      <c r="C109" s="7" t="s">
+        <v>345</v>
+      </c>
       <c r="D109" s="7"/>
       <c r="E109" s="22"/>
-      <c r="F109" s="22"/>
+      <c r="F109" s="22" t="s">
+        <v>284</v>
+      </c>
       <c r="G109" s="23"/>
       <c r="H109" s="7"/>
       <c r="I109" s="24"/>
       <c r="J109" s="24"/>
     </row>
+    <row r="110" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A110" s="52" t="s">
+        <v>348</v>
+      </c>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D110" s="7"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="G110" s="23"/>
+      <c r="H110" s="7"/>
+      <c r="I110" s="24"/>
+      <c r="J110" s="24"/>
+    </row>
+    <row r="111" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A111" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="D111" s="7"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="G111" s="23"/>
+      <c r="H111" s="7"/>
+      <c r="I111" s="24"/>
+      <c r="J111" s="24"/>
+    </row>
+    <row r="112" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A112" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D112" s="7"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="G112" s="23"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="24"/>
+      <c r="J112" s="24"/>
+    </row>
+    <row r="113" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A113" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D113" s="7"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="G113" s="23"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="24"/>
+      <c r="J113" s="24"/>
+    </row>
+    <row r="114" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A114" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="B114" s="7"/>
+      <c r="C114" s="53" t="s">
+        <v>307</v>
+      </c>
+      <c r="D114" s="7"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="G114" s="23"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="24"/>
+      <c r="J114" s="24"/>
+    </row>
+    <row r="115" ht="25" customHeight="1" spans="1:10">
+      <c r="A115" s="21"/>
+      <c r="B115" s="7"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="23"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+    </row>
+    <row r="116" ht="25" customHeight="1" spans="1:10">
+      <c r="A116" s="21"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="22"/>
+      <c r="G116" s="23"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="24"/>
+      <c r="J116" s="24"/>
+    </row>
+    <row r="117" ht="25" customHeight="1" spans="1:10">
+      <c r="A117" s="21"/>
+      <c r="B117" s="7"/>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="23"/>
+      <c r="H117" s="7"/>
+      <c r="I117" s="24"/>
+      <c r="J117" s="24"/>
+    </row>
+    <row r="118" ht="25" customHeight="1" spans="1:10">
+      <c r="A118" s="21"/>
+      <c r="B118" s="7"/>
+      <c r="C118" s="7"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="22"/>
+      <c r="F118" s="22"/>
+      <c r="G118" s="23"/>
+      <c r="H118" s="7"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="24"/>
+    </row>
+    <row r="119" ht="25" customHeight="1" spans="1:10">
+      <c r="A119" s="21"/>
+      <c r="B119" s="7"/>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="22"/>
+      <c r="F119" s="22"/>
+      <c r="G119" s="23"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="24"/>
+      <c r="J119" s="24"/>
+    </row>
+    <row r="120" ht="25" customHeight="1" spans="1:10">
+      <c r="A120" s="21"/>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="22"/>
+      <c r="F120" s="22"/>
+      <c r="G120" s="23"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="24"/>
+      <c r="J120" s="24"/>
+    </row>
+    <row r="121" ht="25" customHeight="1" spans="1:10">
+      <c r="A121" s="21"/>
+      <c r="B121" s="7"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="22"/>
+      <c r="F121" s="22"/>
+      <c r="G121" s="23"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="24"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J108" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J114" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <colorFilter dxfId="0"/>
       <extLst>
@@ -6265,7 +6542,10 @@
         </dxfs>
       </extLst>
     </filterColumn>
-    <sortState ref="A1:J108">
+    <filterColumn colId="4">
+      <colorFilter dxfId="1"/>
+    </filterColumn>
+    <sortState ref="A1:J114">
       <sortCondition ref="F1:F87"/>
     </sortState>
     <extLst/>
@@ -6297,7 +6577,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6306,22 +6586,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6335,22 +6615,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6364,22 +6644,22 @@
         <v>11</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6393,22 +6673,22 @@
         <v>11</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6422,22 +6702,22 @@
         <v>11</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6451,22 +6731,22 @@
         <v>11</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6480,22 +6760,22 @@
         <v>138</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6503,28 +6783,28 @@
         <v>8</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6538,22 +6818,22 @@
         <v>157</v>
       </c>
       <c r="D9" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="F9" s="39" t="s">
         <v>369</v>
       </c>
-      <c r="E9" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>345</v>
-      </c>
       <c r="G9" s="39" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6567,22 +6847,22 @@
         <v>157</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -6596,22 +6876,22 @@
         <v>138</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -6625,22 +6905,22 @@
         <v>138</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -6648,28 +6928,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -6683,22 +6963,22 @@
         <v>145</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -6706,28 +6986,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -6735,28 +7015,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -6764,28 +7044,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -6793,28 +7073,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -6822,28 +7102,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -6851,28 +7131,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -6880,28 +7160,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -6909,28 +7189,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -6938,28 +7218,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -6976,7 +7256,7 @@
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -7056,13 +7336,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -7077,28 +7357,28 @@
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>14</v>
@@ -7107,28 +7387,28 @@
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>14</v>
@@ -7137,22 +7417,22 @@
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
@@ -7167,28 +7447,28 @@
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>14</v>
@@ -7197,28 +7477,28 @@
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>14</v>
@@ -7227,28 +7507,28 @@
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>14</v>
@@ -7257,28 +7537,28 @@
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>14</v>
@@ -7287,28 +7567,28 @@
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>14</v>
@@ -7317,28 +7597,28 @@
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>14</v>
@@ -7347,28 +7627,28 @@
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>459</v>
+        <v>483</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>14</v>
@@ -7377,28 +7657,28 @@
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>14</v>
@@ -7407,28 +7687,28 @@
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>14</v>
@@ -7437,28 +7717,28 @@
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>14</v>
@@ -7467,22 +7747,22 @@
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
@@ -7497,16 +7777,16 @@
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7518,13 +7798,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7536,13 +7816,13 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7554,13 +7834,13 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>487</v>
+        <v>511</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7571,13 +7851,13 @@
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -7589,13 +7869,13 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7606,13 +7886,13 @@
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>492</v>
+        <v>516</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7624,13 +7904,13 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7642,13 +7922,13 @@
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>497</v>
+        <v>521</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7659,13 +7939,13 @@
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7677,13 +7957,13 @@
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>501</v>
+        <v>525</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7695,16 +7975,16 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -7715,16 +7995,16 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -7735,16 +8015,16 @@
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -7755,16 +8035,16 @@
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -7775,16 +8055,16 @@
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -7795,7 +8075,7 @@
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -7813,13 +8093,13 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
@@ -7832,18 +8112,18 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -7857,7 +8137,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -7871,7 +8151,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -7885,7 +8165,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -7899,7 +8179,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -7912,7 +8192,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>517</v>
+        <v>541</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -7926,7 +8206,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -7939,7 +8219,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -7952,7 +8232,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -7965,17 +8245,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>521</v>
+        <v>545</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>159</v>
@@ -7984,24 +8264,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>159</v>
@@ -8010,24 +8290,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>526</v>
+        <v>550</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>159</v>
@@ -8036,24 +8316,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>159</v>
@@ -8062,17 +8342,17 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>535</v>
+        <v>559</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>536</v>
+        <v>560</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
     <sheet name="已删" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">在播剧更新时间表!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已删!$A$1:$J$48</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="566">
   <si>
     <t>剧名</t>
   </si>
@@ -1581,6 +1581,21 @@
   </si>
   <si>
     <t>71</t>
+  </si>
+  <si>
+    <t>数到三</t>
+  </si>
+  <si>
+    <t>一颗心脏，竟藏了三个人的秘密</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>蜕变之后</t>
+  </si>
+  <si>
+    <t>94</t>
   </si>
   <si>
     <t>序号</t>
@@ -2504,23 +2519,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2535,6 +2544,12 @@
       <b/>
       <sz val="19.5"/>
       <color rgb="FF494949"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
       <name val="Helvetica"/>
       <charset val="134"/>
     </font>
@@ -3075,7 +3090,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3221,34 +3236,28 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3309,20 +3318,12 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3519,25 +3520,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="totalRow" dxfId="6"/>
-      <tableStyleElement type="firstColumn" dxfId="5"/>
-      <tableStyleElement type="lastColumn" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
-      <tableStyleElement type="pageFieldValues" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3811,7 +3812,7 @@
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
     <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.625" style="35" customWidth="1"/>
     <col min="6" max="6" width="10.625" style="1" customWidth="1"/>
@@ -3854,7 +3855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="21" hidden="1" customHeight="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
       <c r="A2" s="25" t="s">
         <v>10</v>
       </c>
@@ -3886,7 +3887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="3" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="21" t="s">
         <v>18</v>
       </c>
@@ -3918,7 +3919,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="4" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="21" t="s">
         <v>23</v>
       </c>
@@ -3950,7 +3951,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="5" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="21" t="s">
         <v>28</v>
       </c>
@@ -3982,7 +3983,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="6" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="21" t="s">
         <v>33</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="7" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="43" t="s">
         <v>38</v>
       </c>
@@ -4046,7 +4047,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="8" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="21" t="s">
         <v>42</v>
       </c>
@@ -4078,7 +4079,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="9" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="25" t="s">
         <v>47</v>
       </c>
@@ -4110,7 +4111,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="10" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="21" t="s">
         <v>52</v>
       </c>
@@ -4142,7 +4143,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="11" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="21" t="s">
         <v>57</v>
       </c>
@@ -4174,7 +4175,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="12" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="21" t="s">
         <v>62</v>
       </c>
@@ -4206,7 +4207,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="13" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="25" t="s">
         <v>67</v>
       </c>
@@ -4236,7 +4237,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="14" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="25" t="s">
         <v>73</v>
       </c>
@@ -4266,7 +4267,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="15" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="25" t="s">
         <v>78</v>
       </c>
@@ -4296,7 +4297,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="16" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="21" t="s">
         <v>83</v>
       </c>
@@ -4324,7 +4325,7 @@
       </c>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="17" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="21" t="s">
         <v>87</v>
       </c>
@@ -4352,7 +4353,7 @@
       </c>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="18" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="21" t="s">
         <v>91</v>
       </c>
@@ -4382,7 +4383,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="19" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="21" t="s">
         <v>96</v>
       </c>
@@ -4412,7 +4413,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="20" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="25" t="s">
         <v>101</v>
       </c>
@@ -4444,7 +4445,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="21" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="25" t="s">
         <v>106</v>
       </c>
@@ -4476,7 +4477,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="22" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="25" t="s">
         <v>111</v>
       </c>
@@ -4508,7 +4509,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="23" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="25" t="s">
         <v>116</v>
       </c>
@@ -4540,7 +4541,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="21" t="s">
         <v>121</v>
       </c>
@@ -4570,7 +4571,7 @@
       </c>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="21" t="s">
         <v>125</v>
       </c>
@@ -4600,7 +4601,7 @@
       </c>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="26" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="21" t="s">
         <v>128</v>
       </c>
@@ -4630,7 +4631,7 @@
       </c>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="27" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="21" t="s">
         <v>133</v>
       </c>
@@ -4660,7 +4661,7 @@
       </c>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="28" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="25" t="s">
         <v>137</v>
       </c>
@@ -4692,7 +4693,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="25" t="s">
         <v>144</v>
       </c>
@@ -4724,7 +4725,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="30" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="21" t="s">
         <v>151</v>
       </c>
@@ -4750,7 +4751,7 @@
       </c>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="31" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="25" t="s">
         <v>156</v>
       </c>
@@ -4782,7 +4783,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="32" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="25" t="s">
         <v>163</v>
       </c>
@@ -4814,7 +4815,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="33" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A33" s="25" t="s">
         <v>168</v>
       </c>
@@ -4859,7 +4860,7 @@
       <c r="D34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="E34" s="22" t="s">
         <v>175</v>
       </c>
       <c r="F34" s="23" t="s">
@@ -4891,7 +4892,7 @@
       <c r="D35" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="49" t="s">
+      <c r="E35" s="22" t="s">
         <v>181</v>
       </c>
       <c r="F35" s="23" t="s">
@@ -4903,14 +4904,14 @@
       <c r="H35" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="50" t="s">
+      <c r="I35" s="49" t="s">
         <v>183</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="36" s="6" customFormat="1" ht="34" hidden="1" customHeight="1" spans="1:10">
+    <row r="36" s="6" customFormat="1" ht="34" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
         <v>185</v>
       </c>
@@ -4936,7 +4937,7 @@
         <v>187</v>
       </c>
       <c r="I36" s="24"/>
-      <c r="J36" s="51" t="s">
+      <c r="J36" s="50" t="s">
         <v>188</v>
       </c>
     </row>
@@ -4953,7 +4954,7 @@
       <c r="D37" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="49" t="s">
+      <c r="E37" s="22" t="s">
         <v>190</v>
       </c>
       <c r="F37" s="23" t="s">
@@ -4970,7 +4971,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="38" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A38" s="6" t="s">
         <v>193</v>
       </c>
@@ -5011,7 +5012,7 @@
       <c r="D39" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="49" t="s">
+      <c r="E39" s="22" t="s">
         <v>197</v>
       </c>
       <c r="F39" s="23" t="s">
@@ -5029,62 +5030,62 @@
       </c>
     </row>
     <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A40" s="52" t="s">
+      <c r="A40" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C40" s="54" t="s">
+      <c r="C40" s="48" t="s">
         <v>201</v>
       </c>
-      <c r="D40" s="55" t="s">
+      <c r="D40" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="49" t="s">
+      <c r="E40" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="F40" s="55" t="s">
+      <c r="F40" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G40" s="55">
+      <c r="G40" s="23">
         <v>2026</v>
       </c>
-      <c r="H40" s="56" t="s">
+      <c r="H40" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="I40" s="57"/>
-      <c r="J40" s="53" t="s">
+      <c r="I40" s="24"/>
+      <c r="J40" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="41" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A41" s="52" t="s">
+      <c r="A41" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="B41" s="53" t="s">
+      <c r="B41" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C41" s="54" t="s">
+      <c r="C41" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="55" t="s">
+      <c r="D41" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E41" s="49" t="s">
+      <c r="E41" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="F41" s="55" t="s">
+      <c r="F41" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G41" s="53"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57" t="s">
+      <c r="G41" s="7"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="42" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="42" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A42" s="21"/>
       <c r="B42" s="7"/>
       <c r="C42" s="48"/>
@@ -5098,7 +5099,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="43" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="43" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A43" s="21"/>
       <c r="B43" s="7"/>
       <c r="C43" s="48"/>
@@ -5112,7 +5113,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="44" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A44" s="21"/>
       <c r="B44" s="7"/>
       <c r="C44" s="48"/>
@@ -5126,7 +5127,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="45" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="45" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A45" s="21"/>
       <c r="B45" s="7"/>
       <c r="C45" s="48"/>
@@ -5138,7 +5139,7 @@
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="46" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A46" s="21"/>
       <c r="B46" s="7"/>
       <c r="C46" s="48"/>
@@ -5150,7 +5151,7 @@
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="47" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A47" s="21"/>
       <c r="B47" s="7"/>
       <c r="C47" s="48"/>
@@ -5162,7 +5163,7 @@
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="48" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A48" s="21"/>
       <c r="B48" s="7"/>
       <c r="C48" s="48"/>
@@ -5174,7 +5175,7 @@
       <c r="I48" s="24"/>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="49" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A49" s="25" t="s">
         <v>211</v>
       </c>
@@ -5204,7 +5205,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="50" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A50" s="25" t="s">
         <v>215</v>
       </c>
@@ -5226,7 +5227,7 @@
       <c r="G50" s="23">
         <v>2026</v>
       </c>
-      <c r="H50" s="50"/>
+      <c r="H50" s="49"/>
       <c r="I50" s="46" t="s">
         <v>217</v>
       </c>
@@ -5234,7 +5235,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A51" s="25" t="s">
         <v>219</v>
       </c>
@@ -5254,7 +5255,7 @@
       <c r="G51" s="23">
         <v>2026</v>
       </c>
-      <c r="H51" s="50"/>
+      <c r="H51" s="49"/>
       <c r="I51" s="46" t="s">
         <v>220</v>
       </c>
@@ -5262,7 +5263,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A52" s="25" t="s">
         <v>222</v>
       </c>
@@ -5282,7 +5283,7 @@
       <c r="G52" s="23">
         <v>2026</v>
       </c>
-      <c r="H52" s="50"/>
+      <c r="H52" s="49"/>
       <c r="I52" s="46" t="s">
         <v>223</v>
       </c>
@@ -5290,7 +5291,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="53" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A53" s="21" t="s">
         <v>225</v>
       </c>
@@ -5303,7 +5304,7 @@
       <c r="D53" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="58"/>
+      <c r="E53" s="52"/>
       <c r="F53" s="48" t="s">
         <v>14</v>
       </c>
@@ -5316,7 +5317,7 @@
       </c>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="54" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A54" s="21" t="s">
         <v>228</v>
       </c>
@@ -5329,7 +5330,7 @@
       <c r="D54" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="58"/>
+      <c r="E54" s="52"/>
       <c r="F54" s="48" t="s">
         <v>14</v>
       </c>
@@ -5342,7 +5343,7 @@
       </c>
       <c r="J54" s="7"/>
     </row>
-    <row r="55" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="55" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A55" s="21" t="s">
         <v>230</v>
       </c>
@@ -5364,7 +5365,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="56" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A56" s="21" t="s">
         <v>234</v>
       </c>
@@ -5386,7 +5387,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
         <v>237</v>
       </c>
@@ -5408,7 +5409,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
         <v>240</v>
       </c>
@@ -5428,7 +5429,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A59" s="25" t="s">
         <v>242</v>
       </c>
@@ -5458,7 +5459,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="60" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="60" ht="25" customHeight="1" spans="1:10">
       <c r="A60" s="21" t="s">
         <v>248</v>
       </c>
@@ -5482,7 +5483,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="61" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="61" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A61" s="21" t="s">
         <v>251</v>
       </c>
@@ -5508,7 +5509,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="62" ht="24" hidden="1" customHeight="1" spans="1:10">
+    <row r="62" ht="24" customHeight="1" spans="1:10">
       <c r="A62" s="21" t="s">
         <v>255</v>
       </c>
@@ -5536,7 +5537,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="63" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="63" ht="25" customHeight="1" spans="1:10">
       <c r="A63" s="21" t="s">
         <v>260</v>
       </c>
@@ -5564,7 +5565,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="64" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="64" ht="25" customHeight="1" spans="1:10">
       <c r="A64" s="21"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -5576,14 +5577,14 @@
       <c r="I64" s="24"/>
       <c r="J64" s="24"/>
     </row>
-    <row r="65" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A65" s="52" t="s">
+    <row r="65" ht="25" customHeight="1" spans="1:10">
+      <c r="A65" s="53" t="s">
         <v>265</v>
       </c>
-      <c r="B65" s="53" t="s">
+      <c r="B65" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="53" t="s">
+      <c r="C65" s="54" t="s">
         <v>164</v>
       </c>
       <c r="D65" s="7"/>
@@ -5600,8 +5601,8 @@
       <c r="I65" s="24"/>
       <c r="J65" s="21"/>
     </row>
-    <row r="66" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A66" s="52" t="s">
+    <row r="66" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A66" s="53" t="s">
         <v>267</v>
       </c>
       <c r="B66" s="7" t="s">
@@ -5620,8 +5621,8 @@
       <c r="I66" s="24"/>
       <c r="J66" s="21"/>
     </row>
-    <row r="67" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A67" s="52" t="s">
+    <row r="67" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A67" s="53" t="s">
         <v>269</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -5640,8 +5641,8 @@
       <c r="I67" s="24"/>
       <c r="J67" s="21"/>
     </row>
-    <row r="68" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A68" s="52" t="s">
+    <row r="68" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A68" s="53" t="s">
         <v>270</v>
       </c>
       <c r="B68" s="7" t="s">
@@ -5658,8 +5659,8 @@
       <c r="I68" s="24"/>
       <c r="J68" s="21"/>
     </row>
-    <row r="69" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A69" s="52" t="s">
+    <row r="69" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A69" s="53" t="s">
         <v>271</v>
       </c>
       <c r="B69" s="7" t="s">
@@ -5678,8 +5679,8 @@
       <c r="I69" s="24"/>
       <c r="J69" s="21"/>
     </row>
-    <row r="70" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A70" s="52" t="s">
+    <row r="70" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A70" s="53" t="s">
         <v>272</v>
       </c>
       <c r="B70" s="7" t="s">
@@ -5694,8 +5695,8 @@
       <c r="I70" s="24"/>
       <c r="J70" s="21"/>
     </row>
-    <row r="71" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A71" s="52" t="s">
+    <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A71" s="53" t="s">
         <v>273</v>
       </c>
       <c r="B71" s="7" t="s">
@@ -5712,8 +5713,8 @@
       <c r="I71" s="24"/>
       <c r="J71" s="21"/>
     </row>
-    <row r="72" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A72" s="52" t="s">
+    <row r="72" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A72" s="53" t="s">
         <v>274</v>
       </c>
       <c r="B72" s="7"/>
@@ -5726,8 +5727,8 @@
       <c r="I72" s="24"/>
       <c r="J72" s="21"/>
     </row>
-    <row r="73" s="6" customFormat="1" ht="30" hidden="1" customHeight="1" spans="1:10">
-      <c r="A73" s="52" t="s">
+    <row r="73" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
+      <c r="A73" s="53" t="s">
         <v>275</v>
       </c>
       <c r="B73" s="7"/>
@@ -5740,8 +5741,8 @@
       <c r="I73" s="24"/>
       <c r="J73" s="21"/>
     </row>
-    <row r="74" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A74" s="52" t="s">
+    <row r="74" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A74" s="53" t="s">
         <v>276</v>
       </c>
       <c r="B74" s="7"/>
@@ -5754,8 +5755,8 @@
       <c r="I74" s="24"/>
       <c r="J74" s="21"/>
     </row>
-    <row r="75" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A75" s="52" t="s">
+    <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A75" s="53" t="s">
         <v>277</v>
       </c>
       <c r="B75" s="7"/>
@@ -5768,8 +5769,8 @@
       <c r="I75" s="24"/>
       <c r="J75" s="21"/>
     </row>
-    <row r="76" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A76" s="52" t="s">
+    <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A76" s="53" t="s">
         <v>278</v>
       </c>
       <c r="B76" s="7"/>
@@ -5784,8 +5785,8 @@
       <c r="I76" s="24"/>
       <c r="J76" s="24"/>
     </row>
-    <row r="77" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A77" s="52" t="s">
+    <row r="77" ht="25" customHeight="1" spans="1:10">
+      <c r="A77" s="53" t="s">
         <v>280</v>
       </c>
       <c r="B77" s="7"/>
@@ -5800,7 +5801,7 @@
       <c r="I77" s="24"/>
       <c r="J77" s="24"/>
     </row>
-    <row r="78" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="78" ht="25" customHeight="1" spans="1:10">
       <c r="A78" s="21" t="s">
         <v>255</v>
       </c>
@@ -5816,8 +5817,8 @@
       <c r="I78" s="24"/>
       <c r="J78" s="24"/>
     </row>
-    <row r="79" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A79" s="52" t="s">
+    <row r="79" ht="25" customHeight="1" spans="1:10">
+      <c r="A79" s="53" t="s">
         <v>283</v>
       </c>
       <c r="B79" s="7"/>
@@ -5832,8 +5833,8 @@
       <c r="I79" s="24"/>
       <c r="J79" s="24"/>
     </row>
-    <row r="80" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A80" s="52" t="s">
+    <row r="80" ht="25" customHeight="1" spans="1:10">
+      <c r="A80" s="53" t="s">
         <v>285</v>
       </c>
       <c r="B80" s="7"/>
@@ -5848,8 +5849,8 @@
       <c r="I80" s="24"/>
       <c r="J80" s="24"/>
     </row>
-    <row r="81" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A81" s="52" t="s">
+    <row r="81" ht="25" customHeight="1" spans="1:10">
+      <c r="A81" s="53" t="s">
         <v>286</v>
       </c>
       <c r="B81" s="7"/>
@@ -5864,8 +5865,8 @@
       <c r="I81" s="24"/>
       <c r="J81" s="24"/>
     </row>
-    <row r="82" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A82" s="52" t="s">
+    <row r="82" ht="25" customHeight="1" spans="1:10">
+      <c r="A82" s="53" t="s">
         <v>287</v>
       </c>
       <c r="B82" s="7"/>
@@ -5880,8 +5881,8 @@
       <c r="I82" s="24"/>
       <c r="J82" s="24"/>
     </row>
-    <row r="83" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A83" s="52" t="s">
+    <row r="83" ht="25" customHeight="1" spans="1:10">
+      <c r="A83" s="53" t="s">
         <v>288</v>
       </c>
       <c r="B83" s="7"/>
@@ -5894,8 +5895,8 @@
       <c r="I83" s="24"/>
       <c r="J83" s="24"/>
     </row>
-    <row r="84" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A84" s="52" t="s">
+    <row r="84" ht="25" customHeight="1" spans="1:10">
+      <c r="A84" s="53" t="s">
         <v>289</v>
       </c>
       <c r="B84" s="7"/>
@@ -5910,8 +5911,8 @@
       <c r="I84" s="24"/>
       <c r="J84" s="24"/>
     </row>
-    <row r="85" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A85" s="52" t="s">
+    <row r="85" ht="25" customHeight="1" spans="1:10">
+      <c r="A85" s="53" t="s">
         <v>291</v>
       </c>
       <c r="B85" s="7"/>
@@ -5924,8 +5925,8 @@
       <c r="I85" s="24"/>
       <c r="J85" s="24"/>
     </row>
-    <row r="86" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A86" s="52" t="s">
+    <row r="86" ht="25" customHeight="1" spans="1:10">
+      <c r="A86" s="53" t="s">
         <v>292</v>
       </c>
       <c r="B86" s="7"/>
@@ -5938,8 +5939,8 @@
       <c r="I86" s="24"/>
       <c r="J86" s="24"/>
     </row>
-    <row r="87" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A87" s="52" t="s">
+    <row r="87" ht="25" customHeight="1" spans="1:10">
+      <c r="A87" s="53" t="s">
         <v>293</v>
       </c>
       <c r="B87" s="7"/>
@@ -5954,8 +5955,8 @@
       <c r="I87" s="24"/>
       <c r="J87" s="24"/>
     </row>
-    <row r="88" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A88" s="52" t="s">
+    <row r="88" ht="25" customHeight="1" spans="1:10">
+      <c r="A88" s="53" t="s">
         <v>295</v>
       </c>
       <c r="B88" s="7"/>
@@ -5970,8 +5971,8 @@
       <c r="I88" s="24"/>
       <c r="J88" s="24"/>
     </row>
-    <row r="89" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A89" s="52" t="s">
+    <row r="89" ht="25" customHeight="1" spans="1:10">
+      <c r="A89" s="53" t="s">
         <v>297</v>
       </c>
       <c r="B89" s="7"/>
@@ -5988,8 +5989,8 @@
       <c r="I89" s="24"/>
       <c r="J89" s="24"/>
     </row>
-    <row r="90" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A90" s="52" t="s">
+    <row r="90" ht="25" customHeight="1" spans="1:10">
+      <c r="A90" s="53" t="s">
         <v>300</v>
       </c>
       <c r="B90" s="7"/>
@@ -6006,8 +6007,8 @@
       <c r="I90" s="24"/>
       <c r="J90" s="24"/>
     </row>
-    <row r="91" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A91" s="52" t="s">
+    <row r="91" ht="25" customHeight="1" spans="1:10">
+      <c r="A91" s="53" t="s">
         <v>303</v>
       </c>
       <c r="B91" s="7"/>
@@ -6024,8 +6025,8 @@
       <c r="I91" s="24"/>
       <c r="J91" s="24"/>
     </row>
-    <row r="92" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A92" s="52" t="s">
+    <row r="92" ht="25" customHeight="1" spans="1:10">
+      <c r="A92" s="53" t="s">
         <v>306</v>
       </c>
       <c r="B92" s="7"/>
@@ -6042,8 +6043,8 @@
       <c r="I92" s="24"/>
       <c r="J92" s="24"/>
     </row>
-    <row r="93" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A93" s="52" t="s">
+    <row r="93" ht="25" customHeight="1" spans="1:10">
+      <c r="A93" s="53" t="s">
         <v>308</v>
       </c>
       <c r="B93" s="7"/>
@@ -6060,8 +6061,8 @@
       <c r="I93" s="24"/>
       <c r="J93" s="24"/>
     </row>
-    <row r="94" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A94" s="52" t="s">
+    <row r="94" ht="25" customHeight="1" spans="1:10">
+      <c r="A94" s="53" t="s">
         <v>311</v>
       </c>
       <c r="B94" s="7"/>
@@ -6078,8 +6079,8 @@
       <c r="I94" s="24"/>
       <c r="J94" s="24"/>
     </row>
-    <row r="95" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A95" s="52" t="s">
+    <row r="95" ht="25" customHeight="1" spans="1:10">
+      <c r="A95" s="53" t="s">
         <v>314</v>
       </c>
       <c r="B95" s="7"/>
@@ -6096,8 +6097,8 @@
       <c r="I95" s="24"/>
       <c r="J95" s="24"/>
     </row>
-    <row r="96" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A96" s="52" t="s">
+    <row r="96" ht="25" customHeight="1" spans="1:10">
+      <c r="A96" s="53" t="s">
         <v>317</v>
       </c>
       <c r="B96" s="7"/>
@@ -6114,8 +6115,8 @@
       <c r="I96" s="24"/>
       <c r="J96" s="24"/>
     </row>
-    <row r="97" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A97" s="52" t="s">
+    <row r="97" ht="25" customHeight="1" spans="1:10">
+      <c r="A97" s="53" t="s">
         <v>319</v>
       </c>
       <c r="B97" s="7"/>
@@ -6132,8 +6133,8 @@
       <c r="I97" s="24"/>
       <c r="J97" s="24"/>
     </row>
-    <row r="98" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A98" s="52" t="s">
+    <row r="98" ht="25" customHeight="1" spans="1:10">
+      <c r="A98" s="53" t="s">
         <v>322</v>
       </c>
       <c r="B98" s="7"/>
@@ -6150,8 +6151,8 @@
       <c r="I98" s="24"/>
       <c r="J98" s="24"/>
     </row>
-    <row r="99" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A99" s="52" t="s">
+    <row r="99" ht="25" customHeight="1" spans="1:10">
+      <c r="A99" s="53" t="s">
         <v>324</v>
       </c>
       <c r="B99" s="7"/>
@@ -6168,69 +6169,69 @@
       <c r="I99" s="24"/>
       <c r="J99" s="24"/>
     </row>
-    <row r="100" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A100" s="52" t="s">
+    <row r="100" ht="25" customHeight="1" spans="1:10">
+      <c r="A100" s="53" t="s">
         <v>327</v>
       </c>
-      <c r="B100" s="53"/>
-      <c r="C100" s="53" t="s">
+      <c r="B100" s="54"/>
+      <c r="C100" s="54" t="s">
         <v>328</v>
       </c>
-      <c r="D100" s="53"/>
+      <c r="D100" s="54"/>
       <c r="E100" s="22"/>
-      <c r="F100" s="49" t="s">
+      <c r="F100" s="55" t="s">
         <v>296</v>
       </c>
-      <c r="G100" s="55"/>
+      <c r="G100" s="56"/>
       <c r="H100" s="7"/>
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
     </row>
-    <row r="101" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A101" s="52" t="s">
+    <row r="101" ht="25" customHeight="1" spans="1:10">
+      <c r="A101" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="B101" s="53"/>
-      <c r="C101" s="53" t="s">
+      <c r="B101" s="54"/>
+      <c r="C101" s="54" t="s">
         <v>307</v>
       </c>
-      <c r="D101" s="53"/>
+      <c r="D101" s="54"/>
       <c r="E101" s="22"/>
-      <c r="F101" s="49" t="s">
+      <c r="F101" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="G101" s="55"/>
+      <c r="G101" s="56"/>
       <c r="H101" s="7"/>
       <c r="I101" s="24"/>
       <c r="J101" s="24"/>
     </row>
-    <row r="102" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A102" s="52" t="s">
+    <row r="102" ht="25" customHeight="1" spans="1:10">
+      <c r="A102" s="53" t="s">
         <v>331</v>
       </c>
-      <c r="B102" s="53"/>
-      <c r="C102" s="53"/>
-      <c r="D102" s="53"/>
+      <c r="B102" s="54"/>
+      <c r="C102" s="54"/>
+      <c r="D102" s="54"/>
       <c r="E102" s="22"/>
-      <c r="F102" s="49" t="s">
+      <c r="F102" s="55" t="s">
         <v>332</v>
       </c>
-      <c r="G102" s="55"/>
+      <c r="G102" s="56"/>
       <c r="H102" s="7"/>
       <c r="I102" s="24"/>
       <c r="J102" s="24"/>
     </row>
-    <row r="103" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A103" s="52" t="s">
+    <row r="103" ht="25" customHeight="1" spans="1:10">
+      <c r="A103" s="53" t="s">
         <v>333</v>
       </c>
-      <c r="B103" s="53"/>
-      <c r="C103" s="53" t="s">
+      <c r="B103" s="54"/>
+      <c r="C103" s="54" t="s">
         <v>334</v>
       </c>
-      <c r="D103" s="53"/>
+      <c r="D103" s="54"/>
       <c r="E103" s="22"/>
-      <c r="F103" s="49" t="s">
+      <c r="F103" s="55" t="s">
         <v>335</v>
       </c>
       <c r="G103" s="23"/>
@@ -6238,17 +6239,17 @@
       <c r="I103" s="24"/>
       <c r="J103" s="24"/>
     </row>
-    <row r="104" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A104" s="52" t="s">
+    <row r="104" ht="25" customHeight="1" spans="1:10">
+      <c r="A104" s="53" t="s">
         <v>336</v>
       </c>
-      <c r="B104" s="53"/>
-      <c r="C104" s="53" t="s">
+      <c r="B104" s="54"/>
+      <c r="C104" s="54" t="s">
         <v>337</v>
       </c>
-      <c r="D104" s="53"/>
+      <c r="D104" s="54"/>
       <c r="E104" s="22"/>
-      <c r="F104" s="49" t="s">
+      <c r="F104" s="55" t="s">
         <v>338</v>
       </c>
       <c r="G104" s="23"/>
@@ -6256,8 +6257,8 @@
       <c r="I104" s="24"/>
       <c r="J104" s="24"/>
     </row>
-    <row r="105" s="40" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A105" s="59" t="s">
+    <row r="105" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A105" s="57" t="s">
         <v>339</v>
       </c>
       <c r="B105" s="48"/>
@@ -6265,51 +6266,51 @@
         <v>298</v>
       </c>
       <c r="D105" s="48"/>
-      <c r="E105" s="58"/>
-      <c r="F105" s="58" t="s">
+      <c r="E105" s="52"/>
+      <c r="F105" s="52" t="s">
         <v>296</v>
       </c>
       <c r="G105" s="23"/>
       <c r="H105" s="48"/>
-      <c r="I105" s="60"/>
-      <c r="J105" s="60"/>
-    </row>
-    <row r="106" s="40" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A106" s="59" t="s">
+      <c r="I105" s="58"/>
+      <c r="J105" s="58"/>
+    </row>
+    <row r="106" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A106" s="57" t="s">
         <v>340</v>
       </c>
       <c r="B106" s="48"/>
       <c r="C106" s="48"/>
       <c r="D106" s="48"/>
-      <c r="E106" s="58"/>
-      <c r="F106" s="58" t="s">
+      <c r="E106" s="52"/>
+      <c r="F106" s="52" t="s">
         <v>341</v>
       </c>
       <c r="G106" s="23"/>
       <c r="H106" s="48"/>
-      <c r="I106" s="60"/>
-      <c r="J106" s="60"/>
-    </row>
-    <row r="107" s="40" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A107" s="59" t="s">
+      <c r="I106" s="58"/>
+      <c r="J106" s="58"/>
+    </row>
+    <row r="107" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A107" s="57" t="s">
         <v>342</v>
       </c>
       <c r="B107" s="48"/>
-      <c r="C107" s="53" t="s">
+      <c r="C107" s="54" t="s">
         <v>328</v>
       </c>
       <c r="D107" s="48"/>
-      <c r="E107" s="58"/>
-      <c r="F107" s="58" t="s">
+      <c r="E107" s="52"/>
+      <c r="F107" s="52" t="s">
         <v>343</v>
       </c>
       <c r="G107" s="23"/>
       <c r="H107" s="48"/>
-      <c r="I107" s="60"/>
-      <c r="J107" s="60"/>
-    </row>
-    <row r="108" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A108" s="52" t="s">
+      <c r="I107" s="58"/>
+      <c r="J107" s="58"/>
+    </row>
+    <row r="108" ht="25" customHeight="1" spans="1:10">
+      <c r="A108" s="53" t="s">
         <v>344</v>
       </c>
       <c r="B108" s="7"/>
@@ -6326,8 +6327,8 @@
       <c r="I108" s="24"/>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A109" s="52" t="s">
+    <row r="109" ht="25" customHeight="1" spans="1:10">
+      <c r="A109" s="53" t="s">
         <v>347</v>
       </c>
       <c r="B109" s="7"/>
@@ -6344,8 +6345,8 @@
       <c r="I109" s="24"/>
       <c r="J109" s="24"/>
     </row>
-    <row r="110" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A110" s="52" t="s">
+    <row r="110" ht="25" customHeight="1" spans="1:10">
+      <c r="A110" s="53" t="s">
         <v>348</v>
       </c>
       <c r="B110" s="7"/>
@@ -6362,17 +6363,17 @@
       <c r="I110" s="24"/>
       <c r="J110" s="24"/>
     </row>
-    <row r="111" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A111" s="21" t="s">
+    <row r="111" ht="25" customHeight="1" spans="1:10">
+      <c r="A111" s="53" t="s">
         <v>349</v>
       </c>
-      <c r="B111" s="7"/>
-      <c r="C111" s="7" t="s">
+      <c r="B111" s="54"/>
+      <c r="C111" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="D111" s="7"/>
-      <c r="E111" s="22"/>
-      <c r="F111" s="22" t="s">
+      <c r="D111" s="54"/>
+      <c r="E111" s="55"/>
+      <c r="F111" s="55" t="s">
         <v>350</v>
       </c>
       <c r="G111" s="23"/>
@@ -6380,17 +6381,17 @@
       <c r="I111" s="24"/>
       <c r="J111" s="24"/>
     </row>
-    <row r="112" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A112" s="21" t="s">
+    <row r="112" ht="25" customHeight="1" spans="1:10">
+      <c r="A112" s="53" t="s">
         <v>351</v>
       </c>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7" t="s">
+      <c r="B112" s="54"/>
+      <c r="C112" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="D112" s="7"/>
-      <c r="E112" s="22"/>
-      <c r="F112" s="22" t="s">
+      <c r="D112" s="54"/>
+      <c r="E112" s="55"/>
+      <c r="F112" s="55" t="s">
         <v>343</v>
       </c>
       <c r="G112" s="23"/>
@@ -6398,17 +6399,17 @@
       <c r="I112" s="24"/>
       <c r="J112" s="24"/>
     </row>
-    <row r="113" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A113" s="21" t="s">
+    <row r="113" ht="25" customHeight="1" spans="1:10">
+      <c r="A113" s="53" t="s">
         <v>353</v>
       </c>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7" t="s">
+      <c r="B113" s="54"/>
+      <c r="C113" s="54" t="s">
         <v>354</v>
       </c>
-      <c r="D113" s="7"/>
-      <c r="E113" s="22"/>
-      <c r="F113" s="22" t="s">
+      <c r="D113" s="54"/>
+      <c r="E113" s="55"/>
+      <c r="F113" s="55" t="s">
         <v>355</v>
       </c>
       <c r="G113" s="23"/>
@@ -6416,17 +6417,17 @@
       <c r="I113" s="24"/>
       <c r="J113" s="24"/>
     </row>
-    <row r="114" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A114" s="21" t="s">
+    <row r="114" ht="25" customHeight="1" spans="1:10">
+      <c r="A114" s="53" t="s">
         <v>356</v>
       </c>
-      <c r="B114" s="7"/>
-      <c r="C114" s="53" t="s">
+      <c r="B114" s="54"/>
+      <c r="C114" s="54" t="s">
         <v>307</v>
       </c>
-      <c r="D114" s="7"/>
-      <c r="E114" s="22"/>
-      <c r="F114" s="22" t="s">
+      <c r="D114" s="54"/>
+      <c r="E114" s="55"/>
+      <c r="F114" s="55" t="s">
         <v>357</v>
       </c>
       <c r="G114" s="23"/>
@@ -6435,24 +6436,37 @@
       <c r="J114" s="24"/>
     </row>
     <row r="115" ht="25" customHeight="1" spans="1:10">
-      <c r="A115" s="21"/>
+      <c r="A115" s="21" t="s">
+        <v>358</v>
+      </c>
       <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
+      <c r="C115" s="7" t="s">
+        <v>359</v>
+      </c>
       <c r="D115" s="7"/>
       <c r="E115" s="22"/>
-      <c r="F115" s="22"/>
+      <c r="F115" s="22" t="s">
+        <v>360</v>
+      </c>
       <c r="G115" s="23"/>
       <c r="H115" s="7"/>
       <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
+      <c r="J115" s="24">
+        <f>2100*60</f>
+        <v>126000</v>
+      </c>
     </row>
     <row r="116" ht="25" customHeight="1" spans="1:10">
-      <c r="A116" s="21"/>
+      <c r="A116" s="21" t="s">
+        <v>361</v>
+      </c>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
       <c r="E116" s="22"/>
-      <c r="F116" s="22"/>
+      <c r="F116" s="22" t="s">
+        <v>362</v>
+      </c>
       <c r="G116" s="23"/>
       <c r="H116" s="7"/>
       <c r="I116" s="24"/>
@@ -6519,7 +6533,7 @@
       <c r="J121" s="24"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J114" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J115" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <colorFilter dxfId="0"/>
       <extLst>
@@ -6542,10 +6556,7 @@
         </dxfs>
       </extLst>
     </filterColumn>
-    <filterColumn colId="4">
-      <colorFilter dxfId="1"/>
-    </filterColumn>
-    <sortState ref="A1:J114">
+    <sortState ref="A1:J115">
       <sortCondition ref="F1:F87"/>
     </sortState>
     <extLst/>
@@ -6577,7 +6588,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6586,22 +6597,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6615,22 +6626,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6644,22 +6655,22 @@
         <v>11</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G3" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="H3" s="39" t="s">
         <v>374</v>
       </c>
-      <c r="H3" s="39" t="s">
-        <v>369</v>
-      </c>
       <c r="I3" s="39" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6673,22 +6684,22 @@
         <v>11</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6702,22 +6713,22 @@
         <v>11</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6731,22 +6742,22 @@
         <v>11</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6760,22 +6771,22 @@
         <v>138</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6789,22 +6800,22 @@
         <v>138</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6818,22 +6829,22 @@
         <v>157</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6847,22 +6858,22 @@
         <v>157</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -6876,22 +6887,22 @@
         <v>138</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -6905,22 +6916,22 @@
         <v>138</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -6928,28 +6939,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -6963,22 +6974,22 @@
         <v>145</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -6992,22 +7003,22 @@
         <v>157</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -7021,22 +7032,22 @@
         <v>157</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -7050,22 +7061,22 @@
         <v>157</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -7079,22 +7090,22 @@
         <v>157</v>
       </c>
       <c r="D18" s="39" t="s">
+        <v>423</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>422</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>422</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>422</v>
+      </c>
+      <c r="I18" s="39" t="s">
         <v>418</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>417</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>417</v>
-      </c>
-      <c r="H18" s="39" t="s">
-        <v>417</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -7102,28 +7113,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>243</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -7137,22 +7148,22 @@
         <v>243</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -7160,28 +7171,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>243</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -7189,28 +7200,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>243</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -7218,28 +7229,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>243</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -7256,7 +7267,7 @@
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -7336,13 +7347,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -7357,28 +7368,28 @@
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>14</v>
@@ -7387,28 +7398,28 @@
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>14</v>
@@ -7417,22 +7428,22 @@
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
@@ -7447,28 +7458,28 @@
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>14</v>
@@ -7477,28 +7488,28 @@
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>14</v>
@@ -7507,28 +7518,28 @@
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>14</v>
@@ -7537,28 +7548,28 @@
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>14</v>
@@ -7567,28 +7578,28 @@
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>14</v>
@@ -7597,28 +7608,28 @@
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>14</v>
@@ -7627,28 +7638,28 @@
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>14</v>
@@ -7657,28 +7668,28 @@
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>14</v>
@@ -7687,28 +7698,28 @@
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>14</v>
@@ -7717,28 +7728,28 @@
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>14</v>
@@ -7747,22 +7758,22 @@
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
@@ -7777,16 +7788,16 @@
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7798,13 +7809,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7816,13 +7827,13 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7834,13 +7845,13 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7851,13 +7862,13 @@
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -7869,13 +7880,13 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7886,13 +7897,13 @@
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7904,13 +7915,13 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7922,13 +7933,13 @@
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7939,13 +7950,13 @@
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7957,13 +7968,13 @@
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7975,13 +7986,13 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>231</v>
@@ -7995,13 +8006,13 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>231</v>
@@ -8015,13 +8026,13 @@
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>231</v>
@@ -8035,13 +8046,13 @@
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>231</v>
@@ -8055,13 +8066,13 @@
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>231</v>
@@ -8075,7 +8086,7 @@
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -8137,7 +8148,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -8151,7 +8162,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -8165,7 +8176,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -8179,7 +8190,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -8192,7 +8203,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -8206,7 +8217,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -8219,7 +8230,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -8232,7 +8243,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -8245,17 +8256,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>243</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>159</v>
@@ -8264,24 +8275,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>243</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>159</v>
@@ -8290,24 +8301,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>243</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>159</v>
@@ -8316,24 +8327,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>159</v>
@@ -8342,14 +8353,14 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>243</v>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="571">
   <si>
     <t>剧名</t>
   </si>
@@ -903,7 +903,7 @@
     </r>
   </si>
   <si>
-    <t>12/14</t>
+    <t>13/14</t>
   </si>
   <si>
     <r>
@@ -990,7 +990,7 @@
     <t>家庭关系证明书</t>
   </si>
   <si>
-    <t>52</t>
+    <t>53</t>
   </si>
   <si>
     <t xml:space="preserve">朴世荣 / 韩高恩 / 林志恩 / 成伊言 / 朴率拉 </t>
@@ -1008,7 +1008,7 @@
     <t>剧情 / 犯罪</t>
   </si>
   <si>
-    <t>28/100</t>
+    <t>29/100</t>
   </si>
   <si>
     <t xml:space="preserve"> 张瑞希 / 田惠媛 / 薛正焕 / 周清晨 / 尹海英 /</t>
@@ -1048,6 +1048,9 @@
     <t>从犯规开始吧？</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>链接：https://pan.quark.cn/s/9a4c405f64dc?pwd=UvZi 提取码：UvZi</t>
   </si>
   <si>
@@ -1081,22 +1084,16 @@
     <t>链接：https://pan.quark.cn/s/547e99636d86?pwd=daM5  提取码：daM5</t>
   </si>
   <si>
-    <t>寄生之心</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/902364e3ea98?pwd=6375  提取码：6375</t>
-  </si>
-  <si>
-    <t>/~172c3awu68~:/</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/902364e3ea98?pwd=6375</t>
-  </si>
-  <si>
-    <t>提取码：6375</t>
+    <t>乌鸦俱乐部</t>
+  </si>
+  <si>
+    <t>1/16</t>
+  </si>
+  <si>
+    <t>赫马维奇·卡皖纳姆派潘 /塔纳朋·艾恩坤柴</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/0b721e243e8d?pwd=EZFU 提取码：EZFU</t>
   </si>
   <si>
     <t>神的游戏</t>
@@ -1216,24 +1213,6 @@
     <t>链接：https://pan.quark.cn/s/8106b86259d0?pwd=sqNP 提取码：sqNP</t>
   </si>
   <si>
-    <t>深夜怪谈会第6季</t>
-  </si>
-  <si>
-    <t>韩国综艺</t>
-  </si>
-  <si>
-    <t>脱口秀</t>
-  </si>
-  <si>
-    <t>九拉 / 金淑 / 金浩英</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1obVL8_jm_p5acdzaiM3yOA?pwd=ce45 提取码: ce45 </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/3e5d38724fff?pwd=jeHy 提取码：jeHy</t>
-  </si>
-  <si>
     <t>去你的岛</t>
   </si>
   <si>
@@ -1598,6 +1577,24 @@
     <t>94</t>
   </si>
   <si>
+    <t>四重心影</t>
+  </si>
+  <si>
+    <t>催眠解锁童年真相，这场自我博弈，她能与破碎的自己和解吗</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>窃心之人</t>
+  </si>
+  <si>
+    <t>经典家庭惊悚新作</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
     <t>序号</t>
   </si>
   <si>
@@ -1784,12 +1781,18 @@
     <t>我遇见的精神病患者</t>
   </si>
   <si>
+    <t>韩国综艺</t>
+  </si>
+  <si>
     <t>韩国MBN＋SBS Plus</t>
   </si>
   <si>
     <t>7月12日起每周日晚22:20（韩国时间）</t>
   </si>
   <si>
+    <t>深夜怪谈会第6季</t>
+  </si>
+  <si>
     <t>韩国MBC</t>
   </si>
   <si>
@@ -2133,6 +2136,18 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/10adBSzL63iK0CsWUdKtXsQ 提取码: tj5r </t>
+  </si>
+  <si>
+    <t>脱口秀</t>
+  </si>
+  <si>
+    <t>九拉 / 金淑 / 金浩英</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1obVL8_jm_p5acdzaiM3yOA?pwd=ce45 提取码: ce45 </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/3e5d38724fff?pwd=jeHy 提取码：jeHy</t>
   </si>
   <si>
     <t>夏日狂热</t>
@@ -2530,6 +2545,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2544,12 +2565,6 @@
       <b/>
       <sz val="19.5"/>
       <color rgb="FF494949"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
       <name val="Helvetica"/>
       <charset val="134"/>
     </font>
@@ -3090,7 +3105,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3236,8 +3251,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3807,7 +3831,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
@@ -3817,7 +3841,7 @@
     <col min="5" max="5" width="10.625" style="35" customWidth="1"/>
     <col min="6" max="6" width="10.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="36.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="4.875" style="5" customWidth="1"/>
     <col min="10" max="10" width="74.5" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="6"/>
@@ -4828,7 +4852,7 @@
       <c r="D33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="41" t="s">
+      <c r="E33" s="49" t="s">
         <v>170</v>
       </c>
       <c r="F33" s="23" t="s">
@@ -4860,7 +4884,7 @@
       <c r="D34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="50" t="s">
         <v>175</v>
       </c>
       <c r="F34" s="23" t="s">
@@ -4892,7 +4916,7 @@
       <c r="D35" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="50" t="s">
         <v>181</v>
       </c>
       <c r="F35" s="23" t="s">
@@ -4904,7 +4928,7 @@
       <c r="H35" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="49" t="s">
+      <c r="I35" s="51" t="s">
         <v>183</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -4924,7 +4948,7 @@
       <c r="D36" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="52" t="s">
         <v>186</v>
       </c>
       <c r="F36" s="23" t="s">
@@ -4937,7 +4961,7 @@
         <v>187</v>
       </c>
       <c r="I36" s="24"/>
-      <c r="J36" s="50" t="s">
+      <c r="J36" s="53" t="s">
         <v>188</v>
       </c>
     </row>
@@ -4954,7 +4978,7 @@
       <c r="D37" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="52" t="s">
         <v>190</v>
       </c>
       <c r="F37" s="23" t="s">
@@ -4984,8 +5008,8 @@
       <c r="D38" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="22">
-        <v>1</v>
+      <c r="E38" s="50" t="s">
+        <v>194</v>
       </c>
       <c r="F38" s="23" t="s">
         <v>159</v>
@@ -4996,24 +5020,24 @@
       <c r="H38" s="23"/>
       <c r="I38" s="24"/>
       <c r="J38" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>138</v>
       </c>
       <c r="C39" s="48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D39" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="22" t="s">
-        <v>197</v>
+      <c r="E39" s="52" t="s">
+        <v>198</v>
       </c>
       <c r="F39" s="23" t="s">
         <v>159</v>
@@ -5022,28 +5046,28 @@
         <v>2026</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I39" s="24"/>
       <c r="J39" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>138</v>
       </c>
       <c r="C40" s="48" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="22" t="s">
-        <v>202</v>
+      <c r="E40" s="52" t="s">
+        <v>203</v>
       </c>
       <c r="F40" s="23" t="s">
         <v>159</v>
@@ -5051,38 +5075,42 @@
       <c r="G40" s="23">
         <v>2026</v>
       </c>
-      <c r="H40" s="51" t="s">
-        <v>203</v>
+      <c r="H40" s="54" t="s">
+        <v>204</v>
       </c>
       <c r="I40" s="24"/>
       <c r="J40" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>145</v>
       </c>
       <c r="C41" s="48" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E41" s="22" t="s">
-        <v>206</v>
+      <c r="E41" s="50" t="s">
+        <v>207</v>
       </c>
       <c r="F41" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G41" s="7"/>
-      <c r="H41" s="23"/>
+      <c r="G41" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>208</v>
+      </c>
       <c r="I41" s="24"/>
-      <c r="J41" s="24" t="s">
-        <v>207</v>
+      <c r="J41" s="7" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="42" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
@@ -5095,9 +5123,7 @@
       <c r="G42" s="7"/>
       <c r="H42" s="23"/>
       <c r="I42" s="24"/>
-      <c r="J42" s="7" t="s">
-        <v>208</v>
-      </c>
+      <c r="J42" s="7"/>
     </row>
     <row r="43" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A43" s="21"/>
@@ -5109,9 +5135,7 @@
       <c r="G43" s="7"/>
       <c r="H43" s="23"/>
       <c r="I43" s="24"/>
-      <c r="J43" s="7" t="s">
-        <v>209</v>
-      </c>
+      <c r="J43" s="7"/>
     </row>
     <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A44" s="21"/>
@@ -5123,9 +5147,7 @@
       <c r="G44" s="7"/>
       <c r="H44" s="23"/>
       <c r="I44" s="24"/>
-      <c r="J44" s="7" t="s">
-        <v>210</v>
-      </c>
+      <c r="J44" s="7"/>
     </row>
     <row r="45" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A45" s="21"/>
@@ -5163,33 +5185,51 @@
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A48" s="21"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
+    <row r="48" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A48" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="41">
+        <v>7</v>
+      </c>
+      <c r="F48" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G48" s="23">
+        <v>2026</v>
+      </c>
       <c r="H48" s="23"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="7"/>
+      <c r="I48" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="J48" s="23" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A49" s="25" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>157</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="41">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F49" s="23" t="s">
         <v>159</v>
@@ -5197,29 +5237,27 @@
       <c r="G49" s="23">
         <v>2026</v>
       </c>
-      <c r="H49" s="23"/>
+      <c r="H49" s="51"/>
       <c r="I49" s="46" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J49" s="23" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A50" s="25" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="C50" s="23" t="s">
-        <v>216</v>
-      </c>
+      <c r="C50" s="23"/>
       <c r="D50" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="41">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F50" s="23" t="s">
         <v>159</v>
@@ -5227,17 +5265,17 @@
       <c r="G50" s="23">
         <v>2026</v>
       </c>
-      <c r="H50" s="49"/>
+      <c r="H50" s="51"/>
       <c r="I50" s="46" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J50" s="23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A51" s="25" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>157</v>
@@ -5247,7 +5285,7 @@
         <v>13</v>
       </c>
       <c r="E51" s="41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" s="23" t="s">
         <v>159</v>
@@ -5255,56 +5293,54 @@
       <c r="G51" s="23">
         <v>2026</v>
       </c>
-      <c r="H51" s="49"/>
+      <c r="H51" s="51"/>
       <c r="I51" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="J51" s="23" t="s">
-        <v>221</v>
+        <v>222</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A52" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="B52" s="23" t="s">
+      <c r="A52" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C52" s="23"/>
+      <c r="C52" s="48" t="s">
+        <v>225</v>
+      </c>
       <c r="D52" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E52" s="41">
-        <v>4</v>
-      </c>
-      <c r="F52" s="23" t="s">
-        <v>159</v>
+      <c r="E52" s="55"/>
+      <c r="F52" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="G52" s="23">
         <v>2026</v>
       </c>
-      <c r="H52" s="49"/>
-      <c r="I52" s="46" t="s">
-        <v>223</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>224</v>
-      </c>
+      <c r="H52" s="23"/>
+      <c r="I52" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="J52" s="7"/>
     </row>
     <row r="53" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A53" s="21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>157</v>
       </c>
       <c r="C53" s="48" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="52"/>
+      <c r="E53" s="55"/>
       <c r="F53" s="48" t="s">
         <v>14</v>
       </c>
@@ -5313,42 +5349,38 @@
       </c>
       <c r="H53" s="23"/>
       <c r="I53" s="24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J53" s="7"/>
     </row>
     <row r="54" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A54" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C54" s="48" t="s">
-        <v>226</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="52"/>
-      <c r="F54" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G54" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H54" s="23"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
       <c r="I54" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="J54" s="7"/>
+        <v>231</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A55" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>230</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>231</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -5359,18 +5391,18 @@
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
       <c r="I55" s="24" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A56" s="21" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -5381,18 +5413,18 @@
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -5402,49 +5434,47 @@
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
-      <c r="I57" s="24" t="s">
-        <v>238</v>
-      </c>
+      <c r="I57" s="24"/>
       <c r="J57" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" ht="25" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>231</v>
+        <v>68</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="22"/>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G58" s="7"/>
+      <c r="G58" s="23">
+        <v>2026</v>
+      </c>
       <c r="H58" s="7"/>
-      <c r="I58" s="24"/>
-      <c r="J58" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A59" s="25" t="s">
+      <c r="I58" s="24" t="s">
         <v>242</v>
       </c>
+      <c r="J58" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A59" s="21" t="s">
+        <v>244</v>
+      </c>
       <c r="B59" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C59" s="26" t="s">
-        <v>244</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C59" s="7"/>
       <c r="D59" s="7"/>
-      <c r="E59" s="22">
-        <v>10</v>
-      </c>
+      <c r="E59" s="22"/>
       <c r="F59" s="22" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="G59" s="23">
         <v>2026</v>
@@ -5452,21 +5482,23 @@
       <c r="H59" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="I59" s="7" t="s">
+      <c r="I59" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="J59" s="7" t="s">
+      <c r="J59" s="24" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="60" ht="25" customHeight="1" spans="1:10">
+    <row r="60" ht="24" customHeight="1" spans="1:10">
       <c r="A60" s="21" t="s">
         <v>248</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C60" s="7"/>
+      <c r="C60" s="7" t="s">
+        <v>249</v>
+      </c>
       <c r="D60" s="7"/>
       <c r="E60" s="22"/>
       <c r="F60" s="22" t="s">
@@ -5475,22 +5507,26 @@
       <c r="G60" s="23">
         <v>2026</v>
       </c>
-      <c r="H60" s="7"/>
+      <c r="H60" s="7" t="s">
+        <v>250</v>
+      </c>
       <c r="I60" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="J60" s="21" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="61" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>251</v>
+      </c>
+      <c r="J60" s="24" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="61" ht="25" customHeight="1" spans="1:10">
       <c r="A61" s="21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="7"/>
+      <c r="C61" s="7" t="s">
+        <v>254</v>
+      </c>
       <c r="D61" s="7"/>
       <c r="E61" s="22"/>
       <c r="F61" s="22" t="s">
@@ -5500,52 +5536,36 @@
         <v>2026</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J61" s="24" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1" spans="1:10">
-      <c r="A62" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>256</v>
-      </c>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="62" ht="25" customHeight="1" spans="1:10">
+      <c r="A62" s="21"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="22"/>
-      <c r="F62" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="I62" s="24" t="s">
+      <c r="F62" s="22"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="24"/>
+    </row>
+    <row r="63" ht="25" customHeight="1" spans="1:10">
+      <c r="A63" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="J62" s="24" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="63" ht="25" customHeight="1" spans="1:10">
-      <c r="A63" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>261</v>
+      <c r="C63" s="57" t="s">
+        <v>164</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="22"/>
@@ -5553,57 +5573,57 @@
         <v>14</v>
       </c>
       <c r="G63" s="23">
-        <v>2026</v>
+        <v>8.25</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="I63" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="J63" s="24" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="64" ht="25" customHeight="1" spans="1:10">
-      <c r="A64" s="21"/>
-      <c r="B64" s="7"/>
+        <v>259</v>
+      </c>
+      <c r="I63" s="24"/>
+      <c r="J63" s="21"/>
+    </row>
+    <row r="64" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A64" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="23"/>
+      <c r="F64" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" s="23" t="s">
+        <v>261</v>
+      </c>
       <c r="H64" s="7"/>
       <c r="I64" s="24"/>
-      <c r="J64" s="24"/>
-    </row>
-    <row r="65" ht="25" customHeight="1" spans="1:10">
-      <c r="A65" s="53" t="s">
-        <v>265</v>
-      </c>
-      <c r="B65" s="54" t="s">
+      <c r="J64" s="21"/>
+    </row>
+    <row r="65" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A65" s="56" t="s">
+        <v>262</v>
+      </c>
+      <c r="B65" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="54" t="s">
-        <v>164</v>
-      </c>
+      <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="22"/>
       <c r="F65" s="22" t="s">
         <v>14</v>
       </c>
       <c r="G65" s="23">
-        <v>8.25</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>266</v>
-      </c>
+        <v>8.23</v>
+      </c>
+      <c r="H65" s="7"/>
       <c r="I65" s="24"/>
       <c r="J65" s="21"/>
     </row>
     <row r="66" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A66" s="53" t="s">
-        <v>267</v>
+      <c r="A66" s="56" t="s">
+        <v>263</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>68</v>
@@ -5611,19 +5631,17 @@
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="22"/>
-      <c r="F66" s="22" t="s">
-        <v>14</v>
-      </c>
+      <c r="F66" s="22"/>
       <c r="G66" s="23" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="H66" s="7"/>
       <c r="I66" s="24"/>
       <c r="J66" s="21"/>
     </row>
     <row r="67" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A67" s="53" t="s">
-        <v>269</v>
+      <c r="A67" s="56" t="s">
+        <v>264</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>68</v>
@@ -5635,15 +5653,15 @@
         <v>14</v>
       </c>
       <c r="G67" s="23">
-        <v>8.23</v>
+        <v>8.21</v>
       </c>
       <c r="H67" s="7"/>
       <c r="I67" s="24"/>
       <c r="J67" s="21"/>
     </row>
     <row r="68" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A68" s="53" t="s">
-        <v>270</v>
+      <c r="A68" s="56" t="s">
+        <v>265</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>68</v>
@@ -5652,16 +5670,14 @@
       <c r="D68" s="7"/>
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
-      <c r="G68" s="23" t="s">
-        <v>268</v>
-      </c>
+      <c r="G68" s="23"/>
       <c r="H68" s="7"/>
       <c r="I68" s="24"/>
       <c r="J68" s="21"/>
     </row>
     <row r="69" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A69" s="53" t="s">
-        <v>271</v>
+      <c r="A69" s="56" t="s">
+        <v>266</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>68</v>
@@ -5669,23 +5685,19 @@
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
       <c r="E69" s="22"/>
-      <c r="F69" s="22" t="s">
-        <v>14</v>
-      </c>
+      <c r="F69" s="22"/>
       <c r="G69" s="23">
-        <v>8.21</v>
+        <v>5.15</v>
       </c>
       <c r="H69" s="7"/>
       <c r="I69" s="24"/>
       <c r="J69" s="21"/>
     </row>
     <row r="70" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A70" s="53" t="s">
-        <v>272</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>68</v>
-      </c>
+      <c r="A70" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="22"/>
@@ -5695,27 +5707,23 @@
       <c r="I70" s="24"/>
       <c r="J70" s="21"/>
     </row>
-    <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A71" s="53" t="s">
-        <v>273</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>68</v>
-      </c>
+    <row r="71" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
+      <c r="A71" s="56" t="s">
+        <v>268</v>
+      </c>
+      <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
-      <c r="G71" s="23">
-        <v>5.15</v>
-      </c>
+      <c r="G71" s="23"/>
       <c r="H71" s="7"/>
       <c r="I71" s="24"/>
       <c r="J71" s="21"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A72" s="53" t="s">
-        <v>274</v>
+      <c r="A72" s="56" t="s">
+        <v>269</v>
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -5727,9 +5735,9 @@
       <c r="I72" s="24"/>
       <c r="J72" s="21"/>
     </row>
-    <row r="73" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A73" s="53" t="s">
-        <v>275</v>
+    <row r="73" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A73" s="56" t="s">
+        <v>270</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -5742,43 +5750,47 @@
       <c r="J73" s="21"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A74" s="53" t="s">
-        <v>276</v>
+      <c r="A74" s="56" t="s">
+        <v>271</v>
       </c>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
+      <c r="F74" s="22" t="s">
+        <v>272</v>
+      </c>
       <c r="G74" s="23"/>
       <c r="H74" s="7"/>
       <c r="I74" s="24"/>
-      <c r="J74" s="21"/>
-    </row>
-    <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A75" s="53" t="s">
-        <v>277</v>
+      <c r="J74" s="24"/>
+    </row>
+    <row r="75" ht="25" customHeight="1" spans="1:10">
+      <c r="A75" s="56" t="s">
+        <v>273</v>
       </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
+      <c r="F75" s="22" t="s">
+        <v>274</v>
+      </c>
       <c r="G75" s="23"/>
       <c r="H75" s="7"/>
       <c r="I75" s="24"/>
-      <c r="J75" s="21"/>
-    </row>
-    <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A76" s="53" t="s">
-        <v>278</v>
+      <c r="J75" s="24"/>
+    </row>
+    <row r="76" ht="25" customHeight="1" spans="1:10">
+      <c r="A76" s="21" t="s">
+        <v>248</v>
       </c>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="22"/>
       <c r="F76" s="22" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G76" s="23"/>
       <c r="H76" s="7"/>
@@ -5786,15 +5798,15 @@
       <c r="J76" s="24"/>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:10">
-      <c r="A77" s="53" t="s">
-        <v>280</v>
+      <c r="A77" s="56" t="s">
+        <v>276</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="22"/>
       <c r="F77" s="22" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G77" s="23"/>
       <c r="H77" s="7"/>
@@ -5802,15 +5814,15 @@
       <c r="J77" s="24"/>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:10">
-      <c r="A78" s="21" t="s">
-        <v>255</v>
+      <c r="A78" s="56" t="s">
+        <v>278</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="22"/>
-      <c r="F78" s="22" t="s">
-        <v>282</v>
+      <c r="F78" s="22">
+        <v>102</v>
       </c>
       <c r="G78" s="23"/>
       <c r="H78" s="7"/>
@@ -5818,15 +5830,15 @@
       <c r="J78" s="24"/>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:10">
-      <c r="A79" s="53" t="s">
-        <v>283</v>
+      <c r="A79" s="56" t="s">
+        <v>279</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="22"/>
-      <c r="F79" s="22" t="s">
-        <v>284</v>
+      <c r="F79" s="22">
+        <v>69</v>
       </c>
       <c r="G79" s="23"/>
       <c r="H79" s="7"/>
@@ -5834,15 +5846,15 @@
       <c r="J79" s="24"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:10">
-      <c r="A80" s="53" t="s">
-        <v>285</v>
+      <c r="A80" s="56" t="s">
+        <v>280</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="22"/>
       <c r="F80" s="22">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="G80" s="23"/>
       <c r="H80" s="7"/>
@@ -5850,31 +5862,29 @@
       <c r="J80" s="24"/>
     </row>
     <row r="81" ht="25" customHeight="1" spans="1:10">
-      <c r="A81" s="53" t="s">
-        <v>286</v>
+      <c r="A81" s="56" t="s">
+        <v>281</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="22"/>
-      <c r="F81" s="22">
-        <v>69</v>
-      </c>
+      <c r="F81" s="22"/>
       <c r="G81" s="23"/>
       <c r="H81" s="7"/>
       <c r="I81" s="24"/>
       <c r="J81" s="24"/>
     </row>
     <row r="82" ht="25" customHeight="1" spans="1:10">
-      <c r="A82" s="53" t="s">
-        <v>287</v>
+      <c r="A82" s="56" t="s">
+        <v>282</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="22"/>
-      <c r="F82" s="22">
-        <v>86</v>
+      <c r="F82" s="22" t="s">
+        <v>283</v>
       </c>
       <c r="G82" s="23"/>
       <c r="H82" s="7"/>
@@ -5882,8 +5892,8 @@
       <c r="J82" s="24"/>
     </row>
     <row r="83" ht="25" customHeight="1" spans="1:10">
-      <c r="A83" s="53" t="s">
-        <v>288</v>
+      <c r="A83" s="56" t="s">
+        <v>284</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -5896,59 +5906,63 @@
       <c r="J83" s="24"/>
     </row>
     <row r="84" ht="25" customHeight="1" spans="1:10">
-      <c r="A84" s="53" t="s">
-        <v>289</v>
+      <c r="A84" s="56" t="s">
+        <v>285</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="22"/>
-      <c r="F84" s="22" t="s">
-        <v>290</v>
-      </c>
+      <c r="F84" s="22"/>
       <c r="G84" s="23"/>
       <c r="H84" s="7"/>
       <c r="I84" s="24"/>
       <c r="J84" s="24"/>
     </row>
     <row r="85" ht="25" customHeight="1" spans="1:10">
-      <c r="A85" s="53" t="s">
-        <v>291</v>
+      <c r="A85" s="56" t="s">
+        <v>286</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="22"/>
-      <c r="F85" s="22"/>
+      <c r="F85" s="22" t="s">
+        <v>287</v>
+      </c>
       <c r="G85" s="23"/>
       <c r="H85" s="7"/>
       <c r="I85" s="24"/>
       <c r="J85" s="24"/>
     </row>
     <row r="86" ht="25" customHeight="1" spans="1:10">
-      <c r="A86" s="53" t="s">
-        <v>292</v>
+      <c r="A86" s="56" t="s">
+        <v>288</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="22"/>
-      <c r="F86" s="22"/>
+      <c r="F86" s="22" t="s">
+        <v>289</v>
+      </c>
       <c r="G86" s="23"/>
       <c r="H86" s="7"/>
       <c r="I86" s="24"/>
       <c r="J86" s="24"/>
     </row>
     <row r="87" ht="25" customHeight="1" spans="1:10">
-      <c r="A87" s="53" t="s">
-        <v>293</v>
+      <c r="A87" s="56" t="s">
+        <v>290</v>
       </c>
       <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
+      <c r="C87" s="7" t="s">
+        <v>291</v>
+      </c>
       <c r="D87" s="7"/>
       <c r="E87" s="22"/>
       <c r="F87" s="22" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G87" s="23"/>
       <c r="H87" s="7"/>
@@ -5956,15 +5970,17 @@
       <c r="J87" s="24"/>
     </row>
     <row r="88" ht="25" customHeight="1" spans="1:10">
-      <c r="A88" s="53" t="s">
-        <v>295</v>
+      <c r="A88" s="56" t="s">
+        <v>293</v>
       </c>
       <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
+      <c r="C88" s="7" t="s">
+        <v>294</v>
+      </c>
       <c r="D88" s="7"/>
       <c r="E88" s="22"/>
       <c r="F88" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G88" s="23"/>
       <c r="H88" s="7"/>
@@ -5972,17 +5988,17 @@
       <c r="J88" s="24"/>
     </row>
     <row r="89" ht="25" customHeight="1" spans="1:10">
-      <c r="A89" s="53" t="s">
-        <v>297</v>
+      <c r="A89" s="56" t="s">
+        <v>296</v>
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D89" s="7"/>
       <c r="E89" s="22"/>
       <c r="F89" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G89" s="23"/>
       <c r="H89" s="7"/>
@@ -5990,17 +6006,17 @@
       <c r="J89" s="24"/>
     </row>
     <row r="90" ht="25" customHeight="1" spans="1:10">
-      <c r="A90" s="53" t="s">
-        <v>300</v>
+      <c r="A90" s="56" t="s">
+        <v>299</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D90" s="7"/>
       <c r="E90" s="22"/>
       <c r="F90" s="22" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="G90" s="23"/>
       <c r="H90" s="7"/>
@@ -6008,17 +6024,17 @@
       <c r="J90" s="24"/>
     </row>
     <row r="91" ht="25" customHeight="1" spans="1:10">
-      <c r="A91" s="53" t="s">
-        <v>303</v>
+      <c r="A91" s="56" t="s">
+        <v>301</v>
       </c>
       <c r="B91" s="7"/>
       <c r="C91" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="22"/>
       <c r="F91" s="22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G91" s="23"/>
       <c r="H91" s="7"/>
@@ -6026,17 +6042,17 @@
       <c r="J91" s="24"/>
     </row>
     <row r="92" ht="25" customHeight="1" spans="1:10">
-      <c r="A92" s="53" t="s">
-        <v>306</v>
+      <c r="A92" s="56" t="s">
+        <v>304</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D92" s="7"/>
       <c r="E92" s="22"/>
       <c r="F92" s="22" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="G92" s="23"/>
       <c r="H92" s="7"/>
@@ -6044,17 +6060,17 @@
       <c r="J92" s="24"/>
     </row>
     <row r="93" ht="25" customHeight="1" spans="1:10">
-      <c r="A93" s="53" t="s">
-        <v>308</v>
+      <c r="A93" s="56" t="s">
+        <v>307</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G93" s="23"/>
       <c r="H93" s="7"/>
@@ -6062,17 +6078,17 @@
       <c r="J93" s="24"/>
     </row>
     <row r="94" ht="25" customHeight="1" spans="1:10">
-      <c r="A94" s="53" t="s">
-        <v>311</v>
+      <c r="A94" s="56" t="s">
+        <v>310</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="22"/>
       <c r="F94" s="22" t="s">
-        <v>313</v>
+        <v>277</v>
       </c>
       <c r="G94" s="23"/>
       <c r="H94" s="7"/>
@@ -6080,17 +6096,17 @@
       <c r="J94" s="24"/>
     </row>
     <row r="95" ht="25" customHeight="1" spans="1:10">
-      <c r="A95" s="53" t="s">
-        <v>314</v>
+      <c r="A95" s="56" t="s">
+        <v>312</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G95" s="23"/>
       <c r="H95" s="7"/>
@@ -6098,17 +6114,17 @@
       <c r="J95" s="24"/>
     </row>
     <row r="96" ht="25" customHeight="1" spans="1:10">
-      <c r="A96" s="53" t="s">
-        <v>317</v>
+      <c r="A96" s="56" t="s">
+        <v>315</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="22"/>
       <c r="F96" s="22" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="G96" s="23"/>
       <c r="H96" s="7"/>
@@ -6116,17 +6132,17 @@
       <c r="J96" s="24"/>
     </row>
     <row r="97" ht="25" customHeight="1" spans="1:10">
-      <c r="A97" s="53" t="s">
-        <v>319</v>
+      <c r="A97" s="56" t="s">
+        <v>317</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G97" s="23"/>
       <c r="H97" s="7"/>
@@ -6134,193 +6150,193 @@
       <c r="J97" s="24"/>
     </row>
     <row r="98" ht="25" customHeight="1" spans="1:10">
-      <c r="A98" s="53" t="s">
-        <v>322</v>
-      </c>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="D98" s="7"/>
+      <c r="A98" s="56" t="s">
+        <v>320</v>
+      </c>
+      <c r="B98" s="57"/>
+      <c r="C98" s="57" t="s">
+        <v>321</v>
+      </c>
+      <c r="D98" s="57"/>
       <c r="E98" s="22"/>
-      <c r="F98" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="G98" s="23"/>
+      <c r="F98" s="58" t="s">
+        <v>289</v>
+      </c>
+      <c r="G98" s="59"/>
       <c r="H98" s="7"/>
       <c r="I98" s="24"/>
       <c r="J98" s="24"/>
     </row>
     <row r="99" ht="25" customHeight="1" spans="1:10">
-      <c r="A99" s="53" t="s">
-        <v>324</v>
-      </c>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="D99" s="7"/>
+      <c r="A99" s="56" t="s">
+        <v>322</v>
+      </c>
+      <c r="B99" s="57"/>
+      <c r="C99" s="57" t="s">
+        <v>300</v>
+      </c>
+      <c r="D99" s="57"/>
       <c r="E99" s="22"/>
-      <c r="F99" s="22" t="s">
-        <v>326</v>
-      </c>
-      <c r="G99" s="23"/>
+      <c r="F99" s="58" t="s">
+        <v>323</v>
+      </c>
+      <c r="G99" s="59"/>
       <c r="H99" s="7"/>
       <c r="I99" s="24"/>
       <c r="J99" s="24"/>
     </row>
     <row r="100" ht="25" customHeight="1" spans="1:10">
-      <c r="A100" s="53" t="s">
-        <v>327</v>
-      </c>
-      <c r="B100" s="54"/>
-      <c r="C100" s="54" t="s">
-        <v>328</v>
-      </c>
-      <c r="D100" s="54"/>
+      <c r="A100" s="56" t="s">
+        <v>324</v>
+      </c>
+      <c r="B100" s="57"/>
+      <c r="C100" s="57"/>
+      <c r="D100" s="57"/>
       <c r="E100" s="22"/>
-      <c r="F100" s="55" t="s">
-        <v>296</v>
-      </c>
-      <c r="G100" s="56"/>
+      <c r="F100" s="58" t="s">
+        <v>325</v>
+      </c>
+      <c r="G100" s="59"/>
       <c r="H100" s="7"/>
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
     </row>
     <row r="101" ht="25" customHeight="1" spans="1:10">
-      <c r="A101" s="53" t="s">
-        <v>329</v>
-      </c>
-      <c r="B101" s="54"/>
-      <c r="C101" s="54" t="s">
-        <v>307</v>
-      </c>
-      <c r="D101" s="54"/>
+      <c r="A101" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="B101" s="57"/>
+      <c r="C101" s="57" t="s">
+        <v>327</v>
+      </c>
+      <c r="D101" s="57"/>
       <c r="E101" s="22"/>
-      <c r="F101" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="G101" s="56"/>
+      <c r="F101" s="58" t="s">
+        <v>328</v>
+      </c>
+      <c r="G101" s="23"/>
       <c r="H101" s="7"/>
       <c r="I101" s="24"/>
       <c r="J101" s="24"/>
     </row>
     <row r="102" ht="25" customHeight="1" spans="1:10">
-      <c r="A102" s="53" t="s">
+      <c r="A102" s="56" t="s">
+        <v>329</v>
+      </c>
+      <c r="B102" s="57"/>
+      <c r="C102" s="57" t="s">
+        <v>330</v>
+      </c>
+      <c r="D102" s="57"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="58" t="s">
         <v>331</v>
       </c>
-      <c r="B102" s="54"/>
-      <c r="C102" s="54"/>
-      <c r="D102" s="54"/>
-      <c r="E102" s="22"/>
-      <c r="F102" s="55" t="s">
-        <v>332</v>
-      </c>
-      <c r="G102" s="56"/>
+      <c r="G102" s="23"/>
       <c r="H102" s="7"/>
       <c r="I102" s="24"/>
       <c r="J102" s="24"/>
     </row>
-    <row r="103" ht="25" customHeight="1" spans="1:10">
-      <c r="A103" s="53" t="s">
+    <row r="103" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A103" s="60" t="s">
+        <v>332</v>
+      </c>
+      <c r="B103" s="48"/>
+      <c r="C103" s="48" t="s">
+        <v>291</v>
+      </c>
+      <c r="D103" s="48"/>
+      <c r="E103" s="55"/>
+      <c r="F103" s="55" t="s">
+        <v>289</v>
+      </c>
+      <c r="G103" s="23"/>
+      <c r="H103" s="48"/>
+      <c r="I103" s="61"/>
+      <c r="J103" s="61"/>
+    </row>
+    <row r="104" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A104" s="60" t="s">
         <v>333</v>
       </c>
-      <c r="B103" s="54"/>
-      <c r="C103" s="54" t="s">
+      <c r="B104" s="48"/>
+      <c r="C104" s="48"/>
+      <c r="D104" s="48"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D103" s="54"/>
-      <c r="E103" s="22"/>
-      <c r="F103" s="55" t="s">
+      <c r="G104" s="23"/>
+      <c r="H104" s="48"/>
+      <c r="I104" s="61"/>
+      <c r="J104" s="61"/>
+    </row>
+    <row r="105" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A105" s="60" t="s">
         <v>335</v>
       </c>
-      <c r="G103" s="23"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="24"/>
-      <c r="J103" s="24"/>
-    </row>
-    <row r="104" ht="25" customHeight="1" spans="1:10">
-      <c r="A104" s="53" t="s">
+      <c r="B105" s="48"/>
+      <c r="C105" s="57" t="s">
+        <v>321</v>
+      </c>
+      <c r="D105" s="48"/>
+      <c r="E105" s="55"/>
+      <c r="F105" s="55" t="s">
         <v>336</v>
-      </c>
-      <c r="B104" s="54"/>
-      <c r="C104" s="54" t="s">
-        <v>337</v>
-      </c>
-      <c r="D104" s="54"/>
-      <c r="E104" s="22"/>
-      <c r="F104" s="55" t="s">
-        <v>338</v>
-      </c>
-      <c r="G104" s="23"/>
-      <c r="H104" s="7"/>
-      <c r="I104" s="24"/>
-      <c r="J104" s="24"/>
-    </row>
-    <row r="105" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A105" s="57" t="s">
-        <v>339</v>
-      </c>
-      <c r="B105" s="48"/>
-      <c r="C105" s="48" t="s">
-        <v>298</v>
-      </c>
-      <c r="D105" s="48"/>
-      <c r="E105" s="52"/>
-      <c r="F105" s="52" t="s">
-        <v>296</v>
       </c>
       <c r="G105" s="23"/>
       <c r="H105" s="48"/>
-      <c r="I105" s="58"/>
-      <c r="J105" s="58"/>
-    </row>
-    <row r="106" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A106" s="57" t="s">
+      <c r="I105" s="61"/>
+      <c r="J105" s="61"/>
+    </row>
+    <row r="106" ht="25" customHeight="1" spans="1:10">
+      <c r="A106" s="56" t="s">
+        <v>337</v>
+      </c>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D106" s="7"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="G106" s="23"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="24"/>
+      <c r="J106" s="24"/>
+    </row>
+    <row r="107" ht="25" customHeight="1" spans="1:10">
+      <c r="A107" s="56" t="s">
         <v>340</v>
       </c>
-      <c r="B106" s="48"/>
-      <c r="C106" s="48"/>
-      <c r="D106" s="48"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52" t="s">
+      <c r="B107" s="7"/>
+      <c r="C107" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D107" s="7"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="G107" s="23"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="24"/>
+    </row>
+    <row r="108" ht="25" customHeight="1" spans="1:10">
+      <c r="A108" s="56" t="s">
         <v>341</v>
-      </c>
-      <c r="G106" s="23"/>
-      <c r="H106" s="48"/>
-      <c r="I106" s="58"/>
-      <c r="J106" s="58"/>
-    </row>
-    <row r="107" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A107" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="B107" s="48"/>
-      <c r="C107" s="54" t="s">
-        <v>328</v>
-      </c>
-      <c r="D107" s="48"/>
-      <c r="E107" s="52"/>
-      <c r="F107" s="52" t="s">
-        <v>343</v>
-      </c>
-      <c r="G107" s="23"/>
-      <c r="H107" s="48"/>
-      <c r="I107" s="58"/>
-      <c r="J107" s="58"/>
-    </row>
-    <row r="108" ht="25" customHeight="1" spans="1:10">
-      <c r="A108" s="53" t="s">
-        <v>344</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7" t="s">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="D108" s="7"/>
       <c r="E108" s="22"/>
       <c r="F108" s="22" t="s">
-        <v>346</v>
+        <v>277</v>
       </c>
       <c r="G108" s="23"/>
       <c r="H108" s="7"/>
@@ -6328,17 +6344,17 @@
       <c r="J108" s="24"/>
     </row>
     <row r="109" ht="25" customHeight="1" spans="1:10">
-      <c r="A109" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="D109" s="7"/>
-      <c r="E109" s="22"/>
-      <c r="F109" s="22" t="s">
-        <v>284</v>
+      <c r="A109" s="56" t="s">
+        <v>342</v>
+      </c>
+      <c r="B109" s="57"/>
+      <c r="C109" s="57" t="s">
+        <v>308</v>
+      </c>
+      <c r="D109" s="57"/>
+      <c r="E109" s="58"/>
+      <c r="F109" s="58" t="s">
+        <v>343</v>
       </c>
       <c r="G109" s="23"/>
       <c r="H109" s="7"/>
@@ -6346,17 +6362,17 @@
       <c r="J109" s="24"/>
     </row>
     <row r="110" ht="25" customHeight="1" spans="1:10">
-      <c r="A110" s="53" t="s">
-        <v>348</v>
-      </c>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="D110" s="7"/>
-      <c r="E110" s="22"/>
-      <c r="F110" s="22" t="s">
-        <v>284</v>
+      <c r="A110" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="B110" s="57"/>
+      <c r="C110" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="D110" s="57"/>
+      <c r="E110" s="58"/>
+      <c r="F110" s="58" t="s">
+        <v>336</v>
       </c>
       <c r="G110" s="23"/>
       <c r="H110" s="7"/>
@@ -6364,17 +6380,17 @@
       <c r="J110" s="24"/>
     </row>
     <row r="111" ht="25" customHeight="1" spans="1:10">
-      <c r="A111" s="53" t="s">
-        <v>349</v>
-      </c>
-      <c r="B111" s="54"/>
-      <c r="C111" s="54" t="s">
-        <v>315</v>
-      </c>
-      <c r="D111" s="54"/>
-      <c r="E111" s="55"/>
-      <c r="F111" s="55" t="s">
-        <v>350</v>
+      <c r="A111" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="B111" s="57"/>
+      <c r="C111" s="57" t="s">
+        <v>347</v>
+      </c>
+      <c r="D111" s="57"/>
+      <c r="E111" s="58"/>
+      <c r="F111" s="58" t="s">
+        <v>348</v>
       </c>
       <c r="G111" s="23"/>
       <c r="H111" s="7"/>
@@ -6382,17 +6398,17 @@
       <c r="J111" s="24"/>
     </row>
     <row r="112" ht="25" customHeight="1" spans="1:10">
-      <c r="A112" s="53" t="s">
-        <v>351</v>
-      </c>
-      <c r="B112" s="54"/>
-      <c r="C112" s="54" t="s">
-        <v>352</v>
-      </c>
-      <c r="D112" s="54"/>
-      <c r="E112" s="55"/>
-      <c r="F112" s="55" t="s">
-        <v>343</v>
+      <c r="A112" s="56" t="s">
+        <v>349</v>
+      </c>
+      <c r="B112" s="57"/>
+      <c r="C112" s="57" t="s">
+        <v>300</v>
+      </c>
+      <c r="D112" s="57"/>
+      <c r="E112" s="58"/>
+      <c r="F112" s="58" t="s">
+        <v>350</v>
       </c>
       <c r="G112" s="23"/>
       <c r="H112" s="7"/>
@@ -6400,35 +6416,36 @@
       <c r="J112" s="24"/>
     </row>
     <row r="113" ht="25" customHeight="1" spans="1:10">
-      <c r="A113" s="53" t="s">
+      <c r="A113" s="56" t="s">
+        <v>351</v>
+      </c>
+      <c r="B113" s="57"/>
+      <c r="C113" s="57" t="s">
+        <v>352</v>
+      </c>
+      <c r="D113" s="57"/>
+      <c r="E113" s="58"/>
+      <c r="F113" s="58" t="s">
         <v>353</v>
-      </c>
-      <c r="B113" s="54"/>
-      <c r="C113" s="54" t="s">
-        <v>354</v>
-      </c>
-      <c r="D113" s="54"/>
-      <c r="E113" s="55"/>
-      <c r="F113" s="55" t="s">
-        <v>355</v>
       </c>
       <c r="G113" s="23"/>
       <c r="H113" s="7"/>
       <c r="I113" s="24"/>
-      <c r="J113" s="24"/>
+      <c r="J113" s="24">
+        <f>2100*60</f>
+        <v>126000</v>
+      </c>
     </row>
     <row r="114" ht="25" customHeight="1" spans="1:10">
-      <c r="A114" s="53" t="s">
-        <v>356</v>
-      </c>
-      <c r="B114" s="54"/>
-      <c r="C114" s="54" t="s">
-        <v>307</v>
-      </c>
-      <c r="D114" s="54"/>
-      <c r="E114" s="55"/>
-      <c r="F114" s="55" t="s">
-        <v>357</v>
+      <c r="A114" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="B114" s="57"/>
+      <c r="C114" s="57"/>
+      <c r="D114" s="57"/>
+      <c r="E114" s="58"/>
+      <c r="F114" s="58" t="s">
+        <v>355</v>
       </c>
       <c r="G114" s="23"/>
       <c r="H114" s="7"/>
@@ -6437,35 +6454,34 @@
     </row>
     <row r="115" ht="25" customHeight="1" spans="1:10">
       <c r="A115" s="21" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B115" s="7"/>
       <c r="C115" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D115" s="7"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G115" s="23"/>
       <c r="H115" s="7"/>
       <c r="I115" s="24"/>
-      <c r="J115" s="24">
-        <f>2100*60</f>
-        <v>126000</v>
-      </c>
+      <c r="J115" s="24"/>
     </row>
     <row r="116" ht="25" customHeight="1" spans="1:10">
       <c r="A116" s="21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
+      <c r="C116" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="D116" s="7"/>
       <c r="E116" s="22"/>
       <c r="F116" s="22" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G116" s="23"/>
       <c r="H116" s="7"/>
@@ -6507,30 +6523,6 @@
       <c r="H119" s="7"/>
       <c r="I119" s="24"/>
       <c r="J119" s="24"/>
-    </row>
-    <row r="120" ht="25" customHeight="1" spans="1:10">
-      <c r="A120" s="21"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="22"/>
-      <c r="F120" s="22"/>
-      <c r="G120" s="23"/>
-      <c r="H120" s="7"/>
-      <c r="I120" s="24"/>
-      <c r="J120" s="24"/>
-    </row>
-    <row r="121" ht="25" customHeight="1" spans="1:10">
-      <c r="A121" s="21"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="22"/>
-      <c r="F121" s="22"/>
-      <c r="G121" s="23"/>
-      <c r="H121" s="7"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="24"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J115" etc:filterBottomFollowUsedRange="0">
@@ -6588,7 +6580,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6597,22 +6589,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="E1" s="37" t="s">
         <v>364</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="F1" s="37" t="s">
         <v>365</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="G1" s="37" t="s">
         <v>366</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="H1" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="I1" s="37" t="s">
         <v>368</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6626,22 +6618,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="E2" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="F2" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="39" t="s">
         <v>372</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="H2" s="39" t="s">
         <v>373</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="I2" s="39" t="s">
         <v>374</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6655,22 +6647,22 @@
         <v>11</v>
       </c>
       <c r="D3" s="39" t="s">
+        <v>375</v>
+      </c>
+      <c r="E3" s="39" t="s">
         <v>376</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="F3" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="G3" s="39" t="s">
         <v>378</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="H3" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="I3" s="39" t="s">
         <v>379</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="I3" s="39" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6684,22 +6676,22 @@
         <v>11</v>
       </c>
       <c r="D4" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="E4" s="39" t="s">
         <v>381</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="F4" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="G4" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="F4" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="G4" s="39" t="s">
+      <c r="H4" s="39" t="s">
         <v>383</v>
       </c>
-      <c r="H4" s="39" t="s">
-        <v>384</v>
-      </c>
       <c r="I4" s="39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6713,22 +6705,22 @@
         <v>11</v>
       </c>
       <c r="D5" s="39" t="s">
+        <v>384</v>
+      </c>
+      <c r="E5" s="39" t="s">
         <v>385</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="F5" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="G5" s="39" t="s">
         <v>387</v>
       </c>
-      <c r="G5" s="39" t="s">
-        <v>388</v>
-      </c>
       <c r="H5" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="I5" s="39" t="s">
         <v>374</v>
-      </c>
-      <c r="I5" s="39" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6742,22 +6734,22 @@
         <v>11</v>
       </c>
       <c r="D6" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>389</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="F6" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="H6" s="39" t="s">
         <v>390</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="I6" s="39" t="s">
         <v>374</v>
-      </c>
-      <c r="G6" s="39" t="s">
-        <v>388</v>
-      </c>
-      <c r="H6" s="39" t="s">
-        <v>391</v>
-      </c>
-      <c r="I6" s="39" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6771,22 +6763,22 @@
         <v>138</v>
       </c>
       <c r="D7" s="39" t="s">
+        <v>391</v>
+      </c>
+      <c r="E7" s="39" t="s">
         <v>392</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="F7" s="39" t="s">
         <v>393</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="G7" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="H7" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="G7" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="H7" s="39" t="s">
-        <v>395</v>
-      </c>
       <c r="I7" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6800,22 +6792,22 @@
         <v>138</v>
       </c>
       <c r="D8" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="E8" s="39" t="s">
         <v>396</v>
       </c>
-      <c r="E8" s="39" t="s">
-        <v>397</v>
-      </c>
       <c r="F8" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="H8" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="G8" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>395</v>
-      </c>
       <c r="I8" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6829,22 +6821,22 @@
         <v>157</v>
       </c>
       <c r="D9" s="39" t="s">
+        <v>397</v>
+      </c>
+      <c r="E9" s="39" t="s">
         <v>398</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="F9" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="G9" s="39" t="s">
         <v>399</v>
       </c>
-      <c r="F9" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>400</v>
-      </c>
       <c r="H9" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6858,22 +6850,22 @@
         <v>157</v>
       </c>
       <c r="D10" s="39" t="s">
+        <v>400</v>
+      </c>
+      <c r="E10" s="39" t="s">
         <v>401</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="F10" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>402</v>
       </c>
-      <c r="F10" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>403</v>
-      </c>
       <c r="H10" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -6887,22 +6879,22 @@
         <v>138</v>
       </c>
       <c r="D11" s="39" t="s">
+        <v>403</v>
+      </c>
+      <c r="E11" s="39" t="s">
         <v>404</v>
       </c>
-      <c r="E11" s="39" t="s">
-        <v>405</v>
-      </c>
       <c r="F11" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="H11" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="G11" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>395</v>
-      </c>
       <c r="I11" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -6916,22 +6908,22 @@
         <v>138</v>
       </c>
       <c r="D12" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="E12" s="39" t="s">
         <v>406</v>
       </c>
-      <c r="E12" s="39" t="s">
-        <v>407</v>
-      </c>
       <c r="F12" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="H12" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="G12" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>395</v>
-      </c>
       <c r="I12" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -6939,28 +6931,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D13" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="E13" s="39" t="s">
         <v>409</v>
       </c>
-      <c r="E13" s="39" t="s">
-        <v>410</v>
-      </c>
       <c r="F13" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="H13" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="G13" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>395</v>
-      </c>
       <c r="I13" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -6974,22 +6966,22 @@
         <v>145</v>
       </c>
       <c r="D14" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="E14" s="39" t="s">
         <v>411</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="F14" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="H14" s="39" t="s">
         <v>412</v>
       </c>
-      <c r="F14" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="H14" s="39" t="s">
-        <v>413</v>
-      </c>
       <c r="I14" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -6997,28 +6989,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D15" s="39" t="s">
+        <v>413</v>
+      </c>
+      <c r="E15" s="39" t="s">
         <v>414</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="F15" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="G15" s="39" t="s">
+        <v>415</v>
+      </c>
+      <c r="H15" s="39" t="s">
         <v>416</v>
       </c>
-      <c r="G15" s="39" t="s">
-        <v>416</v>
-      </c>
-      <c r="H15" s="39" t="s">
+      <c r="I15" s="39" t="s">
         <v>417</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -7026,28 +7018,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D16" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="E16" s="39" t="s">
         <v>419</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="F16" s="39" t="s">
         <v>420</v>
       </c>
-      <c r="F16" s="39" t="s">
-        <v>421</v>
-      </c>
       <c r="G16" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -7055,28 +7047,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -7084,28 +7076,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -7113,10 +7105,10 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
+        <v>423</v>
+      </c>
+      <c r="C19" s="38" t="s">
         <v>424</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>243</v>
       </c>
       <c r="D19" s="39" t="s">
         <v>425</v>
@@ -7125,16 +7117,16 @@
         <v>426</v>
       </c>
       <c r="F19" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="H19" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="G19" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>395</v>
-      </c>
       <c r="I19" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -7142,28 +7134,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>242</v>
+        <v>427</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F20" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="H20" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="G20" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>395</v>
-      </c>
       <c r="I20" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -7171,28 +7163,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -7200,28 +7192,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="H22" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="G22" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>395</v>
-      </c>
       <c r="I22" s="39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -7229,28 +7221,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -7267,7 +7259,7 @@
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -7347,13 +7339,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -7368,28 +7360,28 @@
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>14</v>
@@ -7398,28 +7390,28 @@
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>14</v>
@@ -7428,22 +7420,22 @@
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
@@ -7458,28 +7450,28 @@
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>14</v>
@@ -7488,28 +7480,28 @@
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>14</v>
@@ -7518,28 +7510,28 @@
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>14</v>
@@ -7548,28 +7540,28 @@
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>14</v>
@@ -7578,28 +7570,28 @@
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>14</v>
@@ -7608,28 +7600,28 @@
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>14</v>
@@ -7638,28 +7630,28 @@
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>14</v>
@@ -7668,28 +7660,28 @@
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>14</v>
@@ -7698,28 +7690,28 @@
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>14</v>
@@ -7728,28 +7720,28 @@
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>14</v>
@@ -7758,22 +7750,22 @@
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
@@ -7788,16 +7780,16 @@
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7809,13 +7801,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7827,13 +7819,13 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7845,13 +7837,13 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7862,13 +7854,13 @@
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -7880,13 +7872,13 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7897,13 +7889,13 @@
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7915,13 +7907,13 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7933,13 +7925,13 @@
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7950,13 +7942,13 @@
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7968,13 +7960,13 @@
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7986,16 +7978,16 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -8006,16 +7998,16 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -8026,16 +8018,16 @@
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -8046,16 +8038,16 @@
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -8066,16 +8058,16 @@
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -8086,7 +8078,7 @@
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -8104,13 +8096,13 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>242</v>
+        <v>427</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>244</v>
+        <v>543</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
@@ -8123,13 +8115,13 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>245</v>
+        <v>544</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>246</v>
+        <v>545</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>247</v>
+        <v>546</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
@@ -8148,7 +8140,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -8162,7 +8154,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -8176,7 +8168,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -8190,7 +8182,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -8203,7 +8195,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -8217,7 +8209,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -8230,7 +8222,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -8243,7 +8235,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -8256,17 +8248,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>159</v>
@@ -8275,24 +8267,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>159</v>
@@ -8301,24 +8293,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>159</v>
@@ -8327,24 +8319,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>159</v>
@@ -8353,17 +8345,17 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
     <sheet name="已删" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">在播剧更新时间表!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已删!$A$1:$J$48</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="574">
   <si>
     <t>剧名</t>
   </si>
@@ -903,9 +903,6 @@
     </r>
   </si>
   <si>
-    <t>13/14</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1023,7 +1020,7 @@
     <t>爱情来了</t>
   </si>
   <si>
-    <t>16/50</t>
+    <t>17/50</t>
   </si>
   <si>
     <t>安喜延 / 河锡辰</t>
@@ -1075,7 +1072,7 @@
     <t xml:space="preserve">剧情 / 爱情 </t>
   </si>
   <si>
-    <t>2/14</t>
+    <t>3/14</t>
   </si>
   <si>
     <t xml:space="preserve"> 徐康俊 / 安恩真 / 李周安 / 赵雅兰</t>
@@ -1094,6 +1091,18 @@
   </si>
   <si>
     <t>链接：https://pan.quark.cn/s/0b721e243e8d?pwd=EZFU 提取码：EZFU</t>
+  </si>
+  <si>
+    <t>寄生之心</t>
+  </si>
+  <si>
+    <t>4/28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">瓦拉甘·萨瓦功 / 澈丁娜拉·朋琵拉德 </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/a39245d804f1?pwd=5XKj  提取码：5XKj</t>
   </si>
   <si>
     <t>神的游戏</t>
@@ -2534,23 +2543,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2574,6 +2577,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -3105,7 +3114,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3251,18 +3260,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3276,12 +3276,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3831,7 +3825,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
@@ -4852,28 +4846,28 @@
       <c r="D33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>159</v>
+      <c r="E33" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="G33" s="23">
         <v>2026</v>
       </c>
       <c r="H33" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="I33" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="I33" s="24" t="s">
+      <c r="J33" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="34" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A34" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>138</v>
@@ -4884,8 +4878,8 @@
       <c r="D34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="50" t="s">
-        <v>175</v>
+      <c r="E34" s="22" t="s">
+        <v>174</v>
       </c>
       <c r="F34" s="23" t="s">
         <v>159</v>
@@ -4894,30 +4888,30 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="I34" s="24" t="s">
+      <c r="J34" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="35" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>138</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="50" t="s">
-        <v>181</v>
+      <c r="E35" s="22" t="s">
+        <v>180</v>
       </c>
       <c r="F35" s="23" t="s">
         <v>159</v>
@@ -4926,18 +4920,18 @@
         <v>2026</v>
       </c>
       <c r="H35" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="I35" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="51" t="s">
+      <c r="J35" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="36" s="6" customFormat="1" ht="34" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>138</v>
@@ -4948,8 +4942,8 @@
       <c r="D36" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="52" t="s">
-        <v>186</v>
+      <c r="E36" s="22" t="s">
+        <v>185</v>
       </c>
       <c r="F36" s="23" t="s">
         <v>159</v>
@@ -4958,16 +4952,16 @@
         <v>2026</v>
       </c>
       <c r="H36" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="I36" s="24"/>
+      <c r="J36" s="50" t="s">
         <v>187</v>
-      </c>
-      <c r="I36" s="24"/>
-      <c r="J36" s="53" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="37" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>138</v>
@@ -4978,8 +4972,8 @@
       <c r="D37" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="52" t="s">
-        <v>190</v>
+      <c r="E37" s="22" t="s">
+        <v>189</v>
       </c>
       <c r="F37" s="23" t="s">
         <v>159</v>
@@ -4988,16 +4982,16 @@
         <v>2026</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I37" s="24"/>
       <c r="J37" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A38" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>138</v>
@@ -5008,8 +5002,8 @@
       <c r="D38" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="50" t="s">
-        <v>194</v>
+      <c r="E38" s="22" t="s">
+        <v>193</v>
       </c>
       <c r="F38" s="23" t="s">
         <v>159</v>
@@ -5020,24 +5014,24 @@
       <c r="H38" s="23"/>
       <c r="I38" s="24"/>
       <c r="J38" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>138</v>
       </c>
       <c r="C39" s="48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D39" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="52" t="s">
-        <v>198</v>
+      <c r="E39" s="22" t="s">
+        <v>197</v>
       </c>
       <c r="F39" s="23" t="s">
         <v>159</v>
@@ -5046,28 +5040,28 @@
         <v>2026</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I39" s="24"/>
       <c r="J39" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>138</v>
       </c>
       <c r="C40" s="48" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="52" t="s">
-        <v>203</v>
+      <c r="E40" s="22" t="s">
+        <v>202</v>
       </c>
       <c r="F40" s="23" t="s">
         <v>159</v>
@@ -5075,17 +5069,17 @@
       <c r="G40" s="23">
         <v>2026</v>
       </c>
-      <c r="H40" s="54" t="s">
-        <v>204</v>
+      <c r="H40" s="51" t="s">
+        <v>203</v>
       </c>
       <c r="I40" s="24"/>
       <c r="J40" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>145</v>
@@ -5096,8 +5090,8 @@
       <c r="D41" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E41" s="50" t="s">
-        <v>207</v>
+      <c r="E41" s="22" t="s">
+        <v>206</v>
       </c>
       <c r="F41" s="23" t="s">
         <v>159</v>
@@ -5106,32 +5100,48 @@
         <v>2026</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I41" s="24"/>
       <c r="J41" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A42" s="21" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="42" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A42" s="21"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="7"/>
+      <c r="B42" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>159</v>
+      </c>
       <c r="G42" s="7"/>
-      <c r="H42" s="23"/>
+      <c r="H42" s="23" t="s">
+        <v>211</v>
+      </c>
       <c r="I42" s="24"/>
-      <c r="J42" s="7"/>
+      <c r="J42" s="7" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="43" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A43" s="21"/>
       <c r="B43" s="7"/>
       <c r="C43" s="48"/>
-      <c r="D43" s="7"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="22"/>
-      <c r="F43" s="7"/>
+      <c r="F43" s="23"/>
       <c r="G43" s="7"/>
       <c r="H43" s="23"/>
       <c r="I43" s="24"/>
@@ -5141,9 +5151,9 @@
       <c r="A44" s="21"/>
       <c r="B44" s="7"/>
       <c r="C44" s="48"/>
-      <c r="D44" s="7"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="22"/>
-      <c r="F44" s="7"/>
+      <c r="F44" s="23"/>
       <c r="G44" s="7"/>
       <c r="H44" s="23"/>
       <c r="I44" s="24"/>
@@ -5153,9 +5163,9 @@
       <c r="A45" s="21"/>
       <c r="B45" s="7"/>
       <c r="C45" s="48"/>
-      <c r="D45" s="7"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="22"/>
-      <c r="F45" s="7"/>
+      <c r="F45" s="23"/>
       <c r="G45" s="7"/>
       <c r="H45" s="23"/>
       <c r="I45" s="24"/>
@@ -5185,107 +5195,57 @@
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A48" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="B48" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="41">
-        <v>7</v>
-      </c>
-      <c r="F48" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G48" s="23">
-        <v>2026</v>
-      </c>
+    <row r="48" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A48" s="21"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
       <c r="H48" s="23"/>
-      <c r="I48" s="46" t="s">
-        <v>212</v>
-      </c>
-      <c r="J48" s="23" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A49" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="B49" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="41">
-        <v>10</v>
-      </c>
-      <c r="F49" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G49" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H49" s="51"/>
-      <c r="I49" s="46" t="s">
-        <v>216</v>
-      </c>
-      <c r="J49" s="23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A50" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="B50" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="41">
-        <v>2</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G50" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H50" s="51"/>
-      <c r="I50" s="46" t="s">
-        <v>219</v>
-      </c>
-      <c r="J50" s="23" t="s">
-        <v>220</v>
-      </c>
+      <c r="I48" s="24"/>
+      <c r="J48" s="7"/>
+    </row>
+    <row r="49" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A49" s="21"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="7"/>
+    </row>
+    <row r="50" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A50" s="21"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="7"/>
     </row>
     <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A51" s="25" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="C51" s="23"/>
+      <c r="C51" s="23" t="s">
+        <v>214</v>
+      </c>
       <c r="D51" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F51" s="23" t="s">
         <v>159</v>
@@ -5293,138 +5253,158 @@
       <c r="G51" s="23">
         <v>2026</v>
       </c>
-      <c r="H51" s="51"/>
+      <c r="H51" s="23"/>
       <c r="I51" s="46" t="s">
-        <v>222</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>223</v>
+        <v>215</v>
+      </c>
+      <c r="J51" s="23" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A52" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="B52" s="7" t="s">
+      <c r="A52" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="B52" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="C52" s="48" t="s">
-        <v>225</v>
+      <c r="C52" s="23" t="s">
+        <v>218</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E52" s="55"/>
-      <c r="F52" s="48" t="s">
-        <v>14</v>
+      <c r="E52" s="41">
+        <v>10</v>
+      </c>
+      <c r="F52" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="G52" s="23">
         <v>2026</v>
       </c>
-      <c r="H52" s="23"/>
-      <c r="I52" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="J52" s="7"/>
+      <c r="H52" s="49"/>
+      <c r="I52" s="46" t="s">
+        <v>219</v>
+      </c>
+      <c r="J52" s="23" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A53" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="B53" s="7" t="s">
+      <c r="A53" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="B53" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="C53" s="48" t="s">
-        <v>225</v>
-      </c>
+      <c r="C53" s="23"/>
       <c r="D53" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="55"/>
-      <c r="F53" s="48" t="s">
-        <v>14</v>
+      <c r="E53" s="41">
+        <v>2</v>
+      </c>
+      <c r="F53" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="G53" s="23">
         <v>2026</v>
       </c>
-      <c r="H53" s="23"/>
-      <c r="I53" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="J53" s="7"/>
+      <c r="H53" s="49"/>
+      <c r="I53" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="J53" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A54" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="24" t="s">
-        <v>231</v>
+      <c r="A54" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="41">
+        <v>4</v>
+      </c>
+      <c r="F54" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G54" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H54" s="49"/>
+      <c r="I54" s="46" t="s">
+        <v>225</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A55" s="21" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" s="48" t="s">
+        <v>228</v>
+      </c>
+      <c r="D55" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="52"/>
+      <c r="F55" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
+      <c r="G55" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H55" s="23"/>
       <c r="I55" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>235</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="J55" s="7"/>
     </row>
     <row r="56" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A56" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" s="48" t="s">
+        <v>228</v>
+      </c>
+      <c r="D56" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="52"/>
+      <c r="F56" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
+      <c r="G56" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H56" s="23"/>
       <c r="I56" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>238</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="J56" s="7"/>
     </row>
     <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -5434,99 +5414,85 @@
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
-      <c r="I57" s="24"/>
+      <c r="I57" s="24" t="s">
+        <v>234</v>
+      </c>
       <c r="J57" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="58" ht="25" customHeight="1" spans="1:10">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="22"/>
-      <c r="F58" s="22" t="s">
+      <c r="F58" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G58" s="23">
-        <v>2026</v>
-      </c>
+      <c r="G58" s="7"/>
       <c r="H58" s="7"/>
       <c r="I58" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="J58" s="21" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="59" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>237</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A59" s="21" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="22"/>
-      <c r="F59" s="22" t="s">
+      <c r="F59" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G59" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>245</v>
-      </c>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
       <c r="I59" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="J59" s="24" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="60" ht="24" customHeight="1" spans="1:10">
+        <v>240</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A60" s="21" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>249</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="22"/>
-      <c r="F60" s="22" t="s">
+      <c r="F60" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G60" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="I60" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="J60" s="24" t="s">
-        <v>252</v>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="24"/>
+      <c r="J60" s="7" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:10">
       <c r="A61" s="21" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="7" t="s">
-        <v>254</v>
-      </c>
+      <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="22"/>
       <c r="F61" s="22" t="s">
@@ -5535,37 +5501,49 @@
       <c r="G61" s="23">
         <v>2026</v>
       </c>
-      <c r="H61" s="7" t="s">
-        <v>255</v>
-      </c>
+      <c r="H61" s="7"/>
       <c r="I61" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="J61" s="24" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="62" ht="25" customHeight="1" spans="1:10">
-      <c r="A62" s="21"/>
-      <c r="B62" s="7"/>
+        <v>245</v>
+      </c>
+      <c r="J61" s="21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="62" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A62" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="24"/>
-      <c r="J62" s="24"/>
-    </row>
-    <row r="63" ht="25" customHeight="1" spans="1:10">
-      <c r="A63" s="56" t="s">
-        <v>258</v>
-      </c>
-      <c r="B63" s="57" t="s">
+      <c r="F62" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I62" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="J62" s="24" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1" spans="1:10">
+      <c r="A63" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C63" s="57" t="s">
-        <v>164</v>
+      <c r="C63" s="7" t="s">
+        <v>252</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="22"/>
@@ -5573,75 +5551,85 @@
         <v>14</v>
       </c>
       <c r="G63" s="23">
-        <v>8.25</v>
+        <v>2026</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="I63" s="24"/>
-      <c r="J63" s="21"/>
-    </row>
-    <row r="64" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A64" s="56" t="s">
-        <v>260</v>
+        <v>253</v>
+      </c>
+      <c r="I63" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="J63" s="24" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" ht="25" customHeight="1" spans="1:10">
+      <c r="A64" s="21" t="s">
+        <v>256</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C64" s="7"/>
+      <c r="C64" s="7" t="s">
+        <v>257</v>
+      </c>
       <c r="D64" s="7"/>
       <c r="E64" s="22"/>
       <c r="F64" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G64" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="H64" s="7"/>
-      <c r="I64" s="24"/>
-      <c r="J64" s="21"/>
-    </row>
-    <row r="65" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A65" s="56" t="s">
-        <v>262</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>68</v>
-      </c>
+      <c r="G64" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I64" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="J64" s="24" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" ht="25" customHeight="1" spans="1:10">
+      <c r="A65" s="21"/>
+      <c r="B65" s="7"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="22"/>
-      <c r="F65" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G65" s="23">
-        <v>8.23</v>
-      </c>
+      <c r="F65" s="22"/>
+      <c r="G65" s="23"/>
       <c r="H65" s="7"/>
       <c r="I65" s="24"/>
-      <c r="J65" s="21"/>
-    </row>
-    <row r="66" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A66" s="56" t="s">
-        <v>263</v>
-      </c>
-      <c r="B66" s="7" t="s">
+      <c r="J65" s="24"/>
+    </row>
+    <row r="66" ht="25" customHeight="1" spans="1:10">
+      <c r="A66" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="B66" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="C66" s="7"/>
+      <c r="C66" s="54" t="s">
+        <v>164</v>
+      </c>
       <c r="D66" s="7"/>
       <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="H66" s="7"/>
+      <c r="F66" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="23">
+        <v>8.25</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>262</v>
+      </c>
       <c r="I66" s="24"/>
       <c r="J66" s="21"/>
     </row>
     <row r="67" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A67" s="56" t="s">
-        <v>264</v>
+      <c r="A67" s="53" t="s">
+        <v>263</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>68</v>
@@ -5652,15 +5640,15 @@
       <c r="F67" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G67" s="23">
-        <v>8.21</v>
+      <c r="G67" s="23" t="s">
+        <v>264</v>
       </c>
       <c r="H67" s="7"/>
       <c r="I67" s="24"/>
       <c r="J67" s="21"/>
     </row>
     <row r="68" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A68" s="56" t="s">
+      <c r="A68" s="53" t="s">
         <v>265</v>
       </c>
       <c r="B68" s="7" t="s">
@@ -5669,14 +5657,18 @@
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="23"/>
+      <c r="F68" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="23">
+        <v>8.23</v>
+      </c>
       <c r="H68" s="7"/>
       <c r="I68" s="24"/>
       <c r="J68" s="21"/>
     </row>
     <row r="69" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A69" s="56" t="s">
+      <c r="A69" s="53" t="s">
         <v>266</v>
       </c>
       <c r="B69" s="7" t="s">
@@ -5686,32 +5678,40 @@
       <c r="D69" s="7"/>
       <c r="E69" s="22"/>
       <c r="F69" s="22"/>
-      <c r="G69" s="23">
-        <v>5.15</v>
+      <c r="G69" s="23" t="s">
+        <v>264</v>
       </c>
       <c r="H69" s="7"/>
       <c r="I69" s="24"/>
       <c r="J69" s="21"/>
     </row>
     <row r="70" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A70" s="56" t="s">
+      <c r="A70" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="B70" s="7"/>
+      <c r="B70" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="23"/>
+      <c r="F70" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="23">
+        <v>8.21</v>
+      </c>
       <c r="H70" s="7"/>
       <c r="I70" s="24"/>
       <c r="J70" s="21"/>
     </row>
-    <row r="71" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A71" s="56" t="s">
+    <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A71" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="B71" s="7"/>
+      <c r="B71" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="22"/>
@@ -5722,21 +5722,25 @@
       <c r="J71" s="21"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A72" s="56" t="s">
+      <c r="A72" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="B72" s="7"/>
+      <c r="B72" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="22"/>
       <c r="F72" s="22"/>
-      <c r="G72" s="23"/>
+      <c r="G72" s="23">
+        <v>5.15</v>
+      </c>
       <c r="H72" s="7"/>
       <c r="I72" s="24"/>
       <c r="J72" s="21"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A73" s="56" t="s">
+      <c r="A73" s="53" t="s">
         <v>270</v>
       </c>
       <c r="B73" s="7"/>
@@ -5749,64 +5753,58 @@
       <c r="I73" s="24"/>
       <c r="J73" s="21"/>
     </row>
-    <row r="74" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A74" s="56" t="s">
+    <row r="74" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
+      <c r="A74" s="53" t="s">
         <v>271</v>
       </c>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="22"/>
-      <c r="F74" s="22" t="s">
-        <v>272</v>
-      </c>
+      <c r="F74" s="22"/>
       <c r="G74" s="23"/>
       <c r="H74" s="7"/>
       <c r="I74" s="24"/>
-      <c r="J74" s="24"/>
-    </row>
-    <row r="75" ht="25" customHeight="1" spans="1:10">
-      <c r="A75" s="56" t="s">
-        <v>273</v>
+      <c r="J74" s="21"/>
+    </row>
+    <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A75" s="53" t="s">
+        <v>272</v>
       </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="22"/>
-      <c r="F75" s="22" t="s">
-        <v>274</v>
-      </c>
+      <c r="F75" s="22"/>
       <c r="G75" s="23"/>
       <c r="H75" s="7"/>
       <c r="I75" s="24"/>
-      <c r="J75" s="24"/>
-    </row>
-    <row r="76" ht="25" customHeight="1" spans="1:10">
-      <c r="A76" s="21" t="s">
-        <v>248</v>
+      <c r="J75" s="21"/>
+    </row>
+    <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A76" s="53" t="s">
+        <v>273</v>
       </c>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="22"/>
-      <c r="F76" s="22" t="s">
-        <v>275</v>
-      </c>
+      <c r="F76" s="22"/>
       <c r="G76" s="23"/>
       <c r="H76" s="7"/>
       <c r="I76" s="24"/>
-      <c r="J76" s="24"/>
-    </row>
-    <row r="77" ht="25" customHeight="1" spans="1:10">
-      <c r="A77" s="56" t="s">
-        <v>276</v>
+      <c r="J76" s="21"/>
+    </row>
+    <row r="77" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A77" s="53" t="s">
+        <v>274</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="22"/>
       <c r="F77" s="22" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G77" s="23"/>
       <c r="H77" s="7"/>
@@ -5814,15 +5812,15 @@
       <c r="J77" s="24"/>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:10">
-      <c r="A78" s="56" t="s">
-        <v>278</v>
+      <c r="A78" s="53" t="s">
+        <v>276</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="22"/>
-      <c r="F78" s="22">
-        <v>102</v>
+      <c r="F78" s="22" t="s">
+        <v>277</v>
       </c>
       <c r="G78" s="23"/>
       <c r="H78" s="7"/>
@@ -5830,15 +5828,15 @@
       <c r="J78" s="24"/>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:10">
-      <c r="A79" s="56" t="s">
-        <v>279</v>
+      <c r="A79" s="21" t="s">
+        <v>251</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="22"/>
-      <c r="F79" s="22">
-        <v>69</v>
+      <c r="F79" s="22" t="s">
+        <v>278</v>
       </c>
       <c r="G79" s="23"/>
       <c r="H79" s="7"/>
@@ -5846,15 +5844,15 @@
       <c r="J79" s="24"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:10">
-      <c r="A80" s="56" t="s">
-        <v>280</v>
+      <c r="A80" s="53" t="s">
+        <v>279</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="22"/>
-      <c r="F80" s="22">
-        <v>86</v>
+      <c r="F80" s="22" t="s">
+        <v>280</v>
       </c>
       <c r="G80" s="23"/>
       <c r="H80" s="7"/>
@@ -5862,29 +5860,31 @@
       <c r="J80" s="24"/>
     </row>
     <row r="81" ht="25" customHeight="1" spans="1:10">
-      <c r="A81" s="56" t="s">
+      <c r="A81" s="53" t="s">
         <v>281</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="22"/>
-      <c r="F81" s="22"/>
+      <c r="F81" s="22">
+        <v>102</v>
+      </c>
       <c r="G81" s="23"/>
       <c r="H81" s="7"/>
       <c r="I81" s="24"/>
       <c r="J81" s="24"/>
     </row>
     <row r="82" ht="25" customHeight="1" spans="1:10">
-      <c r="A82" s="56" t="s">
+      <c r="A82" s="53" t="s">
         <v>282</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="22"/>
-      <c r="F82" s="22" t="s">
-        <v>283</v>
+      <c r="F82" s="22">
+        <v>69</v>
       </c>
       <c r="G82" s="23"/>
       <c r="H82" s="7"/>
@@ -5892,22 +5892,24 @@
       <c r="J82" s="24"/>
     </row>
     <row r="83" ht="25" customHeight="1" spans="1:10">
-      <c r="A83" s="56" t="s">
-        <v>284</v>
+      <c r="A83" s="53" t="s">
+        <v>283</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
+      <c r="F83" s="22">
+        <v>86</v>
+      </c>
       <c r="G83" s="23"/>
       <c r="H83" s="7"/>
       <c r="I83" s="24"/>
       <c r="J83" s="24"/>
     </row>
     <row r="84" ht="25" customHeight="1" spans="1:10">
-      <c r="A84" s="56" t="s">
-        <v>285</v>
+      <c r="A84" s="53" t="s">
+        <v>284</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -5920,15 +5922,15 @@
       <c r="J84" s="24"/>
     </row>
     <row r="85" ht="25" customHeight="1" spans="1:10">
-      <c r="A85" s="56" t="s">
-        <v>286</v>
+      <c r="A85" s="53" t="s">
+        <v>285</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="22"/>
       <c r="F85" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G85" s="23"/>
       <c r="H85" s="7"/>
@@ -5936,51 +5938,43 @@
       <c r="J85" s="24"/>
     </row>
     <row r="86" ht="25" customHeight="1" spans="1:10">
-      <c r="A86" s="56" t="s">
-        <v>288</v>
+      <c r="A86" s="53" t="s">
+        <v>287</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="22"/>
-      <c r="F86" s="22" t="s">
-        <v>289</v>
-      </c>
+      <c r="F86" s="22"/>
       <c r="G86" s="23"/>
       <c r="H86" s="7"/>
       <c r="I86" s="24"/>
       <c r="J86" s="24"/>
     </row>
     <row r="87" ht="25" customHeight="1" spans="1:10">
-      <c r="A87" s="56" t="s">
-        <v>290</v>
+      <c r="A87" s="53" t="s">
+        <v>288</v>
       </c>
       <c r="B87" s="7"/>
-      <c r="C87" s="7" t="s">
-        <v>291</v>
-      </c>
+      <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="22"/>
-      <c r="F87" s="22" t="s">
-        <v>292</v>
-      </c>
+      <c r="F87" s="22"/>
       <c r="G87" s="23"/>
       <c r="H87" s="7"/>
       <c r="I87" s="24"/>
       <c r="J87" s="24"/>
     </row>
     <row r="88" ht="25" customHeight="1" spans="1:10">
-      <c r="A88" s="56" t="s">
-        <v>293</v>
+      <c r="A88" s="53" t="s">
+        <v>289</v>
       </c>
       <c r="B88" s="7"/>
-      <c r="C88" s="7" t="s">
-        <v>294</v>
-      </c>
+      <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="22"/>
       <c r="F88" s="22" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G88" s="23"/>
       <c r="H88" s="7"/>
@@ -5988,17 +5982,15 @@
       <c r="J88" s="24"/>
     </row>
     <row r="89" ht="25" customHeight="1" spans="1:10">
-      <c r="A89" s="56" t="s">
-        <v>296</v>
+      <c r="A89" s="53" t="s">
+        <v>291</v>
       </c>
       <c r="B89" s="7"/>
-      <c r="C89" s="7" t="s">
-        <v>297</v>
-      </c>
+      <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="22"/>
       <c r="F89" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="G89" s="23"/>
       <c r="H89" s="7"/>
@@ -6006,17 +5998,17 @@
       <c r="J89" s="24"/>
     </row>
     <row r="90" ht="25" customHeight="1" spans="1:10">
-      <c r="A90" s="56" t="s">
-        <v>299</v>
+      <c r="A90" s="53" t="s">
+        <v>293</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D90" s="7"/>
       <c r="E90" s="22"/>
       <c r="F90" s="22" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G90" s="23"/>
       <c r="H90" s="7"/>
@@ -6024,17 +6016,17 @@
       <c r="J90" s="24"/>
     </row>
     <row r="91" ht="25" customHeight="1" spans="1:10">
-      <c r="A91" s="56" t="s">
-        <v>301</v>
+      <c r="A91" s="53" t="s">
+        <v>296</v>
       </c>
       <c r="B91" s="7"/>
       <c r="C91" s="7" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="22"/>
       <c r="F91" s="22" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G91" s="23"/>
       <c r="H91" s="7"/>
@@ -6042,17 +6034,17 @@
       <c r="J91" s="24"/>
     </row>
     <row r="92" ht="25" customHeight="1" spans="1:10">
-      <c r="A92" s="56" t="s">
-        <v>304</v>
+      <c r="A92" s="53" t="s">
+        <v>299</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D92" s="7"/>
       <c r="E92" s="22"/>
       <c r="F92" s="22" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="G92" s="23"/>
       <c r="H92" s="7"/>
@@ -6060,17 +6052,17 @@
       <c r="J92" s="24"/>
     </row>
     <row r="93" ht="25" customHeight="1" spans="1:10">
-      <c r="A93" s="56" t="s">
-        <v>307</v>
+      <c r="A93" s="53" t="s">
+        <v>302</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="G93" s="23"/>
       <c r="H93" s="7"/>
@@ -6078,17 +6070,17 @@
       <c r="J93" s="24"/>
     </row>
     <row r="94" ht="25" customHeight="1" spans="1:10">
-      <c r="A94" s="56" t="s">
-        <v>310</v>
+      <c r="A94" s="53" t="s">
+        <v>304</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="22"/>
       <c r="F94" s="22" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="G94" s="23"/>
       <c r="H94" s="7"/>
@@ -6096,17 +6088,17 @@
       <c r="J94" s="24"/>
     </row>
     <row r="95" ht="25" customHeight="1" spans="1:10">
-      <c r="A95" s="56" t="s">
-        <v>312</v>
+      <c r="A95" s="53" t="s">
+        <v>307</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="G95" s="23"/>
       <c r="H95" s="7"/>
@@ -6114,17 +6106,17 @@
       <c r="J95" s="24"/>
     </row>
     <row r="96" ht="25" customHeight="1" spans="1:10">
-      <c r="A96" s="56" t="s">
-        <v>315</v>
+      <c r="A96" s="53" t="s">
+        <v>310</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="22"/>
       <c r="F96" s="22" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G96" s="23"/>
       <c r="H96" s="7"/>
@@ -6132,17 +6124,17 @@
       <c r="J96" s="24"/>
     </row>
     <row r="97" ht="25" customHeight="1" spans="1:10">
-      <c r="A97" s="56" t="s">
-        <v>317</v>
+      <c r="A97" s="53" t="s">
+        <v>313</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22" t="s">
-        <v>319</v>
+        <v>280</v>
       </c>
       <c r="G97" s="23"/>
       <c r="H97" s="7"/>
@@ -6150,69 +6142,71 @@
       <c r="J97" s="24"/>
     </row>
     <row r="98" ht="25" customHeight="1" spans="1:10">
-      <c r="A98" s="56" t="s">
-        <v>320</v>
-      </c>
-      <c r="B98" s="57"/>
-      <c r="C98" s="57" t="s">
-        <v>321</v>
-      </c>
-      <c r="D98" s="57"/>
+      <c r="A98" s="53" t="s">
+        <v>315</v>
+      </c>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D98" s="7"/>
       <c r="E98" s="22"/>
-      <c r="F98" s="58" t="s">
-        <v>289</v>
-      </c>
-      <c r="G98" s="59"/>
+      <c r="F98" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="G98" s="23"/>
       <c r="H98" s="7"/>
       <c r="I98" s="24"/>
       <c r="J98" s="24"/>
     </row>
     <row r="99" ht="25" customHeight="1" spans="1:10">
-      <c r="A99" s="56" t="s">
-        <v>322</v>
-      </c>
-      <c r="B99" s="57"/>
-      <c r="C99" s="57" t="s">
-        <v>300</v>
-      </c>
-      <c r="D99" s="57"/>
+      <c r="A99" s="53" t="s">
+        <v>318</v>
+      </c>
+      <c r="B99" s="7"/>
+      <c r="C99" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D99" s="7"/>
       <c r="E99" s="22"/>
-      <c r="F99" s="58" t="s">
-        <v>323</v>
-      </c>
-      <c r="G99" s="59"/>
+      <c r="F99" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="G99" s="23"/>
       <c r="H99" s="7"/>
       <c r="I99" s="24"/>
       <c r="J99" s="24"/>
     </row>
     <row r="100" ht="25" customHeight="1" spans="1:10">
-      <c r="A100" s="56" t="s">
-        <v>324</v>
-      </c>
-      <c r="B100" s="57"/>
-      <c r="C100" s="57"/>
-      <c r="D100" s="57"/>
+      <c r="A100" s="53" t="s">
+        <v>320</v>
+      </c>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="D100" s="7"/>
       <c r="E100" s="22"/>
-      <c r="F100" s="58" t="s">
-        <v>325</v>
-      </c>
-      <c r="G100" s="59"/>
+      <c r="F100" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="G100" s="23"/>
       <c r="H100" s="7"/>
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
     </row>
     <row r="101" ht="25" customHeight="1" spans="1:10">
-      <c r="A101" s="56" t="s">
-        <v>326</v>
-      </c>
-      <c r="B101" s="57"/>
-      <c r="C101" s="57" t="s">
-        <v>327</v>
-      </c>
-      <c r="D101" s="57"/>
+      <c r="A101" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D101" s="7"/>
       <c r="E101" s="22"/>
-      <c r="F101" s="58" t="s">
-        <v>328</v>
+      <c r="F101" s="22" t="s">
+        <v>292</v>
       </c>
       <c r="G101" s="23"/>
       <c r="H101" s="7"/>
@@ -6220,141 +6214,139 @@
       <c r="J101" s="24"/>
     </row>
     <row r="102" ht="25" customHeight="1" spans="1:10">
-      <c r="A102" s="56" t="s">
-        <v>329</v>
-      </c>
-      <c r="B102" s="57"/>
-      <c r="C102" s="57" t="s">
-        <v>330</v>
-      </c>
-      <c r="D102" s="57"/>
+      <c r="A102" s="53" t="s">
+        <v>325</v>
+      </c>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D102" s="7"/>
       <c r="E102" s="22"/>
-      <c r="F102" s="58" t="s">
-        <v>331</v>
+      <c r="F102" s="22" t="s">
+        <v>326</v>
       </c>
       <c r="G102" s="23"/>
       <c r="H102" s="7"/>
       <c r="I102" s="24"/>
       <c r="J102" s="24"/>
     </row>
-    <row r="103" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A103" s="60" t="s">
+    <row r="103" ht="25" customHeight="1" spans="1:10">
+      <c r="A103" s="53" t="s">
+        <v>327</v>
+      </c>
+      <c r="B103" s="7"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="G103" s="23"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="24"/>
+      <c r="J103" s="24"/>
+    </row>
+    <row r="104" ht="25" customHeight="1" spans="1:10">
+      <c r="A104" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D104" s="7"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="G104" s="23"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="24"/>
+      <c r="J104" s="24"/>
+    </row>
+    <row r="105" ht="25" customHeight="1" spans="1:10">
+      <c r="A105" s="53" t="s">
         <v>332</v>
       </c>
-      <c r="B103" s="48"/>
-      <c r="C103" s="48" t="s">
-        <v>291</v>
-      </c>
-      <c r="D103" s="48"/>
-      <c r="E103" s="55"/>
-      <c r="F103" s="55" t="s">
-        <v>289</v>
-      </c>
-      <c r="G103" s="23"/>
-      <c r="H103" s="48"/>
-      <c r="I103" s="61"/>
-      <c r="J103" s="61"/>
-    </row>
-    <row r="104" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A104" s="60" t="s">
+      <c r="B105" s="7"/>
+      <c r="C105" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="B104" s="48"/>
-      <c r="C104" s="48"/>
-      <c r="D104" s="48"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="55" t="s">
+      <c r="D105" s="7"/>
+      <c r="E105" s="22"/>
+      <c r="F105" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="G104" s="23"/>
-      <c r="H104" s="48"/>
-      <c r="I104" s="61"/>
-      <c r="J104" s="61"/>
-    </row>
-    <row r="105" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A105" s="60" t="s">
+      <c r="G105" s="23"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="24"/>
+      <c r="J105" s="24"/>
+    </row>
+    <row r="106" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A106" s="55" t="s">
         <v>335</v>
       </c>
-      <c r="B105" s="48"/>
-      <c r="C105" s="57" t="s">
-        <v>321</v>
-      </c>
-      <c r="D105" s="48"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="55" t="s">
+      <c r="B106" s="48"/>
+      <c r="C106" s="48" t="s">
+        <v>294</v>
+      </c>
+      <c r="D106" s="48"/>
+      <c r="E106" s="52"/>
+      <c r="F106" s="52" t="s">
+        <v>292</v>
+      </c>
+      <c r="G106" s="23"/>
+      <c r="H106" s="48"/>
+      <c r="I106" s="56"/>
+      <c r="J106" s="56"/>
+    </row>
+    <row r="107" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A107" s="55" t="s">
         <v>336</v>
       </c>
-      <c r="G105" s="23"/>
-      <c r="H105" s="48"/>
-      <c r="I105" s="61"/>
-      <c r="J105" s="61"/>
-    </row>
-    <row r="106" ht="25" customHeight="1" spans="1:10">
-      <c r="A106" s="56" t="s">
+      <c r="B107" s="48"/>
+      <c r="C107" s="48"/>
+      <c r="D107" s="48"/>
+      <c r="E107" s="52"/>
+      <c r="F107" s="52" t="s">
         <v>337</v>
       </c>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7" t="s">
+      <c r="G107" s="23"/>
+      <c r="H107" s="48"/>
+      <c r="I107" s="56"/>
+      <c r="J107" s="56"/>
+    </row>
+    <row r="108" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A108" s="55" t="s">
         <v>338</v>
       </c>
-      <c r="D106" s="7"/>
-      <c r="E106" s="22"/>
-      <c r="F106" s="22" t="s">
+      <c r="B108" s="48"/>
+      <c r="C108" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D108" s="48"/>
+      <c r="E108" s="52"/>
+      <c r="F108" s="52" t="s">
         <v>339</v>
       </c>
-      <c r="G106" s="23"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="24"/>
-      <c r="J106" s="24"/>
-    </row>
-    <row r="107" ht="25" customHeight="1" spans="1:10">
-      <c r="A107" s="56" t="s">
+      <c r="G108" s="23"/>
+      <c r="H108" s="48"/>
+      <c r="I108" s="56"/>
+      <c r="J108" s="56"/>
+    </row>
+    <row r="109" ht="25" customHeight="1" spans="1:10">
+      <c r="A109" s="53" t="s">
         <v>340</v>
       </c>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="D107" s="7"/>
-      <c r="E107" s="22"/>
-      <c r="F107" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="G107" s="23"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="24"/>
-      <c r="J107" s="24"/>
-    </row>
-    <row r="108" ht="25" customHeight="1" spans="1:10">
-      <c r="A108" s="56" t="s">
+      <c r="B109" s="7"/>
+      <c r="C109" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B108" s="7"/>
-      <c r="C108" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="D108" s="7"/>
-      <c r="E108" s="22"/>
-      <c r="F108" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="G108" s="23"/>
-      <c r="H108" s="7"/>
-      <c r="I108" s="24"/>
-      <c r="J108" s="24"/>
-    </row>
-    <row r="109" ht="25" customHeight="1" spans="1:10">
-      <c r="A109" s="56" t="s">
+      <c r="D109" s="7"/>
+      <c r="E109" s="22"/>
+      <c r="F109" s="22" t="s">
         <v>342</v>
-      </c>
-      <c r="B109" s="57"/>
-      <c r="C109" s="57" t="s">
-        <v>308</v>
-      </c>
-      <c r="D109" s="57"/>
-      <c r="E109" s="58"/>
-      <c r="F109" s="58" t="s">
-        <v>343</v>
       </c>
       <c r="G109" s="23"/>
       <c r="H109" s="7"/>
@@ -6362,17 +6354,17 @@
       <c r="J109" s="24"/>
     </row>
     <row r="110" ht="25" customHeight="1" spans="1:10">
-      <c r="A110" s="56" t="s">
-        <v>344</v>
-      </c>
-      <c r="B110" s="57"/>
-      <c r="C110" s="57" t="s">
-        <v>345</v>
-      </c>
-      <c r="D110" s="57"/>
-      <c r="E110" s="58"/>
-      <c r="F110" s="58" t="s">
-        <v>336</v>
+      <c r="A110" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D110" s="7"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="22" t="s">
+        <v>280</v>
       </c>
       <c r="G110" s="23"/>
       <c r="H110" s="7"/>
@@ -6380,17 +6372,17 @@
       <c r="J110" s="24"/>
     </row>
     <row r="111" ht="25" customHeight="1" spans="1:10">
-      <c r="A111" s="56" t="s">
-        <v>346</v>
-      </c>
-      <c r="B111" s="57"/>
-      <c r="C111" s="57" t="s">
-        <v>347</v>
-      </c>
-      <c r="D111" s="57"/>
-      <c r="E111" s="58"/>
-      <c r="F111" s="58" t="s">
-        <v>348</v>
+      <c r="A111" s="53" t="s">
+        <v>344</v>
+      </c>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D111" s="7"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22" t="s">
+        <v>280</v>
       </c>
       <c r="G111" s="23"/>
       <c r="H111" s="7"/>
@@ -6398,17 +6390,17 @@
       <c r="J111" s="24"/>
     </row>
     <row r="112" ht="25" customHeight="1" spans="1:10">
-      <c r="A112" s="56" t="s">
-        <v>349</v>
-      </c>
-      <c r="B112" s="57"/>
-      <c r="C112" s="57" t="s">
-        <v>300</v>
-      </c>
-      <c r="D112" s="57"/>
-      <c r="E112" s="58"/>
-      <c r="F112" s="58" t="s">
-        <v>350</v>
+      <c r="A112" s="53" t="s">
+        <v>345</v>
+      </c>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D112" s="7"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="22" t="s">
+        <v>346</v>
       </c>
       <c r="G112" s="23"/>
       <c r="H112" s="7"/>
@@ -6416,36 +6408,35 @@
       <c r="J112" s="24"/>
     </row>
     <row r="113" ht="25" customHeight="1" spans="1:10">
-      <c r="A113" s="56" t="s">
-        <v>351</v>
-      </c>
-      <c r="B113" s="57"/>
-      <c r="C113" s="57" t="s">
-        <v>352</v>
-      </c>
-      <c r="D113" s="57"/>
-      <c r="E113" s="58"/>
-      <c r="F113" s="58" t="s">
-        <v>353</v>
+      <c r="A113" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="D113" s="7"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="22" t="s">
+        <v>339</v>
       </c>
       <c r="G113" s="23"/>
       <c r="H113" s="7"/>
       <c r="I113" s="24"/>
-      <c r="J113" s="24">
-        <f>2100*60</f>
-        <v>126000</v>
-      </c>
+      <c r="J113" s="24"/>
     </row>
     <row r="114" ht="25" customHeight="1" spans="1:10">
-      <c r="A114" s="56" t="s">
-        <v>354</v>
-      </c>
-      <c r="B114" s="57"/>
-      <c r="C114" s="57"/>
-      <c r="D114" s="57"/>
-      <c r="E114" s="58"/>
-      <c r="F114" s="58" t="s">
-        <v>355</v>
+      <c r="A114" s="53" t="s">
+        <v>349</v>
+      </c>
+      <c r="B114" s="7"/>
+      <c r="C114" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="D114" s="7"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="22" t="s">
+        <v>351</v>
       </c>
       <c r="G114" s="23"/>
       <c r="H114" s="7"/>
@@ -6453,17 +6444,17 @@
       <c r="J114" s="24"/>
     </row>
     <row r="115" ht="25" customHeight="1" spans="1:10">
-      <c r="A115" s="21" t="s">
-        <v>356</v>
+      <c r="A115" s="53" t="s">
+        <v>352</v>
       </c>
       <c r="B115" s="7"/>
       <c r="C115" s="7" t="s">
-        <v>357</v>
+        <v>303</v>
       </c>
       <c r="D115" s="7"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G115" s="23"/>
       <c r="H115" s="7"/>
@@ -6471,61 +6462,212 @@
       <c r="J115" s="24"/>
     </row>
     <row r="116" ht="25" customHeight="1" spans="1:10">
-      <c r="A116" s="21" t="s">
-        <v>359</v>
+      <c r="A116" s="53" t="s">
+        <v>354</v>
       </c>
       <c r="B116" s="7"/>
       <c r="C116" s="7" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D116" s="7"/>
       <c r="E116" s="22"/>
       <c r="F116" s="22" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="G116" s="23"/>
       <c r="H116" s="7"/>
       <c r="I116" s="24"/>
-      <c r="J116" s="24"/>
+      <c r="J116" s="24">
+        <f>2100*60</f>
+        <v>126000</v>
+      </c>
     </row>
     <row r="117" ht="25" customHeight="1" spans="1:10">
-      <c r="A117" s="21"/>
+      <c r="A117" s="53" t="s">
+        <v>357</v>
+      </c>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
       <c r="E117" s="22"/>
-      <c r="F117" s="22"/>
+      <c r="F117" s="22" t="s">
+        <v>358</v>
+      </c>
       <c r="G117" s="23"/>
       <c r="H117" s="7"/>
       <c r="I117" s="24"/>
       <c r="J117" s="24"/>
     </row>
     <row r="118" ht="25" customHeight="1" spans="1:10">
-      <c r="A118" s="21"/>
+      <c r="A118" s="53" t="s">
+        <v>359</v>
+      </c>
       <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
+      <c r="C118" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="D118" s="7"/>
       <c r="E118" s="22"/>
-      <c r="F118" s="22"/>
+      <c r="F118" s="22" t="s">
+        <v>361</v>
+      </c>
       <c r="G118" s="23"/>
       <c r="H118" s="7"/>
       <c r="I118" s="24"/>
       <c r="J118" s="24"/>
     </row>
     <row r="119" ht="25" customHeight="1" spans="1:10">
-      <c r="A119" s="21"/>
+      <c r="A119" s="53" t="s">
+        <v>362</v>
+      </c>
       <c r="B119" s="7"/>
-      <c r="C119" s="7"/>
+      <c r="C119" s="7" t="s">
+        <v>363</v>
+      </c>
       <c r="D119" s="7"/>
       <c r="E119" s="22"/>
-      <c r="F119" s="22"/>
+      <c r="F119" s="22" t="s">
+        <v>364</v>
+      </c>
       <c r="G119" s="23"/>
       <c r="H119" s="7"/>
       <c r="I119" s="24"/>
       <c r="J119" s="24"/>
     </row>
+    <row r="120" ht="25" customHeight="1" spans="1:10">
+      <c r="A120" s="21"/>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="22"/>
+      <c r="F120" s="22"/>
+      <c r="G120" s="23"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="24"/>
+      <c r="J120" s="24"/>
+    </row>
+    <row r="121" ht="25" customHeight="1" spans="1:10">
+      <c r="A121" s="21"/>
+      <c r="B121" s="7"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="22"/>
+      <c r="F121" s="22"/>
+      <c r="G121" s="23"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="24"/>
+    </row>
+    <row r="122" ht="25" customHeight="1" spans="1:10">
+      <c r="A122" s="21"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="22"/>
+      <c r="F122" s="22"/>
+      <c r="G122" s="23"/>
+      <c r="H122" s="7"/>
+      <c r="I122" s="24"/>
+      <c r="J122" s="24"/>
+    </row>
+    <row r="123" ht="25" customHeight="1" spans="1:10">
+      <c r="A123" s="21"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="22"/>
+      <c r="G123" s="23"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="24"/>
+    </row>
+    <row r="124" ht="25" customHeight="1" spans="1:10">
+      <c r="A124" s="21"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="22"/>
+      <c r="F124" s="22"/>
+      <c r="G124" s="23"/>
+      <c r="H124" s="7"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="24"/>
+    </row>
+    <row r="125" ht="25" customHeight="1" spans="1:10">
+      <c r="A125" s="21"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="22"/>
+      <c r="F125" s="22"/>
+      <c r="G125" s="23"/>
+      <c r="H125" s="7"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="24"/>
+    </row>
+    <row r="126" ht="25" customHeight="1" spans="1:10">
+      <c r="A126" s="21"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="22"/>
+      <c r="F126" s="22"/>
+      <c r="G126" s="23"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="24"/>
+      <c r="J126" s="24"/>
+    </row>
+    <row r="127" ht="25" customHeight="1" spans="1:10">
+      <c r="A127" s="21"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="23"/>
+      <c r="H127" s="7"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="24"/>
+    </row>
+    <row r="128" ht="25" customHeight="1" spans="1:10">
+      <c r="A128" s="21"/>
+      <c r="B128" s="7"/>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="22"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="23"/>
+      <c r="H128" s="7"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="24"/>
+    </row>
+    <row r="129" ht="25" customHeight="1" spans="1:10">
+      <c r="A129" s="21"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22"/>
+      <c r="G129" s="23"/>
+      <c r="H129" s="7"/>
+      <c r="I129" s="24"/>
+      <c r="J129" s="24"/>
+    </row>
+    <row r="130" ht="25" customHeight="1" spans="1:10">
+      <c r="A130" s="21"/>
+      <c r="B130" s="7"/>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="22"/>
+      <c r="F130" s="22"/>
+      <c r="G130" s="23"/>
+      <c r="H130" s="7"/>
+      <c r="I130" s="24"/>
+      <c r="J130" s="24"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J115" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J119" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <colorFilter dxfId="0"/>
       <extLst>
@@ -6548,7 +6690,7 @@
         </dxfs>
       </extLst>
     </filterColumn>
-    <sortState ref="A1:J115">
+    <sortState ref="A1:J119">
       <sortCondition ref="F1:F87"/>
     </sortState>
     <extLst/>
@@ -6580,7 +6722,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6589,22 +6731,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6618,22 +6760,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6647,22 +6789,22 @@
         <v>11</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E3" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="F3" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="G3" s="39" t="s">
+        <v>381</v>
+      </c>
+      <c r="H3" s="39" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="39" t="s">
-        <v>377</v>
-      </c>
-      <c r="G3" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>373</v>
-      </c>
       <c r="I3" s="39" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6676,22 +6818,22 @@
         <v>11</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G4" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>386</v>
+      </c>
+      <c r="I4" s="39" t="s">
         <v>382</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>383</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6705,22 +6847,22 @@
         <v>11</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6734,22 +6876,22 @@
         <v>11</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6757,28 +6899,28 @@
         <v>7</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6786,28 +6928,28 @@
         <v>8</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E8" s="39" t="s">
+        <v>399</v>
+      </c>
+      <c r="F8" s="39" t="s">
         <v>396</v>
       </c>
-      <c r="F8" s="39" t="s">
-        <v>393</v>
-      </c>
       <c r="G8" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6821,22 +6963,22 @@
         <v>157</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6850,22 +6992,22 @@
         <v>157</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -6879,22 +7021,22 @@
         <v>138</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -6908,22 +7050,22 @@
         <v>138</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -6931,28 +7073,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -6966,22 +7108,22 @@
         <v>145</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -6989,28 +7131,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -7018,28 +7160,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F16" s="39" t="s">
+        <v>423</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>423</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="I16" s="39" t="s">
         <v>420</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>420</v>
-      </c>
-      <c r="H16" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -7047,28 +7189,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -7076,28 +7218,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>157</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -7105,28 +7247,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -7134,28 +7276,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
+        <v>430</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>427</v>
       </c>
-      <c r="C20" s="38" t="s">
-        <v>424</v>
-      </c>
       <c r="D20" s="39" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -7163,28 +7305,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -7192,28 +7334,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -7221,28 +7363,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -7259,7 +7401,7 @@
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -7339,13 +7481,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -7360,28 +7502,28 @@
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>14</v>
@@ -7390,28 +7532,28 @@
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>14</v>
@@ -7420,22 +7562,22 @@
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
@@ -7450,28 +7592,28 @@
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>14</v>
@@ -7480,28 +7622,28 @@
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>14</v>
@@ -7510,28 +7652,28 @@
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>14</v>
@@ -7540,28 +7682,28 @@
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>14</v>
@@ -7570,28 +7712,28 @@
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>14</v>
@@ -7600,28 +7742,28 @@
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>14</v>
@@ -7630,28 +7772,28 @@
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>14</v>
@@ -7660,28 +7802,28 @@
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>14</v>
@@ -7690,28 +7832,28 @@
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>14</v>
@@ -7720,28 +7862,28 @@
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>14</v>
@@ -7750,22 +7892,22 @@
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
@@ -7780,16 +7922,16 @@
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7801,13 +7943,13 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7819,13 +7961,13 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7837,13 +7979,13 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7854,13 +7996,13 @@
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -7872,13 +8014,13 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7889,13 +8031,13 @@
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7907,13 +8049,13 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7925,13 +8067,13 @@
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7942,13 +8084,13 @@
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7960,13 +8102,13 @@
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7978,16 +8120,16 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -7998,16 +8140,16 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -8018,16 +8160,16 @@
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -8038,16 +8180,16 @@
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -8058,16 +8200,16 @@
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -8078,7 +8220,7 @@
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -8096,13 +8238,13 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>424</v>
-      </c>
       <c r="C34" s="26" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
@@ -8115,18 +8257,18 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -8140,7 +8282,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -8154,7 +8296,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -8168,7 +8310,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -8182,7 +8324,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -8195,7 +8337,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -8209,7 +8351,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -8222,7 +8364,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -8235,7 +8377,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -8248,17 +8390,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>159</v>
@@ -8267,24 +8409,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>159</v>
@@ -8293,24 +8435,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>159</v>
@@ -8319,24 +8461,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>159</v>
@@ -8345,17 +8487,17 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
     <sheet name="已删" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">在播剧更新时间表!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已删!$A$1:$J$48</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="585">
   <si>
     <t>剧名</t>
   </si>
@@ -71,6 +71,385 @@
     <t>夸克链接</t>
   </si>
   <si>
+    <t>家庭关系证明书</t>
+  </si>
+  <si>
+    <t>韩剧</t>
+  </si>
+  <si>
+    <t>剧情</t>
+  </si>
+  <si>
+    <t>1080P</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>更新中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">朴世荣 / 韩高恩 / 林志恩 / 成伊言 / 朴率拉 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1inTr-QEh-UzsyRlDfM0gbA?pwd=4t8g 提取码: 4t8g </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/1ff35bc35c9e?pwd=XNbw 提取码：XNbw</t>
+  </si>
+  <si>
+    <t>欲望的陷阱</t>
+  </si>
+  <si>
+    <t>剧情 / 犯罪</t>
+  </si>
+  <si>
+    <t>29/100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 张瑞希 / 田惠媛 / 薛正焕 / 周清晨 / 尹海英 /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1RGqtoh0fV1lUW7LgB0erEA?pwd=ndie 提取码: ndie </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/996d38348f46?pwd=6rC8 提取码：6rC8</t>
+  </si>
+  <si>
+    <t>爱情来了</t>
+  </si>
+  <si>
+    <t>剧情 / 爱情 / 奇幻</t>
+  </si>
+  <si>
+    <t>18/50</t>
+  </si>
+  <si>
+    <t>安喜延 / 河锡辰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接：https://pan.quark.cn/s/c2c8aa7ff0c2?pwd=JZEy  提取码：JZEy
+ </t>
+  </si>
+  <si>
+    <t>我们愉快的好日子</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>严贤京/尹仲勋/申正允/尹多英/金惠玉</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/77097bff82c1?pwd=G2jr  提取码：G2jr</t>
+  </si>
+  <si>
+    <t>从犯规开始吧？</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/9a4c405f64dc?pwd=UvZi 提取码：UvZi</t>
+  </si>
+  <si>
+    <t>中头奖还是要上班</t>
+  </si>
+  <si>
+    <t>剧情 / 喜剧</t>
+  </si>
+  <si>
+    <t>4/10</t>
+  </si>
+  <si>
+    <t>李浚赫 / 徐现宇 / 吴代焕 / 玉子妍</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/9bd91cf9b311?pwd=Nzk6   提取码：Nzk6</t>
+  </si>
+  <si>
+    <t>不是你的恋爱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">剧情 / 爱情 </t>
+  </si>
+  <si>
+    <t>4/14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 徐康俊 / 安恩真 / 李周安 / 赵雅兰</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/547e99636d86?pwd=daM5  提取码：daM5</t>
+  </si>
+  <si>
+    <t>乌鸦俱乐部</t>
+  </si>
+  <si>
+    <t>泰剧</t>
+  </si>
+  <si>
+    <t>1/16</t>
+  </si>
+  <si>
+    <t>赫马维奇·卡皖纳姆派潘 /塔纳朋·艾恩坤柴</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/0b721e243e8d?pwd=EZFU 提取码：EZFU</t>
+  </si>
+  <si>
+    <t>寄生之心</t>
+  </si>
+  <si>
+    <t>6/28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">瓦拉甘·萨瓦功 / 澈丁娜拉·朋琵拉德 </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/a39245d804f1?pwd=5XKj  提取码：5XKj</t>
+  </si>
+  <si>
+    <t>镇灵</t>
+  </si>
+  <si>
+    <t>爱情/悬疑/惊悚/恐怖/同性/奇幻</t>
+  </si>
+  <si>
+    <t>3/10</t>
+  </si>
+  <si>
+    <t>诗丽通·莉阿蓝瓦/甘莫拉·笙萨形/阿楠达·蒂维拉</t>
+  </si>
+  <si>
+    <t>接：https://pan.quark.cn/s/24858c62440b?pwd=4tiR 提取码：4tiR</t>
+  </si>
+  <si>
+    <t>李熊猫</t>
+  </si>
+  <si>
+    <t>动漫</t>
+  </si>
+  <si>
+    <t>喜剧/动作/动画/奇幻</t>
+  </si>
+  <si>
+    <t>10/18</t>
+  </si>
+  <si>
+    <t>齐璇/小连杀/ 魏一凡/ 朱祎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1paCsTOrm0Myk2sgF96UkcA 提取码: zb9w </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/9592fd74fe15?pwd=F4zA 提取码：F4zA</t>
+  </si>
+  <si>
+    <t>东大高武学院</t>
+  </si>
+  <si>
+    <t>动作/动画/奇幻</t>
+  </si>
+  <si>
+    <t>10/25</t>
+  </si>
+  <si>
+    <t> 云惟一/万舒心/刘琮/张惠霖/李铮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xgB5NP2JFKwnC0tnE_vV-Q 提取码: grug </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/986b72527b6d?pwd=JyMm 提取码：JyMm</t>
+  </si>
+  <si>
+    <t>牛大力作妖记​</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/8f6ff468962a?pwd=AuSM  提取码：AuSM</t>
+  </si>
+  <si>
+    <t>九宵神女</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/5df681c49e04?pwd=i5B3 提取码：i5B3</t>
+  </si>
+  <si>
+    <t>神的游戏</t>
+  </si>
+  <si>
+    <t>AI真人格斗番</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1IpJblba6yx_ULc6AQ9FKzQ 提取码: 7zcj </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/47fcac021c4d?pwd=sFDT 提取码：sFDT</t>
+  </si>
+  <si>
+    <t>枭除录</t>
+  </si>
+  <si>
+    <t>真人AI/志怪 #法术</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Ll1Z9gnTo6af9Z7H3zOLBw 提取码: vrby </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/13fee7436bda?pwd=RmUb 提取码：RmUb</t>
+  </si>
+  <si>
+    <t>蚀光之城</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ea18jH1vKbcNsxAsUkAoPw?pwd=mxyx 提取码: mxyx </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/5dea986e7d9c?pwd=vQ93 提取码：vQ93</t>
+  </si>
+  <si>
+    <t>龙门</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ZVh0JUSAy6fij-_kxwlKKg?pwd=wpud 提取码: wpud </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/dce3c89fc12d?pwd=HYLy  提取码：HYLy</t>
+  </si>
+  <si>
+    <t>楚人美游记</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>志怪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> #</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>法术</t>
+    </r>
+  </si>
+  <si>
+    <t>已完结</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1hQKA0Oc-JJIQ4XxdY13YmQ 提取码: j1h2 </t>
+  </si>
+  <si>
+    <t>天庭三大反骨仔系列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xQB5aGDByNbjg5T13pwr7w 提取码: eui7 </t>
+  </si>
+  <si>
+    <t>狄仁杰系列电影</t>
+  </si>
+  <si>
+    <t>电影合集</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Jh0RzpHTqh8y3jM5ZbjrWg 提取码: kyvw </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/54c3850296aa?pwd=wVgG  提取码：wVgG</t>
+  </si>
+  <si>
+    <t>盗墓笔记系列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1GDqBaKE92gbyg09xkCrM2w 提取码: ir18 </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/2b26ebc65fc8?pwd=AGf7 提取码：AGf7</t>
+  </si>
+  <si>
+    <t>漫威系列</t>
+  </si>
+  <si>
+    <t>链接: https://pan.baidu.com/s/1nPviMzfRz01VSnmCQCAh4Q?pwd=7jnh 提取码: 7jnh</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/b7b4381c82eb?pwd=ssGG  提取码：ssGG</t>
+  </si>
+  <si>
+    <t>周星驰系列电影</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/8106b86259d0?pwd=sqNP 提取码：sqNP</t>
+  </si>
+  <si>
+    <t>去你的岛</t>
+  </si>
+  <si>
+    <t>电影</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1mU5VCAnqvFIxwFfFcBWvPA?pwd=dhwb 提取码: dhwb </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/644c46729a6d?pwd=SyGd 提取码：SyGd</t>
+  </si>
+  <si>
+    <t>抓特务</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 雷佳音/胡歌/啜妮/张瑶/林晓凡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1PpNPs5ANcuuvHmUmczbz1A?pwd=3gqi 提取码: 3gqi </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/d53679b91d3b?pwd=iq9C 提取码：iq9C</t>
+  </si>
+  <si>
+    <t>污点</t>
+  </si>
+  <si>
+    <t>喜剧/恐怖</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 瑛法·瓦拉哈/莎露彩·查金哈/杰迪帕·迪拉朋帕</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1k1jN616TWuYJ0fDa4530uA?pwd=i78c 提取码: i78c </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/30bbfab35499?pwd=MvVq 提取码：MvVq</t>
+  </si>
+  <si>
+    <t>千门之群龙夺宝</t>
+  </si>
+  <si>
+    <t>剧情/悬疑/奇幻</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 薛闻君/刘凡菲/王俊棠/申琦/许子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1M3LF03DrwRa-MA-idGBqpA?pwd=db78 提取码: db78 </t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/3ac561799dd2?pwd=JYsB 提取码：JYsB</t>
+  </si>
+  <si>
     <t>花开锦绣</t>
   </si>
   <si>
@@ -80,12 +459,6 @@
     <t>剧情/古装</t>
   </si>
   <si>
-    <t>1080P</t>
-  </si>
-  <si>
-    <t>已完结</t>
-  </si>
-  <si>
     <t>丁禹兮/邓恩熙/尤靖茹/白澍/吕晓霖</t>
   </si>
   <si>
@@ -98,9 +471,6 @@
     <t>重器</t>
   </si>
   <si>
-    <t>剧情</t>
-  </si>
-  <si>
     <t xml:space="preserve">黄景瑜/蒋奇明/于和伟/闫佩伦/张佳宁 </t>
   </si>
   <si>
@@ -126,9 +496,6 @@
   </si>
   <si>
     <t>她的涅槃</t>
-  </si>
-  <si>
-    <t>剧情 / 爱情 / 奇幻</t>
   </si>
   <si>
     <t>方瑾 / 李嘉豪 / 王鹤宇 / 孙莉 / 黄奕搏</t>
@@ -325,9 +692,6 @@
     <t>欢迎再次登录</t>
   </si>
   <si>
-    <t>电影</t>
-  </si>
-  <si>
     <t>悬疑/犯罪</t>
   </si>
   <si>
@@ -668,9 +1032,6 @@
     <t>杀手妈咪</t>
   </si>
   <si>
-    <t>韩剧</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -771,9 +1132,6 @@
     <t>绘梦婚礼</t>
   </si>
   <si>
-    <t>泰剧</t>
-  </si>
-  <si>
     <t>泰剧/爱情</t>
   </si>
   <si>
@@ -842,42 +1200,6 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/17IfE4v3SrPF6Y18CdlHkaA 提取码: kxjd </t>
-  </si>
-  <si>
-    <t>李熊猫</t>
-  </si>
-  <si>
-    <t>动漫</t>
-  </si>
-  <si>
-    <t>喜剧/动作/动画/奇幻</t>
-  </si>
-  <si>
-    <t>更新中</t>
-  </si>
-  <si>
-    <t>齐璇/小连杀/ 魏一凡/ 朱祎</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1paCsTOrm0Myk2sgF96UkcA 提取码: zb9w </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/9592fd74fe15?pwd=F4zA 提取码：F4zA</t>
-  </si>
-  <si>
-    <t>东大高武学院</t>
-  </si>
-  <si>
-    <t>动作/动画/奇幻</t>
-  </si>
-  <si>
-    <t> 云惟一/万舒心/刘琮/张惠霖/李铮</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xgB5NP2JFKwnC0tnE_vV-Q 提取码: grug </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/986b72527b6d?pwd=JyMm 提取码：JyMm</t>
   </si>
   <si>
     <t>财阀X刑警 第二季</t>
@@ -982,295 +1304,6 @@
   </si>
   <si>
     <t>链接：https://pan.quark.cn/s/3b6a404a18cf?pwd=KZQM 提取码：KZQM</t>
-  </si>
-  <si>
-    <t>家庭关系证明书</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">朴世荣 / 韩高恩 / 林志恩 / 成伊言 / 朴率拉 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1inTr-QEh-UzsyRlDfM0gbA?pwd=4t8g 提取码: 4t8g </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/1ff35bc35c9e?pwd=XNbw 提取码：XNbw</t>
-  </si>
-  <si>
-    <t>欲望的陷阱</t>
-  </si>
-  <si>
-    <t>剧情 / 犯罪</t>
-  </si>
-  <si>
-    <t>29/100</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 张瑞希 / 田惠媛 / 薛正焕 / 周清晨 / 尹海英 /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1RGqtoh0fV1lUW7LgB0erEA?pwd=ndie 提取码: ndie </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/996d38348f46?pwd=6rC8 提取码：6rC8</t>
-  </si>
-  <si>
-    <t>爱情来了</t>
-  </si>
-  <si>
-    <t>17/50</t>
-  </si>
-  <si>
-    <t>安喜延 / 河锡辰</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/c2c8aa7ff0c2?pwd=JZEy
-提取码：JZEy</t>
-  </si>
-  <si>
-    <t>我们愉快的好日子</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>严贤京/尹仲勋/申正允/尹多英/金惠玉</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/77097bff82c1?pwd=G2jr  提取码：G2jr</t>
-  </si>
-  <si>
-    <t>从犯规开始吧？</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/9a4c405f64dc?pwd=UvZi 提取码：UvZi</t>
-  </si>
-  <si>
-    <t>中头奖还是要上班</t>
-  </si>
-  <si>
-    <t>剧情 / 喜剧</t>
-  </si>
-  <si>
-    <t>4/10</t>
-  </si>
-  <si>
-    <t>李浚赫 / 徐现宇 / 吴代焕 / 玉子妍</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/9bd91cf9b311?pwd=Nzk6   提取码：Nzk6</t>
-  </si>
-  <si>
-    <t>不是你的恋爱</t>
-  </si>
-  <si>
-    <t xml:space="preserve">剧情 / 爱情 </t>
-  </si>
-  <si>
-    <t>3/14</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 徐康俊 / 安恩真 / 李周安 / 赵雅兰</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/547e99636d86?pwd=daM5  提取码：daM5</t>
-  </si>
-  <si>
-    <t>乌鸦俱乐部</t>
-  </si>
-  <si>
-    <t>1/16</t>
-  </si>
-  <si>
-    <t>赫马维奇·卡皖纳姆派潘 /塔纳朋·艾恩坤柴</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/0b721e243e8d?pwd=EZFU 提取码：EZFU</t>
-  </si>
-  <si>
-    <t>寄生之心</t>
-  </si>
-  <si>
-    <t>4/28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">瓦拉甘·萨瓦功 / 澈丁娜拉·朋琵拉德 </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/a39245d804f1?pwd=5XKj  提取码：5XKj</t>
-  </si>
-  <si>
-    <t>神的游戏</t>
-  </si>
-  <si>
-    <t>AI真人格斗番</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1IpJblba6yx_ULc6AQ9FKzQ 提取码: 7zcj </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/47fcac021c4d?pwd=sFDT 提取码：sFDT</t>
-  </si>
-  <si>
-    <t>枭除录</t>
-  </si>
-  <si>
-    <t>真人AI/志怪 #法术</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Ll1Z9gnTo6af9Z7H3zOLBw 提取码: vrby </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/13fee7436bda?pwd=RmUb 提取码：RmUb</t>
-  </si>
-  <si>
-    <t>蚀光之城</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ea18jH1vKbcNsxAsUkAoPw?pwd=mxyx 提取码: mxyx </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/5dea986e7d9c?pwd=vQ93 提取码：vQ93</t>
-  </si>
-  <si>
-    <t>龙门</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1ZVh0JUSAy6fij-_kxwlKKg?pwd=wpud 提取码: wpud </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/dce3c89fc12d?pwd=HYLy  提取码：HYLy</t>
-  </si>
-  <si>
-    <t>楚人美游记</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>志怪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> #</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>法术</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1hQKA0Oc-JJIQ4XxdY13YmQ 提取码: j1h2 </t>
-  </si>
-  <si>
-    <t>天庭三大反骨仔系列</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xQB5aGDByNbjg5T13pwr7w 提取码: eui7 </t>
-  </si>
-  <si>
-    <t>狄仁杰系列电影</t>
-  </si>
-  <si>
-    <t>电影合集</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Jh0RzpHTqh8y3jM5ZbjrWg 提取码: kyvw </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/54c3850296aa?pwd=wVgG  提取码：wVgG</t>
-  </si>
-  <si>
-    <t>盗墓笔记系列</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1GDqBaKE92gbyg09xkCrM2w 提取码: ir18 </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/2b26ebc65fc8?pwd=AGf7 提取码：AGf7</t>
-  </si>
-  <si>
-    <t>漫威系列</t>
-  </si>
-  <si>
-    <t>链接: https://pan.baidu.com/s/1nPviMzfRz01VSnmCQCAh4Q?pwd=7jnh 提取码: 7jnh</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/b7b4381c82eb?pwd=ssGG  提取码：ssGG</t>
-  </si>
-  <si>
-    <t>周星驰系列电影</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/8106b86259d0?pwd=sqNP 提取码：sqNP</t>
-  </si>
-  <si>
-    <t>去你的岛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1mU5VCAnqvFIxwFfFcBWvPA?pwd=dhwb 提取码: dhwb </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/644c46729a6d?pwd=SyGd 提取码：SyGd</t>
-  </si>
-  <si>
-    <t>抓特务</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 雷佳音/胡歌/啜妮/张瑶/林晓凡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1PpNPs5ANcuuvHmUmczbz1A?pwd=3gqi 提取码: 3gqi </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/d53679b91d3b?pwd=iq9C 提取码：iq9C</t>
-  </si>
-  <si>
-    <t>污点</t>
-  </si>
-  <si>
-    <t>喜剧/恐怖</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 瑛法·瓦拉哈/莎露彩·查金哈/杰迪帕·迪拉朋帕</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1k1jN616TWuYJ0fDa4530uA?pwd=i78c 提取码: i78c </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/30bbfab35499?pwd=MvVq 提取码：MvVq</t>
-  </si>
-  <si>
-    <t>千门之群龙夺宝</t>
-  </si>
-  <si>
-    <t>剧情/悬疑/奇幻</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 薛闻君/刘凡菲/王俊棠/申琦/许子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1M3LF03DrwRa-MA-idGBqpA?pwd=db78 提取码: db78 </t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/3ac561799dd2?pwd=JYsB 提取码：JYsB</t>
   </si>
   <si>
     <t>杯雪</t>
@@ -3114,7 +3147,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3233,12 +3266,57 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3251,25 +3329,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3825,7 +3885,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
@@ -3873,194 +3933,184 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
-      <c r="A2" s="25" t="s">
+    <row r="2" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A2" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="41">
-        <v>36</v>
+      <c r="E2" s="42" t="s">
+        <v>14</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="23">
         <v>2026</v>
       </c>
-      <c r="H2" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="42" t="s">
+      <c r="H2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="I2" s="24" t="s">
         <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="22">
-        <v>33</v>
+      <c r="E3" s="22" t="s">
+        <v>21</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="23">
         <v>2026</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>24</v>
+      <c r="C4" s="44" t="s">
+        <v>26</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="22">
-        <v>23</v>
+      <c r="E4" s="42" t="s">
+        <v>27</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="23">
         <v>2026</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="H4" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="24"/>
+      <c r="J4" s="45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>29</v>
+      <c r="C5" s="44" t="s">
+        <v>12</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="22">
-        <v>23</v>
+      <c r="E5" s="22" t="s">
+        <v>31</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="23">
         <v>2026</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>31</v>
-      </c>
+      <c r="H5" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="24"/>
       <c r="J5" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A6" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="23" t="s">
+    </row>
+    <row r="6" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>34</v>
+      <c r="C6" s="44" t="s">
+        <v>12</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="22">
-        <v>24</v>
+      <c r="E6" s="22" t="s">
+        <v>35</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="23">
         <v>2026</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="H6" s="23"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="7" t="s">
+    </row>
+    <row r="7" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A7" s="21" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A7" s="43" t="s">
+      <c r="B7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="28">
-        <v>32</v>
+      <c r="E7" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="29">
+        <v>15</v>
+      </c>
+      <c r="G7" s="23">
         <v>2026</v>
       </c>
-      <c r="H7" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="H7" s="23" t="s">
         <v>40</v>
       </c>
+      <c r="I7" s="24"/>
       <c r="J7" s="7" t="s">
         <v>41</v>
       </c>
@@ -4069,7 +4119,7 @@
       <c r="A8" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="44" t="s">
@@ -4078,53 +4128,49 @@
       <c r="D8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="22">
-        <v>24</v>
+      <c r="E8" s="42" t="s">
+        <v>44</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="23">
         <v>2026</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="24" t="s">
+      <c r="H8" s="46" t="s">
         <v>45</v>
       </c>
+      <c r="I8" s="24"/>
       <c r="J8" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="7" t="s">
         <v>48</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>26</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="22">
-        <v>24</v>
+      <c r="E9" s="22" t="s">
+        <v>49</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="23">
         <v>2026</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="24" t="s">
+      <c r="H9" s="23" t="s">
         <v>50</v>
       </c>
+      <c r="I9" s="24"/>
       <c r="J9" s="7" t="s">
         <v>51</v>
       </c>
@@ -4133,1616 +4179,1624 @@
       <c r="A10" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>53</v>
+      <c r="B10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>12</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="22">
-        <v>25</v>
+      <c r="E10" s="42" t="s">
+        <v>53</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" s="23">
         <v>2026</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="24"/>
+      <c r="J10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="7" t="s">
+    </row>
+    <row r="11" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A11" s="47" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="11" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A11" s="21" t="s">
+      <c r="B11" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="22">
-        <v>26</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="23">
+      <c r="F11" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="50">
         <v>2026</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="51"/>
+      <c r="J11" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="7" t="s">
+    </row>
+    <row r="12" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A12" s="21"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A13" s="21"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A14" s="21"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="23"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A15" s="25" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="12" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A12" s="21" t="s">
+      <c r="B15" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="C15" s="23" t="s">
         <v>63</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="22">
-        <v>24</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A13" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A14" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A15" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="22"/>
+      <c r="E15" s="52" t="s">
+        <v>64</v>
+      </c>
       <c r="F15" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15" s="23">
         <v>2026</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>82</v>
+      <c r="H15" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A16" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="A16" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>84</v>
+      <c r="B16" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>69</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="7" t="s">
-        <v>14</v>
+      <c r="E16" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="G16" s="23">
         <v>2026</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="7"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A17" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="23" t="s">
+      <c r="H16" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A17" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="49"/>
+      <c r="D17" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="23">
+      <c r="E17" s="52">
+        <v>7</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="50">
         <v>2026</v>
       </c>
-      <c r="H17" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="J17" s="7"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A18" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" s="23" t="s">
+      <c r="H17" s="50"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A18" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="49"/>
+      <c r="D18" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="23">
+      <c r="E18" s="52">
+        <v>7</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="50">
         <v>2026</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>95</v>
+      <c r="H18" s="50"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="48" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A19" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>97</v>
+      <c r="A19" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>79</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="7" t="s">
-        <v>14</v>
+      <c r="E19" s="55">
+        <v>7</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="G19" s="23">
         <v>2026</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>100</v>
+      <c r="H19" s="23"/>
+      <c r="I19" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="25" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="41">
-        <v>30</v>
+      <c r="E20" s="55">
+        <v>10</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" s="23">
         <v>2026</v>
       </c>
-      <c r="H20" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="I20" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>105</v>
+      <c r="H20" s="43"/>
+      <c r="I20" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="25" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>107</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C21" s="23"/>
       <c r="D21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="41">
-        <v>32</v>
+      <c r="E21" s="55">
+        <v>2</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G21" s="23">
         <v>2026</v>
       </c>
-      <c r="H21" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>110</v>
+      <c r="H21" s="43"/>
+      <c r="I21" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="23" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="25" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>112</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C22" s="23"/>
       <c r="D22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="41">
-        <v>33</v>
+      <c r="E22" s="55">
+        <v>4</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" s="23">
         <v>2026</v>
       </c>
-      <c r="H22" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" s="46" t="s">
-        <v>114</v>
+      <c r="H22" s="43"/>
+      <c r="I22" s="53" t="s">
+        <v>90</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A23" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="41">
-        <v>36</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="A23" s="25"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A24" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="22">
-        <v>22</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>124</v>
-      </c>
+      <c r="A24" s="25"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="53"/>
       <c r="J24" s="7"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A25" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="22">
-        <v>24</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>127</v>
-      </c>
+      <c r="A25" s="25"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="53"/>
       <c r="J25" s="7"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A26" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="7">
-        <v>2026</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>132</v>
-      </c>
+      <c r="A26" s="25"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="53"/>
       <c r="J26" s="7"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A27" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="7">
-        <v>2026</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>136</v>
-      </c>
+      <c r="A27" s="25"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="53"/>
       <c r="J27" s="7"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A28" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H28" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="I28" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>143</v>
-      </c>
+      <c r="A28" s="25"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="7"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A29" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="41" t="s">
-        <v>147</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="I29" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A30" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C30" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="7"/>
-      <c r="H30" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>155</v>
-      </c>
+      <c r="A29" s="25"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="7"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A30" s="25"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="53"/>
       <c r="J30" s="7"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A31" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="41">
-        <v>9</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G31" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H31" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="I31" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>162</v>
-      </c>
+      <c r="A31" s="25"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="7"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A32" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="41">
-        <v>9</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G32" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="I32" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>167</v>
-      </c>
+      <c r="A32" s="25"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="7"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A33" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>169</v>
+      <c r="A33" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>93</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>14</v>
+      <c r="E33" s="56"/>
+      <c r="F33" s="44" t="s">
+        <v>94</v>
       </c>
       <c r="G33" s="23">
         <v>2026</v>
       </c>
-      <c r="H33" s="23" t="s">
-        <v>170</v>
-      </c>
+      <c r="H33" s="23"/>
       <c r="I33" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="34" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>95</v>
+      </c>
+      <c r="J33" s="7"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A34" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>19</v>
+        <v>96</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>93</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="F34" s="23" t="s">
-        <v>159</v>
+      <c r="E34" s="56"/>
+      <c r="F34" s="44" t="s">
+        <v>94</v>
       </c>
       <c r="G34" s="23">
         <v>2026</v>
       </c>
-      <c r="H34" s="7" t="s">
-        <v>175</v>
-      </c>
+      <c r="H34" s="23"/>
       <c r="I34" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="35" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>97</v>
+      </c>
+      <c r="J34" s="7"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="F35" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G35" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="I35" s="49" t="s">
-        <v>182</v>
+        <v>98</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="24" t="s">
+        <v>100</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" s="6" customFormat="1" ht="34" customHeight="1" spans="1:10">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="F36" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G36" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="I36" s="24"/>
-      <c r="J36" s="50" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>99</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C37" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G37" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H37" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="I37" s="24"/>
+        <v>99</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="24" t="s">
+        <v>106</v>
+      </c>
       <c r="J37" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="38" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A38" s="6" t="s">
-        <v>192</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A38" s="21" t="s">
+        <v>108</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C38" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G38" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H38" s="23"/>
+        <v>99</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
       <c r="I38" s="24"/>
       <c r="J38" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="39" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" ht="25" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" s="48" t="s">
-        <v>196</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>159</v>
+        <v>111</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22" t="s">
+        <v>94</v>
       </c>
       <c r="G39" s="23">
         <v>2026</v>
       </c>
-      <c r="H39" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="I39" s="24"/>
-      <c r="J39" s="7" t="s">
-        <v>199</v>
+      <c r="H39" s="7"/>
+      <c r="I39" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="J39" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C40" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>159</v>
+        <v>111</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22" t="s">
+        <v>94</v>
       </c>
       <c r="G40" s="23">
         <v>2026</v>
       </c>
-      <c r="H40" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="I40" s="24"/>
-      <c r="J40" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="41" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="H40" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="J40" s="24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>159</v>
+        <v>111</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="7"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22" t="s">
+        <v>94</v>
       </c>
       <c r="G41" s="23">
         <v>2026</v>
       </c>
-      <c r="H41" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="I41" s="24"/>
-      <c r="J41" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="42" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="H41" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="J41" s="24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>209</v>
+        <v>123</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G42" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="J42" s="24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
+      <c r="A43" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="55">
+        <v>36</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G43" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H43" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="I43" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A44" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="22">
+        <v>33</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G44" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I44" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A45" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="22">
+        <v>23</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G45" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A46" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="22">
+        <v>23</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G46" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I46" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="23" t="s">
+      <c r="J46" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A47" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D47" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="F42" s="23" t="s">
+      <c r="E47" s="22">
+        <v>24</v>
+      </c>
+      <c r="F47" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G47" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A48" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="28">
+        <v>32</v>
+      </c>
+      <c r="F48" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G48" s="29">
+        <v>2026</v>
+      </c>
+      <c r="H48" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A49" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="22">
+        <v>24</v>
+      </c>
+      <c r="F49" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G49" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="I49" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="I42" s="24"/>
-      <c r="J42" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="43" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A43" s="21"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="7"/>
-    </row>
-    <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A44" s="21"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="7"/>
-    </row>
-    <row r="45" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A45" s="21"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="7"/>
-    </row>
-    <row r="46" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A46" s="21"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="7"/>
-    </row>
-    <row r="47" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A47" s="21"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="7"/>
-    </row>
-    <row r="48" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A48" s="21"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="7"/>
-    </row>
-    <row r="49" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A49" s="21"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="7"/>
+      <c r="J49" s="7" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="50" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A50" s="21"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="7"/>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A51" s="25" t="s">
-        <v>213</v>
+      <c r="A50" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="22">
+        <v>24</v>
+      </c>
+      <c r="F50" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G50" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I50" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A51" s="21" t="s">
+        <v>166</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>214</v>
+        <v>129</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="41">
-        <v>7</v>
+      <c r="E51" s="22">
+        <v>25</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
       <c r="G51" s="23">
         <v>2026</v>
       </c>
-      <c r="H51" s="23"/>
-      <c r="I51" s="46" t="s">
-        <v>215</v>
-      </c>
-      <c r="J51" s="23" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A52" s="25" t="s">
-        <v>217</v>
+      <c r="H51" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I51" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="52" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A52" s="21" t="s">
+        <v>171</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>218</v>
+        <v>129</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E52" s="41">
-        <v>10</v>
+      <c r="E52" s="22">
+        <v>26</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
       <c r="G52" s="23">
         <v>2026</v>
       </c>
-      <c r="H52" s="49"/>
-      <c r="I52" s="46" t="s">
-        <v>219</v>
-      </c>
-      <c r="J52" s="23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A53" s="25" t="s">
-        <v>221</v>
+      <c r="H52" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="I52" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A53" s="21" t="s">
+        <v>176</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C53" s="23"/>
+        <v>129</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>177</v>
+      </c>
       <c r="D53" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="41">
-        <v>2</v>
+      <c r="E53" s="22">
+        <v>24</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
       <c r="G53" s="23">
         <v>2026</v>
       </c>
-      <c r="H53" s="49"/>
-      <c r="I53" s="46" t="s">
-        <v>222</v>
-      </c>
-      <c r="J53" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="H53" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="I53" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A54" s="25" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C54" s="23"/>
+        <v>111</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>182</v>
+      </c>
       <c r="D54" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="41">
-        <v>4</v>
-      </c>
+      <c r="E54" s="22"/>
       <c r="F54" s="23" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
       <c r="G54" s="23">
         <v>2026</v>
       </c>
-      <c r="H54" s="49"/>
-      <c r="I54" s="46" t="s">
-        <v>225</v>
+      <c r="H54" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="I54" s="24" t="s">
+        <v>184</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A55" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C55" s="48" t="s">
-        <v>228</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A55" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E55" s="52"/>
-      <c r="F55" s="48" t="s">
-        <v>14</v>
+      <c r="E55" s="22"/>
+      <c r="F55" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="G55" s="23">
         <v>2026</v>
       </c>
-      <c r="H55" s="23"/>
+      <c r="H55" s="7" t="s">
+        <v>188</v>
+      </c>
       <c r="I55" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="J55" s="7"/>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A56" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C56" s="48" t="s">
-        <v>228</v>
+        <v>189</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A56" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E56" s="52"/>
-      <c r="F56" s="48" t="s">
-        <v>14</v>
+      <c r="E56" s="22"/>
+      <c r="F56" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="G56" s="23">
         <v>2026</v>
       </c>
-      <c r="H56" s="23"/>
+      <c r="H56" s="7" t="s">
+        <v>193</v>
+      </c>
       <c r="I56" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="J56" s="7"/>
+        <v>194</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
+        <v>111</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>13</v>
+      </c>
       <c r="E57" s="22"/>
       <c r="F57" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
+        <v>94</v>
+      </c>
+      <c r="G57" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>198</v>
+      </c>
       <c r="I57" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>235</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="J57" s="7"/>
     </row>
     <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
+        <v>111</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>13</v>
+      </c>
       <c r="E58" s="22"/>
       <c r="F58" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
+        <v>94</v>
+      </c>
+      <c r="G58" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H58" s="60" t="s">
+        <v>202</v>
+      </c>
       <c r="I58" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>238</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="J58" s="7"/>
     </row>
     <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A59" s="21" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
+        <v>111</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>13</v>
+      </c>
       <c r="E59" s="22"/>
       <c r="F59" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
+        <v>94</v>
+      </c>
+      <c r="G59" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>206</v>
+      </c>
       <c r="I59" s="24" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A60" s="21" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
+        <v>111</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="23" t="s">
+        <v>13</v>
+      </c>
       <c r="E60" s="22"/>
       <c r="F60" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="24"/>
+        <v>94</v>
+      </c>
+      <c r="G60" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I60" s="24" t="s">
+        <v>212</v>
+      </c>
       <c r="J60" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="61" ht="25" customHeight="1" spans="1:10">
-      <c r="A61" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22" t="s">
-        <v>14</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A61" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="D61" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="55">
+        <v>30</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="G61" s="23">
         <v>2026</v>
       </c>
-      <c r="H61" s="7"/>
-      <c r="I61" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="J61" s="21" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="62" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A62" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22" t="s">
-        <v>14</v>
+      <c r="H61" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="I61" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A62" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="D62" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="55">
+        <v>32</v>
+      </c>
+      <c r="F62" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="G62" s="23">
         <v>2026</v>
       </c>
-      <c r="H62" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="I62" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="J62" s="24" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="63" ht="24" customHeight="1" spans="1:10">
-      <c r="A63" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="D63" s="7"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22" t="s">
-        <v>14</v>
+      <c r="H62" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="I62" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A63" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="55">
+        <v>33</v>
+      </c>
+      <c r="F63" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="G63" s="23">
         <v>2026</v>
       </c>
-      <c r="H63" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="I63" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="J63" s="24" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="64" ht="25" customHeight="1" spans="1:10">
-      <c r="A64" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D64" s="7"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22" t="s">
-        <v>14</v>
+      <c r="H63" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="I63" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A64" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="D64" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="55">
+        <v>36</v>
+      </c>
+      <c r="F64" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="G64" s="23">
         <v>2026</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="H64" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="I64" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A65" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="22">
+        <v>22</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G65" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="I65" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="J65" s="7"/>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A66" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="22">
+        <v>24</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G66" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="I66" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="J66" s="7"/>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A67" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G67" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J67" s="7"/>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A68" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G68" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I68" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="J68" s="7"/>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A69" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="F69" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G69" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H69" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="I69" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A70" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="55" t="s">
         <v>258</v>
       </c>
-      <c r="I64" s="24" t="s">
+      <c r="F70" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G70" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H70" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="J64" s="24" t="s">
+      <c r="I70" s="53" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="65" ht="25" customHeight="1" spans="1:10">
-      <c r="A65" s="21"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="23"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="24"/>
-      <c r="J65" s="24"/>
-    </row>
-    <row r="66" ht="25" customHeight="1" spans="1:10">
-      <c r="A66" s="53" t="s">
+      <c r="J70" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="B66" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="C66" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="D66" s="7"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G66" s="23">
-        <v>8.25</v>
-      </c>
-      <c r="H66" s="7" t="s">
+    </row>
+    <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A71" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="I66" s="24"/>
-      <c r="J66" s="21"/>
-    </row>
-    <row r="67" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A67" s="53" t="s">
+      <c r="B71" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C71" s="44" t="s">
         <v>263</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G67" s="23" t="s">
+      <c r="D71" s="7"/>
+      <c r="E71" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="H67" s="7"/>
-      <c r="I67" s="24"/>
-      <c r="J67" s="21"/>
-    </row>
-    <row r="68" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A68" s="53" t="s">
+      <c r="F71" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G71" s="7"/>
+      <c r="H71" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="23">
-        <v>8.23</v>
-      </c>
-      <c r="H68" s="7"/>
-      <c r="I68" s="24"/>
-      <c r="J68" s="21"/>
-    </row>
-    <row r="69" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A69" s="53" t="s">
+      <c r="I71" s="24" t="s">
         <v>266</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="H69" s="7"/>
-      <c r="I69" s="24"/>
-      <c r="J69" s="21"/>
-    </row>
-    <row r="70" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A70" s="53" t="s">
+      <c r="J71" s="7"/>
+    </row>
+    <row r="72" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A72" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G70" s="23">
-        <v>8.21</v>
-      </c>
-      <c r="H70" s="7"/>
-      <c r="I70" s="24"/>
-      <c r="J70" s="21"/>
-    </row>
-    <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A71" s="53" t="s">
+      <c r="B72" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="23" t="s">
         <v>268</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="24"/>
-      <c r="J71" s="21"/>
-    </row>
-    <row r="72" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A72" s="53" t="s">
+      <c r="D72" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G72" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H72" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="B72" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="23">
-        <v>5.15</v>
-      </c>
-      <c r="H72" s="7"/>
-      <c r="I72" s="24"/>
-      <c r="J72" s="21"/>
-    </row>
-    <row r="73" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A73" s="53" t="s">
+      <c r="I72" s="24" t="s">
         <v>270</v>
       </c>
+      <c r="J72" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="73" ht="25" customHeight="1" spans="1:10">
+      <c r="A73" s="21"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -5751,164 +5805,188 @@
       <c r="G73" s="23"/>
       <c r="H73" s="7"/>
       <c r="I73" s="24"/>
-      <c r="J73" s="21"/>
-    </row>
-    <row r="74" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A74" s="53" t="s">
-        <v>271</v>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
+      <c r="J73" s="24"/>
+    </row>
+    <row r="74" ht="25" customHeight="1" spans="1:10">
+      <c r="A74" s="62" t="s">
+        <v>272</v>
+      </c>
+      <c r="B74" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="C74" s="63" t="s">
+        <v>69</v>
+      </c>
       <c r="D74" s="7"/>
       <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="7"/>
+      <c r="F74" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G74" s="23">
+        <v>8.25</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="I74" s="24"/>
       <c r="J74" s="21"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A75" s="53" t="s">
-        <v>272</v>
-      </c>
-      <c r="B75" s="7"/>
+      <c r="A75" s="62" t="s">
+        <v>274</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="23"/>
+      <c r="F75" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G75" s="23" t="s">
+        <v>275</v>
+      </c>
       <c r="H75" s="7"/>
       <c r="I75" s="24"/>
       <c r="J75" s="21"/>
     </row>
     <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A76" s="53" t="s">
-        <v>273</v>
-      </c>
-      <c r="B76" s="7"/>
+      <c r="A76" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="23"/>
+      <c r="F76" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G76" s="23">
+        <v>8.23</v>
+      </c>
       <c r="H76" s="7"/>
       <c r="I76" s="24"/>
       <c r="J76" s="21"/>
     </row>
     <row r="77" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A77" s="53" t="s">
-        <v>274</v>
-      </c>
-      <c r="B77" s="7"/>
+      <c r="A77" s="62" t="s">
+        <v>277</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="22"/>
-      <c r="F77" s="22" t="s">
+      <c r="F77" s="22"/>
+      <c r="G77" s="23" t="s">
         <v>275</v>
       </c>
-      <c r="G77" s="23"/>
       <c r="H77" s="7"/>
       <c r="I77" s="24"/>
-      <c r="J77" s="24"/>
-    </row>
-    <row r="78" ht="25" customHeight="1" spans="1:10">
-      <c r="A78" s="53" t="s">
-        <v>276</v>
-      </c>
-      <c r="B78" s="7"/>
+      <c r="J77" s="21"/>
+    </row>
+    <row r="78" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A78" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="22"/>
       <c r="F78" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="G78" s="23"/>
+        <v>94</v>
+      </c>
+      <c r="G78" s="23">
+        <v>8.21</v>
+      </c>
       <c r="H78" s="7"/>
       <c r="I78" s="24"/>
-      <c r="J78" s="24"/>
-    </row>
-    <row r="79" ht="25" customHeight="1" spans="1:10">
-      <c r="A79" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="B79" s="7"/>
+      <c r="J78" s="21"/>
+    </row>
+    <row r="79" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A79" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="22"/>
-      <c r="F79" s="22" t="s">
-        <v>278</v>
-      </c>
+      <c r="F79" s="22"/>
       <c r="G79" s="23"/>
       <c r="H79" s="7"/>
       <c r="I79" s="24"/>
-      <c r="J79" s="24"/>
-    </row>
-    <row r="80" ht="25" customHeight="1" spans="1:10">
-      <c r="A80" s="53" t="s">
-        <v>279</v>
-      </c>
-      <c r="B80" s="7"/>
+      <c r="J79" s="21"/>
+    </row>
+    <row r="80" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A80" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="22"/>
-      <c r="F80" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="G80" s="23"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="23">
+        <v>5.15</v>
+      </c>
       <c r="H80" s="7"/>
       <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-    </row>
-    <row r="81" ht="25" customHeight="1" spans="1:10">
-      <c r="A81" s="53" t="s">
+      <c r="J80" s="21"/>
+    </row>
+    <row r="81" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A81" s="62" t="s">
         <v>281</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="22"/>
-      <c r="F81" s="22">
-        <v>102</v>
-      </c>
+      <c r="F81" s="22"/>
       <c r="G81" s="23"/>
       <c r="H81" s="7"/>
       <c r="I81" s="24"/>
-      <c r="J81" s="24"/>
-    </row>
-    <row r="82" ht="25" customHeight="1" spans="1:10">
-      <c r="A82" s="53" t="s">
+      <c r="J81" s="21"/>
+    </row>
+    <row r="82" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
+      <c r="A82" s="62" t="s">
         <v>282</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="22"/>
-      <c r="F82" s="22">
-        <v>69</v>
-      </c>
+      <c r="F82" s="22"/>
       <c r="G82" s="23"/>
       <c r="H82" s="7"/>
       <c r="I82" s="24"/>
-      <c r="J82" s="24"/>
-    </row>
-    <row r="83" ht="25" customHeight="1" spans="1:10">
-      <c r="A83" s="53" t="s">
+      <c r="J82" s="21"/>
+    </row>
+    <row r="83" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A83" s="62" t="s">
         <v>283</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="22"/>
-      <c r="F83" s="22">
-        <v>86</v>
-      </c>
+      <c r="F83" s="22"/>
       <c r="G83" s="23"/>
       <c r="H83" s="7"/>
       <c r="I83" s="24"/>
-      <c r="J83" s="24"/>
-    </row>
-    <row r="84" ht="25" customHeight="1" spans="1:10">
-      <c r="A84" s="53" t="s">
+      <c r="J83" s="21"/>
+    </row>
+    <row r="84" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A84" s="62" t="s">
         <v>284</v>
       </c>
       <c r="B84" s="7"/>
@@ -5919,10 +5997,10 @@
       <c r="G84" s="23"/>
       <c r="H84" s="7"/>
       <c r="I84" s="24"/>
-      <c r="J84" s="24"/>
-    </row>
-    <row r="85" ht="25" customHeight="1" spans="1:10">
-      <c r="A85" s="53" t="s">
+      <c r="J84" s="21"/>
+    </row>
+    <row r="85" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A85" s="62" t="s">
         <v>285</v>
       </c>
       <c r="B85" s="7"/>
@@ -5938,43 +6016,47 @@
       <c r="J85" s="24"/>
     </row>
     <row r="86" ht="25" customHeight="1" spans="1:10">
-      <c r="A86" s="53" t="s">
+      <c r="A86" s="62" t="s">
         <v>287</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="22"/>
-      <c r="F86" s="22"/>
+      <c r="F86" s="22" t="s">
+        <v>288</v>
+      </c>
       <c r="G86" s="23"/>
       <c r="H86" s="7"/>
       <c r="I86" s="24"/>
       <c r="J86" s="24"/>
     </row>
     <row r="87" ht="25" customHeight="1" spans="1:10">
-      <c r="A87" s="53" t="s">
-        <v>288</v>
+      <c r="A87" s="21" t="s">
+        <v>118</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
+      <c r="F87" s="22" t="s">
+        <v>289</v>
+      </c>
       <c r="G87" s="23"/>
       <c r="H87" s="7"/>
       <c r="I87" s="24"/>
       <c r="J87" s="24"/>
     </row>
     <row r="88" ht="25" customHeight="1" spans="1:10">
-      <c r="A88" s="53" t="s">
-        <v>289</v>
+      <c r="A88" s="62" t="s">
+        <v>290</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="22"/>
       <c r="F88" s="22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G88" s="23"/>
       <c r="H88" s="7"/>
@@ -5982,15 +6064,15 @@
       <c r="J88" s="24"/>
     </row>
     <row r="89" ht="25" customHeight="1" spans="1:10">
-      <c r="A89" s="53" t="s">
-        <v>291</v>
+      <c r="A89" s="62" t="s">
+        <v>292</v>
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="22"/>
-      <c r="F89" s="22" t="s">
-        <v>292</v>
+      <c r="F89" s="22">
+        <v>102</v>
       </c>
       <c r="G89" s="23"/>
       <c r="H89" s="7"/>
@@ -5998,17 +6080,15 @@
       <c r="J89" s="24"/>
     </row>
     <row r="90" ht="25" customHeight="1" spans="1:10">
-      <c r="A90" s="53" t="s">
+      <c r="A90" s="62" t="s">
         <v>293</v>
       </c>
       <c r="B90" s="7"/>
-      <c r="C90" s="7" t="s">
-        <v>294</v>
-      </c>
+      <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="22"/>
-      <c r="F90" s="22" t="s">
-        <v>295</v>
+      <c r="F90" s="22">
+        <v>69</v>
       </c>
       <c r="G90" s="23"/>
       <c r="H90" s="7"/>
@@ -6016,17 +6096,15 @@
       <c r="J90" s="24"/>
     </row>
     <row r="91" ht="25" customHeight="1" spans="1:10">
-      <c r="A91" s="53" t="s">
-        <v>296</v>
+      <c r="A91" s="62" t="s">
+        <v>294</v>
       </c>
       <c r="B91" s="7"/>
-      <c r="C91" s="7" t="s">
-        <v>297</v>
-      </c>
+      <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="22"/>
-      <c r="F91" s="22" t="s">
-        <v>298</v>
+      <c r="F91" s="22">
+        <v>86</v>
       </c>
       <c r="G91" s="23"/>
       <c r="H91" s="7"/>
@@ -6034,35 +6112,29 @@
       <c r="J91" s="24"/>
     </row>
     <row r="92" ht="25" customHeight="1" spans="1:10">
-      <c r="A92" s="53" t="s">
-        <v>299</v>
+      <c r="A92" s="62" t="s">
+        <v>295</v>
       </c>
       <c r="B92" s="7"/>
-      <c r="C92" s="7" t="s">
-        <v>300</v>
-      </c>
+      <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="22"/>
-      <c r="F92" s="22" t="s">
-        <v>301</v>
-      </c>
+      <c r="F92" s="22"/>
       <c r="G92" s="23"/>
       <c r="H92" s="7"/>
       <c r="I92" s="24"/>
       <c r="J92" s="24"/>
     </row>
     <row r="93" ht="25" customHeight="1" spans="1:10">
-      <c r="A93" s="53" t="s">
-        <v>302</v>
+      <c r="A93" s="62" t="s">
+        <v>296</v>
       </c>
       <c r="B93" s="7"/>
-      <c r="C93" s="7" t="s">
-        <v>303</v>
-      </c>
+      <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="G93" s="23"/>
       <c r="H93" s="7"/>
@@ -6070,53 +6142,43 @@
       <c r="J93" s="24"/>
     </row>
     <row r="94" ht="25" customHeight="1" spans="1:10">
-      <c r="A94" s="53" t="s">
-        <v>304</v>
+      <c r="A94" s="62" t="s">
+        <v>298</v>
       </c>
       <c r="B94" s="7"/>
-      <c r="C94" s="7" t="s">
-        <v>305</v>
-      </c>
+      <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="22"/>
-      <c r="F94" s="22" t="s">
-        <v>306</v>
-      </c>
+      <c r="F94" s="22"/>
       <c r="G94" s="23"/>
       <c r="H94" s="7"/>
       <c r="I94" s="24"/>
       <c r="J94" s="24"/>
     </row>
     <row r="95" ht="25" customHeight="1" spans="1:10">
-      <c r="A95" s="53" t="s">
-        <v>307</v>
+      <c r="A95" s="62" t="s">
+        <v>299</v>
       </c>
       <c r="B95" s="7"/>
-      <c r="C95" s="7" t="s">
-        <v>308</v>
-      </c>
+      <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="22"/>
-      <c r="F95" s="22" t="s">
-        <v>309</v>
-      </c>
+      <c r="F95" s="22"/>
       <c r="G95" s="23"/>
       <c r="H95" s="7"/>
       <c r="I95" s="24"/>
       <c r="J95" s="24"/>
     </row>
     <row r="96" ht="25" customHeight="1" spans="1:10">
-      <c r="A96" s="53" t="s">
-        <v>310</v>
+      <c r="A96" s="62" t="s">
+        <v>300</v>
       </c>
       <c r="B96" s="7"/>
-      <c r="C96" s="7" t="s">
-        <v>311</v>
-      </c>
+      <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="22"/>
       <c r="F96" s="22" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="G96" s="23"/>
       <c r="H96" s="7"/>
@@ -6124,17 +6186,15 @@
       <c r="J96" s="24"/>
     </row>
     <row r="97" ht="25" customHeight="1" spans="1:10">
-      <c r="A97" s="53" t="s">
-        <v>313</v>
+      <c r="A97" s="62" t="s">
+        <v>302</v>
       </c>
       <c r="B97" s="7"/>
-      <c r="C97" s="7" t="s">
-        <v>314</v>
-      </c>
+      <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="G97" s="23"/>
       <c r="H97" s="7"/>
@@ -6142,17 +6202,17 @@
       <c r="J97" s="24"/>
     </row>
     <row r="98" ht="25" customHeight="1" spans="1:10">
-      <c r="A98" s="53" t="s">
-        <v>315</v>
+      <c r="A98" s="62" t="s">
+        <v>304</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="22"/>
       <c r="F98" s="22" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="G98" s="23"/>
       <c r="H98" s="7"/>
@@ -6160,17 +6220,17 @@
       <c r="J98" s="24"/>
     </row>
     <row r="99" ht="25" customHeight="1" spans="1:10">
-      <c r="A99" s="53" t="s">
-        <v>318</v>
+      <c r="A99" s="62" t="s">
+        <v>307</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="22"/>
       <c r="F99" s="22" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="G99" s="23"/>
       <c r="H99" s="7"/>
@@ -6178,17 +6238,17 @@
       <c r="J99" s="24"/>
     </row>
     <row r="100" ht="25" customHeight="1" spans="1:10">
-      <c r="A100" s="53" t="s">
-        <v>320</v>
+      <c r="A100" s="62" t="s">
+        <v>310</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="22"/>
       <c r="F100" s="22" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="G100" s="23"/>
       <c r="H100" s="7"/>
@@ -6196,17 +6256,17 @@
       <c r="J100" s="24"/>
     </row>
     <row r="101" ht="25" customHeight="1" spans="1:10">
-      <c r="A101" s="53" t="s">
-        <v>323</v>
+      <c r="A101" s="62" t="s">
+        <v>313</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="22"/>
       <c r="F101" s="22" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="G101" s="23"/>
       <c r="H101" s="7"/>
@@ -6214,17 +6274,17 @@
       <c r="J101" s="24"/>
     </row>
     <row r="102" ht="25" customHeight="1" spans="1:10">
-      <c r="A102" s="53" t="s">
-        <v>325</v>
+      <c r="A102" s="62" t="s">
+        <v>315</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="22"/>
       <c r="F102" s="22" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="G102" s="23"/>
       <c r="H102" s="7"/>
@@ -6232,15 +6292,17 @@
       <c r="J102" s="24"/>
     </row>
     <row r="103" ht="25" customHeight="1" spans="1:10">
-      <c r="A103" s="53" t="s">
-        <v>327</v>
+      <c r="A103" s="62" t="s">
+        <v>318</v>
       </c>
       <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
+      <c r="C103" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="D103" s="7"/>
       <c r="E103" s="22"/>
       <c r="F103" s="22" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="G103" s="23"/>
       <c r="H103" s="7"/>
@@ -6248,17 +6310,17 @@
       <c r="J103" s="24"/>
     </row>
     <row r="104" ht="25" customHeight="1" spans="1:10">
-      <c r="A104" s="53" t="s">
-        <v>329</v>
+      <c r="A104" s="62" t="s">
+        <v>321</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D104" s="7"/>
       <c r="E104" s="22"/>
       <c r="F104" s="22" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="G104" s="23"/>
       <c r="H104" s="7"/>
@@ -6266,87 +6328,89 @@
       <c r="J104" s="24"/>
     </row>
     <row r="105" ht="25" customHeight="1" spans="1:10">
-      <c r="A105" s="53" t="s">
-        <v>332</v>
+      <c r="A105" s="62" t="s">
+        <v>324</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="22"/>
       <c r="F105" s="22" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="G105" s="23"/>
       <c r="H105" s="7"/>
       <c r="I105" s="24"/>
       <c r="J105" s="24"/>
     </row>
-    <row r="106" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A106" s="55" t="s">
-        <v>335</v>
-      </c>
-      <c r="B106" s="48"/>
-      <c r="C106" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="D106" s="48"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52" t="s">
-        <v>292</v>
+    <row r="106" ht="25" customHeight="1" spans="1:10">
+      <c r="A106" s="62" t="s">
+        <v>326</v>
+      </c>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D106" s="7"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="22" t="s">
+        <v>328</v>
       </c>
       <c r="G106" s="23"/>
-      <c r="H106" s="48"/>
-      <c r="I106" s="56"/>
-      <c r="J106" s="56"/>
-    </row>
-    <row r="107" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A107" s="55" t="s">
-        <v>336</v>
-      </c>
-      <c r="B107" s="48"/>
-      <c r="C107" s="48"/>
-      <c r="D107" s="48"/>
-      <c r="E107" s="52"/>
-      <c r="F107" s="52" t="s">
-        <v>337</v>
+      <c r="H106" s="7"/>
+      <c r="I106" s="24"/>
+      <c r="J106" s="24"/>
+    </row>
+    <row r="107" ht="25" customHeight="1" spans="1:10">
+      <c r="A107" s="62" t="s">
+        <v>329</v>
+      </c>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D107" s="7"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="22" t="s">
+        <v>330</v>
       </c>
       <c r="G107" s="23"/>
-      <c r="H107" s="48"/>
-      <c r="I107" s="56"/>
-      <c r="J107" s="56"/>
-    </row>
-    <row r="108" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A108" s="55" t="s">
-        <v>338</v>
-      </c>
-      <c r="B108" s="48"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="24"/>
+    </row>
+    <row r="108" ht="25" customHeight="1" spans="1:10">
+      <c r="A108" s="62" t="s">
+        <v>331</v>
+      </c>
+      <c r="B108" s="7"/>
       <c r="C108" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="D108" s="48"/>
-      <c r="E108" s="52"/>
-      <c r="F108" s="52" t="s">
-        <v>339</v>
+        <v>332</v>
+      </c>
+      <c r="D108" s="7"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22" t="s">
+        <v>333</v>
       </c>
       <c r="G108" s="23"/>
-      <c r="H108" s="48"/>
-      <c r="I108" s="56"/>
-      <c r="J108" s="56"/>
+      <c r="H108" s="7"/>
+      <c r="I108" s="24"/>
+      <c r="J108" s="24"/>
     </row>
     <row r="109" ht="25" customHeight="1" spans="1:10">
-      <c r="A109" s="53" t="s">
-        <v>340</v>
+      <c r="A109" s="62" t="s">
+        <v>334</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D109" s="7"/>
       <c r="E109" s="22"/>
       <c r="F109" s="22" t="s">
-        <v>342</v>
+        <v>303</v>
       </c>
       <c r="G109" s="23"/>
       <c r="H109" s="7"/>
@@ -6354,17 +6418,17 @@
       <c r="J109" s="24"/>
     </row>
     <row r="110" ht="25" customHeight="1" spans="1:10">
-      <c r="A110" s="53" t="s">
-        <v>343</v>
+      <c r="A110" s="62" t="s">
+        <v>336</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c r="D110" s="7"/>
       <c r="E110" s="22"/>
       <c r="F110" s="22" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="G110" s="23"/>
       <c r="H110" s="7"/>
@@ -6372,17 +6436,15 @@
       <c r="J110" s="24"/>
     </row>
     <row r="111" ht="25" customHeight="1" spans="1:10">
-      <c r="A111" s="53" t="s">
-        <v>344</v>
+      <c r="A111" s="62" t="s">
+        <v>338</v>
       </c>
       <c r="B111" s="7"/>
-      <c r="C111" s="7" t="s">
-        <v>294</v>
-      </c>
+      <c r="C111" s="7"/>
       <c r="D111" s="7"/>
       <c r="E111" s="22"/>
       <c r="F111" s="22" t="s">
-        <v>280</v>
+        <v>339</v>
       </c>
       <c r="G111" s="23"/>
       <c r="H111" s="7"/>
@@ -6390,17 +6452,17 @@
       <c r="J111" s="24"/>
     </row>
     <row r="112" ht="25" customHeight="1" spans="1:10">
-      <c r="A112" s="53" t="s">
-        <v>345</v>
+      <c r="A112" s="62" t="s">
+        <v>340</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="D112" s="7"/>
       <c r="E112" s="22"/>
       <c r="F112" s="22" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G112" s="23"/>
       <c r="H112" s="7"/>
@@ -6408,90 +6470,87 @@
       <c r="J112" s="24"/>
     </row>
     <row r="113" ht="25" customHeight="1" spans="1:10">
-      <c r="A113" s="53" t="s">
-        <v>347</v>
+      <c r="A113" s="62" t="s">
+        <v>343</v>
       </c>
       <c r="B113" s="7"/>
       <c r="C113" s="7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D113" s="7"/>
       <c r="E113" s="22"/>
       <c r="F113" s="22" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G113" s="23"/>
       <c r="H113" s="7"/>
       <c r="I113" s="24"/>
       <c r="J113" s="24"/>
     </row>
-    <row r="114" ht="25" customHeight="1" spans="1:10">
-      <c r="A114" s="53" t="s">
+    <row r="114" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A114" s="64" t="s">
+        <v>346</v>
+      </c>
+      <c r="B114" s="44"/>
+      <c r="C114" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="D114" s="44"/>
+      <c r="E114" s="56"/>
+      <c r="F114" s="56" t="s">
+        <v>303</v>
+      </c>
+      <c r="G114" s="23"/>
+      <c r="H114" s="44"/>
+      <c r="I114" s="65"/>
+      <c r="J114" s="65"/>
+    </row>
+    <row r="115" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A115" s="64" t="s">
+        <v>347</v>
+      </c>
+      <c r="B115" s="44"/>
+      <c r="C115" s="44"/>
+      <c r="D115" s="44"/>
+      <c r="E115" s="56"/>
+      <c r="F115" s="56" t="s">
+        <v>348</v>
+      </c>
+      <c r="G115" s="23"/>
+      <c r="H115" s="44"/>
+      <c r="I115" s="65"/>
+      <c r="J115" s="65"/>
+    </row>
+    <row r="116" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A116" s="64" t="s">
         <v>349</v>
       </c>
-      <c r="B114" s="7"/>
-      <c r="C114" s="7" t="s">
+      <c r="B116" s="44"/>
+      <c r="C116" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D116" s="44"/>
+      <c r="E116" s="56"/>
+      <c r="F116" s="56" t="s">
         <v>350</v>
       </c>
-      <c r="D114" s="7"/>
-      <c r="E114" s="22"/>
-      <c r="F114" s="22" t="s">
+      <c r="G116" s="23"/>
+      <c r="H116" s="44"/>
+      <c r="I116" s="65"/>
+      <c r="J116" s="65"/>
+    </row>
+    <row r="117" ht="25" customHeight="1" spans="1:10">
+      <c r="A117" s="62" t="s">
         <v>351</v>
       </c>
-      <c r="G114" s="23"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="24"/>
-      <c r="J114" s="24"/>
-    </row>
-    <row r="115" ht="25" customHeight="1" spans="1:10">
-      <c r="A115" s="53" t="s">
+      <c r="B117" s="7"/>
+      <c r="C117" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D115" s="7"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="G115" s="23"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-    </row>
-    <row r="116" ht="25" customHeight="1" spans="1:10">
-      <c r="A116" s="53" t="s">
-        <v>354</v>
-      </c>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="D116" s="7"/>
-      <c r="E116" s="22"/>
-      <c r="F116" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="G116" s="23"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="24"/>
-      <c r="J116" s="24">
-        <f>2100*60</f>
-        <v>126000</v>
-      </c>
-    </row>
-    <row r="117" ht="25" customHeight="1" spans="1:10">
-      <c r="A117" s="53" t="s">
-        <v>357</v>
-      </c>
-      <c r="B117" s="7"/>
-      <c r="C117" s="7"/>
       <c r="D117" s="7"/>
       <c r="E117" s="22"/>
       <c r="F117" s="22" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G117" s="23"/>
       <c r="H117" s="7"/>
@@ -6499,17 +6558,17 @@
       <c r="J117" s="24"/>
     </row>
     <row r="118" ht="25" customHeight="1" spans="1:10">
-      <c r="A118" s="53" t="s">
-        <v>359</v>
+      <c r="A118" s="62" t="s">
+        <v>354</v>
       </c>
       <c r="B118" s="7"/>
       <c r="C118" s="7" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="22"/>
       <c r="F118" s="22" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="G118" s="23"/>
       <c r="H118" s="7"/>
@@ -6517,17 +6576,17 @@
       <c r="J118" s="24"/>
     </row>
     <row r="119" ht="25" customHeight="1" spans="1:10">
-      <c r="A119" s="53" t="s">
-        <v>362</v>
+      <c r="A119" s="62" t="s">
+        <v>355</v>
       </c>
       <c r="B119" s="7"/>
       <c r="C119" s="7" t="s">
-        <v>363</v>
+        <v>305</v>
       </c>
       <c r="D119" s="7"/>
       <c r="E119" s="22"/>
       <c r="F119" s="22" t="s">
-        <v>364</v>
+        <v>291</v>
       </c>
       <c r="G119" s="23"/>
       <c r="H119" s="7"/>
@@ -6535,96 +6594,145 @@
       <c r="J119" s="24"/>
     </row>
     <row r="120" ht="25" customHeight="1" spans="1:10">
-      <c r="A120" s="21"/>
+      <c r="A120" s="62" t="s">
+        <v>356</v>
+      </c>
       <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
+      <c r="C120" s="7" t="s">
+        <v>322</v>
+      </c>
       <c r="D120" s="7"/>
       <c r="E120" s="22"/>
-      <c r="F120" s="22"/>
+      <c r="F120" s="22" t="s">
+        <v>357</v>
+      </c>
       <c r="G120" s="23"/>
       <c r="H120" s="7"/>
       <c r="I120" s="24"/>
       <c r="J120" s="24"/>
     </row>
     <row r="121" ht="25" customHeight="1" spans="1:10">
-      <c r="A121" s="21"/>
+      <c r="A121" s="62" t="s">
+        <v>358</v>
+      </c>
       <c r="B121" s="7"/>
-      <c r="C121" s="7"/>
+      <c r="C121" s="7" t="s">
+        <v>359</v>
+      </c>
       <c r="D121" s="7"/>
       <c r="E121" s="22"/>
-      <c r="F121" s="22"/>
+      <c r="F121" s="22" t="s">
+        <v>350</v>
+      </c>
       <c r="G121" s="23"/>
       <c r="H121" s="7"/>
       <c r="I121" s="24"/>
       <c r="J121" s="24"/>
     </row>
     <row r="122" ht="25" customHeight="1" spans="1:10">
-      <c r="A122" s="21"/>
+      <c r="A122" s="62" t="s">
+        <v>360</v>
+      </c>
       <c r="B122" s="7"/>
-      <c r="C122" s="7"/>
+      <c r="C122" s="7" t="s">
+        <v>361</v>
+      </c>
       <c r="D122" s="7"/>
       <c r="E122" s="22"/>
-      <c r="F122" s="22"/>
+      <c r="F122" s="22" t="s">
+        <v>362</v>
+      </c>
       <c r="G122" s="23"/>
       <c r="H122" s="7"/>
       <c r="I122" s="24"/>
       <c r="J122" s="24"/>
     </row>
     <row r="123" ht="25" customHeight="1" spans="1:10">
-      <c r="A123" s="21"/>
+      <c r="A123" s="62" t="s">
+        <v>363</v>
+      </c>
       <c r="B123" s="7"/>
-      <c r="C123" s="7"/>
+      <c r="C123" s="7" t="s">
+        <v>314</v>
+      </c>
       <c r="D123" s="7"/>
       <c r="E123" s="22"/>
-      <c r="F123" s="22"/>
+      <c r="F123" s="22" t="s">
+        <v>364</v>
+      </c>
       <c r="G123" s="23"/>
       <c r="H123" s="7"/>
       <c r="I123" s="24"/>
       <c r="J123" s="24"/>
     </row>
     <row r="124" ht="25" customHeight="1" spans="1:10">
-      <c r="A124" s="21"/>
+      <c r="A124" s="62" t="s">
+        <v>365</v>
+      </c>
       <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
+      <c r="C124" s="7" t="s">
+        <v>366</v>
+      </c>
       <c r="D124" s="7"/>
       <c r="E124" s="22"/>
-      <c r="F124" s="22"/>
+      <c r="F124" s="22" t="s">
+        <v>367</v>
+      </c>
       <c r="G124" s="23"/>
       <c r="H124" s="7"/>
       <c r="I124" s="24"/>
-      <c r="J124" s="24"/>
+      <c r="J124" s="24">
+        <f>2100*60</f>
+        <v>126000</v>
+      </c>
     </row>
     <row r="125" ht="25" customHeight="1" spans="1:10">
-      <c r="A125" s="21"/>
+      <c r="A125" s="62" t="s">
+        <v>368</v>
+      </c>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
       <c r="E125" s="22"/>
-      <c r="F125" s="22"/>
+      <c r="F125" s="22" t="s">
+        <v>369</v>
+      </c>
       <c r="G125" s="23"/>
       <c r="H125" s="7"/>
       <c r="I125" s="24"/>
       <c r="J125" s="24"/>
     </row>
     <row r="126" ht="25" customHeight="1" spans="1:10">
-      <c r="A126" s="21"/>
+      <c r="A126" s="62" t="s">
+        <v>370</v>
+      </c>
       <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
+      <c r="C126" s="7" t="s">
+        <v>371</v>
+      </c>
       <c r="D126" s="7"/>
       <c r="E126" s="22"/>
-      <c r="F126" s="22"/>
+      <c r="F126" s="22" t="s">
+        <v>372</v>
+      </c>
       <c r="G126" s="23"/>
       <c r="H126" s="7"/>
       <c r="I126" s="24"/>
       <c r="J126" s="24"/>
     </row>
     <row r="127" ht="25" customHeight="1" spans="1:10">
-      <c r="A127" s="21"/>
+      <c r="A127" s="62" t="s">
+        <v>373</v>
+      </c>
       <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
+      <c r="C127" s="7" t="s">
+        <v>374</v>
+      </c>
       <c r="D127" s="7"/>
       <c r="E127" s="22"/>
-      <c r="F127" s="22"/>
+      <c r="F127" s="22" t="s">
+        <v>375</v>
+      </c>
       <c r="G127" s="23"/>
       <c r="H127" s="7"/>
       <c r="I127" s="24"/>
@@ -6666,8 +6774,104 @@
       <c r="I130" s="24"/>
       <c r="J130" s="24"/>
     </row>
+    <row r="131" ht="25" customHeight="1" spans="1:10">
+      <c r="A131" s="21"/>
+      <c r="B131" s="7"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="22"/>
+      <c r="F131" s="22"/>
+      <c r="G131" s="23"/>
+      <c r="H131" s="7"/>
+      <c r="I131" s="24"/>
+      <c r="J131" s="24"/>
+    </row>
+    <row r="132" ht="25" customHeight="1" spans="1:10">
+      <c r="A132" s="21"/>
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="22"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="23"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="24"/>
+    </row>
+    <row r="133" ht="25" customHeight="1" spans="1:10">
+      <c r="A133" s="21"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="22"/>
+      <c r="F133" s="22"/>
+      <c r="G133" s="23"/>
+      <c r="H133" s="7"/>
+      <c r="I133" s="24"/>
+      <c r="J133" s="24"/>
+    </row>
+    <row r="134" ht="25" customHeight="1" spans="1:10">
+      <c r="A134" s="21"/>
+      <c r="B134" s="7"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="22"/>
+      <c r="F134" s="22"/>
+      <c r="G134" s="23"/>
+      <c r="H134" s="7"/>
+      <c r="I134" s="24"/>
+      <c r="J134" s="24"/>
+    </row>
+    <row r="135" ht="25" customHeight="1" spans="1:10">
+      <c r="A135" s="21"/>
+      <c r="B135" s="7"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="22"/>
+      <c r="F135" s="22"/>
+      <c r="G135" s="23"/>
+      <c r="H135" s="7"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="24"/>
+    </row>
+    <row r="136" ht="25" customHeight="1" spans="1:10">
+      <c r="A136" s="21"/>
+      <c r="B136" s="7"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="22"/>
+      <c r="F136" s="22"/>
+      <c r="G136" s="23"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="24"/>
+      <c r="J136" s="24"/>
+    </row>
+    <row r="137" ht="25" customHeight="1" spans="1:10">
+      <c r="A137" s="21"/>
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="22"/>
+      <c r="G137" s="23"/>
+      <c r="H137" s="7"/>
+      <c r="I137" s="24"/>
+      <c r="J137" s="24"/>
+    </row>
+    <row r="138" ht="25" customHeight="1" spans="1:10">
+      <c r="A138" s="21"/>
+      <c r="B138" s="7"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="23"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="24"/>
+      <c r="J138" s="24"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J119" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J127" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <colorFilter dxfId="0"/>
       <extLst>
@@ -6690,13 +6894,13 @@
         </dxfs>
       </extLst>
     </filterColumn>
-    <sortState ref="A1:J119">
+    <sortState ref="A1:J127">
       <sortCondition ref="F1:F87"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H30" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H71" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6722,7 +6926,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6731,22 +6935,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6754,28 +6958,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6783,28 +6987,28 @@
         <v>3</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6812,28 +7016,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6841,28 +7045,28 @@
         <v>5</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="D5" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>399</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>400</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>401</v>
+      </c>
+      <c r="H5" s="39" t="s">
         <v>387</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="I5" s="39" t="s">
         <v>388</v>
-      </c>
-      <c r="F5" s="39" t="s">
-        <v>389</v>
-      </c>
-      <c r="G5" s="39" t="s">
-        <v>390</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>376</v>
-      </c>
-      <c r="I5" s="39" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6870,28 +7074,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6899,28 +7103,28 @@
         <v>7</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6928,28 +7132,28 @@
         <v>8</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6957,28 +7161,28 @@
         <v>9</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6986,28 +7190,28 @@
         <v>10</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -7015,28 +7219,28 @@
         <v>11</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>168</v>
+        <v>267</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="E11" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="F11" s="39" t="s">
         <v>407</v>
       </c>
-      <c r="F11" s="39" t="s">
-        <v>396</v>
-      </c>
       <c r="G11" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -7044,28 +7248,28 @@
         <v>12</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>137</v>
+        <v>250</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="D12" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>420</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="H12" s="39" t="s">
         <v>408</v>
       </c>
-      <c r="E12" s="39" t="s">
-        <v>409</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>396</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>396</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>397</v>
-      </c>
       <c r="I12" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -7073,28 +7277,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -7102,28 +7306,28 @@
         <v>14</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>144</v>
+        <v>256</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -7131,28 +7335,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -7160,28 +7364,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -7189,28 +7393,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>221</v>
+        <v>86</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -7218,28 +7422,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>224</v>
+        <v>89</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -7247,28 +7451,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -7276,28 +7480,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -7305,28 +7509,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -7334,28 +7538,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -7363,28 +7567,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -7392,16 +7596,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -7481,13 +7685,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -7496,731 +7700,731 @@
         <v>24</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G2" s="10">
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G3" s="11">
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G4" s="11">
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>153</v>
+        <v>264</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G5" s="11">
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G6" s="11">
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G7" s="11">
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G8" s="11">
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G9" s="11">
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G10" s="11">
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G11" s="11">
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G12" s="11">
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G13" s="11">
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G14" s="11">
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G15" s="11">
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>153</v>
+        <v>264</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G16" s="11">
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="20" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="20" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="20" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -8238,37 +8442,37 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
         <v>9</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="G34" s="23">
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>184</v>
+        <v>25</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -8282,7 +8486,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -8296,7 +8500,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -8310,7 +8514,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -8324,7 +8528,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -8337,7 +8541,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -8351,7 +8555,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -8364,7 +8568,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -8377,7 +8581,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -8390,120 +8594,120 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="G44" s="23">
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="G45" s="23">
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="G46" s="23">
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="G47" s="23">
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="22" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="G48" s="23">
         <v>2026</v>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
     <sheet name="已删" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">在播剧更新时间表!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已删!$A$1:$J$48</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="490">
   <si>
     <t>剧名</t>
   </si>
@@ -225,16 +225,43 @@
     <t>接：https://pan.quark.cn/s/24858c62440b?pwd=4tiR 提取码：4tiR</t>
   </si>
   <si>
+    <t>永夜之王</t>
+  </si>
+  <si>
+    <t>动漫</t>
+  </si>
+  <si>
+    <t>13/40</t>
+  </si>
+  <si>
+    <t>三角洲：造物主玩家</t>
+  </si>
+  <si>
+    <t>23/28</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/38c631aeeb25?pwd=w23Y 提取码：w23Y</t>
+  </si>
+  <si>
+    <t>牛大力作妖记​</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/8f6ff468962a?pwd=AuSM  提取码：AuSM</t>
+  </si>
+  <si>
+    <t>九宵神女</t>
+  </si>
+  <si>
+    <t>链接：https://pan.quark.cn/s/5df681c49e04?pwd=i5B3 提取码：i5B3</t>
+  </si>
+  <si>
     <t>李熊猫</t>
   </si>
   <si>
-    <t>动漫</t>
-  </si>
-  <si>
     <t>喜剧/动作/动画/奇幻</t>
   </si>
   <si>
-    <t>10/18</t>
+    <t>11/18</t>
   </si>
   <si>
     <t>齐璇/小连杀/ 魏一凡/ 朱祎</t>
@@ -264,18 +291,6 @@
     <t>链接：https://pan.quark.cn/s/986b72527b6d?pwd=JyMm 提取码：JyMm</t>
   </si>
   <si>
-    <t>牛大力作妖记​</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/8f6ff468962a?pwd=AuSM  提取码：AuSM</t>
-  </si>
-  <si>
-    <t>九宵神女</t>
-  </si>
-  <si>
-    <t>链接：https://pan.quark.cn/s/5df681c49e04?pwd=i5B3 提取码：i5B3</t>
-  </si>
-  <si>
     <t>神的游戏</t>
   </si>
   <si>
@@ -316,6 +331,12 @@
   </si>
   <si>
     <t>链接：https://pan.quark.cn/s/dce3c89fc12d?pwd=HYLy  提取码：HYLy</t>
+  </si>
+  <si>
+    <t>我用夸克网盘给你分享了「SJ造j物主」，点击链接或复制整段内容，打开「夸克APP」即可获取。</t>
+  </si>
+  <si>
+    <t>/~726a3b3RPt~:/</t>
   </si>
   <si>
     <t>楚人美游记</t>
@@ -1306,335 +1327,10 @@
     <t>链接：https://pan.quark.cn/s/3b6a404a18cf?pwd=KZQM 提取码：KZQM</t>
   </si>
   <si>
-    <t>杯雪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">藤新/李兰陵/杨昕燃/常蓉珊/沈念如 </t>
-  </si>
-  <si>
-    <t>怒之杀</t>
-  </si>
-  <si>
-    <t>未上映</t>
-  </si>
-  <si>
-    <t>第九层反转</t>
-  </si>
-  <si>
-    <t>玩具总动员5</t>
-  </si>
-  <si>
-    <t>爱恋成婚</t>
-  </si>
-  <si>
-    <t>智能车劫</t>
-  </si>
-  <si>
-    <t>追踪者游戏W 水鱼交融</t>
-  </si>
-  <si>
-    <t>歪心狼对阵ACME</t>
-  </si>
-  <si>
-    <t>鲨笼绝境</t>
-  </si>
-  <si>
-    <t>蝙蝠侠：骑士陨落 第一部</t>
-  </si>
-  <si>
-    <t>最后的刺客</t>
-  </si>
-  <si>
-    <t>顺风车杀手</t>
-  </si>
-  <si>
-    <t>95分</t>
-  </si>
-  <si>
-    <t>核战边缘</t>
-  </si>
-  <si>
-    <t>117分</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>小黄人与大怪兽</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>奇幻变身大冒险</t>
-  </si>
-  <si>
-    <t>乌女山怪谈</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.5"/>
-        <color rgb="FF494949"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>罪案重现</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.5"/>
-        <color rgb="FF494949"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>空枪</t>
-  </si>
-  <si>
-    <t>和平精英：地铁逃生</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>2026惊悚片《滑索惊魂》</t>
-  </si>
-  <si>
-    <t>失控的关系</t>
-  </si>
-  <si>
-    <t>奇门遁甲：逢凶化吉</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>阴风诡影</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>热血部落</t>
-  </si>
-  <si>
-    <t>最新动作片</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>山竹刀</t>
-  </si>
-  <si>
-    <t>最新武侠片</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>古寨枪声</t>
-  </si>
-  <si>
-    <t>最新战争片</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>午夜车库</t>
-  </si>
-  <si>
-    <t>最新恐怖片</t>
-  </si>
-  <si>
-    <t>非法闯入者</t>
-  </si>
-  <si>
-    <t>连环杀人案揭露网络信任危机和家庭暴力之恶</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>河神之渡阴</t>
-  </si>
-  <si>
-    <t>最新悬疑大片</t>
-  </si>
-  <si>
-    <t>58+68</t>
-  </si>
-  <si>
-    <t>我为什么又结婚了</t>
-  </si>
-  <si>
-    <t>最新喜剧片</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>生化杀机</t>
-  </si>
-  <si>
-    <t>恐怖丧尸片</t>
-  </si>
-  <si>
-    <t>蜂鸟行动</t>
-  </si>
-  <si>
-    <t>任贤齐最新战争大片</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>暴烈司机</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>崩溃边缘</t>
-  </si>
-  <si>
-    <t>最新惊悚大片</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>管控成瘾</t>
-  </si>
-  <si>
-    <t>最新科幻</t>
-  </si>
-  <si>
-    <t>醉胆追凶</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>冰雪猴</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>逃出绝命街</t>
-  </si>
-  <si>
-    <t>安妮·海瑟薇最新科幻大片</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>韩国死灵</t>
-  </si>
-  <si>
-    <t>最新奇幻喜剧大片</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>惩罚者</t>
-  </si>
-  <si>
-    <t>东游令</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>完美复制品</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>最后之吻</t>
-  </si>
-  <si>
-    <t>悬疑</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>荒山野店</t>
-  </si>
-  <si>
-    <t>狮拳 </t>
-  </si>
-  <si>
-    <t>歌剧般的潜入搜查官</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>当世主宰</t>
-  </si>
-  <si>
-    <t>这一切究竟是失控的科技，还是潜藏于世的邪恶力量</t>
-  </si>
-  <si>
-    <t>鬼界网红</t>
-  </si>
-  <si>
-    <t>最新喜剧</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>诺顿溪大屠杀</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>数到三</t>
-  </si>
-  <si>
-    <t>一颗心脏，竟藏了三个人的秘密</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>蜕变之后</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>四重心影</t>
-  </si>
-  <si>
-    <t>催眠解锁童年真相，这场自我博弈，她能与破碎的自己和解吗</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>窃心之人</t>
-  </si>
-  <si>
-    <t>经典家庭惊悚新作</t>
-  </si>
-  <si>
-    <t>86</t>
+    <t>八面埋伏</t>
+  </si>
+  <si>
+    <t>最新武侠动作片</t>
   </si>
   <si>
     <t>序号</t>
@@ -2362,7 +2058,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2429,6 +2125,13 @@
       <sz val="11"/>
       <color rgb="FF111111"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="19.5"/>
+      <color rgb="FF494949"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2581,26 +2284,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="19.5"/>
-      <color rgb="FF494949"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="19.5"/>
-      <color rgb="FF494949"/>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
       <name val="Helvetica"/>
       <charset val="134"/>
     </font>
@@ -2612,9 +2297,13 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3017,137 +2706,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3266,15 +2955,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3287,33 +2967,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3332,17 +3012,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3885,7 +3556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
@@ -3895,8 +3566,8 @@
     <col min="5" max="5" width="10.625" style="35" customWidth="1"/>
     <col min="6" max="6" width="10.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="44.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="4.875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="45.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="3.375" style="5" customWidth="1"/>
     <col min="10" max="10" width="74.5" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="6"/>
   </cols>
@@ -3946,7 +3617,7 @@
       <c r="D2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="23" t="s">
@@ -3990,7 +3661,7 @@
       <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="I3" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
@@ -4004,13 +3675,13 @@
       <c r="B4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="41" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="22" t="s">
         <v>27</v>
       </c>
       <c r="F4" s="23" t="s">
@@ -4023,7 +3694,7 @@
         <v>28</v>
       </c>
       <c r="I4" s="24"/>
-      <c r="J4" s="45" t="s">
+      <c r="J4" s="42" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4034,7 +3705,7 @@
       <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="41" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="23" t="s">
@@ -4064,7 +3735,7 @@
       <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="41" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="23" t="s">
@@ -4092,7 +3763,7 @@
       <c r="B7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="41" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="23" t="s">
@@ -4122,13 +3793,13 @@
       <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="41" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="22" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="23" t="s">
@@ -4137,7 +3808,7 @@
       <c r="G8" s="23">
         <v>2026</v>
       </c>
-      <c r="H8" s="46" t="s">
+      <c r="H8" s="43" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="24"/>
@@ -4152,7 +3823,7 @@
       <c r="B9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="41" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="23" t="s">
@@ -4182,13 +3853,13 @@
       <c r="B10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="41" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="22" t="s">
         <v>53</v>
       </c>
       <c r="F10" s="23" t="s">
@@ -4205,40 +3876,40 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A11" s="47" t="s">
+    <row r="11" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A11" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="23">
         <v>2026</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="48" t="s">
+      <c r="I11" s="24"/>
+      <c r="J11" s="7" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="12" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="21"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="44"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="23"/>
       <c r="E12" s="22"/>
       <c r="F12" s="23"/>
@@ -4248,44 +3919,68 @@
       <c r="J12" s="7"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A13" s="21"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="7"/>
+      <c r="A13" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="46"/>
+      <c r="D13" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="45">
+        <v>2026</v>
+      </c>
+      <c r="H13" s="45"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A14" s="21"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="23"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A15" s="25" t="s">
-        <v>61</v>
+      <c r="A14" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="46"/>
+      <c r="D14" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="45">
+        <v>2026</v>
+      </c>
+      <c r="H14" s="45"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A15" s="21" t="s">
+        <v>67</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>63</v>
-      </c>
+      <c r="C15" s="41"/>
       <c r="D15" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="52" t="s">
-        <v>64</v>
+      <c r="E15" s="50">
+        <v>7</v>
       </c>
       <c r="F15" s="23" t="s">
         <v>15</v>
@@ -4293,31 +3988,25 @@
       <c r="G15" s="23">
         <v>2026</v>
       </c>
-      <c r="H15" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="I15" s="53" t="s">
-        <v>66</v>
-      </c>
+      <c r="H15" s="23"/>
+      <c r="I15" s="24"/>
       <c r="J15" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A16" s="25" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="16" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A16" s="21" t="s">
+        <v>69</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>69</v>
-      </c>
+      <c r="C16" s="41"/>
       <c r="D16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="52" t="s">
-        <v>70</v>
+      <c r="E16" s="50">
+        <v>7</v>
       </c>
       <c r="F16" s="23" t="s">
         <v>15</v>
@@ -4325,82 +4014,90 @@
       <c r="G16" s="23">
         <v>2026</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A17" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="I16" s="53" t="s">
+      <c r="B17" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="D17" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="51" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="17" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A17" s="47" t="s">
+      <c r="F17" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H17" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="I17" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A18" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="50" t="s">
+      <c r="C18" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="52">
-        <v>7</v>
-      </c>
-      <c r="F17" s="50" t="s">
+      <c r="E18" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="50">
+      <c r="G18" s="23">
         <v>2026</v>
       </c>
-      <c r="H17" s="50"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="54" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A18" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="52">
-        <v>7</v>
-      </c>
-      <c r="F18" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="50">
-        <v>2026</v>
-      </c>
-      <c r="H18" s="50"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="48" t="s">
-        <v>77</v>
+      <c r="H18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="25" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>62</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="50">
         <v>7</v>
       </c>
       <c r="F19" s="23" t="s">
@@ -4410,27 +4107,27 @@
         <v>2026</v>
       </c>
       <c r="H19" s="23"/>
-      <c r="I19" s="53" t="s">
-        <v>80</v>
+      <c r="I19" s="52" t="s">
+        <v>85</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>62</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="50">
         <v>10</v>
       </c>
       <c r="F20" s="23" t="s">
@@ -4439,17 +4136,17 @@
       <c r="G20" s="23">
         <v>2026</v>
       </c>
-      <c r="H20" s="43"/>
-      <c r="I20" s="53" t="s">
-        <v>84</v>
+      <c r="H20" s="40"/>
+      <c r="I20" s="52" t="s">
+        <v>89</v>
       </c>
       <c r="J20" s="23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="25" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>62</v>
@@ -4458,7 +4155,7 @@
       <c r="D21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="50">
         <v>2</v>
       </c>
       <c r="F21" s="23" t="s">
@@ -4467,17 +4164,17 @@
       <c r="G21" s="23">
         <v>2026</v>
       </c>
-      <c r="H21" s="43"/>
-      <c r="I21" s="53" t="s">
-        <v>87</v>
+      <c r="H21" s="40"/>
+      <c r="I21" s="52" t="s">
+        <v>92</v>
       </c>
       <c r="J21" s="23" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="25" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>62</v>
@@ -4486,7 +4183,7 @@
       <c r="D22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="50">
         <v>4</v>
       </c>
       <c r="F22" s="23" t="s">
@@ -4495,12 +4192,12 @@
       <c r="G22" s="23">
         <v>2026</v>
       </c>
-      <c r="H22" s="43"/>
-      <c r="I22" s="53" t="s">
-        <v>90</v>
+      <c r="H22" s="40"/>
+      <c r="I22" s="52" t="s">
+        <v>95</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
@@ -4508,11 +4205,11 @@
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
-      <c r="E23" s="55"/>
+      <c r="E23" s="50"/>
       <c r="F23" s="23"/>
       <c r="G23" s="23"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="53"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="52"/>
       <c r="J23" s="7"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
@@ -4520,11 +4217,11 @@
       <c r="B24" s="23"/>
       <c r="C24" s="23"/>
       <c r="D24" s="23"/>
-      <c r="E24" s="55"/>
+      <c r="E24" s="50"/>
       <c r="F24" s="23"/>
       <c r="G24" s="23"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="53"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="52"/>
       <c r="J24" s="7"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
@@ -4532,11 +4229,11 @@
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
-      <c r="E25" s="55"/>
+      <c r="E25" s="50"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="53"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="52"/>
       <c r="J25" s="7"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
@@ -4544,47 +4241,53 @@
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
-      <c r="E26" s="55"/>
+      <c r="E26" s="50"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="7"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="7" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="25"/>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
-      <c r="E27" s="55"/>
+      <c r="E27" s="50"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="7"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="7" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="25"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
-      <c r="E28" s="55"/>
+      <c r="E28" s="50"/>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="7"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="7" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="25"/>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
-      <c r="E29" s="55"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="23"/>
       <c r="G29" s="23"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="53"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="52"/>
       <c r="J29" s="7"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
@@ -4592,11 +4295,11 @@
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
-      <c r="E30" s="55"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="23"/>
       <c r="G30" s="23"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="53"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="52"/>
       <c r="J30" s="7"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
@@ -4604,11 +4307,11 @@
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
-      <c r="E31" s="55"/>
+      <c r="E31" s="50"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="53"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="52"/>
       <c r="J31" s="7"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
@@ -4616,295 +4319,295 @@
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
-      <c r="E32" s="55"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="23"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="53"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="52"/>
       <c r="J32" s="7"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A33" s="21" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="44" t="s">
-        <v>93</v>
+      <c r="C33" s="41" t="s">
+        <v>100</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="56"/>
-      <c r="F33" s="44" t="s">
-        <v>94</v>
+      <c r="E33" s="53"/>
+      <c r="F33" s="41" t="s">
+        <v>101</v>
       </c>
       <c r="G33" s="23">
         <v>2026</v>
       </c>
       <c r="H33" s="23"/>
       <c r="I33" s="24" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J33" s="7"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A34" s="21" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="44" t="s">
-        <v>93</v>
+      <c r="C34" s="41" t="s">
+        <v>100</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="56"/>
-      <c r="F34" s="44" t="s">
-        <v>94</v>
+      <c r="E34" s="53"/>
+      <c r="F34" s="41" t="s">
+        <v>101</v>
       </c>
       <c r="G34" s="23">
         <v>2026</v>
       </c>
       <c r="H34" s="23"/>
       <c r="I34" s="24" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J34" s="7"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="22"/>
       <c r="F35" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
       <c r="I35" s="24" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="22"/>
       <c r="F36" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="24" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="22"/>
       <c r="F37" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
       <c r="I37" s="24" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="22"/>
       <c r="F38" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="24"/>
       <c r="J38" s="7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="22"/>
       <c r="F39" s="22" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G39" s="23">
         <v>2026</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="24" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="J39" s="21" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="22"/>
       <c r="F40" s="22" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G40" s="23">
         <v>2026</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="J40" s="24" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="C41" s="7" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="22"/>
       <c r="F41" s="22" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G41" s="23">
         <v>2026</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="J41" s="24" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="22"/>
       <c r="F42" s="22" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G42" s="23">
         <v>2026</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="J42" s="24" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
       <c r="A43" s="25" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="55">
+      <c r="E43" s="50">
         <v>36</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G43" s="23">
         <v>2026</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="I43" s="57" t="s">
-        <v>132</v>
+        <v>138</v>
+      </c>
+      <c r="I43" s="54" t="s">
+        <v>139</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A44" s="21" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>12</v>
@@ -4916,30 +4619,30 @@
         <v>33</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G44" s="23">
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="I44" s="57" t="s">
-        <v>136</v>
+        <v>142</v>
+      </c>
+      <c r="I44" s="54" t="s">
+        <v>143</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A45" s="21" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D45" s="23" t="s">
         <v>13</v>
@@ -4948,27 +4651,27 @@
         <v>23</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G45" s="23">
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A46" s="21" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>26</v>
@@ -4980,30 +4683,30 @@
         <v>23</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G46" s="23">
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A47" s="21" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>13</v>
@@ -5012,27 +4715,27 @@
         <v>24</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G47" s="23">
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A48" s="58" t="s">
-        <v>152</v>
+      <c r="A48" s="55" t="s">
+        <v>159</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C48" s="27" t="s">
         <v>12</v>
@@ -5044,30 +4747,30 @@
         <v>32</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G48" s="29">
         <v>2026</v>
       </c>
       <c r="H48" s="27" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A49" s="21" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C49" s="59" t="s">
-        <v>157</v>
+        <v>136</v>
+      </c>
+      <c r="C49" s="56" t="s">
+        <v>164</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>13</v>
@@ -5076,30 +4779,30 @@
         <v>24</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G49" s="23">
         <v>2026</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A50" s="25" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>13</v>
@@ -5108,30 +4811,30 @@
         <v>24</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G50" s="23">
         <v>2026</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A51" s="21" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>13</v>
@@ -5140,30 +4843,30 @@
         <v>25</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G51" s="23">
         <v>2026</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A52" s="21" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>13</v>
@@ -5172,30 +4875,30 @@
         <v>26</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G52" s="23">
         <v>2026</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A53" s="21" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>13</v>
@@ -5204,364 +4907,364 @@
         <v>24</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G53" s="23">
         <v>2026</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A54" s="25" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G54" s="23">
         <v>2026</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A55" s="25" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G55" s="23">
         <v>2026</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A56" s="25" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G56" s="23">
         <v>2026</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D57" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G57" s="23">
         <v>2026</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J57" s="7"/>
     </row>
     <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G58" s="23">
         <v>2026</v>
       </c>
-      <c r="H58" s="60" t="s">
-        <v>202</v>
+      <c r="H58" s="57" t="s">
+        <v>209</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="J58" s="7"/>
     </row>
     <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A59" s="21" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D59" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G59" s="23">
         <v>2026</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A60" s="21" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D60" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G60" s="23">
         <v>2026</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A61" s="25" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D61" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="55">
+      <c r="E61" s="50">
         <v>30</v>
       </c>
       <c r="F61" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G61" s="23">
         <v>2026</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="I61" s="53" t="s">
-        <v>217</v>
+        <v>223</v>
+      </c>
+      <c r="I61" s="52" t="s">
+        <v>224</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A62" s="25" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D62" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E62" s="55">
+      <c r="E62" s="50">
         <v>32</v>
       </c>
       <c r="F62" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G62" s="23">
         <v>2026</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="I62" s="53" t="s">
-        <v>222</v>
+        <v>228</v>
+      </c>
+      <c r="I62" s="52" t="s">
+        <v>229</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A63" s="25" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D63" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="55">
+      <c r="E63" s="50">
         <v>33</v>
       </c>
       <c r="F63" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G63" s="23">
         <v>2026</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="I63" s="53" t="s">
-        <v>227</v>
+        <v>233</v>
+      </c>
+      <c r="I63" s="52" t="s">
+        <v>234</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A64" s="25" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D64" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="55">
+      <c r="E64" s="50">
         <v>36</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G64" s="23">
         <v>2026</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="I64" s="53" t="s">
-        <v>232</v>
+        <v>238</v>
+      </c>
+      <c r="I64" s="52" t="s">
+        <v>239</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A65" s="21" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D65" s="23" t="s">
         <v>13</v>
@@ -5570,25 +5273,25 @@
         <v>22</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G65" s="23">
         <v>2026</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J65" s="7"/>
     </row>
     <row r="66" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A66" s="21" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>12</v>
@@ -5600,199 +5303,199 @@
         <v>24</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G66" s="23">
         <v>2026</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="J66" s="7"/>
     </row>
     <row r="67" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A67" s="21" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G67" s="7">
         <v>2026</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="J67" s="7"/>
     </row>
     <row r="68" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A68" s="21" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G68" s="7">
         <v>2026</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="J68" s="7"/>
     </row>
     <row r="69" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A69" s="25" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B69" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C69" s="61" t="s">
-        <v>251</v>
+      <c r="C69" s="58" t="s">
+        <v>258</v>
       </c>
       <c r="D69" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E69" s="55" t="s">
-        <v>252</v>
+      <c r="E69" s="50" t="s">
+        <v>259</v>
       </c>
       <c r="F69" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G69" s="23">
         <v>2026</v>
       </c>
       <c r="H69" s="23" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A70" s="25" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B70" s="23" t="s">
         <v>48</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D70" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E70" s="55" t="s">
-        <v>258</v>
+      <c r="E70" s="50" t="s">
+        <v>265</v>
       </c>
       <c r="F70" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G70" s="23">
         <v>2026</v>
       </c>
       <c r="H70" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="I70" s="53" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="I70" s="52" t="s">
+        <v>267</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A71" s="21" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C71" s="44" t="s">
-        <v>263</v>
+      <c r="C71" s="41" t="s">
+        <v>270</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="22" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="23" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="J71" s="7"/>
     </row>
     <row r="72" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A72" s="25" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B72" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="D72" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="55" t="s">
-        <v>252</v>
+      <c r="E72" s="50" t="s">
+        <v>259</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G72" s="23">
         <v>2026</v>
       </c>
       <c r="H72" s="23" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="I72" s="24" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="73" ht="25" customHeight="1" spans="1:10">
@@ -5808,114 +5511,68 @@
       <c r="J73" s="24"/>
     </row>
     <row r="74" ht="25" customHeight="1" spans="1:10">
-      <c r="A74" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="B74" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="C74" s="63" t="s">
-        <v>69</v>
-      </c>
+      <c r="A74" s="21"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="22"/>
-      <c r="F74" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="G74" s="23">
-        <v>8.25</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="F74" s="22"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="7"/>
       <c r="I74" s="24"/>
-      <c r="J74" s="21"/>
-    </row>
-    <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A75" s="62" t="s">
-        <v>274</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="J74" s="24"/>
+    </row>
+    <row r="75" ht="25" customHeight="1" spans="1:10">
+      <c r="A75" s="21"/>
+      <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="22"/>
-      <c r="F75" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="G75" s="23" t="s">
-        <v>275</v>
-      </c>
+      <c r="F75" s="22"/>
+      <c r="G75" s="23"/>
       <c r="H75" s="7"/>
       <c r="I75" s="24"/>
-      <c r="J75" s="21"/>
-    </row>
-    <row r="76" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A76" s="62" t="s">
-        <v>276</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="J75" s="24"/>
+    </row>
+    <row r="76" ht="25" customHeight="1" spans="1:10">
+      <c r="A76" s="21"/>
+      <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="22"/>
-      <c r="F76" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="G76" s="23">
-        <v>8.23</v>
-      </c>
+      <c r="F76" s="22"/>
+      <c r="G76" s="23"/>
       <c r="H76" s="7"/>
       <c r="I76" s="24"/>
-      <c r="J76" s="21"/>
-    </row>
-    <row r="77" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A77" s="62" t="s">
-        <v>277</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="J76" s="24"/>
+    </row>
+    <row r="77" ht="25" customHeight="1" spans="1:10">
+      <c r="A77" s="21"/>
+      <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="22"/>
       <c r="F77" s="22"/>
-      <c r="G77" s="23" t="s">
-        <v>275</v>
-      </c>
+      <c r="G77" s="23"/>
       <c r="H77" s="7"/>
       <c r="I77" s="24"/>
-      <c r="J77" s="21"/>
-    </row>
-    <row r="78" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A78" s="62" t="s">
-        <v>278</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="J77" s="24"/>
+    </row>
+    <row r="78" ht="25" customHeight="1" spans="1:10">
+      <c r="A78" s="21"/>
+      <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="22"/>
-      <c r="F78" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="G78" s="23">
-        <v>8.21</v>
-      </c>
+      <c r="F78" s="22"/>
+      <c r="G78" s="23"/>
       <c r="H78" s="7"/>
       <c r="I78" s="24"/>
-      <c r="J78" s="21"/>
-    </row>
-    <row r="79" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A79" s="62" t="s">
-        <v>279</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="J78" s="24"/>
+    </row>
+    <row r="79" ht="25" customHeight="1" spans="1:10">
+      <c r="A79" s="21"/>
+      <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="22"/>
@@ -5923,30 +5580,26 @@
       <c r="G79" s="23"/>
       <c r="H79" s="7"/>
       <c r="I79" s="24"/>
-      <c r="J79" s="21"/>
-    </row>
-    <row r="80" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A80" s="62" t="s">
+      <c r="J79" s="24"/>
+    </row>
+    <row r="80" ht="25" customHeight="1" spans="1:10">
+      <c r="A80" s="59" t="s">
+        <v>279</v>
+      </c>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="B80" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="22"/>
       <c r="F80" s="22"/>
-      <c r="G80" s="23">
-        <v>5.15</v>
-      </c>
+      <c r="G80" s="23"/>
       <c r="H80" s="7"/>
       <c r="I80" s="24"/>
-      <c r="J80" s="21"/>
-    </row>
-    <row r="81" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A81" s="62" t="s">
-        <v>281</v>
-      </c>
+      <c r="J80" s="24"/>
+    </row>
+    <row r="81" ht="25" customHeight="1" spans="1:10">
+      <c r="A81" s="21"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
@@ -5955,12 +5608,10 @@
       <c r="G81" s="23"/>
       <c r="H81" s="7"/>
       <c r="I81" s="24"/>
-      <c r="J81" s="21"/>
-    </row>
-    <row r="82" s="6" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A82" s="62" t="s">
-        <v>282</v>
-      </c>
+      <c r="J81" s="24"/>
+    </row>
+    <row r="82" ht="25" customHeight="1" spans="1:10">
+      <c r="A82" s="21"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -5969,12 +5620,10 @@
       <c r="G82" s="23"/>
       <c r="H82" s="7"/>
       <c r="I82" s="24"/>
-      <c r="J82" s="21"/>
-    </row>
-    <row r="83" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A83" s="62" t="s">
-        <v>283</v>
-      </c>
+      <c r="J82" s="24"/>
+    </row>
+    <row r="83" ht="25" customHeight="1" spans="1:10">
+      <c r="A83" s="21"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -5983,12 +5632,10 @@
       <c r="G83" s="23"/>
       <c r="H83" s="7"/>
       <c r="I83" s="24"/>
-      <c r="J83" s="21"/>
-    </row>
-    <row r="84" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A84" s="62" t="s">
-        <v>284</v>
-      </c>
+      <c r="J83" s="24"/>
+    </row>
+    <row r="84" ht="25" customHeight="1" spans="1:10">
+      <c r="A84" s="21"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -5997,124 +5644,94 @@
       <c r="G84" s="23"/>
       <c r="H84" s="7"/>
       <c r="I84" s="24"/>
-      <c r="J84" s="21"/>
-    </row>
-    <row r="85" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A85" s="62" t="s">
-        <v>285</v>
-      </c>
+      <c r="J84" s="24"/>
+    </row>
+    <row r="85" ht="25" customHeight="1" spans="1:10">
+      <c r="A85" s="21"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="22"/>
-      <c r="F85" s="22" t="s">
-        <v>286</v>
-      </c>
+      <c r="F85" s="22"/>
       <c r="G85" s="23"/>
       <c r="H85" s="7"/>
       <c r="I85" s="24"/>
       <c r="J85" s="24"/>
     </row>
     <row r="86" ht="25" customHeight="1" spans="1:10">
-      <c r="A86" s="62" t="s">
-        <v>287</v>
-      </c>
+      <c r="A86" s="21"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="22"/>
-      <c r="F86" s="22" t="s">
-        <v>288</v>
-      </c>
+      <c r="F86" s="22"/>
       <c r="G86" s="23"/>
       <c r="H86" s="7"/>
       <c r="I86" s="24"/>
       <c r="J86" s="24"/>
     </row>
     <row r="87" ht="25" customHeight="1" spans="1:10">
-      <c r="A87" s="21" t="s">
-        <v>118</v>
-      </c>
+      <c r="A87" s="21"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="22"/>
-      <c r="F87" s="22" t="s">
-        <v>289</v>
-      </c>
+      <c r="F87" s="22"/>
       <c r="G87" s="23"/>
       <c r="H87" s="7"/>
       <c r="I87" s="24"/>
       <c r="J87" s="24"/>
     </row>
     <row r="88" ht="25" customHeight="1" spans="1:10">
-      <c r="A88" s="62" t="s">
-        <v>290</v>
-      </c>
+      <c r="A88" s="21"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="22"/>
-      <c r="F88" s="22" t="s">
-        <v>291</v>
-      </c>
+      <c r="F88" s="22"/>
       <c r="G88" s="23"/>
       <c r="H88" s="7"/>
       <c r="I88" s="24"/>
       <c r="J88" s="24"/>
     </row>
     <row r="89" ht="25" customHeight="1" spans="1:10">
-      <c r="A89" s="62" t="s">
-        <v>292</v>
-      </c>
+      <c r="A89" s="21"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="22"/>
-      <c r="F89" s="22">
-        <v>102</v>
-      </c>
+      <c r="F89" s="22"/>
       <c r="G89" s="23"/>
       <c r="H89" s="7"/>
       <c r="I89" s="24"/>
       <c r="J89" s="24"/>
     </row>
     <row r="90" ht="25" customHeight="1" spans="1:10">
-      <c r="A90" s="62" t="s">
-        <v>293</v>
-      </c>
+      <c r="A90" s="21"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="22"/>
-      <c r="F90" s="22">
-        <v>69</v>
-      </c>
+      <c r="F90" s="22"/>
       <c r="G90" s="23"/>
       <c r="H90" s="7"/>
       <c r="I90" s="24"/>
       <c r="J90" s="24"/>
     </row>
     <row r="91" ht="25" customHeight="1" spans="1:10">
-      <c r="A91" s="62" t="s">
-        <v>294</v>
-      </c>
+      <c r="A91" s="21"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="22"/>
-      <c r="F91" s="22">
-        <v>86</v>
-      </c>
+      <c r="F91" s="22"/>
       <c r="G91" s="23"/>
       <c r="H91" s="7"/>
       <c r="I91" s="24"/>
       <c r="J91" s="24"/>
     </row>
     <row r="92" ht="25" customHeight="1" spans="1:10">
-      <c r="A92" s="62" t="s">
-        <v>295</v>
-      </c>
+      <c r="A92" s="21"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -6126,25 +5743,19 @@
       <c r="J92" s="24"/>
     </row>
     <row r="93" ht="25" customHeight="1" spans="1:10">
-      <c r="A93" s="62" t="s">
-        <v>296</v>
-      </c>
+      <c r="A93" s="21"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="22"/>
-      <c r="F93" s="22" t="s">
-        <v>297</v>
-      </c>
+      <c r="F93" s="22"/>
       <c r="G93" s="23"/>
       <c r="H93" s="7"/>
       <c r="I93" s="24"/>
       <c r="J93" s="24"/>
     </row>
     <row r="94" ht="25" customHeight="1" spans="1:10">
-      <c r="A94" s="62" t="s">
-        <v>298</v>
-      </c>
+      <c r="A94" s="21"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -6156,9 +5767,7 @@
       <c r="J94" s="24"/>
     </row>
     <row r="95" ht="25" customHeight="1" spans="1:10">
-      <c r="A95" s="62" t="s">
-        <v>299</v>
-      </c>
+      <c r="A95" s="21"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -6170,708 +5779,319 @@
       <c r="J95" s="24"/>
     </row>
     <row r="96" ht="25" customHeight="1" spans="1:10">
-      <c r="A96" s="62" t="s">
-        <v>300</v>
-      </c>
+      <c r="A96" s="21"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="22"/>
-      <c r="F96" s="22" t="s">
-        <v>301</v>
-      </c>
+      <c r="F96" s="22"/>
       <c r="G96" s="23"/>
       <c r="H96" s="7"/>
       <c r="I96" s="24"/>
       <c r="J96" s="24"/>
     </row>
     <row r="97" ht="25" customHeight="1" spans="1:10">
-      <c r="A97" s="62" t="s">
-        <v>302</v>
-      </c>
+      <c r="A97" s="21"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="22"/>
-      <c r="F97" s="22" t="s">
-        <v>303</v>
-      </c>
+      <c r="F97" s="22"/>
       <c r="G97" s="23"/>
       <c r="H97" s="7"/>
       <c r="I97" s="24"/>
       <c r="J97" s="24"/>
     </row>
     <row r="98" ht="25" customHeight="1" spans="1:10">
-      <c r="A98" s="62" t="s">
-        <v>304</v>
-      </c>
+      <c r="A98" s="21"/>
       <c r="B98" s="7"/>
-      <c r="C98" s="7" t="s">
-        <v>305</v>
-      </c>
+      <c r="C98" s="7"/>
       <c r="D98" s="7"/>
       <c r="E98" s="22"/>
-      <c r="F98" s="22" t="s">
-        <v>306</v>
-      </c>
+      <c r="F98" s="22"/>
       <c r="G98" s="23"/>
       <c r="H98" s="7"/>
       <c r="I98" s="24"/>
       <c r="J98" s="24"/>
     </row>
     <row r="99" ht="25" customHeight="1" spans="1:10">
-      <c r="A99" s="62" t="s">
-        <v>307</v>
-      </c>
+      <c r="A99" s="21"/>
       <c r="B99" s="7"/>
-      <c r="C99" s="7" t="s">
-        <v>308</v>
-      </c>
+      <c r="C99" s="7"/>
       <c r="D99" s="7"/>
       <c r="E99" s="22"/>
-      <c r="F99" s="22" t="s">
-        <v>309</v>
-      </c>
+      <c r="F99" s="22"/>
       <c r="G99" s="23"/>
       <c r="H99" s="7"/>
       <c r="I99" s="24"/>
       <c r="J99" s="24"/>
     </row>
     <row r="100" ht="25" customHeight="1" spans="1:10">
-      <c r="A100" s="62" t="s">
-        <v>310</v>
-      </c>
+      <c r="A100" s="21"/>
       <c r="B100" s="7"/>
-      <c r="C100" s="7" t="s">
-        <v>311</v>
-      </c>
+      <c r="C100" s="7"/>
       <c r="D100" s="7"/>
       <c r="E100" s="22"/>
-      <c r="F100" s="22" t="s">
-        <v>312</v>
-      </c>
+      <c r="F100" s="22"/>
       <c r="G100" s="23"/>
       <c r="H100" s="7"/>
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
     </row>
     <row r="101" ht="25" customHeight="1" spans="1:10">
-      <c r="A101" s="62" t="s">
-        <v>313</v>
-      </c>
+      <c r="A101" s="21"/>
       <c r="B101" s="7"/>
-      <c r="C101" s="7" t="s">
-        <v>314</v>
-      </c>
+      <c r="C101" s="7"/>
       <c r="D101" s="7"/>
       <c r="E101" s="22"/>
-      <c r="F101" s="22" t="s">
-        <v>303</v>
-      </c>
+      <c r="F101" s="22"/>
       <c r="G101" s="23"/>
       <c r="H101" s="7"/>
       <c r="I101" s="24"/>
       <c r="J101" s="24"/>
     </row>
     <row r="102" ht="25" customHeight="1" spans="1:10">
-      <c r="A102" s="62" t="s">
-        <v>315</v>
-      </c>
+      <c r="A102" s="21"/>
       <c r="B102" s="7"/>
-      <c r="C102" s="7" t="s">
-        <v>316</v>
-      </c>
+      <c r="C102" s="7"/>
       <c r="D102" s="7"/>
       <c r="E102" s="22"/>
-      <c r="F102" s="22" t="s">
-        <v>317</v>
-      </c>
+      <c r="F102" s="22"/>
       <c r="G102" s="23"/>
       <c r="H102" s="7"/>
       <c r="I102" s="24"/>
       <c r="J102" s="24"/>
     </row>
     <row r="103" ht="25" customHeight="1" spans="1:10">
-      <c r="A103" s="62" t="s">
-        <v>318</v>
-      </c>
+      <c r="A103" s="21"/>
       <c r="B103" s="7"/>
-      <c r="C103" s="7" t="s">
-        <v>319</v>
-      </c>
+      <c r="C103" s="7"/>
       <c r="D103" s="7"/>
       <c r="E103" s="22"/>
-      <c r="F103" s="22" t="s">
-        <v>320</v>
-      </c>
+      <c r="F103" s="22"/>
       <c r="G103" s="23"/>
       <c r="H103" s="7"/>
       <c r="I103" s="24"/>
       <c r="J103" s="24"/>
     </row>
     <row r="104" ht="25" customHeight="1" spans="1:10">
-      <c r="A104" s="62" t="s">
-        <v>321</v>
-      </c>
+      <c r="A104" s="21"/>
       <c r="B104" s="7"/>
-      <c r="C104" s="7" t="s">
-        <v>322</v>
-      </c>
+      <c r="C104" s="7"/>
       <c r="D104" s="7"/>
       <c r="E104" s="22"/>
-      <c r="F104" s="22" t="s">
-        <v>323</v>
-      </c>
+      <c r="F104" s="22"/>
       <c r="G104" s="23"/>
       <c r="H104" s="7"/>
       <c r="I104" s="24"/>
       <c r="J104" s="24"/>
     </row>
     <row r="105" ht="25" customHeight="1" spans="1:10">
-      <c r="A105" s="62" t="s">
-        <v>324</v>
-      </c>
+      <c r="A105" s="21"/>
       <c r="B105" s="7"/>
-      <c r="C105" s="7" t="s">
-        <v>325</v>
-      </c>
+      <c r="C105" s="7"/>
       <c r="D105" s="7"/>
       <c r="E105" s="22"/>
-      <c r="F105" s="22" t="s">
-        <v>291</v>
-      </c>
+      <c r="F105" s="22"/>
       <c r="G105" s="23"/>
       <c r="H105" s="7"/>
       <c r="I105" s="24"/>
       <c r="J105" s="24"/>
     </row>
     <row r="106" ht="25" customHeight="1" spans="1:10">
-      <c r="A106" s="62" t="s">
-        <v>326</v>
-      </c>
+      <c r="A106" s="21"/>
       <c r="B106" s="7"/>
-      <c r="C106" s="7" t="s">
-        <v>327</v>
-      </c>
+      <c r="C106" s="7"/>
       <c r="D106" s="7"/>
       <c r="E106" s="22"/>
-      <c r="F106" s="22" t="s">
-        <v>328</v>
-      </c>
+      <c r="F106" s="22"/>
       <c r="G106" s="23"/>
       <c r="H106" s="7"/>
       <c r="I106" s="24"/>
       <c r="J106" s="24"/>
     </row>
     <row r="107" ht="25" customHeight="1" spans="1:10">
-      <c r="A107" s="62" t="s">
-        <v>329</v>
-      </c>
+      <c r="A107" s="21"/>
       <c r="B107" s="7"/>
-      <c r="C107" s="7" t="s">
-        <v>305</v>
-      </c>
+      <c r="C107" s="7"/>
       <c r="D107" s="7"/>
       <c r="E107" s="22"/>
-      <c r="F107" s="22" t="s">
-        <v>330</v>
-      </c>
+      <c r="F107" s="22"/>
       <c r="G107" s="23"/>
       <c r="H107" s="7"/>
       <c r="I107" s="24"/>
       <c r="J107" s="24"/>
     </row>
     <row r="108" ht="25" customHeight="1" spans="1:10">
-      <c r="A108" s="62" t="s">
-        <v>331</v>
-      </c>
+      <c r="A108" s="21"/>
       <c r="B108" s="7"/>
-      <c r="C108" s="7" t="s">
-        <v>332</v>
-      </c>
+      <c r="C108" s="7"/>
       <c r="D108" s="7"/>
       <c r="E108" s="22"/>
-      <c r="F108" s="22" t="s">
-        <v>333</v>
-      </c>
+      <c r="F108" s="22"/>
       <c r="G108" s="23"/>
       <c r="H108" s="7"/>
       <c r="I108" s="24"/>
       <c r="J108" s="24"/>
     </row>
     <row r="109" ht="25" customHeight="1" spans="1:10">
-      <c r="A109" s="62" t="s">
-        <v>334</v>
-      </c>
+      <c r="A109" s="21"/>
       <c r="B109" s="7"/>
-      <c r="C109" s="7" t="s">
-        <v>335</v>
-      </c>
+      <c r="C109" s="7"/>
       <c r="D109" s="7"/>
       <c r="E109" s="22"/>
-      <c r="F109" s="22" t="s">
-        <v>303</v>
-      </c>
+      <c r="F109" s="22"/>
       <c r="G109" s="23"/>
       <c r="H109" s="7"/>
       <c r="I109" s="24"/>
       <c r="J109" s="24"/>
     </row>
     <row r="110" ht="25" customHeight="1" spans="1:10">
-      <c r="A110" s="62" t="s">
-        <v>336</v>
-      </c>
+      <c r="A110" s="21"/>
       <c r="B110" s="7"/>
-      <c r="C110" s="7" t="s">
-        <v>314</v>
-      </c>
+      <c r="C110" s="7"/>
       <c r="D110" s="7"/>
       <c r="E110" s="22"/>
-      <c r="F110" s="22" t="s">
-        <v>337</v>
-      </c>
+      <c r="F110" s="22"/>
       <c r="G110" s="23"/>
       <c r="H110" s="7"/>
       <c r="I110" s="24"/>
       <c r="J110" s="24"/>
     </row>
     <row r="111" ht="25" customHeight="1" spans="1:10">
-      <c r="A111" s="62" t="s">
-        <v>338</v>
-      </c>
+      <c r="A111" s="21"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
       <c r="E111" s="22"/>
-      <c r="F111" s="22" t="s">
-        <v>339</v>
-      </c>
+      <c r="F111" s="22"/>
       <c r="G111" s="23"/>
       <c r="H111" s="7"/>
       <c r="I111" s="24"/>
       <c r="J111" s="24"/>
     </row>
     <row r="112" ht="25" customHeight="1" spans="1:10">
-      <c r="A112" s="62" t="s">
-        <v>340</v>
-      </c>
+      <c r="A112" s="21"/>
       <c r="B112" s="7"/>
-      <c r="C112" s="7" t="s">
-        <v>341</v>
-      </c>
+      <c r="C112" s="7"/>
       <c r="D112" s="7"/>
       <c r="E112" s="22"/>
-      <c r="F112" s="22" t="s">
-        <v>342</v>
-      </c>
+      <c r="F112" s="22"/>
       <c r="G112" s="23"/>
       <c r="H112" s="7"/>
       <c r="I112" s="24"/>
       <c r="J112" s="24"/>
     </row>
     <row r="113" ht="25" customHeight="1" spans="1:10">
-      <c r="A113" s="62" t="s">
-        <v>343</v>
-      </c>
+      <c r="A113" s="21"/>
       <c r="B113" s="7"/>
-      <c r="C113" s="7" t="s">
-        <v>344</v>
-      </c>
+      <c r="C113" s="7"/>
       <c r="D113" s="7"/>
       <c r="E113" s="22"/>
-      <c r="F113" s="22" t="s">
-        <v>345</v>
-      </c>
+      <c r="F113" s="22"/>
       <c r="G113" s="23"/>
       <c r="H113" s="7"/>
       <c r="I113" s="24"/>
       <c r="J113" s="24"/>
     </row>
-    <row r="114" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A114" s="64" t="s">
-        <v>346</v>
-      </c>
-      <c r="B114" s="44"/>
-      <c r="C114" s="44" t="s">
-        <v>305</v>
-      </c>
-      <c r="D114" s="44"/>
-      <c r="E114" s="56"/>
-      <c r="F114" s="56" t="s">
-        <v>303</v>
-      </c>
+    <row r="114" ht="25" customHeight="1" spans="1:10">
+      <c r="A114" s="21"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="22"/>
       <c r="G114" s="23"/>
-      <c r="H114" s="44"/>
-      <c r="I114" s="65"/>
-      <c r="J114" s="65"/>
-    </row>
-    <row r="115" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A115" s="64" t="s">
-        <v>347</v>
-      </c>
-      <c r="B115" s="44"/>
-      <c r="C115" s="44"/>
-      <c r="D115" s="44"/>
-      <c r="E115" s="56"/>
-      <c r="F115" s="56" t="s">
-        <v>348</v>
-      </c>
+      <c r="H114" s="7"/>
+      <c r="I114" s="24"/>
+      <c r="J114" s="24"/>
+    </row>
+    <row r="115" ht="25" customHeight="1" spans="1:10">
+      <c r="A115" s="21"/>
+      <c r="B115" s="7"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
       <c r="G115" s="23"/>
-      <c r="H115" s="44"/>
-      <c r="I115" s="65"/>
-      <c r="J115" s="65"/>
-    </row>
-    <row r="116" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A116" s="64" t="s">
-        <v>349</v>
-      </c>
-      <c r="B116" s="44"/>
-      <c r="C116" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="D116" s="44"/>
-      <c r="E116" s="56"/>
-      <c r="F116" s="56" t="s">
-        <v>350</v>
-      </c>
+      <c r="H115" s="7"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+    </row>
+    <row r="116" ht="25" customHeight="1" spans="1:10">
+      <c r="A116" s="21"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="22"/>
       <c r="G116" s="23"/>
-      <c r="H116" s="44"/>
-      <c r="I116" s="65"/>
-      <c r="J116" s="65"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="24"/>
+      <c r="J116" s="24"/>
     </row>
     <row r="117" ht="25" customHeight="1" spans="1:10">
-      <c r="A117" s="62" t="s">
-        <v>351</v>
-      </c>
+      <c r="A117" s="21"/>
       <c r="B117" s="7"/>
-      <c r="C117" s="7" t="s">
-        <v>352</v>
-      </c>
+      <c r="C117" s="7"/>
       <c r="D117" s="7"/>
       <c r="E117" s="22"/>
-      <c r="F117" s="22" t="s">
-        <v>353</v>
-      </c>
+      <c r="F117" s="22"/>
       <c r="G117" s="23"/>
       <c r="H117" s="7"/>
       <c r="I117" s="24"/>
       <c r="J117" s="24"/>
     </row>
     <row r="118" ht="25" customHeight="1" spans="1:10">
-      <c r="A118" s="62" t="s">
-        <v>354</v>
-      </c>
+      <c r="A118" s="21"/>
       <c r="B118" s="7"/>
-      <c r="C118" s="7" t="s">
-        <v>352</v>
-      </c>
+      <c r="C118" s="7"/>
       <c r="D118" s="7"/>
       <c r="E118" s="22"/>
-      <c r="F118" s="22" t="s">
-        <v>291</v>
-      </c>
+      <c r="F118" s="22"/>
       <c r="G118" s="23"/>
       <c r="H118" s="7"/>
       <c r="I118" s="24"/>
       <c r="J118" s="24"/>
     </row>
     <row r="119" ht="25" customHeight="1" spans="1:10">
-      <c r="A119" s="62" t="s">
-        <v>355</v>
-      </c>
+      <c r="A119" s="21"/>
       <c r="B119" s="7"/>
-      <c r="C119" s="7" t="s">
-        <v>305</v>
-      </c>
+      <c r="C119" s="7"/>
       <c r="D119" s="7"/>
       <c r="E119" s="22"/>
-      <c r="F119" s="22" t="s">
-        <v>291</v>
-      </c>
+      <c r="F119" s="22"/>
       <c r="G119" s="23"/>
       <c r="H119" s="7"/>
       <c r="I119" s="24"/>
       <c r="J119" s="24"/>
     </row>
     <row r="120" ht="25" customHeight="1" spans="1:10">
-      <c r="A120" s="62" t="s">
-        <v>356</v>
-      </c>
+      <c r="A120" s="21"/>
       <c r="B120" s="7"/>
-      <c r="C120" s="7" t="s">
-        <v>322</v>
-      </c>
+      <c r="C120" s="7"/>
       <c r="D120" s="7"/>
       <c r="E120" s="22"/>
-      <c r="F120" s="22" t="s">
-        <v>357</v>
-      </c>
+      <c r="F120" s="22"/>
       <c r="G120" s="23"/>
       <c r="H120" s="7"/>
       <c r="I120" s="24"/>
       <c r="J120" s="24"/>
     </row>
     <row r="121" ht="25" customHeight="1" spans="1:10">
-      <c r="A121" s="62" t="s">
-        <v>358</v>
-      </c>
+      <c r="A121" s="21"/>
       <c r="B121" s="7"/>
-      <c r="C121" s="7" t="s">
-        <v>359</v>
-      </c>
+      <c r="C121" s="7"/>
       <c r="D121" s="7"/>
       <c r="E121" s="22"/>
-      <c r="F121" s="22" t="s">
-        <v>350</v>
-      </c>
+      <c r="F121" s="22"/>
       <c r="G121" s="23"/>
       <c r="H121" s="7"/>
       <c r="I121" s="24"/>
       <c r="J121" s="24"/>
     </row>
-    <row r="122" ht="25" customHeight="1" spans="1:10">
-      <c r="A122" s="62" t="s">
-        <v>360</v>
-      </c>
-      <c r="B122" s="7"/>
-      <c r="C122" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="D122" s="7"/>
-      <c r="E122" s="22"/>
-      <c r="F122" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="G122" s="23"/>
-      <c r="H122" s="7"/>
-      <c r="I122" s="24"/>
-      <c r="J122" s="24"/>
-    </row>
-    <row r="123" ht="25" customHeight="1" spans="1:10">
-      <c r="A123" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="B123" s="7"/>
-      <c r="C123" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="D123" s="7"/>
-      <c r="E123" s="22"/>
-      <c r="F123" s="22" t="s">
-        <v>364</v>
-      </c>
-      <c r="G123" s="23"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="24"/>
-    </row>
-    <row r="124" ht="25" customHeight="1" spans="1:10">
-      <c r="A124" s="62" t="s">
-        <v>365</v>
-      </c>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="D124" s="7"/>
-      <c r="E124" s="22"/>
-      <c r="F124" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="G124" s="23"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="24">
-        <f>2100*60</f>
-        <v>126000</v>
-      </c>
-    </row>
-    <row r="125" ht="25" customHeight="1" spans="1:10">
-      <c r="A125" s="62" t="s">
-        <v>368</v>
-      </c>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="22"/>
-      <c r="F125" s="22" t="s">
-        <v>369</v>
-      </c>
-      <c r="G125" s="23"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="24"/>
-    </row>
-    <row r="126" ht="25" customHeight="1" spans="1:10">
-      <c r="A126" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="D126" s="7"/>
-      <c r="E126" s="22"/>
-      <c r="F126" s="22" t="s">
-        <v>372</v>
-      </c>
-      <c r="G126" s="23"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="24"/>
-      <c r="J126" s="24"/>
-    </row>
-    <row r="127" ht="25" customHeight="1" spans="1:10">
-      <c r="A127" s="62" t="s">
-        <v>373</v>
-      </c>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D127" s="7"/>
-      <c r="E127" s="22"/>
-      <c r="F127" s="22" t="s">
-        <v>375</v>
-      </c>
-      <c r="G127" s="23"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="24"/>
-    </row>
-    <row r="128" ht="25" customHeight="1" spans="1:10">
-      <c r="A128" s="21"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
-      <c r="G128" s="23"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="24"/>
-    </row>
-    <row r="129" ht="25" customHeight="1" spans="1:10">
-      <c r="A129" s="21"/>
-      <c r="B129" s="7"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="22"/>
-      <c r="F129" s="22"/>
-      <c r="G129" s="23"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="24"/>
-      <c r="J129" s="24"/>
-    </row>
-    <row r="130" ht="25" customHeight="1" spans="1:10">
-      <c r="A130" s="21"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="22"/>
-      <c r="F130" s="22"/>
-      <c r="G130" s="23"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="24"/>
-      <c r="J130" s="24"/>
-    </row>
-    <row r="131" ht="25" customHeight="1" spans="1:10">
-      <c r="A131" s="21"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="22"/>
-      <c r="F131" s="22"/>
-      <c r="G131" s="23"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="24"/>
-      <c r="J131" s="24"/>
-    </row>
-    <row r="132" ht="25" customHeight="1" spans="1:10">
-      <c r="A132" s="21"/>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
-      <c r="G132" s="23"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-    </row>
-    <row r="133" ht="25" customHeight="1" spans="1:10">
-      <c r="A133" s="21"/>
-      <c r="B133" s="7"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="22"/>
-      <c r="F133" s="22"/>
-      <c r="G133" s="23"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="24"/>
-      <c r="J133" s="24"/>
-    </row>
-    <row r="134" ht="25" customHeight="1" spans="1:10">
-      <c r="A134" s="21"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="22"/>
-      <c r="F134" s="22"/>
-      <c r="G134" s="23"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="24"/>
-      <c r="J134" s="24"/>
-    </row>
-    <row r="135" ht="25" customHeight="1" spans="1:10">
-      <c r="A135" s="21"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="22"/>
-      <c r="F135" s="22"/>
-      <c r="G135" s="23"/>
-      <c r="H135" s="7"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="24"/>
-    </row>
-    <row r="136" ht="25" customHeight="1" spans="1:10">
-      <c r="A136" s="21"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="22"/>
-      <c r="F136" s="22"/>
-      <c r="G136" s="23"/>
-      <c r="H136" s="7"/>
-      <c r="I136" s="24"/>
-      <c r="J136" s="24"/>
-    </row>
-    <row r="137" ht="25" customHeight="1" spans="1:10">
-      <c r="A137" s="21"/>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="22"/>
-      <c r="F137" s="22"/>
-      <c r="G137" s="23"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="24"/>
-      <c r="J137" s="24"/>
-    </row>
-    <row r="138" ht="25" customHeight="1" spans="1:10">
-      <c r="A138" s="21"/>
-      <c r="B138" s="7"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="22"/>
-      <c r="F138" s="22"/>
-      <c r="G138" s="23"/>
-      <c r="H138" s="7"/>
-      <c r="I138" s="24"/>
-      <c r="J138" s="24"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J127" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J73" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <colorFilter dxfId="0"/>
       <extLst>
@@ -6894,7 +6114,7 @@
         </dxfs>
       </extLst>
     </filterColumn>
-    <sortState ref="A1:J127">
+    <sortState ref="A1:J73">
       <sortCondition ref="F1:F87"/>
     </sortState>
     <extLst/>
@@ -6926,7 +6146,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>376</v>
+        <v>281</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6935,22 +6155,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>377</v>
+        <v>282</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>378</v>
+        <v>283</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>379</v>
+        <v>284</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>380</v>
+        <v>285</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>381</v>
+        <v>286</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>382</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6958,28 +6178,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>383</v>
+        <v>288</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>385</v>
+        <v>290</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>386</v>
+        <v>291</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6987,28 +6207,28 @@
         <v>3</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>389</v>
+        <v>294</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>390</v>
+        <v>295</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>391</v>
+        <v>296</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>392</v>
+        <v>297</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>393</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -7016,28 +6236,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>394</v>
+        <v>299</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>395</v>
+        <v>300</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>396</v>
+        <v>301</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>397</v>
+        <v>302</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>393</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -7045,28 +6265,28 @@
         <v>5</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>398</v>
+        <v>303</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>399</v>
+        <v>304</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>400</v>
+        <v>305</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>401</v>
+        <v>306</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -7074,28 +6294,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>402</v>
+        <v>307</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>403</v>
+        <v>308</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>401</v>
+        <v>306</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>404</v>
+        <v>309</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -7109,22 +6329,22 @@
         <v>11</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>406</v>
+        <v>311</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -7138,22 +6358,22 @@
         <v>11</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>409</v>
+        <v>314</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>410</v>
+        <v>315</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -7161,28 +6381,28 @@
         <v>9</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>411</v>
+        <v>316</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>412</v>
+        <v>317</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>413</v>
+        <v>318</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>393</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -7190,28 +6410,28 @@
         <v>10</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>414</v>
+        <v>319</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>415</v>
+        <v>320</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>416</v>
+        <v>321</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>393</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -7219,28 +6439,28 @@
         <v>11</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>417</v>
+        <v>322</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>418</v>
+        <v>323</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -7248,28 +6468,28 @@
         <v>12</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>419</v>
+        <v>324</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -7277,28 +6497,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>421</v>
+        <v>326</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>422</v>
+        <v>327</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>423</v>
+        <v>328</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -7306,28 +6526,28 @@
         <v>14</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>48</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>424</v>
+        <v>329</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>425</v>
+        <v>330</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>426</v>
+        <v>331</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -7335,28 +6555,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>427</v>
+        <v>332</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>428</v>
+        <v>333</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>429</v>
+        <v>334</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>429</v>
+        <v>334</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>430</v>
+        <v>335</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -7364,28 +6584,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>432</v>
+        <v>337</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>433</v>
+        <v>338</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>434</v>
+        <v>339</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>434</v>
+        <v>339</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -7393,28 +6613,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>435</v>
+        <v>340</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>435</v>
+        <v>340</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>435</v>
+        <v>340</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -7422,28 +6642,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>436</v>
+        <v>341</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>435</v>
+        <v>340</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>435</v>
+        <v>340</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>435</v>
+        <v>340</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -7451,28 +6671,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>437</v>
+        <v>342</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>439</v>
+        <v>344</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>440</v>
+        <v>345</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -7480,28 +6700,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>441</v>
+        <v>346</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>442</v>
+        <v>347</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>443</v>
+        <v>348</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -7509,28 +6729,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>444</v>
+        <v>349</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>445</v>
+        <v>350</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>446</v>
+        <v>351</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>447</v>
+        <v>352</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -7538,28 +6758,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>448</v>
+        <v>353</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>449</v>
+        <v>354</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>393</v>
+        <v>298</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -7567,28 +6787,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>451</v>
+        <v>356</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>452</v>
+        <v>357</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>453</v>
+        <v>358</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>454</v>
+        <v>359</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>393</v>
+        <v>298</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -7596,16 +6816,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>455</v>
+        <v>360</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -7685,13 +6905,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>456</v>
+        <v>361</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>457</v>
+        <v>362</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -7700,731 +6920,731 @@
         <v>24</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G2" s="10">
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>458</v>
+        <v>363</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>459</v>
+        <v>364</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>460</v>
+        <v>365</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>461</v>
+        <v>366</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>462</v>
+        <v>367</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G3" s="11">
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>463</v>
+        <v>368</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>464</v>
+        <v>369</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>465</v>
+        <v>370</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>466</v>
+        <v>371</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>467</v>
+        <v>372</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G4" s="11">
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>468</v>
+        <v>373</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>469</v>
+        <v>374</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>470</v>
+        <v>375</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>471</v>
+        <v>376</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G5" s="11">
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>472</v>
+        <v>377</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>473</v>
+        <v>378</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>474</v>
+        <v>379</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>475</v>
+        <v>380</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>476</v>
+        <v>381</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G6" s="11">
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>477</v>
+        <v>382</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>478</v>
+        <v>383</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>479</v>
+        <v>384</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>480</v>
+        <v>385</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>481</v>
+        <v>386</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G7" s="11">
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>482</v>
+        <v>387</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>483</v>
+        <v>388</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>484</v>
+        <v>389</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>485</v>
+        <v>390</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>486</v>
+        <v>391</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G8" s="11">
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>487</v>
+        <v>392</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>488</v>
+        <v>393</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>489</v>
+        <v>394</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>490</v>
+        <v>395</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>491</v>
+        <v>396</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G9" s="11">
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>492</v>
+        <v>397</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>493</v>
+        <v>398</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>494</v>
+        <v>399</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>495</v>
+        <v>400</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>496</v>
+        <v>401</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G10" s="11">
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>497</v>
+        <v>402</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>498</v>
+        <v>403</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>499</v>
+        <v>404</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>500</v>
+        <v>405</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>501</v>
+        <v>406</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G11" s="11">
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>502</v>
+        <v>407</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>503</v>
+        <v>408</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>504</v>
+        <v>409</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>475</v>
+        <v>380</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>476</v>
+        <v>381</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G12" s="11">
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>505</v>
+        <v>410</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>506</v>
+        <v>411</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>507</v>
+        <v>412</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>508</v>
+        <v>413</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>509</v>
+        <v>414</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G13" s="11">
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>510</v>
+        <v>415</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>511</v>
+        <v>416</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>512</v>
+        <v>417</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>513</v>
+        <v>418</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>491</v>
+        <v>396</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G14" s="11">
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>514</v>
+        <v>419</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>515</v>
+        <v>420</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>516</v>
+        <v>421</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>517</v>
+        <v>422</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>491</v>
+        <v>396</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G15" s="11">
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>518</v>
+        <v>423</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>519</v>
+        <v>424</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>520</v>
+        <v>425</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>521</v>
+        <v>426</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>522</v>
+        <v>427</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G16" s="11">
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>523</v>
+        <v>428</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>524</v>
+        <v>429</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>525</v>
+        <v>430</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>526</v>
+        <v>431</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>527</v>
+        <v>432</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>528</v>
+        <v>433</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>529</v>
+        <v>434</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>530</v>
+        <v>435</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>531</v>
+        <v>436</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>532</v>
+        <v>437</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>533</v>
+        <v>438</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>534</v>
+        <v>439</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>535</v>
+        <v>440</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>536</v>
+        <v>441</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>537</v>
+        <v>442</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>538</v>
+        <v>443</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>539</v>
+        <v>444</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>540</v>
+        <v>445</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>541</v>
+        <v>446</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>542</v>
+        <v>447</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>543</v>
+        <v>448</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>544</v>
+        <v>449</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>545</v>
+        <v>450</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>546</v>
+        <v>451</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>547</v>
+        <v>452</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>548</v>
+        <v>453</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>549</v>
+        <v>454</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>550</v>
+        <v>455</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>551</v>
+        <v>456</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="20" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>552</v>
+        <v>457</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>553</v>
+        <v>458</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="20" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>554</v>
+        <v>459</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>555</v>
+        <v>460</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="20" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>556</v>
+        <v>461</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -8442,13 +7662,13 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>441</v>
+        <v>346</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>557</v>
+        <v>462</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
@@ -8461,13 +7681,13 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>559</v>
+        <v>464</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
@@ -8486,7 +7706,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>561</v>
+        <v>466</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -8500,7 +7720,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>562</v>
+        <v>467</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -8514,7 +7734,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>563</v>
+        <v>468</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -8528,7 +7748,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>564</v>
+        <v>469</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -8541,7 +7761,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>565</v>
+        <v>470</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -8555,7 +7775,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>566</v>
+        <v>471</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -8568,7 +7788,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>567</v>
+        <v>472</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -8581,7 +7801,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>568</v>
+        <v>473</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -8594,17 +7814,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>569</v>
+        <v>474</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>570</v>
+        <v>475</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>571</v>
+        <v>476</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>15</v>
@@ -8613,24 +7833,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>572</v>
+        <v>477</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>448</v>
+        <v>353</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>570</v>
+        <v>475</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>573</v>
+        <v>478</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>15</v>
@@ -8639,24 +7859,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>574</v>
+        <v>479</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>575</v>
+        <v>480</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>576</v>
+        <v>481</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>577</v>
+        <v>482</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>15</v>
@@ -8665,24 +7885,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>578</v>
+        <v>483</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>579</v>
+        <v>484</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>580</v>
+        <v>485</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>581</v>
+        <v>486</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>582</v>
+        <v>487</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>15</v>
@@ -8691,17 +7911,17 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>583</v>
+        <v>488</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>584</v>
+        <v>489</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="489">
   <si>
     <t>剧名</t>
   </si>
@@ -201,7 +201,7 @@
     <t>寄生之心</t>
   </si>
   <si>
-    <t>6/28</t>
+    <t>7/28</t>
   </si>
   <si>
     <t xml:space="preserve">瓦拉甘·萨瓦功 / 澈丁娜拉·朋琵拉德 </t>
@@ -232,6 +232,10 @@
   </si>
   <si>
     <t>13/40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接：https://pan.quark.cn/s/8641b9e6d14d?pwd=tiRp  提取码：tiRp
+</t>
   </si>
   <si>
     <t>三角洲：造物主玩家</t>
@@ -1325,12 +1329,6 @@
   </si>
   <si>
     <t>链接：https://pan.quark.cn/s/3b6a404a18cf?pwd=KZQM 提取码：KZQM</t>
-  </si>
-  <si>
-    <t>八面埋伏</t>
-  </si>
-  <si>
-    <t>最新武侠动作片</t>
   </si>
   <si>
     <t>序号</t>
@@ -2279,22 +2277,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -2306,8 +2298,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2318,12 +2316,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
         <bgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -2712,7 +2704,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2736,16 +2728,16 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2754,89 +2746,89 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2955,6 +2947,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2967,33 +2965,57 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3011,6 +3033,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3067,12 +3095,20 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3269,25 +3305,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3604,7 +3640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="2" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A2" s="21" t="s">
         <v>10</v>
       </c>
@@ -3636,7 +3672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="3" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A3" s="21" t="s">
         <v>19</v>
       </c>
@@ -3661,21 +3697,21 @@
       <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="42" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="4" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A4" s="21" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="43" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="23" t="s">
@@ -3694,18 +3730,18 @@
         <v>28</v>
       </c>
       <c r="I4" s="24"/>
-      <c r="J4" s="42" t="s">
+      <c r="J4" s="44" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="5" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A5" s="21" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="43" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="23" t="s">
@@ -3728,14 +3764,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="6" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A6" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="43" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="23" t="s">
@@ -3756,14 +3792,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="7" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A7" s="21" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="43" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="23" t="s">
@@ -3786,14 +3822,14 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="8" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A8" s="21" t="s">
         <v>42</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="43" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="23" t="s">
@@ -3808,7 +3844,7 @@
       <c r="G8" s="23">
         <v>2026</v>
       </c>
-      <c r="H8" s="43" t="s">
+      <c r="H8" s="45" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="24"/>
@@ -3816,14 +3852,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="9" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A9" s="21" t="s">
         <v>47</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="43" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="23" t="s">
@@ -3846,44 +3882,44 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A10" s="21" t="s">
+    <row r="10" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A10" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="49">
         <v>2026</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="51"/>
+      <c r="J10" s="47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="11" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A11" s="21" t="s">
         <v>56</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="43" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="23" t="s">
@@ -3906,10 +3942,10 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="12" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A12" s="21"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="41"/>
+      <c r="C12" s="43"/>
       <c r="D12" s="23"/>
       <c r="E12" s="22"/>
       <c r="F12" s="23"/>
@@ -3918,68 +3954,70 @@
       <c r="I12" s="24"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A13" s="44" t="s">
+    <row r="13" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A13" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="45" t="s">
+      <c r="C13" s="54"/>
+      <c r="D13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="E13" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="53">
         <v>2026</v>
       </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="49"/>
-    </row>
-    <row r="14" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A14" s="44" t="s">
+      <c r="H13" s="53"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="45" t="s">
+    </row>
+    <row r="14" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A14" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="45" t="s">
+      <c r="C14" s="54"/>
+      <c r="D14" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="45" t="s">
+      <c r="E14" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="53">
         <v>2026</v>
       </c>
-      <c r="H14" s="45"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="H14" s="53"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="57" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A15" s="21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="41"/>
+      <c r="C15" s="43"/>
       <c r="D15" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="58">
         <v>7</v>
       </c>
       <c r="F15" s="23" t="s">
@@ -3991,21 +4029,21 @@
       <c r="H15" s="23"/>
       <c r="I15" s="24"/>
       <c r="J15" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A16" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="41"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="58">
         <v>7</v>
       </c>
       <c r="F16" s="23" t="s">
@@ -4017,56 +4055,56 @@
       <c r="H16" s="23"/>
       <c r="I16" s="24"/>
       <c r="J16" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A17" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="23" t="s">
+    </row>
+    <row r="17" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A17" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="23" t="s">
+      <c r="C17" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="23" t="s">
+      <c r="E17" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="49">
         <v>2026</v>
       </c>
-      <c r="H17" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17" s="52" t="s">
+      <c r="H17" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="I17" s="61" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="J17" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A18" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>62</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D18" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="50" t="s">
-        <v>79</v>
+      <c r="E18" s="58" t="s">
+        <v>80</v>
       </c>
       <c r="F18" s="23" t="s">
         <v>15</v>
@@ -4075,29 +4113,29 @@
         <v>2026</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="I18" s="52" t="s">
         <v>81</v>
       </c>
+      <c r="I18" s="62" t="s">
+        <v>82</v>
+      </c>
       <c r="J18" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A19" s="25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>62</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="58">
         <v>7</v>
       </c>
       <c r="F19" s="23" t="s">
@@ -4107,27 +4145,27 @@
         <v>2026</v>
       </c>
       <c r="H19" s="23"/>
-      <c r="I19" s="52" t="s">
-        <v>85</v>
+      <c r="I19" s="62" t="s">
+        <v>86</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A20" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>62</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="58">
         <v>10</v>
       </c>
       <c r="F20" s="23" t="s">
@@ -4136,17 +4174,17 @@
       <c r="G20" s="23">
         <v>2026</v>
       </c>
-      <c r="H20" s="40"/>
-      <c r="I20" s="52" t="s">
-        <v>89</v>
+      <c r="H20" s="42"/>
+      <c r="I20" s="62" t="s">
+        <v>90</v>
       </c>
       <c r="J20" s="23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A21" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>62</v>
@@ -4155,7 +4193,7 @@
       <c r="D21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="58">
         <v>2</v>
       </c>
       <c r="F21" s="23" t="s">
@@ -4164,17 +4202,17 @@
       <c r="G21" s="23">
         <v>2026</v>
       </c>
-      <c r="H21" s="40"/>
-      <c r="I21" s="52" t="s">
-        <v>92</v>
+      <c r="H21" s="42"/>
+      <c r="I21" s="62" t="s">
+        <v>93</v>
       </c>
       <c r="J21" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A22" s="25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>62</v>
@@ -4183,7 +4221,7 @@
       <c r="D22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="58">
         <v>4</v>
       </c>
       <c r="F22" s="23" t="s">
@@ -4192,422 +4230,422 @@
       <c r="G22" s="23">
         <v>2026</v>
       </c>
-      <c r="H22" s="40"/>
-      <c r="I22" s="52" t="s">
-        <v>95</v>
+      <c r="H22" s="42"/>
+      <c r="I22" s="62" t="s">
+        <v>96</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A23" s="25"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
-      <c r="E23" s="50"/>
+      <c r="E23" s="58"/>
       <c r="F23" s="23"/>
       <c r="G23" s="23"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="52"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="62"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="24" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A24" s="25"/>
       <c r="B24" s="23"/>
       <c r="C24" s="23"/>
       <c r="D24" s="23"/>
-      <c r="E24" s="50"/>
+      <c r="E24" s="58"/>
       <c r="F24" s="23"/>
       <c r="G24" s="23"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="52"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="62"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="25" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A25" s="25"/>
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
-      <c r="E25" s="50"/>
+      <c r="E25" s="58"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="52"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="62"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="26" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A26" s="25"/>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
-      <c r="E26" s="50"/>
+      <c r="E26" s="58"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="52"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="62"/>
       <c r="J26" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A27" s="25"/>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
-      <c r="E27" s="50"/>
+      <c r="E27" s="58"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="52"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="62"/>
       <c r="J27" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A28" s="25"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
-      <c r="E28" s="50"/>
+      <c r="E28" s="58"/>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="52"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="62"/>
       <c r="J28" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A29" s="25"/>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
-      <c r="E29" s="50"/>
+      <c r="E29" s="58"/>
       <c r="F29" s="23"/>
       <c r="G29" s="23"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="52"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="62"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="30" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A30" s="25"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
-      <c r="E30" s="50"/>
+      <c r="E30" s="58"/>
       <c r="F30" s="23"/>
       <c r="G30" s="23"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="52"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="62"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="31" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A31" s="25"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
-      <c r="E31" s="50"/>
+      <c r="E31" s="58"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="52"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="62"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="32" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A32" s="25"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
-      <c r="E32" s="50"/>
+      <c r="E32" s="58"/>
       <c r="F32" s="23"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="52"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="62"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="33" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A33" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="41" t="s">
-        <v>100</v>
+      <c r="C33" s="43" t="s">
+        <v>101</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="53"/>
-      <c r="F33" s="41" t="s">
-        <v>101</v>
+      <c r="E33" s="63"/>
+      <c r="F33" s="43" t="s">
+        <v>102</v>
       </c>
       <c r="G33" s="23">
         <v>2026</v>
       </c>
       <c r="H33" s="23"/>
       <c r="I33" s="24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="41" t="s">
-        <v>100</v>
+      <c r="C34" s="43" t="s">
+        <v>101</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="53"/>
-      <c r="F34" s="41" t="s">
-        <v>101</v>
+      <c r="E34" s="63"/>
+      <c r="F34" s="43" t="s">
+        <v>102</v>
       </c>
       <c r="G34" s="23">
         <v>2026</v>
       </c>
       <c r="H34" s="23"/>
       <c r="I34" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A35" s="21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="22"/>
       <c r="F35" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
       <c r="I35" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A36" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A36" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="22"/>
       <c r="F36" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="22"/>
       <c r="F37" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
       <c r="I37" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="22"/>
       <c r="F38" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="24"/>
       <c r="J38" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" ht="25" customHeight="1" spans="1:10">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="22"/>
       <c r="F39" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G39" s="23">
         <v>2026</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="J39" s="21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A40" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="J39" s="21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="40" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A40" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>118</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="22"/>
       <c r="F40" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G40" s="23">
         <v>2026</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J40" s="24" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:10">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" ht="24" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="22"/>
       <c r="F41" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G41" s="23">
         <v>2026</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J41" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="42" ht="25" customHeight="1" spans="1:10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="22"/>
       <c r="F42" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G42" s="23">
         <v>2026</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J42" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="21" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="50">
+      <c r="E43" s="58">
         <v>36</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G43" s="23">
         <v>2026</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="I43" s="54" t="s">
         <v>139</v>
       </c>
+      <c r="I43" s="64" t="s">
+        <v>140</v>
+      </c>
       <c r="J43" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>12</v>
@@ -4619,30 +4657,30 @@
         <v>33</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G44" s="23">
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="I44" s="54" t="s">
         <v>143</v>
       </c>
+      <c r="I44" s="64" t="s">
+        <v>144</v>
+      </c>
       <c r="J44" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D45" s="23" t="s">
         <v>13</v>
@@ -4651,27 +4689,27 @@
         <v>23</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G45" s="23">
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>26</v>
@@ -4683,30 +4721,30 @@
         <v>23</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G46" s="23">
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>13</v>
@@ -4715,27 +4753,27 @@
         <v>24</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G47" s="23">
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A48" s="55" t="s">
         <v>159</v>
       </c>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="A48" s="65" t="s">
+        <v>160</v>
+      </c>
       <c r="B48" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C48" s="27" t="s">
         <v>12</v>
@@ -4747,30 +4785,30 @@
         <v>32</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G48" s="29">
         <v>2026</v>
       </c>
       <c r="H48" s="27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A49" s="21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49" s="56" t="s">
-        <v>164</v>
+        <v>137</v>
+      </c>
+      <c r="C49" s="66" t="s">
+        <v>165</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>13</v>
@@ -4779,30 +4817,30 @@
         <v>24</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G49" s="23">
         <v>2026</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="50" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A50" s="25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>13</v>
@@ -4811,30 +4849,30 @@
         <v>24</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G50" s="23">
         <v>2026</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="51" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A51" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>13</v>
@@ -4843,30 +4881,30 @@
         <v>25</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G51" s="23">
         <v>2026</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A52" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>13</v>
@@ -4875,30 +4913,30 @@
         <v>26</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G52" s="23">
         <v>2026</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="53" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A53" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>13</v>
@@ -4907,364 +4945,364 @@
         <v>24</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G53" s="23">
         <v>2026</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="54" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A54" s="25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G54" s="23">
         <v>2026</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="55" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A55" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G55" s="23">
         <v>2026</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="56" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A56" s="25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G56" s="23">
         <v>2026</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D57" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G57" s="23">
         <v>2026</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="58" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A58" s="21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G58" s="23">
         <v>2026</v>
       </c>
-      <c r="H58" s="57" t="s">
-        <v>209</v>
+      <c r="H58" s="67" t="s">
+        <v>210</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J58" s="7"/>
     </row>
-    <row r="59" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="59" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A59" s="21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D59" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G59" s="23">
         <v>2026</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A60" s="21" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D60" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G60" s="23">
         <v>2026</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A61" s="25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D61" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="58">
         <v>30</v>
       </c>
       <c r="F61" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G61" s="23">
         <v>2026</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="I61" s="52" t="s">
         <v>224</v>
       </c>
+      <c r="I61" s="62" t="s">
+        <v>225</v>
+      </c>
       <c r="J61" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A62" s="25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D62" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="58">
         <v>32</v>
       </c>
       <c r="F62" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G62" s="23">
         <v>2026</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="I62" s="52" t="s">
         <v>229</v>
       </c>
+      <c r="I62" s="62" t="s">
+        <v>230</v>
+      </c>
       <c r="J62" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A63" s="25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D63" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="50">
+      <c r="E63" s="58">
         <v>33</v>
       </c>
       <c r="F63" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G63" s="23">
         <v>2026</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="I63" s="52" t="s">
         <v>234</v>
       </c>
+      <c r="I63" s="62" t="s">
+        <v>235</v>
+      </c>
       <c r="J63" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A64" s="25" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D64" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="50">
+      <c r="E64" s="58">
         <v>36</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G64" s="23">
         <v>2026</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="I64" s="52" t="s">
         <v>239</v>
       </c>
+      <c r="I64" s="62" t="s">
+        <v>240</v>
+      </c>
       <c r="J64" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A65" s="21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D65" s="23" t="s">
         <v>13</v>
@@ -5273,25 +5311,25 @@
         <v>22</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G65" s="23">
         <v>2026</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="66" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A66" s="21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>12</v>
@@ -5303,202 +5341,202 @@
         <v>24</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G66" s="23">
         <v>2026</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="67" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A67" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G67" s="7">
         <v>2026</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="68" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A68" s="21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G68" s="7">
         <v>2026</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="69" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A69" s="25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B69" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C69" s="58" t="s">
-        <v>258</v>
+      <c r="C69" s="68" t="s">
+        <v>259</v>
       </c>
       <c r="D69" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E69" s="50" t="s">
-        <v>259</v>
+      <c r="E69" s="58" t="s">
+        <v>260</v>
       </c>
       <c r="F69" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G69" s="23">
         <v>2026</v>
       </c>
       <c r="H69" s="23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A70" s="25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B70" s="23" t="s">
         <v>48</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D70" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E70" s="50" t="s">
-        <v>265</v>
+      <c r="E70" s="58" t="s">
+        <v>266</v>
       </c>
       <c r="F70" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G70" s="23">
         <v>2026</v>
       </c>
       <c r="H70" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="I70" s="52" t="s">
         <v>267</v>
       </c>
+      <c r="I70" s="62" t="s">
+        <v>268</v>
+      </c>
       <c r="J70" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="71" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="71" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A71" s="21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C71" s="41" t="s">
-        <v>270</v>
+      <c r="C71" s="43" t="s">
+        <v>271</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J71" s="7"/>
     </row>
-    <row r="72" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="72" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A72" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B72" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D72" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="50" t="s">
-        <v>259</v>
+      <c r="E72" s="58" t="s">
+        <v>260</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G72" s="23">
         <v>2026</v>
       </c>
       <c r="H72" s="23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I72" s="24" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="73" ht="25" customHeight="1" spans="1:10">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="73" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A73" s="21"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -5510,17 +5548,17 @@
       <c r="I73" s="24"/>
       <c r="J73" s="24"/>
     </row>
-    <row r="74" ht="25" customHeight="1" spans="1:10">
-      <c r="A74" s="21"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="24"/>
-      <c r="J74" s="24"/>
+    <row r="74" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A74" s="46"/>
+      <c r="B74" s="47"/>
+      <c r="C74" s="47"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="47"/>
+      <c r="I74" s="51"/>
+      <c r="J74" s="51"/>
     </row>
     <row r="75" ht="25" customHeight="1" spans="1:10">
       <c r="A75" s="21"/>
@@ -5556,7 +5594,7 @@
       <c r="G77" s="23"/>
       <c r="H77" s="7"/>
       <c r="I77" s="24"/>
-      <c r="J77" s="24"/>
+      <c r="J77" s="70"/>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:10">
       <c r="A78" s="21"/>
@@ -5583,13 +5621,9 @@
       <c r="J79" s="24"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:10">
-      <c r="A80" s="59" t="s">
-        <v>279</v>
-      </c>
+      <c r="A80" s="71"/>
       <c r="B80" s="7"/>
-      <c r="C80" s="7" t="s">
-        <v>280</v>
-      </c>
+      <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="22"/>
       <c r="F80" s="22"/>
@@ -6113,6 +6147,9 @@
           </dxf>
         </dxfs>
       </extLst>
+    </filterColumn>
+    <filterColumn colId="4">
+      <colorFilter dxfId="1"/>
     </filterColumn>
     <sortState ref="A1:J73">
       <sortCondition ref="F1:F87"/>
@@ -6146,7 +6183,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6155,22 +6192,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="E1" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="F1" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="G1" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="H1" s="37" t="s">
         <v>285</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="I1" s="37" t="s">
         <v>286</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6178,28 +6215,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D2" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="E2" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="F2" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="H2" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="I2" s="39" t="s">
         <v>292</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6207,28 +6244,28 @@
         <v>3</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="F3" s="39" t="s">
         <v>295</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="G3" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="H3" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="I3" s="39" t="s">
         <v>297</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>292</v>
-      </c>
-      <c r="I3" s="39" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6236,28 +6273,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" s="39" t="s">
+        <v>298</v>
+      </c>
+      <c r="E4" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="F4" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="G4" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="F4" s="39" t="s">
-        <v>292</v>
-      </c>
-      <c r="G4" s="39" t="s">
+      <c r="H4" s="39" t="s">
         <v>301</v>
       </c>
-      <c r="H4" s="39" t="s">
-        <v>302</v>
-      </c>
       <c r="I4" s="39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6265,28 +6302,28 @@
         <v>5</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D5" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="F5" s="39" t="s">
         <v>304</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="G5" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="G5" s="39" t="s">
-        <v>306</v>
-      </c>
       <c r="H5" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="I5" s="39" t="s">
         <v>292</v>
-      </c>
-      <c r="I5" s="39" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6294,28 +6331,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D6" s="39" t="s">
+        <v>306</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="F6" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="H6" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="I6" s="39" t="s">
         <v>292</v>
-      </c>
-      <c r="G6" s="39" t="s">
-        <v>306</v>
-      </c>
-      <c r="H6" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="I6" s="39" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6329,22 +6366,22 @@
         <v>11</v>
       </c>
       <c r="D7" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="E7" s="39" t="s">
         <v>310</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="F7" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="G7" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H7" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G7" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H7" s="39" t="s">
-        <v>313</v>
-      </c>
       <c r="I7" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6358,22 +6395,22 @@
         <v>11</v>
       </c>
       <c r="D8" s="39" t="s">
+        <v>313</v>
+      </c>
+      <c r="E8" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="E8" s="39" t="s">
-        <v>315</v>
-      </c>
       <c r="F8" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H8" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G8" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>313</v>
-      </c>
       <c r="I8" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6381,28 +6418,28 @@
         <v>9</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="E9" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="F9" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="G9" s="39" t="s">
         <v>317</v>
       </c>
-      <c r="F9" s="39" t="s">
-        <v>292</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>318</v>
-      </c>
       <c r="H9" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6410,28 +6447,28 @@
         <v>10</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="39" t="s">
+        <v>318</v>
+      </c>
+      <c r="E10" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="F10" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>320</v>
       </c>
-      <c r="F10" s="39" t="s">
-        <v>292</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>321</v>
-      </c>
       <c r="H10" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -6439,28 +6476,28 @@
         <v>11</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="E11" s="39" t="s">
         <v>322</v>
       </c>
-      <c r="E11" s="39" t="s">
-        <v>323</v>
-      </c>
       <c r="F11" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H11" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G11" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>313</v>
-      </c>
       <c r="I11" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -6468,28 +6505,28 @@
         <v>12</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="39" t="s">
+        <v>323</v>
+      </c>
+      <c r="E12" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="E12" s="39" t="s">
-        <v>325</v>
-      </c>
       <c r="F12" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H12" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G12" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>313</v>
-      </c>
       <c r="I12" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -6497,28 +6534,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="39" t="s">
+        <v>326</v>
+      </c>
+      <c r="E13" s="39" t="s">
         <v>327</v>
       </c>
-      <c r="E13" s="39" t="s">
-        <v>328</v>
-      </c>
       <c r="F13" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H13" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G13" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>313</v>
-      </c>
       <c r="I13" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -6526,28 +6563,28 @@
         <v>14</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>48</v>
       </c>
       <c r="D14" s="39" t="s">
+        <v>328</v>
+      </c>
+      <c r="E14" s="39" t="s">
         <v>329</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="F14" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H14" s="39" t="s">
         <v>330</v>
       </c>
-      <c r="F14" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H14" s="39" t="s">
-        <v>331</v>
-      </c>
       <c r="I14" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -6555,28 +6592,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D15" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="E15" s="39" t="s">
         <v>332</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="F15" s="39" t="s">
         <v>333</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="G15" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="H15" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="G15" s="39" t="s">
-        <v>334</v>
-      </c>
-      <c r="H15" s="39" t="s">
+      <c r="I15" s="39" t="s">
         <v>335</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -6584,28 +6621,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="39" t="s">
+        <v>336</v>
+      </c>
+      <c r="E16" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="F16" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="F16" s="39" t="s">
-        <v>339</v>
-      </c>
       <c r="G16" s="39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -6613,28 +6650,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -6642,28 +6679,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -6671,28 +6708,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="38" t="s">
         <v>342</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="D19" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="E19" s="39" t="s">
         <v>344</v>
       </c>
-      <c r="E19" s="39" t="s">
-        <v>345</v>
-      </c>
       <c r="F19" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H19" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G19" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>313</v>
-      </c>
       <c r="I19" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -6700,28 +6737,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="D20" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="C20" s="38" t="s">
-        <v>343</v>
-      </c>
-      <c r="D20" s="39" t="s">
+      <c r="E20" s="39" t="s">
         <v>347</v>
       </c>
-      <c r="E20" s="39" t="s">
-        <v>348</v>
-      </c>
       <c r="F20" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H20" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G20" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>313</v>
-      </c>
       <c r="I20" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -6729,28 +6766,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
+        <v>348</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="D21" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="C21" s="38" t="s">
-        <v>343</v>
-      </c>
-      <c r="D21" s="39" t="s">
+      <c r="E21" s="39" t="s">
         <v>350</v>
       </c>
-      <c r="E21" s="39" t="s">
+      <c r="F21" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H21" s="39" t="s">
         <v>351</v>
       </c>
-      <c r="F21" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>352</v>
-      </c>
       <c r="I21" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -6758,28 +6795,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="D22" s="39" t="s">
         <v>353</v>
       </c>
-      <c r="C22" s="38" t="s">
-        <v>343</v>
-      </c>
-      <c r="D22" s="39" t="s">
+      <c r="E22" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="E22" s="39" t="s">
-        <v>355</v>
-      </c>
       <c r="F22" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H22" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="G22" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>313</v>
-      </c>
       <c r="I22" s="39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -6787,28 +6824,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>356</v>
       </c>
-      <c r="C23" s="38" t="s">
-        <v>343</v>
-      </c>
-      <c r="D23" s="39" t="s">
+      <c r="E23" s="39" t="s">
         <v>357</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="F23" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H23" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="F23" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="H23" s="39" t="s">
-        <v>359</v>
-      </c>
       <c r="I23" s="39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -6816,16 +6853,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -6905,13 +6942,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>361</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>362</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -6920,731 +6957,731 @@
         <v>24</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G2" s="10">
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="I2" s="12" t="s">
         <v>363</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>364</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>365</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>366</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G3" s="11">
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>368</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>369</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>370</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>371</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G4" s="11">
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="I4" s="15" t="s">
         <v>373</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>374</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>375</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>376</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G5" s="11">
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>377</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>378</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>379</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>380</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G6" s="11">
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>382</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>383</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>384</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>385</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G7" s="11">
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>387</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>388</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>389</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>390</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G8" s="11">
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>392</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>393</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>394</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>395</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G9" s="11">
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="I9" s="14" t="s">
         <v>397</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>398</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>399</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>400</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G10" s="11">
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="I10" s="14" t="s">
         <v>402</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>403</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>404</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>405</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G11" s="11">
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="I11" s="14" t="s">
         <v>407</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>408</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G12" s="11">
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="I12" s="14" t="s">
         <v>410</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>411</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>412</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>413</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" s="11">
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="I13" s="14" t="s">
         <v>415</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>416</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>417</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>418</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G14" s="11">
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="I14" s="14" t="s">
         <v>419</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>420</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>421</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>422</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G15" s="11">
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="I15" s="14" t="s">
         <v>423</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>424</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="C16" s="11" t="s">
         <v>426</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>427</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G16" s="11">
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="I16" s="14" t="s">
         <v>428</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>429</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -7662,13 +7699,13 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
@@ -7681,13 +7718,13 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="J34" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
@@ -7706,7 +7743,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -7720,7 +7757,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -7734,7 +7771,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -7748,7 +7785,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -7761,7 +7798,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -7775,7 +7812,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -7788,7 +7825,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -7801,7 +7838,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -7814,17 +7851,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="C44" s="34" t="s">
         <v>474</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="C44" s="34" t="s">
-        <v>475</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>15</v>
@@ -7833,24 +7870,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>15</v>
@@ -7859,24 +7896,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="C46" s="26" t="s">
         <v>480</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>481</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>15</v>
@@ -7885,24 +7922,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
+        <v>483</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="C47" s="26" t="s">
         <v>485</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>486</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>15</v>
@@ -7911,17 +7948,17 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
     <sheet name="已删" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表新!$A$1:$J$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">在播剧更新时间表!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已删!$A$1:$J$48</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="494">
   <si>
     <t>剧名</t>
   </si>
@@ -201,7 +201,7 @@
     <t>寄生之心</t>
   </si>
   <si>
-    <t>7/28</t>
+    <t>8/28</t>
   </si>
   <si>
     <t xml:space="preserve">瓦拉甘·萨瓦功 / 澈丁娜拉·朋琵拉德 </t>
@@ -223,6 +223,21 @@
   </si>
   <si>
     <t>接：https://pan.quark.cn/s/24858c62440b?pwd=4tiR 提取码：4tiR</t>
+  </si>
+  <si>
+    <t>月下之影</t>
+  </si>
+  <si>
+    <t>剧情 / 爱情 / 同性</t>
+  </si>
+  <si>
+    <t>7/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 塔诵·格林尼恩 / 帕特拉帕·博拉查达苏皖 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 链接：https://pan.quark.cn/s/8858fd2db43a?pwd=k9Gp 提取码：k9Gp</t>
   </si>
   <si>
     <t>永夜之王</t>
@@ -2277,6 +2292,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
@@ -2285,7 +2305,8 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2298,14 +2319,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2316,6 +2331,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
         <bgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -2704,7 +2725,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2728,16 +2749,16 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2746,89 +2767,89 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2947,12 +2968,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2965,55 +2980,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3032,9 +3023,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3095,20 +3083,12 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3305,25 +3285,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="totalRow" dxfId="6"/>
-      <tableStyleElement type="firstColumn" dxfId="5"/>
-      <tableStyleElement type="lastColumn" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
-      <tableStyleElement type="pageFieldValues" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3592,7 +3572,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.875" style="4" customWidth="1"/>
@@ -3640,7 +3620,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="2" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="21" t="s">
         <v>10</v>
       </c>
@@ -3672,7 +3652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="3" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="21" t="s">
         <v>19</v>
       </c>
@@ -3697,21 +3677,21 @@
       <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="42" t="s">
+      <c r="I3" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="4" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="21" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="41" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="23" t="s">
@@ -3730,18 +3710,18 @@
         <v>28</v>
       </c>
       <c r="I4" s="24"/>
-      <c r="J4" s="44" t="s">
+      <c r="J4" s="42" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="5" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="21" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="41" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="23" t="s">
@@ -3764,14 +3744,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="6" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="41" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="23" t="s">
@@ -3792,14 +3772,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="7" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="21" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="41" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="23" t="s">
@@ -3822,14 +3802,14 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="8" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="21" t="s">
         <v>42</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="41" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="23" t="s">
@@ -3844,7 +3824,7 @@
       <c r="G8" s="23">
         <v>2026</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="43" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="24"/>
@@ -3852,14 +3832,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="9" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="21" t="s">
         <v>47</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="41" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="23" t="s">
@@ -3882,44 +3862,44 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A10" s="46" t="s">
+    <row r="10" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A10" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="23">
         <v>2026</v>
       </c>
-      <c r="H10" s="49" t="s">
+      <c r="H10" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="51"/>
-      <c r="J10" s="47" t="s">
+      <c r="I10" s="24"/>
+      <c r="J10" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="11" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="21" t="s">
         <v>56</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="41" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="23" t="s">
@@ -3942,169 +3922,123 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A12" s="21"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A13" s="52" t="s">
+    <row r="12" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B12" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="54"/>
-      <c r="D13" s="53" t="s">
+      <c r="D12" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E12" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="53" t="s">
+      <c r="F12" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="53">
+      <c r="G12" s="48">
         <v>2026</v>
       </c>
-      <c r="H13" s="53"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="56" t="s">
+      <c r="H12" s="48" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="14" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A14" s="52" t="s">
+      <c r="I12" s="49"/>
+      <c r="J12" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="53">
-        <v>2026</v>
-      </c>
-      <c r="H14" s="53"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="57" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A15" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="58">
-        <v>7</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="23">
-        <v>2026</v>
-      </c>
+    </row>
+    <row r="13" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A13" s="21"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A14" s="21"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="42"/>
+    </row>
+    <row r="15" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A15" s="21"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
       <c r="H15" s="23"/>
       <c r="I15" s="24"/>
-      <c r="J15" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A16" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="58">
-        <v>7</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="23">
-        <v>2026</v>
-      </c>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A16" s="21"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="7"/>
       <c r="H16" s="23"/>
       <c r="I16" s="24"/>
-      <c r="J16" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" s="41" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A17" s="59" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="49" t="s">
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A17" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="60" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="49" t="s">
+      <c r="E17" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="23">
         <v>2026</v>
       </c>
-      <c r="H17" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17" s="41" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A18" s="25" t="s">
-        <v>78</v>
+      <c r="H17" s="23"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="42" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A18" s="21" t="s">
+        <v>70</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>79</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C18" s="41"/>
       <c r="D18" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="58" t="s">
-        <v>80</v>
+      <c r="E18" s="22" t="s">
+        <v>71</v>
       </c>
       <c r="F18" s="23" t="s">
         <v>15</v>
@@ -4112,30 +4046,24 @@
       <c r="G18" s="23">
         <v>2026</v>
       </c>
-      <c r="H18" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="I18" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A19" s="25" t="s">
-        <v>84</v>
+      <c r="H18" s="23"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A19" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>85</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C19" s="41"/>
       <c r="D19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="51">
         <v>7</v>
       </c>
       <c r="F19" s="23" t="s">
@@ -4145,28 +4073,24 @@
         <v>2026</v>
       </c>
       <c r="H19" s="23"/>
-      <c r="I19" s="62" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A20" s="25" t="s">
-        <v>88</v>
+      <c r="I19" s="24"/>
+      <c r="J19" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A20" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>89</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C20" s="41"/>
       <c r="D20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="58">
-        <v>10</v>
+      <c r="E20" s="51">
+        <v>7</v>
       </c>
       <c r="F20" s="23" t="s">
         <v>15</v>
@@ -4174,27 +4098,27 @@
       <c r="G20" s="23">
         <v>2026</v>
       </c>
-      <c r="H20" s="42"/>
-      <c r="I20" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="J20" s="23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="H20" s="23"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="25" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="23"/>
+        <v>67</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="D21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="58">
-        <v>2</v>
+      <c r="E21" s="51" t="s">
+        <v>79</v>
       </c>
       <c r="F21" s="23" t="s">
         <v>15</v>
@@ -4202,27 +4126,31 @@
       <c r="G21" s="23">
         <v>2026</v>
       </c>
-      <c r="H21" s="42"/>
-      <c r="I21" s="62" t="s">
-        <v>93</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="H21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="25" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="23"/>
+        <v>67</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>84</v>
+      </c>
       <c r="D22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="58">
-        <v>4</v>
+      <c r="E22" s="51" t="s">
+        <v>85</v>
       </c>
       <c r="F22" s="23" t="s">
         <v>15</v>
@@ -4230,713 +4158,703 @@
       <c r="G22" s="23">
         <v>2026</v>
       </c>
-      <c r="H22" s="42"/>
-      <c r="I22" s="62" t="s">
+      <c r="H22" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A23" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="51">
+        <v>7</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H23" s="23"/>
+      <c r="I23" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A24" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="51">
+        <v>10</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H24" s="40"/>
+      <c r="I24" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="J24" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="J22" s="7" t="s">
+    </row>
+    <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A25" s="25" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A23" s="25"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="7"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A24" s="25"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="7"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A25" s="25"/>
-      <c r="B25" s="23"/>
+      <c r="B25" s="23" t="s">
+        <v>67</v>
+      </c>
       <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="7"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A26" s="25"/>
-      <c r="B26" s="23"/>
+      <c r="D25" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="51">
+        <v>2</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H25" s="40"/>
+      <c r="I25" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A26" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>67</v>
+      </c>
       <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="62"/>
+      <c r="D26" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="51">
+        <v>4</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H26" s="40"/>
+      <c r="I26" s="52" t="s">
+        <v>101</v>
+      </c>
       <c r="J26" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="25"/>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
-      <c r="E27" s="58"/>
+      <c r="E27" s="51"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="H27" s="40"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="7"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="25"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
-      <c r="E28" s="58"/>
+      <c r="E28" s="51"/>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="H28" s="40"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="7"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="25"/>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
-      <c r="E29" s="58"/>
+      <c r="E29" s="51"/>
       <c r="F29" s="23"/>
       <c r="G29" s="23"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="62"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="52"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+    <row r="30" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="25"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
-      <c r="E30" s="58"/>
+      <c r="E30" s="51"/>
       <c r="F30" s="23"/>
       <c r="G30" s="23"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="7"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="H30" s="40"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="25"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
-      <c r="E31" s="58"/>
+      <c r="E31" s="51"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="7"/>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="H31" s="40"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="25"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
-      <c r="E32" s="58"/>
+      <c r="E32" s="51"/>
       <c r="F32" s="23"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="7"/>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A33" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" s="23" t="s">
+      <c r="H32" s="40"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A33" s="25"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="7"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A34" s="25"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="7"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A35" s="25"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A36" s="25"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="7"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A37" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="63"/>
-      <c r="F33" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="G33" s="23">
+      <c r="E37" s="53"/>
+      <c r="F37" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="G37" s="23">
         <v>2026</v>
       </c>
-      <c r="H33" s="23"/>
-      <c r="I33" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="J33" s="7"/>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A34" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" s="23" t="s">
+      <c r="H37" s="23"/>
+      <c r="I37" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="J37" s="7"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A38" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="63"/>
-      <c r="F34" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="G34" s="23">
+      <c r="E38" s="53"/>
+      <c r="F38" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="G38" s="23">
         <v>2026</v>
       </c>
-      <c r="H34" s="23"/>
-      <c r="I34" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="J34" s="7"/>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A35" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A36" s="21" t="s">
+      <c r="H38" s="23"/>
+      <c r="I38" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="24" t="s">
+      <c r="J38" s="7"/>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A39" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="B39" s="7" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A37" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A38" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A39" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="22"/>
-      <c r="F39" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G39" s="23">
-        <v>2026</v>
-      </c>
+      <c r="F39" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G39" s="7"/>
       <c r="H39" s="7"/>
       <c r="I39" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="J39" s="21" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="40" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>113</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="22"/>
-      <c r="F40" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G40" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>123</v>
-      </c>
+      <c r="F40" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
       <c r="I40" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="J40" s="24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" ht="24" hidden="1" customHeight="1" spans="1:10">
+        <v>116</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>127</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="22"/>
-      <c r="F41" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G41" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>128</v>
-      </c>
+      <c r="F41" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
       <c r="I41" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="J41" s="24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>119</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>132</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="22"/>
-      <c r="F42" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G42" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="21" hidden="1" customHeight="1" spans="1:10">
-      <c r="A43" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="58">
-        <v>36</v>
-      </c>
-      <c r="F43" s="23" t="s">
-        <v>102</v>
+      <c r="F42" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1" spans="1:10">
+      <c r="A43" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="G43" s="23">
         <v>2026</v>
       </c>
-      <c r="H43" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="I43" s="64" t="s">
-        <v>140</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+      <c r="H43" s="7"/>
+      <c r="I43" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="J43" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A44" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="B44" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="22">
-        <v>33</v>
-      </c>
-      <c r="F44" s="23" t="s">
-        <v>102</v>
+        <v>127</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="G44" s="23">
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="I44" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>128</v>
+      </c>
+      <c r="I44" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="J44" s="24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="1:10">
       <c r="A45" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>137</v>
+        <v>131</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="22">
-        <v>23</v>
-      </c>
-      <c r="F45" s="23" t="s">
-        <v>102</v>
+        <v>132</v>
+      </c>
+      <c r="D45" s="7"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="G45" s="23">
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>133</v>
+      </c>
+      <c r="I45" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="J45" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" ht="25" customHeight="1" spans="1:10">
       <c r="A46" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B46" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="22">
-        <v>23</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>102</v>
+      <c r="D46" s="7"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="G46" s="23">
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A47" s="21" t="s">
-        <v>155</v>
+        <v>139</v>
+      </c>
+      <c r="J46" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
+      <c r="A47" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>156</v>
+        <v>142</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>143</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E47" s="22">
-        <v>24</v>
+      <c r="E47" s="51">
+        <v>36</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G47" s="23">
         <v>2026</v>
       </c>
-      <c r="H47" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>158</v>
+      <c r="H47" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="I47" s="54" t="s">
+        <v>145</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A48" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="B48" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="C48" s="27" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A48" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D48" s="29" t="s">
+      <c r="D48" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="28">
-        <v>32</v>
+      <c r="E48" s="22">
+        <v>33</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="G48" s="29">
+        <v>107</v>
+      </c>
+      <c r="G48" s="23">
         <v>2026</v>
       </c>
-      <c r="H48" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>162</v>
+      <c r="H48" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I48" s="54" t="s">
+        <v>149</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="49" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A49" s="21" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C49" s="66" t="s">
-        <v>165</v>
+        <v>142</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G49" s="23">
         <v>2026</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="I49" s="24" t="s">
-        <v>167</v>
+        <v>153</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>154</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="50" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A50" s="25" t="s">
-        <v>169</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A50" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G50" s="23">
         <v>2026</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="51" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A51" s="21" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G51" s="23">
         <v>2026</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="I51" s="24" t="s">
-        <v>177</v>
+        <v>162</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A52" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="B52" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D52" s="23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A52" s="55" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="C52" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E52" s="22">
-        <v>26</v>
+      <c r="E52" s="28">
+        <v>32</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="G52" s="23">
+        <v>107</v>
+      </c>
+      <c r="G52" s="29">
         <v>2026</v>
       </c>
-      <c r="H52" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="I52" s="24" t="s">
-        <v>182</v>
+      <c r="H52" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="53" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="53" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A53" s="21" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>185</v>
+        <v>142</v>
+      </c>
+      <c r="C53" s="56" t="s">
+        <v>170</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>13</v>
@@ -4945,644 +4863,724 @@
         <v>24</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G53" s="23">
         <v>2026</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="54" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A54" s="25" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="22"/>
+      <c r="E54" s="22">
+        <v>24</v>
+      </c>
       <c r="F54" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G54" s="23">
         <v>2026</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="55" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A55" s="25" t="s">
-        <v>194</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="55" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A55" s="21" t="s">
+        <v>179</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E55" s="22"/>
+      <c r="E55" s="22">
+        <v>25</v>
+      </c>
       <c r="F55" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G55" s="23">
         <v>2026</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="56" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A56" s="25" t="s">
-        <v>199</v>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A56" s="21" t="s">
+        <v>184</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E56" s="22"/>
+      <c r="E56" s="22">
+        <v>26</v>
+      </c>
       <c r="F56" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G56" s="23">
         <v>2026</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="57" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A57" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>119</v>
+        <v>189</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>142</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="D57" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="7" t="s">
-        <v>102</v>
+      <c r="E57" s="22">
+        <v>24</v>
+      </c>
+      <c r="F57" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="G57" s="23">
         <v>2026</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="J57" s="7"/>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A58" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>119</v>
+        <v>192</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A58" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="22"/>
-      <c r="F58" s="7" t="s">
-        <v>102</v>
+      <c r="F58" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="G58" s="23">
         <v>2026</v>
       </c>
-      <c r="H58" s="67" t="s">
-        <v>210</v>
+      <c r="H58" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="J58" s="7"/>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A59" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>119</v>
+        <v>197</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A59" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D59" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="22"/>
-      <c r="F59" s="7" t="s">
-        <v>102</v>
+      <c r="F59" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="G59" s="23">
         <v>2026</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A60" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>119</v>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="60" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A60" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D60" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="22"/>
-      <c r="F60" s="7" t="s">
-        <v>102</v>
+      <c r="F60" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="G60" s="23">
         <v>2026</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A61" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="B61" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C61" s="23" t="s">
-        <v>223</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A61" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="D61" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="58">
-        <v>30</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>102</v>
+      <c r="E61" s="22"/>
+      <c r="F61" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G61" s="23">
         <v>2026</v>
       </c>
-      <c r="H61" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="I61" s="62" t="s">
-        <v>225</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A62" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="B62" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C62" s="23" t="s">
-        <v>228</v>
+      <c r="H61" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I61" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="J61" s="7"/>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A62" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="D62" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E62" s="58">
-        <v>32</v>
-      </c>
-      <c r="F62" s="23" t="s">
-        <v>102</v>
+      <c r="E62" s="22"/>
+      <c r="F62" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G62" s="23">
         <v>2026</v>
       </c>
-      <c r="H62" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="I62" s="62" t="s">
-        <v>230</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A63" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="B63" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C63" s="23" t="s">
-        <v>233</v>
+      <c r="H62" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="I62" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="J62" s="7"/>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A63" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="D63" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="58">
-        <v>33</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>102</v>
+      <c r="E63" s="22"/>
+      <c r="F63" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G63" s="23">
         <v>2026</v>
       </c>
-      <c r="H63" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="I63" s="62" t="s">
-        <v>235</v>
+      <c r="H63" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="I63" s="24" t="s">
+        <v>220</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A64" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="B64" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C64" s="23" t="s">
-        <v>238</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A64" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="D64" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="58">
-        <v>36</v>
-      </c>
-      <c r="F64" s="23" t="s">
-        <v>102</v>
+      <c r="E64" s="22"/>
+      <c r="F64" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G64" s="23">
         <v>2026</v>
       </c>
-      <c r="H64" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="I64" s="62" t="s">
-        <v>240</v>
+      <c r="H64" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="I64" s="24" t="s">
+        <v>225</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A65" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>243</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A65" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>228</v>
       </c>
       <c r="D65" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E65" s="22">
-        <v>22</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>102</v>
+      <c r="E65" s="51">
+        <v>30</v>
+      </c>
+      <c r="F65" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="G65" s="23">
         <v>2026</v>
       </c>
-      <c r="H65" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="I65" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="J65" s="7"/>
-    </row>
-    <row r="66" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A66" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>12</v>
+      <c r="H65" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="I65" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A66" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>233</v>
       </c>
       <c r="D66" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E66" s="22">
-        <v>24</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>102</v>
+      <c r="E66" s="51">
+        <v>32</v>
+      </c>
+      <c r="F66" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="G66" s="23">
         <v>2026</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="H66" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="I66" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A67" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="D67" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="51">
+        <v>33</v>
+      </c>
+      <c r="F67" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G67" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H67" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="I67" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A68" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="51">
+        <v>36</v>
+      </c>
+      <c r="F68" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G68" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H68" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="I68" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A69" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="I66" s="24" t="s">
+      <c r="B69" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>248</v>
-      </c>
-      <c r="J66" s="7"/>
-    </row>
-    <row r="67" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A67" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G67" s="7">
-        <v>2026</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J67" s="7"/>
-    </row>
-    <row r="68" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A68" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G68" s="7">
-        <v>2026</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="I68" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="J68" s="7"/>
-    </row>
-    <row r="69" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A69" s="25" t="s">
-        <v>258</v>
-      </c>
-      <c r="B69" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="68" t="s">
-        <v>259</v>
       </c>
       <c r="D69" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E69" s="58" t="s">
-        <v>260</v>
-      </c>
-      <c r="F69" s="23" t="s">
-        <v>102</v>
+      <c r="E69" s="22">
+        <v>22</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G69" s="23">
         <v>2026</v>
       </c>
-      <c r="H69" s="23" t="s">
-        <v>261</v>
+      <c r="H69" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="J69" s="7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A70" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="B70" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C70" s="23" t="s">
-        <v>265</v>
+        <v>250</v>
+      </c>
+      <c r="J69" s="7"/>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A70" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D70" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E70" s="58" t="s">
-        <v>266</v>
-      </c>
-      <c r="F70" s="23" t="s">
-        <v>102</v>
+      <c r="E70" s="22">
+        <v>24</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G70" s="23">
         <v>2026</v>
       </c>
-      <c r="H70" s="23" t="s">
+      <c r="H70" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="I70" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="J70" s="7"/>
+    </row>
+    <row r="71" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A71" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G71" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="J71" s="7"/>
+    </row>
+    <row r="72" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A72" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G72" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="I72" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="J72" s="7"/>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A73" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="58" t="s">
+        <v>264</v>
+      </c>
+      <c r="D73" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G73" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H73" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="I73" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="I70" s="62" t="s">
+      <c r="J73" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="J70" s="7" t="s">
+    </row>
+    <row r="74" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A74" s="25" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="71" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A71" s="21" t="s">
+      <c r="B74" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="D74" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="F74" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G74" s="23">
+        <v>2026</v>
+      </c>
+      <c r="H74" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="I74" s="52" t="s">
+        <v>273</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="75" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A75" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="B75" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C71" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G71" s="7"/>
-      <c r="H71" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="I71" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="J71" s="7"/>
-    </row>
-    <row r="72" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A72" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="B72" s="23" t="s">
+      <c r="C75" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="D75" s="7"/>
+      <c r="E75" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G75" s="7"/>
+      <c r="H75" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="I75" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="J75" s="7"/>
+    </row>
+    <row r="76" s="1" customFormat="1" ht="25" customHeight="1" spans="1:10">
+      <c r="A76" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="B76" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C72" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="D72" s="23" t="s">
+      <c r="C76" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="D76" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="58" t="s">
-        <v>260</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G72" s="23">
+      <c r="E76" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G76" s="23">
         <v>2026</v>
       </c>
-      <c r="H72" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="I72" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="73" ht="25" hidden="1" customHeight="1" spans="1:10">
-      <c r="A73" s="21"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="24"/>
-      <c r="J73" s="24"/>
-    </row>
-    <row r="74" s="40" customFormat="1" ht="25" customHeight="1" spans="1:10">
-      <c r="A74" s="46"/>
-      <c r="B74" s="47"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="47"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="47"/>
-      <c r="I74" s="51"/>
-      <c r="J74" s="51"/>
-    </row>
-    <row r="75" ht="25" customHeight="1" spans="1:10">
-      <c r="A75" s="21"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="24"/>
-      <c r="J75" s="24"/>
-    </row>
-    <row r="76" ht="25" customHeight="1" spans="1:10">
-      <c r="A76" s="21"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="24"/>
-      <c r="J76" s="24"/>
+      <c r="H76" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="I76" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:10">
       <c r="A77" s="21"/>
@@ -5594,9 +5592,9 @@
       <c r="G77" s="23"/>
       <c r="H77" s="7"/>
       <c r="I77" s="24"/>
-      <c r="J77" s="70"/>
-    </row>
-    <row r="78" ht="25" customHeight="1" spans="1:10">
+      <c r="J77" s="24"/>
+    </row>
+    <row r="78" s="6" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A78" s="21"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -5621,7 +5619,7 @@
       <c r="J79" s="24"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:10">
-      <c r="A80" s="71"/>
+      <c r="A80" s="21"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -5642,7 +5640,7 @@
       <c r="G81" s="23"/>
       <c r="H81" s="7"/>
       <c r="I81" s="24"/>
-      <c r="J81" s="24"/>
+      <c r="J81" s="59"/>
     </row>
     <row r="82" ht="25" customHeight="1" spans="1:10">
       <c r="A82" s="21"/>
@@ -5669,7 +5667,7 @@
       <c r="J83" s="24"/>
     </row>
     <row r="84" ht="25" customHeight="1" spans="1:10">
-      <c r="A84" s="21"/>
+      <c r="A84" s="60"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -6124,8 +6122,56 @@
       <c r="I121" s="24"/>
       <c r="J121" s="24"/>
     </row>
+    <row r="122" ht="25" customHeight="1" spans="1:10">
+      <c r="A122" s="21"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="22"/>
+      <c r="F122" s="22"/>
+      <c r="G122" s="23"/>
+      <c r="H122" s="7"/>
+      <c r="I122" s="24"/>
+      <c r="J122" s="24"/>
+    </row>
+    <row r="123" ht="25" customHeight="1" spans="1:10">
+      <c r="A123" s="21"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="22"/>
+      <c r="G123" s="23"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="24"/>
+    </row>
+    <row r="124" ht="25" customHeight="1" spans="1:10">
+      <c r="A124" s="21"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="22"/>
+      <c r="F124" s="22"/>
+      <c r="G124" s="23"/>
+      <c r="H124" s="7"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="24"/>
+    </row>
+    <row r="125" ht="25" customHeight="1" spans="1:10">
+      <c r="A125" s="21"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="22"/>
+      <c r="F125" s="22"/>
+      <c r="G125" s="23"/>
+      <c r="H125" s="7"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="24"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J73" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J77" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <colorFilter dxfId="0"/>
       <extLst>
@@ -6148,16 +6194,13 @@
         </dxfs>
       </extLst>
     </filterColumn>
-    <filterColumn colId="4">
-      <colorFilter dxfId="1"/>
-    </filterColumn>
-    <sortState ref="A1:J73">
+    <sortState ref="A1:J77">
       <sortCondition ref="F1:F87"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H71" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H75" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6183,7 +6226,7 @@
   <sheetData>
     <row r="1" ht="15" spans="1:9">
       <c r="A1" s="37" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -6192,22 +6235,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" ht="33" spans="1:9">
@@ -6215,28 +6258,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" ht="33" spans="1:9">
@@ -6244,28 +6287,28 @@
         <v>3</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="G3" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="H3" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H3" s="39" t="s">
-        <v>291</v>
-      </c>
       <c r="I3" s="39" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -6273,28 +6316,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" ht="33" spans="1:9">
@@ -6302,28 +6345,28 @@
         <v>5</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" ht="33" spans="1:9">
@@ -6331,28 +6374,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -6366,22 +6409,22 @@
         <v>11</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -6395,22 +6438,22 @@
         <v>11</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" ht="33" spans="1:9">
@@ -6418,28 +6461,28 @@
         <v>9</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" ht="33" spans="1:9">
@@ -6447,28 +6490,28 @@
         <v>10</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" ht="33" spans="1:9">
@@ -6476,28 +6519,28 @@
         <v>11</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -6505,28 +6548,28 @@
         <v>12</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -6534,28 +6577,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -6563,28 +6606,28 @@
         <v>14</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>48</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -6592,28 +6635,28 @@
         <v>17</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -6621,28 +6664,28 @@
         <v>18</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -6650,28 +6693,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -6679,28 +6722,28 @@
         <v>20</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D18" s="39" t="s">
+        <v>345</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>296</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="I18" s="39" t="s">
         <v>340</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>291</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="H18" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -6708,28 +6751,28 @@
         <v>21</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -6737,28 +6780,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -6766,28 +6809,28 @@
         <v>23</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -6795,28 +6838,28 @@
         <v>24</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -6824,28 +6867,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -6853,16 +6896,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -6942,13 +6985,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A2" s="9" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
@@ -6957,731 +7000,731 @@
         <v>24</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G2" s="10">
         <v>2026</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G3" s="11">
         <v>2026</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="13" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G4" s="11">
         <v>2025</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="13" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G5" s="11">
         <v>2026</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J5" s="11"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="13" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G6" s="11">
         <v>2026</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J6" s="11"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G7" s="11">
         <v>2025</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J7" s="11"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="13" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G8" s="11">
         <v>2026</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G9" s="11">
         <v>2026</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J9" s="11"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="13" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G10" s="11">
         <v>2024</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J10" s="11"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G11" s="11">
         <v>2024</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="13" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G12" s="11">
         <v>2026</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="J12" s="11"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="13" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G13" s="11">
         <v>2025</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J13" s="11"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G14" s="11">
         <v>2026</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J14" s="11"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G15" s="11">
         <v>2026</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="J15" s="11"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="13" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G16" s="11">
         <v>2026</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="J16" s="11"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A17" s="13" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="J17" s="11"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A18" s="13" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="J18" s="11"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A19" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="J19" s="11"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A20" s="13" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A21" s="17" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="18" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="J21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A22" s="13" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G22" s="11"/>
       <c r="I22" s="14" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="J22" s="11"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A23" s="13" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="J23" s="11"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A24" s="13" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="J24" s="11"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A25" s="13" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G25" s="11"/>
       <c r="I25" s="14" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="J25" s="11"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="13" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="J26" s="11"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A27" s="13" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A28" s="13" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="J28" s="11"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A29" s="13" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A30" s="13" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="J30" s="11"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A31" s="13" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="J31" s="11"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="25" customHeight="1" spans="1:10">
       <c r="A32" s="13" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -7699,13 +7742,13 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A34" s="25" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7">
@@ -7718,13 +7761,13 @@
         <v>2026</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
@@ -7743,7 +7786,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A36" s="21" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -7757,7 +7800,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A37" s="21" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -7771,7 +7814,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A38" s="21" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -7785,7 +7828,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A39" s="21" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -7798,7 +7841,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A40" s="21" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -7812,7 +7855,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A41" s="21" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B41" s="27"/>
       <c r="C41" s="27"/>
@@ -7825,7 +7868,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A42" s="21" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -7838,7 +7881,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A43" s="30" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -7851,17 +7894,17 @@
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A44" s="25" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="22" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>15</v>
@@ -7870,24 +7913,24 @@
         <v>2026</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A45" s="25" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="22" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>15</v>
@@ -7896,24 +7939,24 @@
         <v>2026</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="7"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="22" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>15</v>
@@ -7922,24 +7965,24 @@
         <v>2026</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="7"/>
     </row>
     <row r="47" ht="22" hidden="1" customHeight="1" spans="1:10">
       <c r="A47" s="25" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="22" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>15</v>
@@ -7948,17 +7991,17 @@
         <v>2026</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="7"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:10">
       <c r="A48" s="25" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
